--- a/turnazione-auto-trinitapoli-foggia-20260921.xlsx
+++ b/turnazione-auto-trinitapoli-foggia-20260921.xlsx
@@ -654,7 +654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -817,144 +817,156 @@
     <row r="18" ht="39" customHeight="1">
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>R5-bis – Più recuperi verso la stessa persona</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>I recuperi dovuti a uno stesso collega si saldano uno per settimana, nell'ordine in cui sono maturati. Chi sta già guidando un turno di recupero non viene scelto come sostituto nella stessa settimana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39" customHeight="1">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
           <t>R6 – Comunicazione del giovedì</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>Entro il giovedì di ogni settimana vanno comunicate a tutti le posizioni della settimana successiva. Usare il foglio «Comunicazione Giovedì»: contiene il prospetto e il testo già pronto da inviare.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>R7 – Recupero non effettuabile</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Se chi deve recuperare è a sua volta assente nella settimana del recupero, il recupero non si perde: resta contabilizzato nel foglio «Riepilogo» alla voce «Recuperi da saldare».</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="20" ht="52" customHeight="1">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>R7 – Slittamento automatico del recupero</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Se chi deve recuperare è a sua volta assente nella settimana del recupero, il turno non si perde: slitta da solo alla prima settimana utile, sempre sul giorno di chi lo aveva sostituito. Se al termine del periodo il debito è ancora aperto, resta contabilizzato nel foglio «Riepilogo» alla voce «Recuperi ancora da saldare».</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>3. COME SI USA IL FILE</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="5" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Foglio da compilare</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Solo «Assenze». Tutti gli altri fogli si aggiornano da soli.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Come inserire un'assenza</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Una riga per ogni assenza: numero della settimana, nome, tipo di assenza dal menù a tendina e — solo per «Altro motivo» — la data del giorno saltato.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Assenza di settimana intera</t>
+          <t>Come inserire un'assenza</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Basta indicare settimana, nome e tipo: la data va lasciata vuota, la regola copre tutti e cinque i giorni.</t>
+          <t>Una riga per ogni assenza: numero della settimana, nome, tipo di assenza dal menù a tendina e — solo per «Altro motivo» — la data del giorno saltato.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="B25" s="5" t="inlineStr">
         <is>
+          <t>Assenza di settimana intera</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Basta indicare settimana, nome e tipo: la data va lasciata vuota, la regola copre tutti e cinque i giorni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>Dove si leggono i risultati</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>«Turnazione» = calendario completo · «Comunicazione Giovedì» = prospetto da inviare · «Riepilogo» = conteggi e recuperi per persona.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="5" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Colonne modificabili a mano</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>Le celle su sfondo giallo. Tutte le altre contengono formule: non sovrascriverle.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>4. LEGENDA DEI TIPI DI TURNO</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Il turno si svolge secondo l'ordine base.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="B30" s="5" t="inlineStr">
         <is>
+          <t>Ordinario</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Il turno si svolge secondo l'ordine base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
           <t>Sostituzione (doppio turno)</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Il titolare è assente: guida un collega, che quella settimana prende la macchina due volte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Recupero</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Turno restituito da chi aveva saltato per motivo non giustificato; il collega che lo aveva sostituito è a riposo compensativo.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="B32" s="5" t="inlineStr">
         <is>
+          <t>Recupero</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Turno restituito da chi aveva saltato per motivo non giustificato; il collega che lo aveva sostituito è a riposo compensativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
           <t>DA ASSEGNARE</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>Nessun sostituto disponibile in automatico (troppe assenze contemporanee): va deciso manualmente.</t>
         </is>
@@ -962,12 +974,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1245,7 +1257,7 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="13" t="n"/>
       <c r="B5" s="8">
-        <f>IF($A5="","",TEXT(Calcoli!$AB$6+($A5-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A5-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A5="","",TEXT(Calcoli!$AG$6+($A5-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A5-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C5" s="13" t="n"/>
@@ -1260,7 +1272,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="13" t="n"/>
       <c r="B6" s="8">
-        <f>IF($A6="","",TEXT(Calcoli!$AB$6+($A6-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A6-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A6="","",TEXT(Calcoli!$AG$6+($A6-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A6-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C6" s="13" t="n"/>
@@ -1275,7 +1287,7 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="13" t="n"/>
       <c r="B7" s="8">
-        <f>IF($A7="","",TEXT(Calcoli!$AB$6+($A7-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A7-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A7="","",TEXT(Calcoli!$AG$6+($A7-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A7-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C7" s="13" t="n"/>
@@ -1290,7 +1302,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="13" t="n"/>
       <c r="B8" s="8">
-        <f>IF($A8="","",TEXT(Calcoli!$AB$6+($A8-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A8-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A8="","",TEXT(Calcoli!$AG$6+($A8-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A8-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C8" s="13" t="n"/>
@@ -1305,7 +1317,7 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="13" t="n"/>
       <c r="B9" s="8">
-        <f>IF($A9="","",TEXT(Calcoli!$AB$6+($A9-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A9-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A9="","",TEXT(Calcoli!$AG$6+($A9-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A9-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C9" s="13" t="n"/>
@@ -1320,7 +1332,7 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="13" t="n"/>
       <c r="B10" s="8">
-        <f>IF($A10="","",TEXT(Calcoli!$AB$6+($A10-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A10-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A10="","",TEXT(Calcoli!$AG$6+($A10-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A10-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C10" s="13" t="n"/>
@@ -1335,7 +1347,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="13" t="n"/>
       <c r="B11" s="8">
-        <f>IF($A11="","",TEXT(Calcoli!$AB$6+($A11-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A11-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A11="","",TEXT(Calcoli!$AG$6+($A11-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A11-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C11" s="13" t="n"/>
@@ -1350,7 +1362,7 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="13" t="n"/>
       <c r="B12" s="8">
-        <f>IF($A12="","",TEXT(Calcoli!$AB$6+($A12-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A12-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A12="","",TEXT(Calcoli!$AG$6+($A12-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A12-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C12" s="13" t="n"/>
@@ -1365,7 +1377,7 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="13" t="n"/>
       <c r="B13" s="8">
-        <f>IF($A13="","",TEXT(Calcoli!$AB$6+($A13-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A13-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A13="","",TEXT(Calcoli!$AG$6+($A13-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A13-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C13" s="13" t="n"/>
@@ -1380,7 +1392,7 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="13" t="n"/>
       <c r="B14" s="8">
-        <f>IF($A14="","",TEXT(Calcoli!$AB$6+($A14-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A14-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A14="","",TEXT(Calcoli!$AG$6+($A14-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A14-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C14" s="13" t="n"/>
@@ -1395,7 +1407,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="13" t="n"/>
       <c r="B15" s="8">
-        <f>IF($A15="","",TEXT(Calcoli!$AB$6+($A15-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A15-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A15="","",TEXT(Calcoli!$AG$6+($A15-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A15-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C15" s="13" t="n"/>
@@ -1410,7 +1422,7 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="13" t="n"/>
       <c r="B16" s="8">
-        <f>IF($A16="","",TEXT(Calcoli!$AB$6+($A16-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A16-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A16="","",TEXT(Calcoli!$AG$6+($A16-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A16-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C16" s="13" t="n"/>
@@ -1425,7 +1437,7 @@
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="13" t="n"/>
       <c r="B17" s="8">
-        <f>IF($A17="","",TEXT(Calcoli!$AB$6+($A17-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A17-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A17="","",TEXT(Calcoli!$AG$6+($A17-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A17-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C17" s="13" t="n"/>
@@ -1440,7 +1452,7 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="13" t="n"/>
       <c r="B18" s="8">
-        <f>IF($A18="","",TEXT(Calcoli!$AB$6+($A18-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A18-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A18="","",TEXT(Calcoli!$AG$6+($A18-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A18-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C18" s="13" t="n"/>
@@ -1455,7 +1467,7 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="13" t="n"/>
       <c r="B19" s="8">
-        <f>IF($A19="","",TEXT(Calcoli!$AB$6+($A19-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A19-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A19="","",TEXT(Calcoli!$AG$6+($A19-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A19-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C19" s="13" t="n"/>
@@ -1470,7 +1482,7 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="13" t="n"/>
       <c r="B20" s="8">
-        <f>IF($A20="","",TEXT(Calcoli!$AB$6+($A20-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A20-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A20="","",TEXT(Calcoli!$AG$6+($A20-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A20-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C20" s="13" t="n"/>
@@ -1485,7 +1497,7 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="13" t="n"/>
       <c r="B21" s="8">
-        <f>IF($A21="","",TEXT(Calcoli!$AB$6+($A21-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A21-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A21="","",TEXT(Calcoli!$AG$6+($A21-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A21-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C21" s="13" t="n"/>
@@ -1500,7 +1512,7 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="8">
-        <f>IF($A22="","",TEXT(Calcoli!$AB$6+($A22-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A22-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A22="","",TEXT(Calcoli!$AG$6+($A22-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A22-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C22" s="13" t="n"/>
@@ -1515,7 +1527,7 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="8">
-        <f>IF($A23="","",TEXT(Calcoli!$AB$6+($A23-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A23-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A23="","",TEXT(Calcoli!$AG$6+($A23-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A23-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C23" s="13" t="n"/>
@@ -1530,7 +1542,7 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="13" t="n"/>
       <c r="B24" s="8">
-        <f>IF($A24="","",TEXT(Calcoli!$AB$6+($A24-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A24-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A24="","",TEXT(Calcoli!$AG$6+($A24-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A24-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C24" s="13" t="n"/>
@@ -1545,7 +1557,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="8">
-        <f>IF($A25="","",TEXT(Calcoli!$AB$6+($A25-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A25-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A25="","",TEXT(Calcoli!$AG$6+($A25-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A25-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C25" s="13" t="n"/>
@@ -1560,7 +1572,7 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="13" t="n"/>
       <c r="B26" s="8">
-        <f>IF($A26="","",TEXT(Calcoli!$AB$6+($A26-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A26-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A26="","",TEXT(Calcoli!$AG$6+($A26-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A26-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C26" s="13" t="n"/>
@@ -1575,7 +1587,7 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="13" t="n"/>
       <c r="B27" s="8">
-        <f>IF($A27="","",TEXT(Calcoli!$AB$6+($A27-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A27-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A27="","",TEXT(Calcoli!$AG$6+($A27-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A27-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C27" s="13" t="n"/>
@@ -1590,7 +1602,7 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="13" t="n"/>
       <c r="B28" s="8">
-        <f>IF($A28="","",TEXT(Calcoli!$AB$6+($A28-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A28-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A28="","",TEXT(Calcoli!$AG$6+($A28-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A28-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C28" s="13" t="n"/>
@@ -1605,7 +1617,7 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="8">
-        <f>IF($A29="","",TEXT(Calcoli!$AB$6+($A29-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A29-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A29="","",TEXT(Calcoli!$AG$6+($A29-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A29-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C29" s="13" t="n"/>
@@ -1620,7 +1632,7 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="13" t="n"/>
       <c r="B30" s="8">
-        <f>IF($A30="","",TEXT(Calcoli!$AB$6+($A30-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A30-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A30="","",TEXT(Calcoli!$AG$6+($A30-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A30-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C30" s="13" t="n"/>
@@ -1635,7 +1647,7 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="13" t="n"/>
       <c r="B31" s="8">
-        <f>IF($A31="","",TEXT(Calcoli!$AB$6+($A31-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A31-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A31="","",TEXT(Calcoli!$AG$6+($A31-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A31-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C31" s="13" t="n"/>
@@ -1650,7 +1662,7 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="13" t="n"/>
       <c r="B32" s="8">
-        <f>IF($A32="","",TEXT(Calcoli!$AB$6+($A32-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A32-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A32="","",TEXT(Calcoli!$AG$6+($A32-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A32-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C32" s="13" t="n"/>
@@ -1665,7 +1677,7 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="13" t="n"/>
       <c r="B33" s="8">
-        <f>IF($A33="","",TEXT(Calcoli!$AB$6+($A33-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A33-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A33="","",TEXT(Calcoli!$AG$6+($A33-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A33-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C33" s="13" t="n"/>
@@ -1680,7 +1692,7 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="13" t="n"/>
       <c r="B34" s="8">
-        <f>IF($A34="","",TEXT(Calcoli!$AB$6+($A34-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A34-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A34="","",TEXT(Calcoli!$AG$6+($A34-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A34-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C34" s="13" t="n"/>
@@ -1695,7 +1707,7 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="13" t="n"/>
       <c r="B35" s="8">
-        <f>IF($A35="","",TEXT(Calcoli!$AB$6+($A35-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A35-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A35="","",TEXT(Calcoli!$AG$6+($A35-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A35-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C35" s="13" t="n"/>
@@ -1710,7 +1722,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="13" t="n"/>
       <c r="B36" s="8">
-        <f>IF($A36="","",TEXT(Calcoli!$AB$6+($A36-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A36-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A36="","",TEXT(Calcoli!$AG$6+($A36-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A36-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C36" s="13" t="n"/>
@@ -1725,7 +1737,7 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="13" t="n"/>
       <c r="B37" s="8">
-        <f>IF($A37="","",TEXT(Calcoli!$AB$6+($A37-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A37-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A37="","",TEXT(Calcoli!$AG$6+($A37-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A37-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C37" s="13" t="n"/>
@@ -1740,7 +1752,7 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="13" t="n"/>
       <c r="B38" s="8">
-        <f>IF($A38="","",TEXT(Calcoli!$AB$6+($A38-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A38-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A38="","",TEXT(Calcoli!$AG$6+($A38-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A38-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C38" s="13" t="n"/>
@@ -1755,7 +1767,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="13" t="n"/>
       <c r="B39" s="8">
-        <f>IF($A39="","",TEXT(Calcoli!$AB$6+($A39-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A39-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A39="","",TEXT(Calcoli!$AG$6+($A39-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A39-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C39" s="13" t="n"/>
@@ -1770,7 +1782,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="13" t="n"/>
       <c r="B40" s="8">
-        <f>IF($A40="","",TEXT(Calcoli!$AB$6+($A40-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A40-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A40="","",TEXT(Calcoli!$AG$6+($A40-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A40-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C40" s="13" t="n"/>
@@ -1785,7 +1797,7 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="13" t="n"/>
       <c r="B41" s="8">
-        <f>IF($A41="","",TEXT(Calcoli!$AB$6+($A41-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A41-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A41="","",TEXT(Calcoli!$AG$6+($A41-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A41-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C41" s="13" t="n"/>
@@ -1800,7 +1812,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="13" t="n"/>
       <c r="B42" s="8">
-        <f>IF($A42="","",TEXT(Calcoli!$AB$6+($A42-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A42-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A42="","",TEXT(Calcoli!$AG$6+($A42-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A42-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C42" s="13" t="n"/>
@@ -1815,7 +1827,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="13" t="n"/>
       <c r="B43" s="8">
-        <f>IF($A43="","",TEXT(Calcoli!$AB$6+($A43-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A43-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A43="","",TEXT(Calcoli!$AG$6+($A43-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A43-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C43" s="13" t="n"/>
@@ -1830,7 +1842,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="13" t="n"/>
       <c r="B44" s="8">
-        <f>IF($A44="","",TEXT(Calcoli!$AB$6+($A44-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A44-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A44="","",TEXT(Calcoli!$AG$6+($A44-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A44-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C44" s="13" t="n"/>
@@ -1845,7 +1857,7 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="13" t="n"/>
       <c r="B45" s="8">
-        <f>IF($A45="","",TEXT(Calcoli!$AB$6+($A45-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A45-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A45="","",TEXT(Calcoli!$AG$6+($A45-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A45-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C45" s="13" t="n"/>
@@ -1860,7 +1872,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="13" t="n"/>
       <c r="B46" s="8">
-        <f>IF($A46="","",TEXT(Calcoli!$AB$6+($A46-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A46-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A46="","",TEXT(Calcoli!$AG$6+($A46-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A46-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C46" s="13" t="n"/>
@@ -1875,7 +1887,7 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="13" t="n"/>
       <c r="B47" s="8">
-        <f>IF($A47="","",TEXT(Calcoli!$AB$6+($A47-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A47-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A47="","",TEXT(Calcoli!$AG$6+($A47-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A47-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C47" s="13" t="n"/>
@@ -1890,7 +1902,7 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="13" t="n"/>
       <c r="B48" s="8">
-        <f>IF($A48="","",TEXT(Calcoli!$AB$6+($A48-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A48-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A48="","",TEXT(Calcoli!$AG$6+($A48-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A48-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C48" s="13" t="n"/>
@@ -1905,7 +1917,7 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="13" t="n"/>
       <c r="B49" s="8">
-        <f>IF($A49="","",TEXT(Calcoli!$AB$6+($A49-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A49-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A49="","",TEXT(Calcoli!$AG$6+($A49-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A49-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C49" s="13" t="n"/>
@@ -1920,7 +1932,7 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="13" t="n"/>
       <c r="B50" s="8">
-        <f>IF($A50="","",TEXT(Calcoli!$AB$6+($A50-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A50-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A50="","",TEXT(Calcoli!$AG$6+($A50-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A50-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C50" s="13" t="n"/>
@@ -1935,7 +1947,7 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="13" t="n"/>
       <c r="B51" s="8">
-        <f>IF($A51="","",TEXT(Calcoli!$AB$6+($A51-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A51-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A51="","",TEXT(Calcoli!$AG$6+($A51-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A51-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C51" s="13" t="n"/>
@@ -1950,7 +1962,7 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="13" t="n"/>
       <c r="B52" s="8">
-        <f>IF($A52="","",TEXT(Calcoli!$AB$6+($A52-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A52-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A52="","",TEXT(Calcoli!$AG$6+($A52-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A52-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C52" s="13" t="n"/>
@@ -1965,7 +1977,7 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="13" t="n"/>
       <c r="B53" s="8">
-        <f>IF($A53="","",TEXT(Calcoli!$AB$6+($A53-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A53-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A53="","",TEXT(Calcoli!$AG$6+($A53-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A53-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C53" s="13" t="n"/>
@@ -1980,7 +1992,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="13" t="n"/>
       <c r="B54" s="8">
-        <f>IF($A54="","",TEXT(Calcoli!$AB$6+($A54-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A54-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A54="","",TEXT(Calcoli!$AG$6+($A54-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A54-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C54" s="13" t="n"/>
@@ -1995,7 +2007,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="13" t="n"/>
       <c r="B55" s="8">
-        <f>IF($A55="","",TEXT(Calcoli!$AB$6+($A55-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A55-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A55="","",TEXT(Calcoli!$AG$6+($A55-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A55-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C55" s="13" t="n"/>
@@ -2010,7 +2022,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="13" t="n"/>
       <c r="B56" s="8">
-        <f>IF($A56="","",TEXT(Calcoli!$AB$6+($A56-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A56-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A56="","",TEXT(Calcoli!$AG$6+($A56-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A56-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C56" s="13" t="n"/>
@@ -2025,7 +2037,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="13" t="n"/>
       <c r="B57" s="8">
-        <f>IF($A57="","",TEXT(Calcoli!$AB$6+($A57-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A57-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A57="","",TEXT(Calcoli!$AG$6+($A57-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A57-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C57" s="13" t="n"/>
@@ -2040,7 +2052,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="13" t="n"/>
       <c r="B58" s="8">
-        <f>IF($A58="","",TEXT(Calcoli!$AB$6+($A58-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A58-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A58="","",TEXT(Calcoli!$AG$6+($A58-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A58-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C58" s="13" t="n"/>
@@ -2055,7 +2067,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="13" t="n"/>
       <c r="B59" s="8">
-        <f>IF($A59="","",TEXT(Calcoli!$AB$6+($A59-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A59-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A59="","",TEXT(Calcoli!$AG$6+($A59-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A59-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C59" s="13" t="n"/>
@@ -2070,7 +2082,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="13" t="n"/>
       <c r="B60" s="8">
-        <f>IF($A60="","",TEXT(Calcoli!$AB$6+($A60-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A60-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A60="","",TEXT(Calcoli!$AG$6+($A60-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A60-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C60" s="13" t="n"/>
@@ -2085,7 +2097,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="13" t="n"/>
       <c r="B61" s="8">
-        <f>IF($A61="","",TEXT(Calcoli!$AB$6+($A61-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A61-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A61="","",TEXT(Calcoli!$AG$6+($A61-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A61-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C61" s="13" t="n"/>
@@ -2100,7 +2112,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="13" t="n"/>
       <c r="B62" s="8">
-        <f>IF($A62="","",TEXT(Calcoli!$AB$6+($A62-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A62-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A62="","",TEXT(Calcoli!$AG$6+($A62-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A62-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C62" s="13" t="n"/>
@@ -2115,7 +2127,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="13" t="n"/>
       <c r="B63" s="8">
-        <f>IF($A63="","",TEXT(Calcoli!$AB$6+($A63-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A63-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A63="","",TEXT(Calcoli!$AG$6+($A63-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A63-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C63" s="13" t="n"/>
@@ -2130,7 +2142,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="13" t="n"/>
       <c r="B64" s="8">
-        <f>IF($A64="","",TEXT(Calcoli!$AB$6+($A64-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A64-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A64="","",TEXT(Calcoli!$AG$6+($A64-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A64-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C64" s="13" t="n"/>
@@ -2145,7 +2157,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="13" t="n"/>
       <c r="B65" s="8">
-        <f>IF($A65="","",TEXT(Calcoli!$AB$6+($A65-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A65-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A65="","",TEXT(Calcoli!$AG$6+($A65-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A65-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C65" s="13" t="n"/>
@@ -2160,7 +2172,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="13" t="n"/>
       <c r="B66" s="8">
-        <f>IF($A66="","",TEXT(Calcoli!$AB$6+($A66-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A66-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A66="","",TEXT(Calcoli!$AG$6+($A66-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A66-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C66" s="13" t="n"/>
@@ -2175,7 +2187,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="13" t="n"/>
       <c r="B67" s="8">
-        <f>IF($A67="","",TEXT(Calcoli!$AB$6+($A67-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A67-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A67="","",TEXT(Calcoli!$AG$6+($A67-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A67-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C67" s="13" t="n"/>
@@ -2190,7 +2202,7 @@
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="13" t="n"/>
       <c r="B68" s="8">
-        <f>IF($A68="","",TEXT(Calcoli!$AB$6+($A68-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A68-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A68="","",TEXT(Calcoli!$AG$6+($A68-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A68-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C68" s="13" t="n"/>
@@ -2205,7 +2217,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="13" t="n"/>
       <c r="B69" s="8">
-        <f>IF($A69="","",TEXT(Calcoli!$AB$6+($A69-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A69-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A69="","",TEXT(Calcoli!$AG$6+($A69-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A69-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C69" s="13" t="n"/>
@@ -2220,7 +2232,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="13" t="n"/>
       <c r="B70" s="8">
-        <f>IF($A70="","",TEXT(Calcoli!$AB$6+($A70-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A70-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A70="","",TEXT(Calcoli!$AG$6+($A70-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A70-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C70" s="13" t="n"/>
@@ -2235,7 +2247,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="13" t="n"/>
       <c r="B71" s="8">
-        <f>IF($A71="","",TEXT(Calcoli!$AB$6+($A71-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A71-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A71="","",TEXT(Calcoli!$AG$6+($A71-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A71-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C71" s="13" t="n"/>
@@ -2250,7 +2262,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="13" t="n"/>
       <c r="B72" s="8">
-        <f>IF($A72="","",TEXT(Calcoli!$AB$6+($A72-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A72-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A72="","",TEXT(Calcoli!$AG$6+($A72-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A72-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C72" s="13" t="n"/>
@@ -2265,7 +2277,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="13" t="n"/>
       <c r="B73" s="8">
-        <f>IF($A73="","",TEXT(Calcoli!$AB$6+($A73-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A73-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A73="","",TEXT(Calcoli!$AG$6+($A73-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A73-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C73" s="13" t="n"/>
@@ -2280,7 +2292,7 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="13" t="n"/>
       <c r="B74" s="8">
-        <f>IF($A74="","",TEXT(Calcoli!$AB$6+($A74-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A74-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A74="","",TEXT(Calcoli!$AG$6+($A74-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A74-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C74" s="13" t="n"/>
@@ -2295,7 +2307,7 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="13" t="n"/>
       <c r="B75" s="8">
-        <f>IF($A75="","",TEXT(Calcoli!$AB$6+($A75-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A75-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A75="","",TEXT(Calcoli!$AG$6+($A75-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A75-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C75" s="13" t="n"/>
@@ -2310,7 +2322,7 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="13" t="n"/>
       <c r="B76" s="8">
-        <f>IF($A76="","",TEXT(Calcoli!$AB$6+($A76-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A76-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A76="","",TEXT(Calcoli!$AG$6+($A76-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A76-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C76" s="13" t="n"/>
@@ -2325,7 +2337,7 @@
     <row r="77" ht="16" customHeight="1">
       <c r="A77" s="13" t="n"/>
       <c r="B77" s="8">
-        <f>IF($A77="","",TEXT(Calcoli!$AB$6+($A77-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A77-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A77="","",TEXT(Calcoli!$AG$6+($A77-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A77-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C77" s="13" t="n"/>
@@ -2340,7 +2352,7 @@
     <row r="78" ht="16" customHeight="1">
       <c r="A78" s="13" t="n"/>
       <c r="B78" s="8">
-        <f>IF($A78="","",TEXT(Calcoli!$AB$6+($A78-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A78-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A78="","",TEXT(Calcoli!$AG$6+($A78-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A78-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C78" s="13" t="n"/>
@@ -2355,7 +2367,7 @@
     <row r="79" ht="16" customHeight="1">
       <c r="A79" s="13" t="n"/>
       <c r="B79" s="8">
-        <f>IF($A79="","",TEXT(Calcoli!$AB$6+($A79-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A79-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A79="","",TEXT(Calcoli!$AG$6+($A79-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A79-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C79" s="13" t="n"/>
@@ -2370,7 +2382,7 @@
     <row r="80" ht="16" customHeight="1">
       <c r="A80" s="13" t="n"/>
       <c r="B80" s="8">
-        <f>IF($A80="","",TEXT(Calcoli!$AB$6+($A80-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A80-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A80="","",TEXT(Calcoli!$AG$6+($A80-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A80-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C80" s="13" t="n"/>
@@ -2385,7 +2397,7 @@
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="13" t="n"/>
       <c r="B81" s="8">
-        <f>IF($A81="","",TEXT(Calcoli!$AB$6+($A81-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A81-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A81="","",TEXT(Calcoli!$AG$6+($A81-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A81-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C81" s="13" t="n"/>
@@ -2400,7 +2412,7 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="13" t="n"/>
       <c r="B82" s="8">
-        <f>IF($A82="","",TEXT(Calcoli!$AB$6+($A82-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A82-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A82="","",TEXT(Calcoli!$AG$6+($A82-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A82-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C82" s="13" t="n"/>
@@ -2415,7 +2427,7 @@
     <row r="83" ht="16" customHeight="1">
       <c r="A83" s="13" t="n"/>
       <c r="B83" s="8">
-        <f>IF($A83="","",TEXT(Calcoli!$AB$6+($A83-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A83-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A83="","",TEXT(Calcoli!$AG$6+($A83-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A83-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C83" s="13" t="n"/>
@@ -2430,7 +2442,7 @@
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="13" t="n"/>
       <c r="B84" s="8">
-        <f>IF($A84="","",TEXT(Calcoli!$AB$6+($A84-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A84-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A84="","",TEXT(Calcoli!$AG$6+($A84-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A84-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C84" s="13" t="n"/>
@@ -2445,7 +2457,7 @@
     <row r="85" ht="16" customHeight="1">
       <c r="A85" s="13" t="n"/>
       <c r="B85" s="8">
-        <f>IF($A85="","",TEXT(Calcoli!$AB$6+($A85-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A85-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A85="","",TEXT(Calcoli!$AG$6+($A85-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A85-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C85" s="13" t="n"/>
@@ -2460,7 +2472,7 @@
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="13" t="n"/>
       <c r="B86" s="8">
-        <f>IF($A86="","",TEXT(Calcoli!$AB$6+($A86-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A86-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A86="","",TEXT(Calcoli!$AG$6+($A86-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A86-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C86" s="13" t="n"/>
@@ -2475,7 +2487,7 @@
     <row r="87" ht="16" customHeight="1">
       <c r="A87" s="13" t="n"/>
       <c r="B87" s="8">
-        <f>IF($A87="","",TEXT(Calcoli!$AB$6+($A87-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A87-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A87="","",TEXT(Calcoli!$AG$6+($A87-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A87-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C87" s="13" t="n"/>
@@ -2490,7 +2502,7 @@
     <row r="88" ht="16" customHeight="1">
       <c r="A88" s="13" t="n"/>
       <c r="B88" s="8">
-        <f>IF($A88="","",TEXT(Calcoli!$AB$6+($A88-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A88-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A88="","",TEXT(Calcoli!$AG$6+($A88-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A88-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C88" s="13" t="n"/>
@@ -2505,7 +2517,7 @@
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="13" t="n"/>
       <c r="B89" s="8">
-        <f>IF($A89="","",TEXT(Calcoli!$AB$6+($A89-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A89-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A89="","",TEXT(Calcoli!$AG$6+($A89-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A89-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C89" s="13" t="n"/>
@@ -2520,7 +2532,7 @@
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="13" t="n"/>
       <c r="B90" s="8">
-        <f>IF($A90="","",TEXT(Calcoli!$AB$6+($A90-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A90-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A90="","",TEXT(Calcoli!$AG$6+($A90-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A90-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C90" s="13" t="n"/>
@@ -2535,7 +2547,7 @@
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="13" t="n"/>
       <c r="B91" s="8">
-        <f>IF($A91="","",TEXT(Calcoli!$AB$6+($A91-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A91-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A91="","",TEXT(Calcoli!$AG$6+($A91-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A91-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C91" s="13" t="n"/>
@@ -2550,7 +2562,7 @@
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="13" t="n"/>
       <c r="B92" s="8">
-        <f>IF($A92="","",TEXT(Calcoli!$AB$6+($A92-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A92-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A92="","",TEXT(Calcoli!$AG$6+($A92-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A92-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C92" s="13" t="n"/>
@@ -2565,7 +2577,7 @@
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="13" t="n"/>
       <c r="B93" s="8">
-        <f>IF($A93="","",TEXT(Calcoli!$AB$6+($A93-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A93-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A93="","",TEXT(Calcoli!$AG$6+($A93-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A93-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C93" s="13" t="n"/>
@@ -2580,7 +2592,7 @@
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="13" t="n"/>
       <c r="B94" s="8">
-        <f>IF($A94="","",TEXT(Calcoli!$AB$6+($A94-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A94-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A94="","",TEXT(Calcoli!$AG$6+($A94-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A94-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C94" s="13" t="n"/>
@@ -2595,7 +2607,7 @@
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="13" t="n"/>
       <c r="B95" s="8">
-        <f>IF($A95="","",TEXT(Calcoli!$AB$6+($A95-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A95-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A95="","",TEXT(Calcoli!$AG$6+($A95-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A95-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C95" s="13" t="n"/>
@@ -2610,7 +2622,7 @@
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="13" t="n"/>
       <c r="B96" s="8">
-        <f>IF($A96="","",TEXT(Calcoli!$AB$6+($A96-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A96-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A96="","",TEXT(Calcoli!$AG$6+($A96-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A96-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C96" s="13" t="n"/>
@@ -2625,7 +2637,7 @@
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="13" t="n"/>
       <c r="B97" s="8">
-        <f>IF($A97="","",TEXT(Calcoli!$AB$6+($A97-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A97-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A97="","",TEXT(Calcoli!$AG$6+($A97-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A97-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C97" s="13" t="n"/>
@@ -2640,7 +2652,7 @@
     <row r="98" ht="16" customHeight="1">
       <c r="A98" s="13" t="n"/>
       <c r="B98" s="8">
-        <f>IF($A98="","",TEXT(Calcoli!$AB$6+($A98-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A98-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A98="","",TEXT(Calcoli!$AG$6+($A98-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A98-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C98" s="13" t="n"/>
@@ -2655,7 +2667,7 @@
     <row r="99" ht="16" customHeight="1">
       <c r="A99" s="13" t="n"/>
       <c r="B99" s="8">
-        <f>IF($A99="","",TEXT(Calcoli!$AB$6+($A99-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A99-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A99="","",TEXT(Calcoli!$AG$6+($A99-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A99-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C99" s="13" t="n"/>
@@ -2670,7 +2682,7 @@
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="13" t="n"/>
       <c r="B100" s="8">
-        <f>IF($A100="","",TEXT(Calcoli!$AB$6+($A100-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A100-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A100="","",TEXT(Calcoli!$AG$6+($A100-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A100-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C100" s="13" t="n"/>
@@ -2685,7 +2697,7 @@
     <row r="101" ht="16" customHeight="1">
       <c r="A101" s="13" t="n"/>
       <c r="B101" s="8">
-        <f>IF($A101="","",TEXT(Calcoli!$AB$6+($A101-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A101-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A101="","",TEXT(Calcoli!$AG$6+($A101-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A101-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C101" s="13" t="n"/>
@@ -2700,7 +2712,7 @@
     <row r="102" ht="16" customHeight="1">
       <c r="A102" s="13" t="n"/>
       <c r="B102" s="8">
-        <f>IF($A102="","",TEXT(Calcoli!$AB$6+($A102-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A102-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A102="","",TEXT(Calcoli!$AG$6+($A102-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A102-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C102" s="13" t="n"/>
@@ -2715,7 +2727,7 @@
     <row r="103" ht="16" customHeight="1">
       <c r="A103" s="13" t="n"/>
       <c r="B103" s="8">
-        <f>IF($A103="","",TEXT(Calcoli!$AB$6+($A103-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A103-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A103="","",TEXT(Calcoli!$AG$6+($A103-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A103-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C103" s="13" t="n"/>
@@ -2730,7 +2742,7 @@
     <row r="104" ht="16" customHeight="1">
       <c r="A104" s="13" t="n"/>
       <c r="B104" s="8">
-        <f>IF($A104="","",TEXT(Calcoli!$AB$6+($A104-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A104-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A104="","",TEXT(Calcoli!$AG$6+($A104-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A104-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C104" s="13" t="n"/>
@@ -2745,7 +2757,7 @@
     <row r="105" ht="16" customHeight="1">
       <c r="A105" s="13" t="n"/>
       <c r="B105" s="8">
-        <f>IF($A105="","",TEXT(Calcoli!$AB$6+($A105-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A105-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A105="","",TEXT(Calcoli!$AG$6+($A105-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A105-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C105" s="13" t="n"/>
@@ -2760,7 +2772,7 @@
     <row r="106" ht="16" customHeight="1">
       <c r="A106" s="13" t="n"/>
       <c r="B106" s="8">
-        <f>IF($A106="","",TEXT(Calcoli!$AB$6+($A106-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A106-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A106="","",TEXT(Calcoli!$AG$6+($A106-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A106-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C106" s="13" t="n"/>
@@ -2775,7 +2787,7 @@
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="13" t="n"/>
       <c r="B107" s="8">
-        <f>IF($A107="","",TEXT(Calcoli!$AB$6+($A107-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A107-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A107="","",TEXT(Calcoli!$AG$6+($A107-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A107-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C107" s="13" t="n"/>
@@ -2790,7 +2802,7 @@
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="13" t="n"/>
       <c r="B108" s="8">
-        <f>IF($A108="","",TEXT(Calcoli!$AB$6+($A108-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A108-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A108="","",TEXT(Calcoli!$AG$6+($A108-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A108-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C108" s="13" t="n"/>
@@ -2805,7 +2817,7 @@
     <row r="109" ht="16" customHeight="1">
       <c r="A109" s="13" t="n"/>
       <c r="B109" s="8">
-        <f>IF($A109="","",TEXT(Calcoli!$AB$6+($A109-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A109-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A109="","",TEXT(Calcoli!$AG$6+($A109-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A109-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C109" s="13" t="n"/>
@@ -2820,7 +2832,7 @@
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="13" t="n"/>
       <c r="B110" s="8">
-        <f>IF($A110="","",TEXT(Calcoli!$AB$6+($A110-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A110-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A110="","",TEXT(Calcoli!$AG$6+($A110-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A110-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C110" s="13" t="n"/>
@@ -2835,7 +2847,7 @@
     <row r="111" ht="16" customHeight="1">
       <c r="A111" s="13" t="n"/>
       <c r="B111" s="8">
-        <f>IF($A111="","",TEXT(Calcoli!$AB$6+($A111-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A111-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A111="","",TEXT(Calcoli!$AG$6+($A111-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A111-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C111" s="13" t="n"/>
@@ -2850,7 +2862,7 @@
     <row r="112" ht="16" customHeight="1">
       <c r="A112" s="13" t="n"/>
       <c r="B112" s="8">
-        <f>IF($A112="","",TEXT(Calcoli!$AB$6+($A112-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A112-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A112="","",TEXT(Calcoli!$AG$6+($A112-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A112-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C112" s="13" t="n"/>
@@ -2865,7 +2877,7 @@
     <row r="113" ht="16" customHeight="1">
       <c r="A113" s="13" t="n"/>
       <c r="B113" s="8">
-        <f>IF($A113="","",TEXT(Calcoli!$AB$6+($A113-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A113-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A113="","",TEXT(Calcoli!$AG$6+($A113-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A113-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C113" s="13" t="n"/>
@@ -2880,7 +2892,7 @@
     <row r="114" ht="16" customHeight="1">
       <c r="A114" s="13" t="n"/>
       <c r="B114" s="8">
-        <f>IF($A114="","",TEXT(Calcoli!$AB$6+($A114-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A114-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A114="","",TEXT(Calcoli!$AG$6+($A114-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A114-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C114" s="13" t="n"/>
@@ -2895,7 +2907,7 @@
     <row r="115" ht="16" customHeight="1">
       <c r="A115" s="13" t="n"/>
       <c r="B115" s="8">
-        <f>IF($A115="","",TEXT(Calcoli!$AB$6+($A115-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A115-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A115="","",TEXT(Calcoli!$AG$6+($A115-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A115-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C115" s="13" t="n"/>
@@ -2910,7 +2922,7 @@
     <row r="116" ht="16" customHeight="1">
       <c r="A116" s="13" t="n"/>
       <c r="B116" s="8">
-        <f>IF($A116="","",TEXT(Calcoli!$AB$6+($A116-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A116-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A116="","",TEXT(Calcoli!$AG$6+($A116-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A116-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C116" s="13" t="n"/>
@@ -2925,7 +2937,7 @@
     <row r="117" ht="16" customHeight="1">
       <c r="A117" s="13" t="n"/>
       <c r="B117" s="8">
-        <f>IF($A117="","",TEXT(Calcoli!$AB$6+($A117-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A117-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A117="","",TEXT(Calcoli!$AG$6+($A117-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A117-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C117" s="13" t="n"/>
@@ -2940,7 +2952,7 @@
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="13" t="n"/>
       <c r="B118" s="8">
-        <f>IF($A118="","",TEXT(Calcoli!$AB$6+($A118-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A118-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A118="","",TEXT(Calcoli!$AG$6+($A118-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A118-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C118" s="13" t="n"/>
@@ -2955,7 +2967,7 @@
     <row r="119" ht="16" customHeight="1">
       <c r="A119" s="13" t="n"/>
       <c r="B119" s="8">
-        <f>IF($A119="","",TEXT(Calcoli!$AB$6+($A119-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A119-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A119="","",TEXT(Calcoli!$AG$6+($A119-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A119-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C119" s="13" t="n"/>
@@ -2970,7 +2982,7 @@
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="13" t="n"/>
       <c r="B120" s="8">
-        <f>IF($A120="","",TEXT(Calcoli!$AB$6+($A120-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A120-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A120="","",TEXT(Calcoli!$AG$6+($A120-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A120-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C120" s="13" t="n"/>
@@ -2985,7 +2997,7 @@
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="13" t="n"/>
       <c r="B121" s="8">
-        <f>IF($A121="","",TEXT(Calcoli!$AB$6+($A121-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A121-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A121="","",TEXT(Calcoli!$AG$6+($A121-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A121-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C121" s="13" t="n"/>
@@ -3000,7 +3012,7 @@
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="13" t="n"/>
       <c r="B122" s="8">
-        <f>IF($A122="","",TEXT(Calcoli!$AB$6+($A122-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A122-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A122="","",TEXT(Calcoli!$AG$6+($A122-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A122-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C122" s="13" t="n"/>
@@ -3015,7 +3027,7 @@
     <row r="123" ht="16" customHeight="1">
       <c r="A123" s="13" t="n"/>
       <c r="B123" s="8">
-        <f>IF($A123="","",TEXT(Calcoli!$AB$6+($A123-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A123-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A123="","",TEXT(Calcoli!$AG$6+($A123-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A123-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C123" s="13" t="n"/>
@@ -3030,7 +3042,7 @@
     <row r="124" ht="16" customHeight="1">
       <c r="A124" s="13" t="n"/>
       <c r="B124" s="8">
-        <f>IF($A124="","",TEXT(Calcoli!$AB$6+($A124-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A124-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A124="","",TEXT(Calcoli!$AG$6+($A124-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A124-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C124" s="13" t="n"/>
@@ -3045,7 +3057,7 @@
     <row r="125" ht="16" customHeight="1">
       <c r="A125" s="13" t="n"/>
       <c r="B125" s="8">
-        <f>IF($A125="","",TEXT(Calcoli!$AB$6+($A125-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A125-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A125="","",TEXT(Calcoli!$AG$6+($A125-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A125-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C125" s="13" t="n"/>
@@ -3060,7 +3072,7 @@
     <row r="126" ht="16" customHeight="1">
       <c r="A126" s="13" t="n"/>
       <c r="B126" s="8">
-        <f>IF($A126="","",TEXT(Calcoli!$AB$6+($A126-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A126-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A126="","",TEXT(Calcoli!$AG$6+($A126-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A126-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C126" s="13" t="n"/>
@@ -3075,7 +3087,7 @@
     <row r="127" ht="16" customHeight="1">
       <c r="A127" s="13" t="n"/>
       <c r="B127" s="8">
-        <f>IF($A127="","",TEXT(Calcoli!$AB$6+($A127-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A127-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A127="","",TEXT(Calcoli!$AG$6+($A127-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A127-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C127" s="13" t="n"/>
@@ -3090,7 +3102,7 @@
     <row r="128" ht="16" customHeight="1">
       <c r="A128" s="13" t="n"/>
       <c r="B128" s="8">
-        <f>IF($A128="","",TEXT(Calcoli!$AB$6+($A128-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A128-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A128="","",TEXT(Calcoli!$AG$6+($A128-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A128-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C128" s="13" t="n"/>
@@ -3105,7 +3117,7 @@
     <row r="129" ht="16" customHeight="1">
       <c r="A129" s="13" t="n"/>
       <c r="B129" s="8">
-        <f>IF($A129="","",TEXT(Calcoli!$AB$6+($A129-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A129-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A129="","",TEXT(Calcoli!$AG$6+($A129-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A129-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C129" s="13" t="n"/>
@@ -3120,7 +3132,7 @@
     <row r="130" ht="16" customHeight="1">
       <c r="A130" s="13" t="n"/>
       <c r="B130" s="8">
-        <f>IF($A130="","",TEXT(Calcoli!$AB$6+($A130-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A130-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A130="","",TEXT(Calcoli!$AG$6+($A130-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A130-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C130" s="13" t="n"/>
@@ -3135,7 +3147,7 @@
     <row r="131" ht="16" customHeight="1">
       <c r="A131" s="13" t="n"/>
       <c r="B131" s="8">
-        <f>IF($A131="","",TEXT(Calcoli!$AB$6+($A131-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A131-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A131="","",TEXT(Calcoli!$AG$6+($A131-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A131-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C131" s="13" t="n"/>
@@ -3150,7 +3162,7 @@
     <row r="132" ht="16" customHeight="1">
       <c r="A132" s="13" t="n"/>
       <c r="B132" s="8">
-        <f>IF($A132="","",TEXT(Calcoli!$AB$6+($A132-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A132-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A132="","",TEXT(Calcoli!$AG$6+($A132-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A132-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C132" s="13" t="n"/>
@@ -3165,7 +3177,7 @@
     <row r="133" ht="16" customHeight="1">
       <c r="A133" s="13" t="n"/>
       <c r="B133" s="8">
-        <f>IF($A133="","",TEXT(Calcoli!$AB$6+($A133-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A133-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A133="","",TEXT(Calcoli!$AG$6+($A133-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A133-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C133" s="13" t="n"/>
@@ -3180,7 +3192,7 @@
     <row r="134" ht="16" customHeight="1">
       <c r="A134" s="13" t="n"/>
       <c r="B134" s="8">
-        <f>IF($A134="","",TEXT(Calcoli!$AB$6+($A134-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A134-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A134="","",TEXT(Calcoli!$AG$6+($A134-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A134-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C134" s="13" t="n"/>
@@ -3195,7 +3207,7 @@
     <row r="135" ht="16" customHeight="1">
       <c r="A135" s="13" t="n"/>
       <c r="B135" s="8">
-        <f>IF($A135="","",TEXT(Calcoli!$AB$6+($A135-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A135-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A135="","",TEXT(Calcoli!$AG$6+($A135-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A135-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C135" s="13" t="n"/>
@@ -3210,7 +3222,7 @@
     <row r="136" ht="16" customHeight="1">
       <c r="A136" s="13" t="n"/>
       <c r="B136" s="8">
-        <f>IF($A136="","",TEXT(Calcoli!$AB$6+($A136-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A136-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A136="","",TEXT(Calcoli!$AG$6+($A136-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A136-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C136" s="13" t="n"/>
@@ -3225,7 +3237,7 @@
     <row r="137" ht="16" customHeight="1">
       <c r="A137" s="13" t="n"/>
       <c r="B137" s="8">
-        <f>IF($A137="","",TEXT(Calcoli!$AB$6+($A137-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A137-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A137="","",TEXT(Calcoli!$AG$6+($A137-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A137-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C137" s="13" t="n"/>
@@ -3240,7 +3252,7 @@
     <row r="138" ht="16" customHeight="1">
       <c r="A138" s="13" t="n"/>
       <c r="B138" s="8">
-        <f>IF($A138="","",TEXT(Calcoli!$AB$6+($A138-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A138-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A138="","",TEXT(Calcoli!$AG$6+($A138-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A138-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C138" s="13" t="n"/>
@@ -3255,7 +3267,7 @@
     <row r="139" ht="16" customHeight="1">
       <c r="A139" s="13" t="n"/>
       <c r="B139" s="8">
-        <f>IF($A139="","",TEXT(Calcoli!$AB$6+($A139-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A139-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A139="","",TEXT(Calcoli!$AG$6+($A139-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A139-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C139" s="13" t="n"/>
@@ -3270,7 +3282,7 @@
     <row r="140" ht="16" customHeight="1">
       <c r="A140" s="13" t="n"/>
       <c r="B140" s="8">
-        <f>IF($A140="","",TEXT(Calcoli!$AB$6+($A140-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A140-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A140="","",TEXT(Calcoli!$AG$6+($A140-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A140-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C140" s="13" t="n"/>
@@ -3285,7 +3297,7 @@
     <row r="141" ht="16" customHeight="1">
       <c r="A141" s="13" t="n"/>
       <c r="B141" s="8">
-        <f>IF($A141="","",TEXT(Calcoli!$AB$6+($A141-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A141-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A141="","",TEXT(Calcoli!$AG$6+($A141-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A141-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C141" s="13" t="n"/>
@@ -3300,7 +3312,7 @@
     <row r="142" ht="16" customHeight="1">
       <c r="A142" s="13" t="n"/>
       <c r="B142" s="8">
-        <f>IF($A142="","",TEXT(Calcoli!$AB$6+($A142-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A142-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A142="","",TEXT(Calcoli!$AG$6+($A142-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A142-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C142" s="13" t="n"/>
@@ -3315,7 +3327,7 @@
     <row r="143" ht="16" customHeight="1">
       <c r="A143" s="13" t="n"/>
       <c r="B143" s="8">
-        <f>IF($A143="","",TEXT(Calcoli!$AB$6+($A143-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A143-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A143="","",TEXT(Calcoli!$AG$6+($A143-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A143-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C143" s="13" t="n"/>
@@ -3330,7 +3342,7 @@
     <row r="144" ht="16" customHeight="1">
       <c r="A144" s="13" t="n"/>
       <c r="B144" s="8">
-        <f>IF($A144="","",TEXT(Calcoli!$AB$6+($A144-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A144-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A144="","",TEXT(Calcoli!$AG$6+($A144-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A144-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C144" s="13" t="n"/>
@@ -3345,7 +3357,7 @@
     <row r="145" ht="16" customHeight="1">
       <c r="A145" s="13" t="n"/>
       <c r="B145" s="8">
-        <f>IF($A145="","",TEXT(Calcoli!$AB$6+($A145-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A145-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A145="","",TEXT(Calcoli!$AG$6+($A145-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A145-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C145" s="13" t="n"/>
@@ -3360,7 +3372,7 @@
     <row r="146" ht="16" customHeight="1">
       <c r="A146" s="13" t="n"/>
       <c r="B146" s="8">
-        <f>IF($A146="","",TEXT(Calcoli!$AB$6+($A146-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A146-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A146="","",TEXT(Calcoli!$AG$6+($A146-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A146-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C146" s="13" t="n"/>
@@ -3375,7 +3387,7 @@
     <row r="147" ht="16" customHeight="1">
       <c r="A147" s="13" t="n"/>
       <c r="B147" s="8">
-        <f>IF($A147="","",TEXT(Calcoli!$AB$6+($A147-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A147-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A147="","",TEXT(Calcoli!$AG$6+($A147-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A147-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C147" s="13" t="n"/>
@@ -3390,7 +3402,7 @@
     <row r="148" ht="16" customHeight="1">
       <c r="A148" s="13" t="n"/>
       <c r="B148" s="8">
-        <f>IF($A148="","",TEXT(Calcoli!$AB$6+($A148-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A148-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A148="","",TEXT(Calcoli!$AG$6+($A148-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A148-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C148" s="13" t="n"/>
@@ -3405,7 +3417,7 @@
     <row r="149" ht="16" customHeight="1">
       <c r="A149" s="13" t="n"/>
       <c r="B149" s="8">
-        <f>IF($A149="","",TEXT(Calcoli!$AB$6+($A149-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A149-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A149="","",TEXT(Calcoli!$AG$6+($A149-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A149-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C149" s="13" t="n"/>
@@ -3420,7 +3432,7 @@
     <row r="150" ht="16" customHeight="1">
       <c r="A150" s="13" t="n"/>
       <c r="B150" s="8">
-        <f>IF($A150="","",TEXT(Calcoli!$AB$6+($A150-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A150-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A150="","",TEXT(Calcoli!$AG$6+($A150-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A150-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C150" s="13" t="n"/>
@@ -3435,7 +3447,7 @@
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="13" t="n"/>
       <c r="B151" s="8">
-        <f>IF($A151="","",TEXT(Calcoli!$AB$6+($A151-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A151-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A151="","",TEXT(Calcoli!$AG$6+($A151-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A151-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C151" s="13" t="n"/>
@@ -3450,7 +3462,7 @@
     <row r="152" ht="16" customHeight="1">
       <c r="A152" s="13" t="n"/>
       <c r="B152" s="8">
-        <f>IF($A152="","",TEXT(Calcoli!$AB$6+($A152-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A152-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A152="","",TEXT(Calcoli!$AG$6+($A152-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A152-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C152" s="13" t="n"/>
@@ -3465,7 +3477,7 @@
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="13" t="n"/>
       <c r="B153" s="8">
-        <f>IF($A153="","",TEXT(Calcoli!$AB$6+($A153-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A153-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A153="","",TEXT(Calcoli!$AG$6+($A153-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A153-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C153" s="13" t="n"/>
@@ -3480,7 +3492,7 @@
     <row r="154" ht="16" customHeight="1">
       <c r="A154" s="13" t="n"/>
       <c r="B154" s="8">
-        <f>IF($A154="","",TEXT(Calcoli!$AB$6+($A154-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A154-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A154="","",TEXT(Calcoli!$AG$6+($A154-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A154-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C154" s="13" t="n"/>
@@ -3495,7 +3507,7 @@
     <row r="155" ht="16" customHeight="1">
       <c r="A155" s="13" t="n"/>
       <c r="B155" s="8">
-        <f>IF($A155="","",TEXT(Calcoli!$AB$6+($A155-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A155-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A155="","",TEXT(Calcoli!$AG$6+($A155-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A155-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C155" s="13" t="n"/>
@@ -3510,7 +3522,7 @@
     <row r="156" ht="16" customHeight="1">
       <c r="A156" s="13" t="n"/>
       <c r="B156" s="8">
-        <f>IF($A156="","",TEXT(Calcoli!$AB$6+($A156-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A156-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A156="","",TEXT(Calcoli!$AG$6+($A156-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A156-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C156" s="13" t="n"/>
@@ -3525,7 +3537,7 @@
     <row r="157" ht="16" customHeight="1">
       <c r="A157" s="13" t="n"/>
       <c r="B157" s="8">
-        <f>IF($A157="","",TEXT(Calcoli!$AB$6+($A157-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A157-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A157="","",TEXT(Calcoli!$AG$6+($A157-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A157-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C157" s="13" t="n"/>
@@ -3540,7 +3552,7 @@
     <row r="158" ht="16" customHeight="1">
       <c r="A158" s="13" t="n"/>
       <c r="B158" s="8">
-        <f>IF($A158="","",TEXT(Calcoli!$AB$6+($A158-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A158-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A158="","",TEXT(Calcoli!$AG$6+($A158-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A158-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C158" s="13" t="n"/>
@@ -3555,7 +3567,7 @@
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="13" t="n"/>
       <c r="B159" s="8">
-        <f>IF($A159="","",TEXT(Calcoli!$AB$6+($A159-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A159-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A159="","",TEXT(Calcoli!$AG$6+($A159-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A159-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C159" s="13" t="n"/>
@@ -3570,7 +3582,7 @@
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="13" t="n"/>
       <c r="B160" s="8">
-        <f>IF($A160="","",TEXT(Calcoli!$AB$6+($A160-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A160-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A160="","",TEXT(Calcoli!$AG$6+($A160-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A160-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C160" s="13" t="n"/>
@@ -3585,7 +3597,7 @@
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="13" t="n"/>
       <c r="B161" s="8">
-        <f>IF($A161="","",TEXT(Calcoli!$AB$6+($A161-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A161-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A161="","",TEXT(Calcoli!$AG$6+($A161-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A161-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C161" s="13" t="n"/>
@@ -3600,7 +3612,7 @@
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="13" t="n"/>
       <c r="B162" s="8">
-        <f>IF($A162="","",TEXT(Calcoli!$AB$6+($A162-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A162-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A162="","",TEXT(Calcoli!$AG$6+($A162-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A162-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C162" s="13" t="n"/>
@@ -3615,7 +3627,7 @@
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="13" t="n"/>
       <c r="B163" s="8">
-        <f>IF($A163="","",TEXT(Calcoli!$AB$6+($A163-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A163-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A163="","",TEXT(Calcoli!$AG$6+($A163-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A163-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C163" s="13" t="n"/>
@@ -3630,7 +3642,7 @@
     <row r="164" ht="16" customHeight="1">
       <c r="A164" s="13" t="n"/>
       <c r="B164" s="8">
-        <f>IF($A164="","",TEXT(Calcoli!$AB$6+($A164-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A164-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A164="","",TEXT(Calcoli!$AG$6+($A164-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A164-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C164" s="13" t="n"/>
@@ -3645,7 +3657,7 @@
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="13" t="n"/>
       <c r="B165" s="8">
-        <f>IF($A165="","",TEXT(Calcoli!$AB$6+($A165-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A165-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A165="","",TEXT(Calcoli!$AG$6+($A165-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A165-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C165" s="13" t="n"/>
@@ -3660,7 +3672,7 @@
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="13" t="n"/>
       <c r="B166" s="8">
-        <f>IF($A166="","",TEXT(Calcoli!$AB$6+($A166-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A166-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A166="","",TEXT(Calcoli!$AG$6+($A166-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A166-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C166" s="13" t="n"/>
@@ -3675,7 +3687,7 @@
     <row r="167" ht="16" customHeight="1">
       <c r="A167" s="13" t="n"/>
       <c r="B167" s="8">
-        <f>IF($A167="","",TEXT(Calcoli!$AB$6+($A167-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A167-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A167="","",TEXT(Calcoli!$AG$6+($A167-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A167-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C167" s="13" t="n"/>
@@ -3690,7 +3702,7 @@
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="13" t="n"/>
       <c r="B168" s="8">
-        <f>IF($A168="","",TEXT(Calcoli!$AB$6+($A168-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A168-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A168="","",TEXT(Calcoli!$AG$6+($A168-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A168-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C168" s="13" t="n"/>
@@ -3705,7 +3717,7 @@
     <row r="169" ht="16" customHeight="1">
       <c r="A169" s="13" t="n"/>
       <c r="B169" s="8">
-        <f>IF($A169="","",TEXT(Calcoli!$AB$6+($A169-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A169-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A169="","",TEXT(Calcoli!$AG$6+($A169-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A169-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C169" s="13" t="n"/>
@@ -3720,7 +3732,7 @@
     <row r="170" ht="16" customHeight="1">
       <c r="A170" s="13" t="n"/>
       <c r="B170" s="8">
-        <f>IF($A170="","",TEXT(Calcoli!$AB$6+($A170-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A170-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A170="","",TEXT(Calcoli!$AG$6+($A170-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A170-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C170" s="13" t="n"/>
@@ -3735,7 +3747,7 @@
     <row r="171" ht="16" customHeight="1">
       <c r="A171" s="13" t="n"/>
       <c r="B171" s="8">
-        <f>IF($A171="","",TEXT(Calcoli!$AB$6+($A171-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A171-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A171="","",TEXT(Calcoli!$AG$6+($A171-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A171-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C171" s="13" t="n"/>
@@ -3750,7 +3762,7 @@
     <row r="172" ht="16" customHeight="1">
       <c r="A172" s="13" t="n"/>
       <c r="B172" s="8">
-        <f>IF($A172="","",TEXT(Calcoli!$AB$6+($A172-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A172-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A172="","",TEXT(Calcoli!$AG$6+($A172-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A172-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C172" s="13" t="n"/>
@@ -3765,7 +3777,7 @@
     <row r="173" ht="16" customHeight="1">
       <c r="A173" s="13" t="n"/>
       <c r="B173" s="8">
-        <f>IF($A173="","",TEXT(Calcoli!$AB$6+($A173-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A173-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A173="","",TEXT(Calcoli!$AG$6+($A173-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A173-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C173" s="13" t="n"/>
@@ -3780,7 +3792,7 @@
     <row r="174" ht="16" customHeight="1">
       <c r="A174" s="13" t="n"/>
       <c r="B174" s="8">
-        <f>IF($A174="","",TEXT(Calcoli!$AB$6+($A174-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A174-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A174="","",TEXT(Calcoli!$AG$6+($A174-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A174-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C174" s="13" t="n"/>
@@ -3795,7 +3807,7 @@
     <row r="175" ht="16" customHeight="1">
       <c r="A175" s="13" t="n"/>
       <c r="B175" s="8">
-        <f>IF($A175="","",TEXT(Calcoli!$AB$6+($A175-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A175-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A175="","",TEXT(Calcoli!$AG$6+($A175-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A175-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C175" s="13" t="n"/>
@@ -3810,7 +3822,7 @@
     <row r="176" ht="16" customHeight="1">
       <c r="A176" s="13" t="n"/>
       <c r="B176" s="8">
-        <f>IF($A176="","",TEXT(Calcoli!$AB$6+($A176-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A176-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A176="","",TEXT(Calcoli!$AG$6+($A176-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A176-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C176" s="13" t="n"/>
@@ -3825,7 +3837,7 @@
     <row r="177" ht="16" customHeight="1">
       <c r="A177" s="13" t="n"/>
       <c r="B177" s="8">
-        <f>IF($A177="","",TEXT(Calcoli!$AB$6+($A177-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A177-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A177="","",TEXT(Calcoli!$AG$6+($A177-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A177-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C177" s="13" t="n"/>
@@ -3840,7 +3852,7 @@
     <row r="178" ht="16" customHeight="1">
       <c r="A178" s="13" t="n"/>
       <c r="B178" s="8">
-        <f>IF($A178="","",TEXT(Calcoli!$AB$6+($A178-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A178-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A178="","",TEXT(Calcoli!$AG$6+($A178-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A178-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C178" s="13" t="n"/>
@@ -3855,7 +3867,7 @@
     <row r="179" ht="16" customHeight="1">
       <c r="A179" s="13" t="n"/>
       <c r="B179" s="8">
-        <f>IF($A179="","",TEXT(Calcoli!$AB$6+($A179-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A179-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A179="","",TEXT(Calcoli!$AG$6+($A179-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A179-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C179" s="13" t="n"/>
@@ -3870,7 +3882,7 @@
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="13" t="n"/>
       <c r="B180" s="8">
-        <f>IF($A180="","",TEXT(Calcoli!$AB$6+($A180-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A180-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A180="","",TEXT(Calcoli!$AG$6+($A180-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A180-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C180" s="13" t="n"/>
@@ -3885,7 +3897,7 @@
     <row r="181" ht="16" customHeight="1">
       <c r="A181" s="13" t="n"/>
       <c r="B181" s="8">
-        <f>IF($A181="","",TEXT(Calcoli!$AB$6+($A181-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A181-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A181="","",TEXT(Calcoli!$AG$6+($A181-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A181-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C181" s="13" t="n"/>
@@ -3900,7 +3912,7 @@
     <row r="182" ht="16" customHeight="1">
       <c r="A182" s="13" t="n"/>
       <c r="B182" s="8">
-        <f>IF($A182="","",TEXT(Calcoli!$AB$6+($A182-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A182-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A182="","",TEXT(Calcoli!$AG$6+($A182-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A182-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C182" s="13" t="n"/>
@@ -3915,7 +3927,7 @@
     <row r="183" ht="16" customHeight="1">
       <c r="A183" s="13" t="n"/>
       <c r="B183" s="8">
-        <f>IF($A183="","",TEXT(Calcoli!$AB$6+($A183-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A183-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A183="","",TEXT(Calcoli!$AG$6+($A183-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A183-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C183" s="13" t="n"/>
@@ -3930,7 +3942,7 @@
     <row r="184" ht="16" customHeight="1">
       <c r="A184" s="13" t="n"/>
       <c r="B184" s="8">
-        <f>IF($A184="","",TEXT(Calcoli!$AB$6+($A184-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A184-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A184="","",TEXT(Calcoli!$AG$6+($A184-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A184-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C184" s="13" t="n"/>
@@ -3945,7 +3957,7 @@
     <row r="185" ht="16" customHeight="1">
       <c r="A185" s="13" t="n"/>
       <c r="B185" s="8">
-        <f>IF($A185="","",TEXT(Calcoli!$AB$6+($A185-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A185-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A185="","",TEXT(Calcoli!$AG$6+($A185-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A185-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C185" s="13" t="n"/>
@@ -3960,7 +3972,7 @@
     <row r="186" ht="16" customHeight="1">
       <c r="A186" s="13" t="n"/>
       <c r="B186" s="8">
-        <f>IF($A186="","",TEXT(Calcoli!$AB$6+($A186-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A186-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A186="","",TEXT(Calcoli!$AG$6+($A186-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A186-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C186" s="13" t="n"/>
@@ -3975,7 +3987,7 @@
     <row r="187" ht="16" customHeight="1">
       <c r="A187" s="13" t="n"/>
       <c r="B187" s="8">
-        <f>IF($A187="","",TEXT(Calcoli!$AB$6+($A187-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A187-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A187="","",TEXT(Calcoli!$AG$6+($A187-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A187-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C187" s="13" t="n"/>
@@ -3990,7 +4002,7 @@
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="13" t="n"/>
       <c r="B188" s="8">
-        <f>IF($A188="","",TEXT(Calcoli!$AB$6+($A188-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A188-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A188="","",TEXT(Calcoli!$AG$6+($A188-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A188-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C188" s="13" t="n"/>
@@ -4005,7 +4017,7 @@
     <row r="189" ht="16" customHeight="1">
       <c r="A189" s="13" t="n"/>
       <c r="B189" s="8">
-        <f>IF($A189="","",TEXT(Calcoli!$AB$6+($A189-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A189-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A189="","",TEXT(Calcoli!$AG$6+($A189-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A189-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C189" s="13" t="n"/>
@@ -4020,7 +4032,7 @@
     <row r="190" ht="16" customHeight="1">
       <c r="A190" s="13" t="n"/>
       <c r="B190" s="8">
-        <f>IF($A190="","",TEXT(Calcoli!$AB$6+($A190-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A190-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A190="","",TEXT(Calcoli!$AG$6+($A190-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A190-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C190" s="13" t="n"/>
@@ -4035,7 +4047,7 @@
     <row r="191" ht="16" customHeight="1">
       <c r="A191" s="13" t="n"/>
       <c r="B191" s="8">
-        <f>IF($A191="","",TEXT(Calcoli!$AB$6+($A191-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A191-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A191="","",TEXT(Calcoli!$AG$6+($A191-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A191-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C191" s="13" t="n"/>
@@ -4050,7 +4062,7 @@
     <row r="192" ht="16" customHeight="1">
       <c r="A192" s="13" t="n"/>
       <c r="B192" s="8">
-        <f>IF($A192="","",TEXT(Calcoli!$AB$6+($A192-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A192-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A192="","",TEXT(Calcoli!$AG$6+($A192-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A192-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C192" s="13" t="n"/>
@@ -4065,7 +4077,7 @@
     <row r="193" ht="16" customHeight="1">
       <c r="A193" s="13" t="n"/>
       <c r="B193" s="8">
-        <f>IF($A193="","",TEXT(Calcoli!$AB$6+($A193-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A193-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A193="","",TEXT(Calcoli!$AG$6+($A193-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A193-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C193" s="13" t="n"/>
@@ -4080,7 +4092,7 @@
     <row r="194" ht="16" customHeight="1">
       <c r="A194" s="13" t="n"/>
       <c r="B194" s="8">
-        <f>IF($A194="","",TEXT(Calcoli!$AB$6+($A194-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A194-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A194="","",TEXT(Calcoli!$AG$6+($A194-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A194-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C194" s="13" t="n"/>
@@ -4095,7 +4107,7 @@
     <row r="195" ht="16" customHeight="1">
       <c r="A195" s="13" t="n"/>
       <c r="B195" s="8">
-        <f>IF($A195="","",TEXT(Calcoli!$AB$6+($A195-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A195-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A195="","",TEXT(Calcoli!$AG$6+($A195-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A195-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C195" s="13" t="n"/>
@@ -4110,7 +4122,7 @@
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="13" t="n"/>
       <c r="B196" s="8">
-        <f>IF($A196="","",TEXT(Calcoli!$AB$6+($A196-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A196-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A196="","",TEXT(Calcoli!$AG$6+($A196-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A196-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C196" s="13" t="n"/>
@@ -4125,7 +4137,7 @@
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="13" t="n"/>
       <c r="B197" s="8">
-        <f>IF($A197="","",TEXT(Calcoli!$AB$6+($A197-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A197-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A197="","",TEXT(Calcoli!$AG$6+($A197-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A197-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C197" s="13" t="n"/>
@@ -4140,7 +4152,7 @@
     <row r="198" ht="16" customHeight="1">
       <c r="A198" s="13" t="n"/>
       <c r="B198" s="8">
-        <f>IF($A198="","",TEXT(Calcoli!$AB$6+($A198-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A198-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A198="","",TEXT(Calcoli!$AG$6+($A198-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A198-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C198" s="13" t="n"/>
@@ -4155,7 +4167,7 @@
     <row r="199" ht="16" customHeight="1">
       <c r="A199" s="13" t="n"/>
       <c r="B199" s="8">
-        <f>IF($A199="","",TEXT(Calcoli!$AB$6+($A199-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A199-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A199="","",TEXT(Calcoli!$AG$6+($A199-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A199-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C199" s="13" t="n"/>
@@ -4170,7 +4182,7 @@
     <row r="200" ht="16" customHeight="1">
       <c r="A200" s="13" t="n"/>
       <c r="B200" s="8">
-        <f>IF($A200="","",TEXT(Calcoli!$AB$6+($A200-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A200-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A200="","",TEXT(Calcoli!$AG$6+($A200-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A200-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C200" s="13" t="n"/>
@@ -4185,7 +4197,7 @@
     <row r="201" ht="16" customHeight="1">
       <c r="A201" s="13" t="n"/>
       <c r="B201" s="8">
-        <f>IF($A201="","",TEXT(Calcoli!$AB$6+($A201-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A201-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A201="","",TEXT(Calcoli!$AG$6+($A201-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A201-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C201" s="13" t="n"/>
@@ -4200,7 +4212,7 @@
     <row r="202" ht="16" customHeight="1">
       <c r="A202" s="13" t="n"/>
       <c r="B202" s="8">
-        <f>IF($A202="","",TEXT(Calcoli!$AB$6+($A202-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A202-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A202="","",TEXT(Calcoli!$AG$6+($A202-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A202-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C202" s="13" t="n"/>
@@ -4215,7 +4227,7 @@
     <row r="203" ht="16" customHeight="1">
       <c r="A203" s="13" t="n"/>
       <c r="B203" s="8">
-        <f>IF($A203="","",TEXT(Calcoli!$AB$6+($A203-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A203-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A203="","",TEXT(Calcoli!$AG$6+($A203-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A203-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C203" s="13" t="n"/>
@@ -4230,7 +4242,7 @@
     <row r="204" ht="16" customHeight="1">
       <c r="A204" s="13" t="n"/>
       <c r="B204" s="8">
-        <f>IF($A204="","",TEXT(Calcoli!$AB$6+($A204-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AB$6+($A204-1)*7+4,"dd/mm/yyyy"))</f>
+        <f>IF($A204="","",TEXT(Calcoli!$AG$6+($A204-1)*7,"dd/mm/yyyy")&amp;" - "&amp;TEXT(Calcoli!$AG$6+($A204-1)*7+4,"dd/mm/yyyy"))</f>
         <v/>
       </c>
       <c r="C204" s="13" t="n"/>
@@ -7498,7 +7510,7 @@
       </c>
       <c r="B17" s="41" t="inlineStr">
         <is>
-          <t>Recuperi maturati e non ancora effettuati, di norma perché la persona era assente anche nella settimana del recupero (R7): vanno riprogrammati.</t>
+          <t>Recuperi maturati e non ancora effettuati entro la fine del periodo. Durante il periodo il recupero slitta da solo alla prima settimana utile (R7): un valore diverso da zero segnala un debito rimasto aperto, da riportare nel calendario successivo.</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AH70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7549,6 +7561,12 @@
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="18" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="18" customWidth="1" min="29" max="29"/>
+    <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7616,7 +7634,7 @@
       </c>
       <c r="L5" s="42" t="inlineStr">
         <is>
-          <t>Recupero da</t>
+          <t>Debitore del recupero</t>
         </is>
       </c>
       <c r="M5" s="42" t="inlineStr">
@@ -7684,7 +7702,37 @@
           <t>Nota sintetica</t>
         </is>
       </c>
-      <c r="AB5" s="31" t="inlineStr">
+      <c r="Z5" s="42" t="inlineStr">
+        <is>
+          <t>Progressivo debito</t>
+        </is>
+      </c>
+      <c r="AA5" s="42" t="inlineStr">
+        <is>
+          <t>Chiave debito</t>
+        </is>
+      </c>
+      <c r="AB5" s="42" t="inlineStr">
+        <is>
+          <t>Debiti maturati</t>
+        </is>
+      </c>
+      <c r="AC5" s="42" t="inlineStr">
+        <is>
+          <t>Debiti saldati</t>
+        </is>
+      </c>
+      <c r="AD5" s="42" t="inlineStr">
+        <is>
+          <t>Riga del debito</t>
+        </is>
+      </c>
+      <c r="AE5" s="42" t="inlineStr">
+        <is>
+          <t>Settimana del debito</t>
+        </is>
+      </c>
+      <c r="AG5" s="31" t="inlineStr">
         <is>
           <t>Inizio servizio</t>
         </is>
@@ -7710,7 +7758,7 @@
         <v/>
       </c>
       <c r="F6">
-        <f>IF($E6=0,0,IF(OR($D6="Licenza - settimana intera",$D6="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M6=1,0,IF($E6=0,0,IF(OR($D6="Licenza - settimana intera",$D6="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G6">
@@ -7739,23 +7787,23 @@
         <v/>
       </c>
       <c r="N6">
-        <f>IF($G6=0,100000,IF(Partecipanti!$B$5=$C6,100000,0*100+MOD(1-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G6=0,100000,IF(Partecipanti!$B$5=$C6,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$5))&gt;0,100000,0*100+MOD(1-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O6">
-        <f>IF($H6=0,100000,IF(Partecipanti!$B$6=$C6,100000,0*100+MOD(2-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H6=0,100000,IF(Partecipanti!$B$6=$C6,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$6))&gt;0,100000,0*100+MOD(2-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P6">
-        <f>IF($I6=0,100000,IF(Partecipanti!$B$7=$C6,100000,0*100+MOD(3-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I6=0,100000,IF(Partecipanti!$B$7=$C6,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$7))&gt;0,100000,0*100+MOD(3-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q6">
-        <f>IF($J6=0,100000,IF(Partecipanti!$B$8=$C6,100000,0*100+MOD(4-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J6=0,100000,IF(Partecipanti!$B$8=$C6,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$8))&gt;0,100000,0*100+MOD(4-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R6">
-        <f>IF($K6=0,100000,IF(Partecipanti!$B$9=$C6,100000,0*100+MOD(5-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K6=0,100000,IF(Partecipanti!$B$9=$C6,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$9))&gt;0,100000,0*100+MOD(5-MATCH($C6,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S6">
@@ -7779,20 +7827,33 @@
         <v/>
       </c>
       <c r="X6">
-        <f>IF($M6=1,$L6&amp;" recupera il turno saltato nella settimana "&amp;($A6-1)&amp;"; "&amp;$C6&amp;" a riposo compensativo",IF($E6=1,$C6&amp;" assente ("&amp;$D6&amp;")"&amp;IF($S6="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S6&amp;" con doppio turno")&amp;IF($F6=1,"; turno da recuperare nella settimana "&amp;($A6+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M6=1,IF($E6=1,$L6&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE6&amp;"; "&amp;$C6&amp;" assente ("&amp;$D6&amp;")",$L6&amp;" recupera il turno saltato nella settimana "&amp;$AE6&amp;"; "&amp;$C6&amp;" a riposo compensativo"),IF($E6=1,$C6&amp;" assente ("&amp;$D6&amp;")"&amp;IF($S6="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S6&amp;" con doppio turno")&amp;IF($F6=1,"; turno da recuperare a partire dalla settimana "&amp;($A6+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y6">
-        <f>IF($M6=1,"recupera il turno saltato nella settimana "&amp;($A6-1)&amp;", "&amp;$C6&amp;" a riposo",IF($E6=1,IF($S6="DA ASSEGNARE","turno da assegnare: "&amp;$C6&amp;" assente","in sostituzione di "&amp;$C6&amp;", doppio turno"),""))</f>
-        <v/>
-      </c>
-      <c r="AB6" s="43" t="n">
+        <f>IF($M6=1,IF($E6=1,"recupero del turno saltato nella settimana "&amp;$AE6&amp;", "&amp;$C6&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE6&amp;", "&amp;$C6&amp;" a riposo"),IF($E6=1,IF($S6="DA ASSEGNARE","turno da assegnare: "&amp;$C6&amp;" assente","in sostituzione di "&amp;$C6&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>IF($T6="","",COUNTIF($T$6:$T6,$T6))</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>IF($T6="","",$T6&amp;"#"&amp;$Z6)</f>
+        <v/>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AG6" s="43" t="n">
         <v>46293</v>
-      </c>
-      <c r="AC6" s="12" t="inlineStr">
-        <is>
-          <t>numero settimane</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -7815,7 +7876,7 @@
         <v/>
       </c>
       <c r="F7">
-        <f>IF($E7=0,0,IF(OR($D7="Licenza - settimana intera",$D7="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M7=1,0,IF($E7=0,0,IF(OR($D7="Licenza - settimana intera",$D7="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G7">
@@ -7844,23 +7905,23 @@
         <v/>
       </c>
       <c r="N7">
-        <f>IF($G7=0,100000,IF(Partecipanti!$B$5=$C7,100000,COUNTIF($S$6:$S6,Partecipanti!$B$5)*100+MOD(1-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G7=0,100000,IF(Partecipanti!$B$5=$C7,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S6,Partecipanti!$B$5)*100+MOD(1-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O7">
-        <f>IF($H7=0,100000,IF(Partecipanti!$B$6=$C7,100000,COUNTIF($S$6:$S6,Partecipanti!$B$6)*100+MOD(2-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H7=0,100000,IF(Partecipanti!$B$6=$C7,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S6,Partecipanti!$B$6)*100+MOD(2-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P7">
-        <f>IF($I7=0,100000,IF(Partecipanti!$B$7=$C7,100000,COUNTIF($S$6:$S6,Partecipanti!$B$7)*100+MOD(3-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I7=0,100000,IF(Partecipanti!$B$7=$C7,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S6,Partecipanti!$B$7)*100+MOD(3-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q7">
-        <f>IF($J7=0,100000,IF(Partecipanti!$B$8=$C7,100000,COUNTIF($S$6:$S6,Partecipanti!$B$8)*100+MOD(4-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J7=0,100000,IF(Partecipanti!$B$8=$C7,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S6,Partecipanti!$B$8)*100+MOD(4-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R7">
-        <f>IF($K7=0,100000,IF(Partecipanti!$B$9=$C7,100000,COUNTIF($S$6:$S6,Partecipanti!$B$9)*100+MOD(5-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K7=0,100000,IF(Partecipanti!$B$9=$C7,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S6,Partecipanti!$B$9)*100+MOD(5-MATCH($C7,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S7">
@@ -7884,15 +7945,38 @@
         <v/>
       </c>
       <c r="X7">
-        <f>IF($M7=1,$L7&amp;" recupera il turno saltato nella settimana "&amp;($A7-1)&amp;"; "&amp;$C7&amp;" a riposo compensativo",IF($E7=1,$C7&amp;" assente ("&amp;$D7&amp;")"&amp;IF($S7="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S7&amp;" con doppio turno")&amp;IF($F7=1,"; turno da recuperare nella settimana "&amp;($A7+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M7=1,IF($E7=1,$L7&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE7&amp;"; "&amp;$C7&amp;" assente ("&amp;$D7&amp;")",$L7&amp;" recupera il turno saltato nella settimana "&amp;$AE7&amp;"; "&amp;$C7&amp;" a riposo compensativo"),IF($E7=1,$C7&amp;" assente ("&amp;$D7&amp;")"&amp;IF($S7="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S7&amp;" con doppio turno")&amp;IF($F7=1,"; turno da recuperare a partire dalla settimana "&amp;($A7+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>IF($M7=1,"recupera il turno saltato nella settimana "&amp;($A7-1)&amp;", "&amp;$C7&amp;" a riposo",IF($E7=1,IF($S7="DA ASSEGNARE","turno da assegnare: "&amp;$C7&amp;" assente","in sostituzione di "&amp;$C7&amp;", doppio turno"),""))</f>
+        <f>IF($M7=1,IF($E7=1,"recupero del turno saltato nella settimana "&amp;$AE7&amp;", "&amp;$C7&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE7&amp;", "&amp;$C7&amp;" a riposo"),IF($E7=1,IF($S7="DA ASSEGNARE","turno da assegnare: "&amp;$C7&amp;" assente","in sostituzione di "&amp;$C7&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>IF($T7="","",COUNTIF($T$6:$T7,$T7))</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>IF($T7="","",$T7&amp;"#"&amp;$Z7)</f>
         <v/>
       </c>
       <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AG7" t="n">
         <v>13</v>
+      </c>
+      <c r="AH7" s="12" t="inlineStr">
+        <is>
+          <t>numero settimane</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -7915,7 +7999,7 @@
         <v/>
       </c>
       <c r="F8">
-        <f>IF($E8=0,0,IF(OR($D8="Licenza - settimana intera",$D8="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M8=1,0,IF($E8=0,0,IF(OR($D8="Licenza - settimana intera",$D8="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G8">
@@ -7944,23 +8028,23 @@
         <v/>
       </c>
       <c r="N8">
-        <f>IF($G8=0,100000,IF(Partecipanti!$B$5=$C8,100000,COUNTIF($S$6:$S7,Partecipanti!$B$5)*100+MOD(1-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G8=0,100000,IF(Partecipanti!$B$5=$C8,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S7,Partecipanti!$B$5)*100+MOD(1-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O8">
-        <f>IF($H8=0,100000,IF(Partecipanti!$B$6=$C8,100000,COUNTIF($S$6:$S7,Partecipanti!$B$6)*100+MOD(2-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H8=0,100000,IF(Partecipanti!$B$6=$C8,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S7,Partecipanti!$B$6)*100+MOD(2-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P8">
-        <f>IF($I8=0,100000,IF(Partecipanti!$B$7=$C8,100000,COUNTIF($S$6:$S7,Partecipanti!$B$7)*100+MOD(3-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I8=0,100000,IF(Partecipanti!$B$7=$C8,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S7,Partecipanti!$B$7)*100+MOD(3-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q8">
-        <f>IF($J8=0,100000,IF(Partecipanti!$B$8=$C8,100000,COUNTIF($S$6:$S7,Partecipanti!$B$8)*100+MOD(4-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J8=0,100000,IF(Partecipanti!$B$8=$C8,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S7,Partecipanti!$B$8)*100+MOD(4-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R8">
-        <f>IF($K8=0,100000,IF(Partecipanti!$B$9=$C8,100000,COUNTIF($S$6:$S7,Partecipanti!$B$9)*100+MOD(5-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K8=0,100000,IF(Partecipanti!$B$9=$C8,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S7,Partecipanti!$B$9)*100+MOD(5-MATCH($C8,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S8">
@@ -7984,13 +8068,31 @@
         <v/>
       </c>
       <c r="X8">
-        <f>IF($M8=1,$L8&amp;" recupera il turno saltato nella settimana "&amp;($A8-1)&amp;"; "&amp;$C8&amp;" a riposo compensativo",IF($E8=1,$C8&amp;" assente ("&amp;$D8&amp;")"&amp;IF($S8="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S8&amp;" con doppio turno")&amp;IF($F8=1,"; turno da recuperare nella settimana "&amp;($A8+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M8=1,IF($E8=1,$L8&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE8&amp;"; "&amp;$C8&amp;" assente ("&amp;$D8&amp;")",$L8&amp;" recupera il turno saltato nella settimana "&amp;$AE8&amp;"; "&amp;$C8&amp;" a riposo compensativo"),IF($E8=1,$C8&amp;" assente ("&amp;$D8&amp;")"&amp;IF($S8="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S8&amp;" con doppio turno")&amp;IF($F8=1,"; turno da recuperare a partire dalla settimana "&amp;($A8+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y8">
-        <f>IF($M8=1,"recupera il turno saltato nella settimana "&amp;($A8-1)&amp;", "&amp;$C8&amp;" a riposo",IF($E8=1,IF($S8="DA ASSEGNARE","turno da assegnare: "&amp;$C8&amp;" assente","in sostituzione di "&amp;$C8&amp;", doppio turno"),""))</f>
-        <v/>
-      </c>
+        <f>IF($M8=1,IF($E8=1,"recupero del turno saltato nella settimana "&amp;$AE8&amp;", "&amp;$C8&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE8&amp;", "&amp;$C8&amp;" a riposo"),IF($E8=1,IF($S8="DA ASSEGNARE","turno da assegnare: "&amp;$C8&amp;" assente","in sostituzione di "&amp;$C8&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>IF($T8="","",COUNTIF($T$6:$T8,$T8))</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>IF($T8="","",$T8&amp;"#"&amp;$Z8)</f>
+        <v/>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8012,7 +8114,7 @@
         <v/>
       </c>
       <c r="F9">
-        <f>IF($E9=0,0,IF(OR($D9="Licenza - settimana intera",$D9="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M9=1,0,IF($E9=0,0,IF(OR($D9="Licenza - settimana intera",$D9="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G9">
@@ -8041,23 +8143,23 @@
         <v/>
       </c>
       <c r="N9">
-        <f>IF($G9=0,100000,IF(Partecipanti!$B$5=$C9,100000,COUNTIF($S$6:$S8,Partecipanti!$B$5)*100+MOD(1-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G9=0,100000,IF(Partecipanti!$B$5=$C9,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S8,Partecipanti!$B$5)*100+MOD(1-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O9">
-        <f>IF($H9=0,100000,IF(Partecipanti!$B$6=$C9,100000,COUNTIF($S$6:$S8,Partecipanti!$B$6)*100+MOD(2-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H9=0,100000,IF(Partecipanti!$B$6=$C9,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S8,Partecipanti!$B$6)*100+MOD(2-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P9">
-        <f>IF($I9=0,100000,IF(Partecipanti!$B$7=$C9,100000,COUNTIF($S$6:$S8,Partecipanti!$B$7)*100+MOD(3-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I9=0,100000,IF(Partecipanti!$B$7=$C9,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S8,Partecipanti!$B$7)*100+MOD(3-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q9">
-        <f>IF($J9=0,100000,IF(Partecipanti!$B$8=$C9,100000,COUNTIF($S$6:$S8,Partecipanti!$B$8)*100+MOD(4-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J9=0,100000,IF(Partecipanti!$B$8=$C9,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S8,Partecipanti!$B$8)*100+MOD(4-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R9">
-        <f>IF($K9=0,100000,IF(Partecipanti!$B$9=$C9,100000,COUNTIF($S$6:$S8,Partecipanti!$B$9)*100+MOD(5-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K9=0,100000,IF(Partecipanti!$B$9=$C9,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S8,Partecipanti!$B$9)*100+MOD(5-MATCH($C9,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S9">
@@ -8081,13 +8183,31 @@
         <v/>
       </c>
       <c r="X9">
-        <f>IF($M9=1,$L9&amp;" recupera il turno saltato nella settimana "&amp;($A9-1)&amp;"; "&amp;$C9&amp;" a riposo compensativo",IF($E9=1,$C9&amp;" assente ("&amp;$D9&amp;")"&amp;IF($S9="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S9&amp;" con doppio turno")&amp;IF($F9=1,"; turno da recuperare nella settimana "&amp;($A9+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M9=1,IF($E9=1,$L9&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE9&amp;"; "&amp;$C9&amp;" assente ("&amp;$D9&amp;")",$L9&amp;" recupera il turno saltato nella settimana "&amp;$AE9&amp;"; "&amp;$C9&amp;" a riposo compensativo"),IF($E9=1,$C9&amp;" assente ("&amp;$D9&amp;")"&amp;IF($S9="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S9&amp;" con doppio turno")&amp;IF($F9=1,"; turno da recuperare a partire dalla settimana "&amp;($A9+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>IF($M9=1,"recupera il turno saltato nella settimana "&amp;($A9-1)&amp;", "&amp;$C9&amp;" a riposo",IF($E9=1,IF($S9="DA ASSEGNARE","turno da assegnare: "&amp;$C9&amp;" assente","in sostituzione di "&amp;$C9&amp;", doppio turno"),""))</f>
-        <v/>
-      </c>
+        <f>IF($M9=1,IF($E9=1,"recupero del turno saltato nella settimana "&amp;$AE9&amp;", "&amp;$C9&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE9&amp;", "&amp;$C9&amp;" a riposo"),IF($E9=1,IF($S9="DA ASSEGNARE","turno da assegnare: "&amp;$C9&amp;" assente","in sostituzione di "&amp;$C9&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>IF($T9="","",COUNTIF($T$6:$T9,$T9))</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>IF($T9="","",$T9&amp;"#"&amp;$Z9)</f>
+        <v/>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8109,7 +8229,7 @@
         <v/>
       </c>
       <c r="F10">
-        <f>IF($E10=0,0,IF(OR($D10="Licenza - settimana intera",$D10="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M10=1,0,IF($E10=0,0,IF(OR($D10="Licenza - settimana intera",$D10="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G10">
@@ -8138,23 +8258,23 @@
         <v/>
       </c>
       <c r="N10">
-        <f>IF($G10=0,100000,IF(Partecipanti!$B$5=$C10,100000,COUNTIF($S$6:$S9,Partecipanti!$B$5)*100+MOD(1-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G10=0,100000,IF(Partecipanti!$B$5=$C10,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S9,Partecipanti!$B$5)*100+MOD(1-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O10">
-        <f>IF($H10=0,100000,IF(Partecipanti!$B$6=$C10,100000,COUNTIF($S$6:$S9,Partecipanti!$B$6)*100+MOD(2-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H10=0,100000,IF(Partecipanti!$B$6=$C10,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S9,Partecipanti!$B$6)*100+MOD(2-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P10">
-        <f>IF($I10=0,100000,IF(Partecipanti!$B$7=$C10,100000,COUNTIF($S$6:$S9,Partecipanti!$B$7)*100+MOD(3-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I10=0,100000,IF(Partecipanti!$B$7=$C10,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S9,Partecipanti!$B$7)*100+MOD(3-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q10">
-        <f>IF($J10=0,100000,IF(Partecipanti!$B$8=$C10,100000,COUNTIF($S$6:$S9,Partecipanti!$B$8)*100+MOD(4-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J10=0,100000,IF(Partecipanti!$B$8=$C10,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S9,Partecipanti!$B$8)*100+MOD(4-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R10">
-        <f>IF($K10=0,100000,IF(Partecipanti!$B$9=$C10,100000,COUNTIF($S$6:$S9,Partecipanti!$B$9)*100+MOD(5-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K10=0,100000,IF(Partecipanti!$B$9=$C10,100000,IF(SUMPRODUCT(($M$6:$M$10=1)*($L$6:$L$10=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S9,Partecipanti!$B$9)*100+MOD(5-MATCH($C10,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S10">
@@ -8178,13 +8298,31 @@
         <v/>
       </c>
       <c r="X10">
-        <f>IF($M10=1,$L10&amp;" recupera il turno saltato nella settimana "&amp;($A10-1)&amp;"; "&amp;$C10&amp;" a riposo compensativo",IF($E10=1,$C10&amp;" assente ("&amp;$D10&amp;")"&amp;IF($S10="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S10&amp;" con doppio turno")&amp;IF($F10=1,"; turno da recuperare nella settimana "&amp;($A10+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M10=1,IF($E10=1,$L10&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE10&amp;"; "&amp;$C10&amp;" assente ("&amp;$D10&amp;")",$L10&amp;" recupera il turno saltato nella settimana "&amp;$AE10&amp;"; "&amp;$C10&amp;" a riposo compensativo"),IF($E10=1,$C10&amp;" assente ("&amp;$D10&amp;")"&amp;IF($S10="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S10&amp;" con doppio turno")&amp;IF($F10=1,"; turno da recuperare a partire dalla settimana "&amp;($A10+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>IF($M10=1,"recupera il turno saltato nella settimana "&amp;($A10-1)&amp;", "&amp;$C10&amp;" a riposo",IF($E10=1,IF($S10="DA ASSEGNARE","turno da assegnare: "&amp;$C10&amp;" assente","in sostituzione di "&amp;$C10&amp;", doppio turno"),""))</f>
-        <v/>
-      </c>
+        <f>IF($M10=1,IF($E10=1,"recupero del turno saltato nella settimana "&amp;$AE10&amp;", "&amp;$C10&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE10&amp;", "&amp;$C10&amp;" a riposo"),IF($E10=1,IF($S10="DA ASSEGNARE","turno da assegnare: "&amp;$C10&amp;" assente","in sostituzione di "&amp;$C10&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z10">
+        <f>IF($T10="","",COUNTIF($T$6:$T10,$T10))</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>IF($T10="","",$T10&amp;"#"&amp;$Z10)</f>
+        <v/>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8206,7 +8344,7 @@
         <v/>
       </c>
       <c r="F11">
-        <f>IF($E11=0,0,IF(OR($D11="Licenza - settimana intera",$D11="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M11=1,0,IF($E11=0,0,IF(OR($D11="Licenza - settimana intera",$D11="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G11">
@@ -8230,7 +8368,7 @@
         <v/>
       </c>
       <c r="L11">
-        <f>IFERROR(INDEX($C6:$C10,MATCH(1,INDEX(($T6:$T10=$C11)*1,0),0)),"")</f>
+        <f>IF($AD11=0,"",INDEX($C$6:$C10,$AD11))</f>
         <v/>
       </c>
       <c r="M11">
@@ -8238,23 +8376,23 @@
         <v/>
       </c>
       <c r="N11">
-        <f>IF($G11=0,100000,IF(Partecipanti!$B$5=$C11,100000,COUNTIF($S$6:$S10,Partecipanti!$B$5)*100+MOD(1-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G11=0,100000,IF(Partecipanti!$B$5=$C11,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S10,Partecipanti!$B$5)*100+MOD(1-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O11">
-        <f>IF($H11=0,100000,IF(Partecipanti!$B$6=$C11,100000,COUNTIF($S$6:$S10,Partecipanti!$B$6)*100+MOD(2-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H11=0,100000,IF(Partecipanti!$B$6=$C11,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S10,Partecipanti!$B$6)*100+MOD(2-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P11">
-        <f>IF($I11=0,100000,IF(Partecipanti!$B$7=$C11,100000,COUNTIF($S$6:$S10,Partecipanti!$B$7)*100+MOD(3-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I11=0,100000,IF(Partecipanti!$B$7=$C11,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S10,Partecipanti!$B$7)*100+MOD(3-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q11">
-        <f>IF($J11=0,100000,IF(Partecipanti!$B$8=$C11,100000,COUNTIF($S$6:$S10,Partecipanti!$B$8)*100+MOD(4-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J11=0,100000,IF(Partecipanti!$B$8=$C11,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S10,Partecipanti!$B$8)*100+MOD(4-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R11">
-        <f>IF($K11=0,100000,IF(Partecipanti!$B$9=$C11,100000,COUNTIF($S$6:$S10,Partecipanti!$B$9)*100+MOD(5-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K11=0,100000,IF(Partecipanti!$B$9=$C11,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S10,Partecipanti!$B$9)*100+MOD(5-MATCH($C11,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S11">
@@ -8278,11 +8416,35 @@
         <v/>
       </c>
       <c r="X11">
-        <f>IF($M11=1,$L11&amp;" recupera il turno saltato nella settimana "&amp;($A11-1)&amp;"; "&amp;$C11&amp;" a riposo compensativo",IF($E11=1,$C11&amp;" assente ("&amp;$D11&amp;")"&amp;IF($S11="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S11&amp;" con doppio turno")&amp;IF($F11=1,"; turno da recuperare nella settimana "&amp;($A11+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M11=1,IF($E11=1,$L11&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE11&amp;"; "&amp;$C11&amp;" assente ("&amp;$D11&amp;")",$L11&amp;" recupera il turno saltato nella settimana "&amp;$AE11&amp;"; "&amp;$C11&amp;" a riposo compensativo"),IF($E11=1,$C11&amp;" assente ("&amp;$D11&amp;")"&amp;IF($S11="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S11&amp;" con doppio turno")&amp;IF($F11=1,"; turno da recuperare a partire dalla settimana "&amp;($A11+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>IF($M11=1,"recupera il turno saltato nella settimana "&amp;($A11-1)&amp;", "&amp;$C11&amp;" a riposo",IF($E11=1,IF($S11="DA ASSEGNARE","turno da assegnare: "&amp;$C11&amp;" assente","in sostituzione di "&amp;$C11&amp;", doppio turno"),""))</f>
+        <f>IF($M11=1,IF($E11=1,"recupero del turno saltato nella settimana "&amp;$AE11&amp;", "&amp;$C11&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE11&amp;", "&amp;$C11&amp;" a riposo"),IF($E11=1,IF($S11="DA ASSEGNARE","turno da assegnare: "&amp;$C11&amp;" assente","in sostituzione di "&amp;$C11&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z11">
+        <f>IF($T11="","",COUNTIF($T$6:$T11,$T11))</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>IF($T11="","",$T11&amp;"#"&amp;$Z11)</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>COUNTIF($T$6:$T10,$C11)</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>COUNTIFS($C$6:$C10,$C11,$M$6:$M10,1)</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>IF($AB11&gt;$AC11,IFERROR(MATCH($C11&amp;"#"&amp;($AC11+1),$AA$6:$AA10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>IF($AD11=0,"",INDEX($A$6:$A10,$AD11))</f>
         <v/>
       </c>
     </row>
@@ -8306,7 +8468,7 @@
         <v/>
       </c>
       <c r="F12">
-        <f>IF($E12=0,0,IF(OR($D12="Licenza - settimana intera",$D12="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M12=1,0,IF($E12=0,0,IF(OR($D12="Licenza - settimana intera",$D12="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G12">
@@ -8330,7 +8492,7 @@
         <v/>
       </c>
       <c r="L12">
-        <f>IFERROR(INDEX($C6:$C10,MATCH(1,INDEX(($T6:$T10=$C12)*1,0),0)),"")</f>
+        <f>IF($AD12=0,"",INDEX($C$6:$C10,$AD12))</f>
         <v/>
       </c>
       <c r="M12">
@@ -8338,23 +8500,23 @@
         <v/>
       </c>
       <c r="N12">
-        <f>IF($G12=0,100000,IF(Partecipanti!$B$5=$C12,100000,COUNTIF($S$6:$S11,Partecipanti!$B$5)*100+MOD(1-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G12=0,100000,IF(Partecipanti!$B$5=$C12,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S11,Partecipanti!$B$5)*100+MOD(1-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O12">
-        <f>IF($H12=0,100000,IF(Partecipanti!$B$6=$C12,100000,COUNTIF($S$6:$S11,Partecipanti!$B$6)*100+MOD(2-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H12=0,100000,IF(Partecipanti!$B$6=$C12,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S11,Partecipanti!$B$6)*100+MOD(2-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P12">
-        <f>IF($I12=0,100000,IF(Partecipanti!$B$7=$C12,100000,COUNTIF($S$6:$S11,Partecipanti!$B$7)*100+MOD(3-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I12=0,100000,IF(Partecipanti!$B$7=$C12,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S11,Partecipanti!$B$7)*100+MOD(3-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q12">
-        <f>IF($J12=0,100000,IF(Partecipanti!$B$8=$C12,100000,COUNTIF($S$6:$S11,Partecipanti!$B$8)*100+MOD(4-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J12=0,100000,IF(Partecipanti!$B$8=$C12,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S11,Partecipanti!$B$8)*100+MOD(4-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R12">
-        <f>IF($K12=0,100000,IF(Partecipanti!$B$9=$C12,100000,COUNTIF($S$6:$S11,Partecipanti!$B$9)*100+MOD(5-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K12=0,100000,IF(Partecipanti!$B$9=$C12,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S11,Partecipanti!$B$9)*100+MOD(5-MATCH($C12,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S12">
@@ -8378,11 +8540,35 @@
         <v/>
       </c>
       <c r="X12">
-        <f>IF($M12=1,$L12&amp;" recupera il turno saltato nella settimana "&amp;($A12-1)&amp;"; "&amp;$C12&amp;" a riposo compensativo",IF($E12=1,$C12&amp;" assente ("&amp;$D12&amp;")"&amp;IF($S12="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S12&amp;" con doppio turno")&amp;IF($F12=1,"; turno da recuperare nella settimana "&amp;($A12+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M12=1,IF($E12=1,$L12&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE12&amp;"; "&amp;$C12&amp;" assente ("&amp;$D12&amp;")",$L12&amp;" recupera il turno saltato nella settimana "&amp;$AE12&amp;"; "&amp;$C12&amp;" a riposo compensativo"),IF($E12=1,$C12&amp;" assente ("&amp;$D12&amp;")"&amp;IF($S12="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S12&amp;" con doppio turno")&amp;IF($F12=1,"; turno da recuperare a partire dalla settimana "&amp;($A12+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>IF($M12=1,"recupera il turno saltato nella settimana "&amp;($A12-1)&amp;", "&amp;$C12&amp;" a riposo",IF($E12=1,IF($S12="DA ASSEGNARE","turno da assegnare: "&amp;$C12&amp;" assente","in sostituzione di "&amp;$C12&amp;", doppio turno"),""))</f>
+        <f>IF($M12=1,IF($E12=1,"recupero del turno saltato nella settimana "&amp;$AE12&amp;", "&amp;$C12&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE12&amp;", "&amp;$C12&amp;" a riposo"),IF($E12=1,IF($S12="DA ASSEGNARE","turno da assegnare: "&amp;$C12&amp;" assente","in sostituzione di "&amp;$C12&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>IF($T12="","",COUNTIF($T$6:$T12,$T12))</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>IF($T12="","",$T12&amp;"#"&amp;$Z12)</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>COUNTIF($T$6:$T10,$C12)</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>COUNTIFS($C$6:$C10,$C12,$M$6:$M10,1)</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>IF($AB12&gt;$AC12,IFERROR(MATCH($C12&amp;"#"&amp;($AC12+1),$AA$6:$AA10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>IF($AD12=0,"",INDEX($A$6:$A10,$AD12))</f>
         <v/>
       </c>
     </row>
@@ -8406,7 +8592,7 @@
         <v/>
       </c>
       <c r="F13">
-        <f>IF($E13=0,0,IF(OR($D13="Licenza - settimana intera",$D13="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M13=1,0,IF($E13=0,0,IF(OR($D13="Licenza - settimana intera",$D13="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G13">
@@ -8430,7 +8616,7 @@
         <v/>
       </c>
       <c r="L13">
-        <f>IFERROR(INDEX($C6:$C10,MATCH(1,INDEX(($T6:$T10=$C13)*1,0),0)),"")</f>
+        <f>IF($AD13=0,"",INDEX($C$6:$C10,$AD13))</f>
         <v/>
       </c>
       <c r="M13">
@@ -8438,23 +8624,23 @@
         <v/>
       </c>
       <c r="N13">
-        <f>IF($G13=0,100000,IF(Partecipanti!$B$5=$C13,100000,COUNTIF($S$6:$S12,Partecipanti!$B$5)*100+MOD(1-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G13=0,100000,IF(Partecipanti!$B$5=$C13,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S12,Partecipanti!$B$5)*100+MOD(1-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O13">
-        <f>IF($H13=0,100000,IF(Partecipanti!$B$6=$C13,100000,COUNTIF($S$6:$S12,Partecipanti!$B$6)*100+MOD(2-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H13=0,100000,IF(Partecipanti!$B$6=$C13,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S12,Partecipanti!$B$6)*100+MOD(2-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P13">
-        <f>IF($I13=0,100000,IF(Partecipanti!$B$7=$C13,100000,COUNTIF($S$6:$S12,Partecipanti!$B$7)*100+MOD(3-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I13=0,100000,IF(Partecipanti!$B$7=$C13,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S12,Partecipanti!$B$7)*100+MOD(3-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q13">
-        <f>IF($J13=0,100000,IF(Partecipanti!$B$8=$C13,100000,COUNTIF($S$6:$S12,Partecipanti!$B$8)*100+MOD(4-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J13=0,100000,IF(Partecipanti!$B$8=$C13,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S12,Partecipanti!$B$8)*100+MOD(4-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R13">
-        <f>IF($K13=0,100000,IF(Partecipanti!$B$9=$C13,100000,COUNTIF($S$6:$S12,Partecipanti!$B$9)*100+MOD(5-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K13=0,100000,IF(Partecipanti!$B$9=$C13,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S12,Partecipanti!$B$9)*100+MOD(5-MATCH($C13,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S13">
@@ -8478,11 +8664,35 @@
         <v/>
       </c>
       <c r="X13">
-        <f>IF($M13=1,$L13&amp;" recupera il turno saltato nella settimana "&amp;($A13-1)&amp;"; "&amp;$C13&amp;" a riposo compensativo",IF($E13=1,$C13&amp;" assente ("&amp;$D13&amp;")"&amp;IF($S13="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S13&amp;" con doppio turno")&amp;IF($F13=1,"; turno da recuperare nella settimana "&amp;($A13+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M13=1,IF($E13=1,$L13&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE13&amp;"; "&amp;$C13&amp;" assente ("&amp;$D13&amp;")",$L13&amp;" recupera il turno saltato nella settimana "&amp;$AE13&amp;"; "&amp;$C13&amp;" a riposo compensativo"),IF($E13=1,$C13&amp;" assente ("&amp;$D13&amp;")"&amp;IF($S13="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S13&amp;" con doppio turno")&amp;IF($F13=1,"; turno da recuperare a partire dalla settimana "&amp;($A13+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>IF($M13=1,"recupera il turno saltato nella settimana "&amp;($A13-1)&amp;", "&amp;$C13&amp;" a riposo",IF($E13=1,IF($S13="DA ASSEGNARE","turno da assegnare: "&amp;$C13&amp;" assente","in sostituzione di "&amp;$C13&amp;", doppio turno"),""))</f>
+        <f>IF($M13=1,IF($E13=1,"recupero del turno saltato nella settimana "&amp;$AE13&amp;", "&amp;$C13&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE13&amp;", "&amp;$C13&amp;" a riposo"),IF($E13=1,IF($S13="DA ASSEGNARE","turno da assegnare: "&amp;$C13&amp;" assente","in sostituzione di "&amp;$C13&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>IF($T13="","",COUNTIF($T$6:$T13,$T13))</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>IF($T13="","",$T13&amp;"#"&amp;$Z13)</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>COUNTIF($T$6:$T10,$C13)</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>COUNTIFS($C$6:$C10,$C13,$M$6:$M10,1)</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>IF($AB13&gt;$AC13,IFERROR(MATCH($C13&amp;"#"&amp;($AC13+1),$AA$6:$AA10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>IF($AD13=0,"",INDEX($A$6:$A10,$AD13))</f>
         <v/>
       </c>
     </row>
@@ -8506,7 +8716,7 @@
         <v/>
       </c>
       <c r="F14">
-        <f>IF($E14=0,0,IF(OR($D14="Licenza - settimana intera",$D14="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M14=1,0,IF($E14=0,0,IF(OR($D14="Licenza - settimana intera",$D14="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G14">
@@ -8530,7 +8740,7 @@
         <v/>
       </c>
       <c r="L14">
-        <f>IFERROR(INDEX($C6:$C10,MATCH(1,INDEX(($T6:$T10=$C14)*1,0),0)),"")</f>
+        <f>IF($AD14=0,"",INDEX($C$6:$C10,$AD14))</f>
         <v/>
       </c>
       <c r="M14">
@@ -8538,23 +8748,23 @@
         <v/>
       </c>
       <c r="N14">
-        <f>IF($G14=0,100000,IF(Partecipanti!$B$5=$C14,100000,COUNTIF($S$6:$S13,Partecipanti!$B$5)*100+MOD(1-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G14=0,100000,IF(Partecipanti!$B$5=$C14,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S13,Partecipanti!$B$5)*100+MOD(1-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O14">
-        <f>IF($H14=0,100000,IF(Partecipanti!$B$6=$C14,100000,COUNTIF($S$6:$S13,Partecipanti!$B$6)*100+MOD(2-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H14=0,100000,IF(Partecipanti!$B$6=$C14,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S13,Partecipanti!$B$6)*100+MOD(2-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P14">
-        <f>IF($I14=0,100000,IF(Partecipanti!$B$7=$C14,100000,COUNTIF($S$6:$S13,Partecipanti!$B$7)*100+MOD(3-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I14=0,100000,IF(Partecipanti!$B$7=$C14,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S13,Partecipanti!$B$7)*100+MOD(3-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q14">
-        <f>IF($J14=0,100000,IF(Partecipanti!$B$8=$C14,100000,COUNTIF($S$6:$S13,Partecipanti!$B$8)*100+MOD(4-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J14=0,100000,IF(Partecipanti!$B$8=$C14,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S13,Partecipanti!$B$8)*100+MOD(4-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R14">
-        <f>IF($K14=0,100000,IF(Partecipanti!$B$9=$C14,100000,COUNTIF($S$6:$S13,Partecipanti!$B$9)*100+MOD(5-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K14=0,100000,IF(Partecipanti!$B$9=$C14,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S13,Partecipanti!$B$9)*100+MOD(5-MATCH($C14,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S14">
@@ -8578,11 +8788,35 @@
         <v/>
       </c>
       <c r="X14">
-        <f>IF($M14=1,$L14&amp;" recupera il turno saltato nella settimana "&amp;($A14-1)&amp;"; "&amp;$C14&amp;" a riposo compensativo",IF($E14=1,$C14&amp;" assente ("&amp;$D14&amp;")"&amp;IF($S14="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S14&amp;" con doppio turno")&amp;IF($F14=1,"; turno da recuperare nella settimana "&amp;($A14+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M14=1,IF($E14=1,$L14&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE14&amp;"; "&amp;$C14&amp;" assente ("&amp;$D14&amp;")",$L14&amp;" recupera il turno saltato nella settimana "&amp;$AE14&amp;"; "&amp;$C14&amp;" a riposo compensativo"),IF($E14=1,$C14&amp;" assente ("&amp;$D14&amp;")"&amp;IF($S14="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S14&amp;" con doppio turno")&amp;IF($F14=1,"; turno da recuperare a partire dalla settimana "&amp;($A14+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>IF($M14=1,"recupera il turno saltato nella settimana "&amp;($A14-1)&amp;", "&amp;$C14&amp;" a riposo",IF($E14=1,IF($S14="DA ASSEGNARE","turno da assegnare: "&amp;$C14&amp;" assente","in sostituzione di "&amp;$C14&amp;", doppio turno"),""))</f>
+        <f>IF($M14=1,IF($E14=1,"recupero del turno saltato nella settimana "&amp;$AE14&amp;", "&amp;$C14&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE14&amp;", "&amp;$C14&amp;" a riposo"),IF($E14=1,IF($S14="DA ASSEGNARE","turno da assegnare: "&amp;$C14&amp;" assente","in sostituzione di "&amp;$C14&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>IF($T14="","",COUNTIF($T$6:$T14,$T14))</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>IF($T14="","",$T14&amp;"#"&amp;$Z14)</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>COUNTIF($T$6:$T10,$C14)</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>COUNTIFS($C$6:$C10,$C14,$M$6:$M10,1)</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>IF($AB14&gt;$AC14,IFERROR(MATCH($C14&amp;"#"&amp;($AC14+1),$AA$6:$AA10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>IF($AD14=0,"",INDEX($A$6:$A10,$AD14))</f>
         <v/>
       </c>
     </row>
@@ -8606,7 +8840,7 @@
         <v/>
       </c>
       <c r="F15">
-        <f>IF($E15=0,0,IF(OR($D15="Licenza - settimana intera",$D15="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M15=1,0,IF($E15=0,0,IF(OR($D15="Licenza - settimana intera",$D15="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G15">
@@ -8630,7 +8864,7 @@
         <v/>
       </c>
       <c r="L15">
-        <f>IFERROR(INDEX($C6:$C10,MATCH(1,INDEX(($T6:$T10=$C15)*1,0),0)),"")</f>
+        <f>IF($AD15=0,"",INDEX($C$6:$C10,$AD15))</f>
         <v/>
       </c>
       <c r="M15">
@@ -8638,23 +8872,23 @@
         <v/>
       </c>
       <c r="N15">
-        <f>IF($G15=0,100000,IF(Partecipanti!$B$5=$C15,100000,COUNTIF($S$6:$S14,Partecipanti!$B$5)*100+MOD(1-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G15=0,100000,IF(Partecipanti!$B$5=$C15,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S14,Partecipanti!$B$5)*100+MOD(1-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O15">
-        <f>IF($H15=0,100000,IF(Partecipanti!$B$6=$C15,100000,COUNTIF($S$6:$S14,Partecipanti!$B$6)*100+MOD(2-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H15=0,100000,IF(Partecipanti!$B$6=$C15,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S14,Partecipanti!$B$6)*100+MOD(2-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P15">
-        <f>IF($I15=0,100000,IF(Partecipanti!$B$7=$C15,100000,COUNTIF($S$6:$S14,Partecipanti!$B$7)*100+MOD(3-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I15=0,100000,IF(Partecipanti!$B$7=$C15,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S14,Partecipanti!$B$7)*100+MOD(3-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q15">
-        <f>IF($J15=0,100000,IF(Partecipanti!$B$8=$C15,100000,COUNTIF($S$6:$S14,Partecipanti!$B$8)*100+MOD(4-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J15=0,100000,IF(Partecipanti!$B$8=$C15,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S14,Partecipanti!$B$8)*100+MOD(4-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R15">
-        <f>IF($K15=0,100000,IF(Partecipanti!$B$9=$C15,100000,COUNTIF($S$6:$S14,Partecipanti!$B$9)*100+MOD(5-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K15=0,100000,IF(Partecipanti!$B$9=$C15,100000,IF(SUMPRODUCT(($M$11:$M$15=1)*($L$11:$L$15=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S14,Partecipanti!$B$9)*100+MOD(5-MATCH($C15,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S15">
@@ -8678,11 +8912,35 @@
         <v/>
       </c>
       <c r="X15">
-        <f>IF($M15=1,$L15&amp;" recupera il turno saltato nella settimana "&amp;($A15-1)&amp;"; "&amp;$C15&amp;" a riposo compensativo",IF($E15=1,$C15&amp;" assente ("&amp;$D15&amp;")"&amp;IF($S15="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S15&amp;" con doppio turno")&amp;IF($F15=1,"; turno da recuperare nella settimana "&amp;($A15+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M15=1,IF($E15=1,$L15&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE15&amp;"; "&amp;$C15&amp;" assente ("&amp;$D15&amp;")",$L15&amp;" recupera il turno saltato nella settimana "&amp;$AE15&amp;"; "&amp;$C15&amp;" a riposo compensativo"),IF($E15=1,$C15&amp;" assente ("&amp;$D15&amp;")"&amp;IF($S15="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S15&amp;" con doppio turno")&amp;IF($F15=1,"; turno da recuperare a partire dalla settimana "&amp;($A15+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>IF($M15=1,"recupera il turno saltato nella settimana "&amp;($A15-1)&amp;", "&amp;$C15&amp;" a riposo",IF($E15=1,IF($S15="DA ASSEGNARE","turno da assegnare: "&amp;$C15&amp;" assente","in sostituzione di "&amp;$C15&amp;", doppio turno"),""))</f>
+        <f>IF($M15=1,IF($E15=1,"recupero del turno saltato nella settimana "&amp;$AE15&amp;", "&amp;$C15&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE15&amp;", "&amp;$C15&amp;" a riposo"),IF($E15=1,IF($S15="DA ASSEGNARE","turno da assegnare: "&amp;$C15&amp;" assente","in sostituzione di "&amp;$C15&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>IF($T15="","",COUNTIF($T$6:$T15,$T15))</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>IF($T15="","",$T15&amp;"#"&amp;$Z15)</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>COUNTIF($T$6:$T10,$C15)</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>COUNTIFS($C$6:$C10,$C15,$M$6:$M10,1)</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>IF($AB15&gt;$AC15,IFERROR(MATCH($C15&amp;"#"&amp;($AC15+1),$AA$6:$AA10,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>IF($AD15=0,"",INDEX($A$6:$A10,$AD15))</f>
         <v/>
       </c>
     </row>
@@ -8706,7 +8964,7 @@
         <v/>
       </c>
       <c r="F16">
-        <f>IF($E16=0,0,IF(OR($D16="Licenza - settimana intera",$D16="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M16=1,0,IF($E16=0,0,IF(OR($D16="Licenza - settimana intera",$D16="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G16">
@@ -8730,7 +8988,7 @@
         <v/>
       </c>
       <c r="L16">
-        <f>IFERROR(INDEX($C11:$C15,MATCH(1,INDEX(($T11:$T15=$C16)*1,0),0)),"")</f>
+        <f>IF($AD16=0,"",INDEX($C$6:$C15,$AD16))</f>
         <v/>
       </c>
       <c r="M16">
@@ -8738,23 +8996,23 @@
         <v/>
       </c>
       <c r="N16">
-        <f>IF($G16=0,100000,IF(Partecipanti!$B$5=$C16,100000,COUNTIF($S$6:$S15,Partecipanti!$B$5)*100+MOD(1-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G16=0,100000,IF(Partecipanti!$B$5=$C16,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S15,Partecipanti!$B$5)*100+MOD(1-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O16">
-        <f>IF($H16=0,100000,IF(Partecipanti!$B$6=$C16,100000,COUNTIF($S$6:$S15,Partecipanti!$B$6)*100+MOD(2-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H16=0,100000,IF(Partecipanti!$B$6=$C16,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S15,Partecipanti!$B$6)*100+MOD(2-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P16">
-        <f>IF($I16=0,100000,IF(Partecipanti!$B$7=$C16,100000,COUNTIF($S$6:$S15,Partecipanti!$B$7)*100+MOD(3-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I16=0,100000,IF(Partecipanti!$B$7=$C16,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S15,Partecipanti!$B$7)*100+MOD(3-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q16">
-        <f>IF($J16=0,100000,IF(Partecipanti!$B$8=$C16,100000,COUNTIF($S$6:$S15,Partecipanti!$B$8)*100+MOD(4-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J16=0,100000,IF(Partecipanti!$B$8=$C16,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S15,Partecipanti!$B$8)*100+MOD(4-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R16">
-        <f>IF($K16=0,100000,IF(Partecipanti!$B$9=$C16,100000,COUNTIF($S$6:$S15,Partecipanti!$B$9)*100+MOD(5-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K16=0,100000,IF(Partecipanti!$B$9=$C16,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S15,Partecipanti!$B$9)*100+MOD(5-MATCH($C16,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S16">
@@ -8778,11 +9036,35 @@
         <v/>
       </c>
       <c r="X16">
-        <f>IF($M16=1,$L16&amp;" recupera il turno saltato nella settimana "&amp;($A16-1)&amp;"; "&amp;$C16&amp;" a riposo compensativo",IF($E16=1,$C16&amp;" assente ("&amp;$D16&amp;")"&amp;IF($S16="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S16&amp;" con doppio turno")&amp;IF($F16=1,"; turno da recuperare nella settimana "&amp;($A16+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M16=1,IF($E16=1,$L16&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE16&amp;"; "&amp;$C16&amp;" assente ("&amp;$D16&amp;")",$L16&amp;" recupera il turno saltato nella settimana "&amp;$AE16&amp;"; "&amp;$C16&amp;" a riposo compensativo"),IF($E16=1,$C16&amp;" assente ("&amp;$D16&amp;")"&amp;IF($S16="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S16&amp;" con doppio turno")&amp;IF($F16=1,"; turno da recuperare a partire dalla settimana "&amp;($A16+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>IF($M16=1,"recupera il turno saltato nella settimana "&amp;($A16-1)&amp;", "&amp;$C16&amp;" a riposo",IF($E16=1,IF($S16="DA ASSEGNARE","turno da assegnare: "&amp;$C16&amp;" assente","in sostituzione di "&amp;$C16&amp;", doppio turno"),""))</f>
+        <f>IF($M16=1,IF($E16=1,"recupero del turno saltato nella settimana "&amp;$AE16&amp;", "&amp;$C16&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE16&amp;", "&amp;$C16&amp;" a riposo"),IF($E16=1,IF($S16="DA ASSEGNARE","turno da assegnare: "&amp;$C16&amp;" assente","in sostituzione di "&amp;$C16&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z16">
+        <f>IF($T16="","",COUNTIF($T$6:$T16,$T16))</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>IF($T16="","",$T16&amp;"#"&amp;$Z16)</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>COUNTIF($T$6:$T15,$C16)</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>COUNTIFS($C$6:$C15,$C16,$M$6:$M15,1)</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>IF($AB16&gt;$AC16,IFERROR(MATCH($C16&amp;"#"&amp;($AC16+1),$AA$6:$AA15,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>IF($AD16=0,"",INDEX($A$6:$A15,$AD16))</f>
         <v/>
       </c>
     </row>
@@ -8806,7 +9088,7 @@
         <v/>
       </c>
       <c r="F17">
-        <f>IF($E17=0,0,IF(OR($D17="Licenza - settimana intera",$D17="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M17=1,0,IF($E17=0,0,IF(OR($D17="Licenza - settimana intera",$D17="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G17">
@@ -8830,7 +9112,7 @@
         <v/>
       </c>
       <c r="L17">
-        <f>IFERROR(INDEX($C11:$C15,MATCH(1,INDEX(($T11:$T15=$C17)*1,0),0)),"")</f>
+        <f>IF($AD17=0,"",INDEX($C$6:$C15,$AD17))</f>
         <v/>
       </c>
       <c r="M17">
@@ -8838,23 +9120,23 @@
         <v/>
       </c>
       <c r="N17">
-        <f>IF($G17=0,100000,IF(Partecipanti!$B$5=$C17,100000,COUNTIF($S$6:$S16,Partecipanti!$B$5)*100+MOD(1-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G17=0,100000,IF(Partecipanti!$B$5=$C17,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S16,Partecipanti!$B$5)*100+MOD(1-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O17">
-        <f>IF($H17=0,100000,IF(Partecipanti!$B$6=$C17,100000,COUNTIF($S$6:$S16,Partecipanti!$B$6)*100+MOD(2-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H17=0,100000,IF(Partecipanti!$B$6=$C17,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S16,Partecipanti!$B$6)*100+MOD(2-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P17">
-        <f>IF($I17=0,100000,IF(Partecipanti!$B$7=$C17,100000,COUNTIF($S$6:$S16,Partecipanti!$B$7)*100+MOD(3-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I17=0,100000,IF(Partecipanti!$B$7=$C17,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S16,Partecipanti!$B$7)*100+MOD(3-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q17">
-        <f>IF($J17=0,100000,IF(Partecipanti!$B$8=$C17,100000,COUNTIF($S$6:$S16,Partecipanti!$B$8)*100+MOD(4-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J17=0,100000,IF(Partecipanti!$B$8=$C17,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S16,Partecipanti!$B$8)*100+MOD(4-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R17">
-        <f>IF($K17=0,100000,IF(Partecipanti!$B$9=$C17,100000,COUNTIF($S$6:$S16,Partecipanti!$B$9)*100+MOD(5-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K17=0,100000,IF(Partecipanti!$B$9=$C17,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S16,Partecipanti!$B$9)*100+MOD(5-MATCH($C17,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S17">
@@ -8878,11 +9160,35 @@
         <v/>
       </c>
       <c r="X17">
-        <f>IF($M17=1,$L17&amp;" recupera il turno saltato nella settimana "&amp;($A17-1)&amp;"; "&amp;$C17&amp;" a riposo compensativo",IF($E17=1,$C17&amp;" assente ("&amp;$D17&amp;")"&amp;IF($S17="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S17&amp;" con doppio turno")&amp;IF($F17=1,"; turno da recuperare nella settimana "&amp;($A17+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M17=1,IF($E17=1,$L17&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE17&amp;"; "&amp;$C17&amp;" assente ("&amp;$D17&amp;")",$L17&amp;" recupera il turno saltato nella settimana "&amp;$AE17&amp;"; "&amp;$C17&amp;" a riposo compensativo"),IF($E17=1,$C17&amp;" assente ("&amp;$D17&amp;")"&amp;IF($S17="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S17&amp;" con doppio turno")&amp;IF($F17=1,"; turno da recuperare a partire dalla settimana "&amp;($A17+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>IF($M17=1,"recupera il turno saltato nella settimana "&amp;($A17-1)&amp;", "&amp;$C17&amp;" a riposo",IF($E17=1,IF($S17="DA ASSEGNARE","turno da assegnare: "&amp;$C17&amp;" assente","in sostituzione di "&amp;$C17&amp;", doppio turno"),""))</f>
+        <f>IF($M17=1,IF($E17=1,"recupero del turno saltato nella settimana "&amp;$AE17&amp;", "&amp;$C17&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE17&amp;", "&amp;$C17&amp;" a riposo"),IF($E17=1,IF($S17="DA ASSEGNARE","turno da assegnare: "&amp;$C17&amp;" assente","in sostituzione di "&amp;$C17&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z17">
+        <f>IF($T17="","",COUNTIF($T$6:$T17,$T17))</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>IF($T17="","",$T17&amp;"#"&amp;$Z17)</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>COUNTIF($T$6:$T15,$C17)</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>COUNTIFS($C$6:$C15,$C17,$M$6:$M15,1)</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>IF($AB17&gt;$AC17,IFERROR(MATCH($C17&amp;"#"&amp;($AC17+1),$AA$6:$AA15,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>IF($AD17=0,"",INDEX($A$6:$A15,$AD17))</f>
         <v/>
       </c>
     </row>
@@ -8906,7 +9212,7 @@
         <v/>
       </c>
       <c r="F18">
-        <f>IF($E18=0,0,IF(OR($D18="Licenza - settimana intera",$D18="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M18=1,0,IF($E18=0,0,IF(OR($D18="Licenza - settimana intera",$D18="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G18">
@@ -8930,7 +9236,7 @@
         <v/>
       </c>
       <c r="L18">
-        <f>IFERROR(INDEX($C11:$C15,MATCH(1,INDEX(($T11:$T15=$C18)*1,0),0)),"")</f>
+        <f>IF($AD18=0,"",INDEX($C$6:$C15,$AD18))</f>
         <v/>
       </c>
       <c r="M18">
@@ -8938,23 +9244,23 @@
         <v/>
       </c>
       <c r="N18">
-        <f>IF($G18=0,100000,IF(Partecipanti!$B$5=$C18,100000,COUNTIF($S$6:$S17,Partecipanti!$B$5)*100+MOD(1-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G18=0,100000,IF(Partecipanti!$B$5=$C18,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S17,Partecipanti!$B$5)*100+MOD(1-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O18">
-        <f>IF($H18=0,100000,IF(Partecipanti!$B$6=$C18,100000,COUNTIF($S$6:$S17,Partecipanti!$B$6)*100+MOD(2-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H18=0,100000,IF(Partecipanti!$B$6=$C18,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S17,Partecipanti!$B$6)*100+MOD(2-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P18">
-        <f>IF($I18=0,100000,IF(Partecipanti!$B$7=$C18,100000,COUNTIF($S$6:$S17,Partecipanti!$B$7)*100+MOD(3-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I18=0,100000,IF(Partecipanti!$B$7=$C18,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S17,Partecipanti!$B$7)*100+MOD(3-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q18">
-        <f>IF($J18=0,100000,IF(Partecipanti!$B$8=$C18,100000,COUNTIF($S$6:$S17,Partecipanti!$B$8)*100+MOD(4-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J18=0,100000,IF(Partecipanti!$B$8=$C18,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S17,Partecipanti!$B$8)*100+MOD(4-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R18">
-        <f>IF($K18=0,100000,IF(Partecipanti!$B$9=$C18,100000,COUNTIF($S$6:$S17,Partecipanti!$B$9)*100+MOD(5-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K18=0,100000,IF(Partecipanti!$B$9=$C18,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S17,Partecipanti!$B$9)*100+MOD(5-MATCH($C18,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S18">
@@ -8978,11 +9284,35 @@
         <v/>
       </c>
       <c r="X18">
-        <f>IF($M18=1,$L18&amp;" recupera il turno saltato nella settimana "&amp;($A18-1)&amp;"; "&amp;$C18&amp;" a riposo compensativo",IF($E18=1,$C18&amp;" assente ("&amp;$D18&amp;")"&amp;IF($S18="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S18&amp;" con doppio turno")&amp;IF($F18=1,"; turno da recuperare nella settimana "&amp;($A18+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M18=1,IF($E18=1,$L18&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE18&amp;"; "&amp;$C18&amp;" assente ("&amp;$D18&amp;")",$L18&amp;" recupera il turno saltato nella settimana "&amp;$AE18&amp;"; "&amp;$C18&amp;" a riposo compensativo"),IF($E18=1,$C18&amp;" assente ("&amp;$D18&amp;")"&amp;IF($S18="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S18&amp;" con doppio turno")&amp;IF($F18=1,"; turno da recuperare a partire dalla settimana "&amp;($A18+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>IF($M18=1,"recupera il turno saltato nella settimana "&amp;($A18-1)&amp;", "&amp;$C18&amp;" a riposo",IF($E18=1,IF($S18="DA ASSEGNARE","turno da assegnare: "&amp;$C18&amp;" assente","in sostituzione di "&amp;$C18&amp;", doppio turno"),""))</f>
+        <f>IF($M18=1,IF($E18=1,"recupero del turno saltato nella settimana "&amp;$AE18&amp;", "&amp;$C18&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE18&amp;", "&amp;$C18&amp;" a riposo"),IF($E18=1,IF($S18="DA ASSEGNARE","turno da assegnare: "&amp;$C18&amp;" assente","in sostituzione di "&amp;$C18&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z18">
+        <f>IF($T18="","",COUNTIF($T$6:$T18,$T18))</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>IF($T18="","",$T18&amp;"#"&amp;$Z18)</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>COUNTIF($T$6:$T15,$C18)</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>COUNTIFS($C$6:$C15,$C18,$M$6:$M15,1)</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>IF($AB18&gt;$AC18,IFERROR(MATCH($C18&amp;"#"&amp;($AC18+1),$AA$6:$AA15,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>IF($AD18=0,"",INDEX($A$6:$A15,$AD18))</f>
         <v/>
       </c>
     </row>
@@ -9006,7 +9336,7 @@
         <v/>
       </c>
       <c r="F19">
-        <f>IF($E19=0,0,IF(OR($D19="Licenza - settimana intera",$D19="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M19=1,0,IF($E19=0,0,IF(OR($D19="Licenza - settimana intera",$D19="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G19">
@@ -9030,7 +9360,7 @@
         <v/>
       </c>
       <c r="L19">
-        <f>IFERROR(INDEX($C11:$C15,MATCH(1,INDEX(($T11:$T15=$C19)*1,0),0)),"")</f>
+        <f>IF($AD19=0,"",INDEX($C$6:$C15,$AD19))</f>
         <v/>
       </c>
       <c r="M19">
@@ -9038,23 +9368,23 @@
         <v/>
       </c>
       <c r="N19">
-        <f>IF($G19=0,100000,IF(Partecipanti!$B$5=$C19,100000,COUNTIF($S$6:$S18,Partecipanti!$B$5)*100+MOD(1-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G19=0,100000,IF(Partecipanti!$B$5=$C19,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S18,Partecipanti!$B$5)*100+MOD(1-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O19">
-        <f>IF($H19=0,100000,IF(Partecipanti!$B$6=$C19,100000,COUNTIF($S$6:$S18,Partecipanti!$B$6)*100+MOD(2-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H19=0,100000,IF(Partecipanti!$B$6=$C19,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S18,Partecipanti!$B$6)*100+MOD(2-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P19">
-        <f>IF($I19=0,100000,IF(Partecipanti!$B$7=$C19,100000,COUNTIF($S$6:$S18,Partecipanti!$B$7)*100+MOD(3-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I19=0,100000,IF(Partecipanti!$B$7=$C19,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S18,Partecipanti!$B$7)*100+MOD(3-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q19">
-        <f>IF($J19=0,100000,IF(Partecipanti!$B$8=$C19,100000,COUNTIF($S$6:$S18,Partecipanti!$B$8)*100+MOD(4-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J19=0,100000,IF(Partecipanti!$B$8=$C19,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S18,Partecipanti!$B$8)*100+MOD(4-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R19">
-        <f>IF($K19=0,100000,IF(Partecipanti!$B$9=$C19,100000,COUNTIF($S$6:$S18,Partecipanti!$B$9)*100+MOD(5-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K19=0,100000,IF(Partecipanti!$B$9=$C19,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S18,Partecipanti!$B$9)*100+MOD(5-MATCH($C19,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S19">
@@ -9078,11 +9408,35 @@
         <v/>
       </c>
       <c r="X19">
-        <f>IF($M19=1,$L19&amp;" recupera il turno saltato nella settimana "&amp;($A19-1)&amp;"; "&amp;$C19&amp;" a riposo compensativo",IF($E19=1,$C19&amp;" assente ("&amp;$D19&amp;")"&amp;IF($S19="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S19&amp;" con doppio turno")&amp;IF($F19=1,"; turno da recuperare nella settimana "&amp;($A19+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M19=1,IF($E19=1,$L19&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE19&amp;"; "&amp;$C19&amp;" assente ("&amp;$D19&amp;")",$L19&amp;" recupera il turno saltato nella settimana "&amp;$AE19&amp;"; "&amp;$C19&amp;" a riposo compensativo"),IF($E19=1,$C19&amp;" assente ("&amp;$D19&amp;")"&amp;IF($S19="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S19&amp;" con doppio turno")&amp;IF($F19=1,"; turno da recuperare a partire dalla settimana "&amp;($A19+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>IF($M19=1,"recupera il turno saltato nella settimana "&amp;($A19-1)&amp;", "&amp;$C19&amp;" a riposo",IF($E19=1,IF($S19="DA ASSEGNARE","turno da assegnare: "&amp;$C19&amp;" assente","in sostituzione di "&amp;$C19&amp;", doppio turno"),""))</f>
+        <f>IF($M19=1,IF($E19=1,"recupero del turno saltato nella settimana "&amp;$AE19&amp;", "&amp;$C19&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE19&amp;", "&amp;$C19&amp;" a riposo"),IF($E19=1,IF($S19="DA ASSEGNARE","turno da assegnare: "&amp;$C19&amp;" assente","in sostituzione di "&amp;$C19&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>IF($T19="","",COUNTIF($T$6:$T19,$T19))</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>IF($T19="","",$T19&amp;"#"&amp;$Z19)</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>COUNTIF($T$6:$T15,$C19)</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>COUNTIFS($C$6:$C15,$C19,$M$6:$M15,1)</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>IF($AB19&gt;$AC19,IFERROR(MATCH($C19&amp;"#"&amp;($AC19+1),$AA$6:$AA15,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>IF($AD19=0,"",INDEX($A$6:$A15,$AD19))</f>
         <v/>
       </c>
     </row>
@@ -9106,7 +9460,7 @@
         <v/>
       </c>
       <c r="F20">
-        <f>IF($E20=0,0,IF(OR($D20="Licenza - settimana intera",$D20="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M20=1,0,IF($E20=0,0,IF(OR($D20="Licenza - settimana intera",$D20="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G20">
@@ -9130,7 +9484,7 @@
         <v/>
       </c>
       <c r="L20">
-        <f>IFERROR(INDEX($C11:$C15,MATCH(1,INDEX(($T11:$T15=$C20)*1,0),0)),"")</f>
+        <f>IF($AD20=0,"",INDEX($C$6:$C15,$AD20))</f>
         <v/>
       </c>
       <c r="M20">
@@ -9138,23 +9492,23 @@
         <v/>
       </c>
       <c r="N20">
-        <f>IF($G20=0,100000,IF(Partecipanti!$B$5=$C20,100000,COUNTIF($S$6:$S19,Partecipanti!$B$5)*100+MOD(1-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G20=0,100000,IF(Partecipanti!$B$5=$C20,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S19,Partecipanti!$B$5)*100+MOD(1-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O20">
-        <f>IF($H20=0,100000,IF(Partecipanti!$B$6=$C20,100000,COUNTIF($S$6:$S19,Partecipanti!$B$6)*100+MOD(2-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H20=0,100000,IF(Partecipanti!$B$6=$C20,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S19,Partecipanti!$B$6)*100+MOD(2-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P20">
-        <f>IF($I20=0,100000,IF(Partecipanti!$B$7=$C20,100000,COUNTIF($S$6:$S19,Partecipanti!$B$7)*100+MOD(3-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I20=0,100000,IF(Partecipanti!$B$7=$C20,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S19,Partecipanti!$B$7)*100+MOD(3-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q20">
-        <f>IF($J20=0,100000,IF(Partecipanti!$B$8=$C20,100000,COUNTIF($S$6:$S19,Partecipanti!$B$8)*100+MOD(4-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J20=0,100000,IF(Partecipanti!$B$8=$C20,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S19,Partecipanti!$B$8)*100+MOD(4-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R20">
-        <f>IF($K20=0,100000,IF(Partecipanti!$B$9=$C20,100000,COUNTIF($S$6:$S19,Partecipanti!$B$9)*100+MOD(5-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K20=0,100000,IF(Partecipanti!$B$9=$C20,100000,IF(SUMPRODUCT(($M$16:$M$20=1)*($L$16:$L$20=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S19,Partecipanti!$B$9)*100+MOD(5-MATCH($C20,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S20">
@@ -9178,11 +9532,35 @@
         <v/>
       </c>
       <c r="X20">
-        <f>IF($M20=1,$L20&amp;" recupera il turno saltato nella settimana "&amp;($A20-1)&amp;"; "&amp;$C20&amp;" a riposo compensativo",IF($E20=1,$C20&amp;" assente ("&amp;$D20&amp;")"&amp;IF($S20="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S20&amp;" con doppio turno")&amp;IF($F20=1,"; turno da recuperare nella settimana "&amp;($A20+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M20=1,IF($E20=1,$L20&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE20&amp;"; "&amp;$C20&amp;" assente ("&amp;$D20&amp;")",$L20&amp;" recupera il turno saltato nella settimana "&amp;$AE20&amp;"; "&amp;$C20&amp;" a riposo compensativo"),IF($E20=1,$C20&amp;" assente ("&amp;$D20&amp;")"&amp;IF($S20="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S20&amp;" con doppio turno")&amp;IF($F20=1,"; turno da recuperare a partire dalla settimana "&amp;($A20+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y20">
-        <f>IF($M20=1,"recupera il turno saltato nella settimana "&amp;($A20-1)&amp;", "&amp;$C20&amp;" a riposo",IF($E20=1,IF($S20="DA ASSEGNARE","turno da assegnare: "&amp;$C20&amp;" assente","in sostituzione di "&amp;$C20&amp;", doppio turno"),""))</f>
+        <f>IF($M20=1,IF($E20=1,"recupero del turno saltato nella settimana "&amp;$AE20&amp;", "&amp;$C20&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE20&amp;", "&amp;$C20&amp;" a riposo"),IF($E20=1,IF($S20="DA ASSEGNARE","turno da assegnare: "&amp;$C20&amp;" assente","in sostituzione di "&amp;$C20&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>IF($T20="","",COUNTIF($T$6:$T20,$T20))</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>IF($T20="","",$T20&amp;"#"&amp;$Z20)</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>COUNTIF($T$6:$T15,$C20)</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>COUNTIFS($C$6:$C15,$C20,$M$6:$M15,1)</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>IF($AB20&gt;$AC20,IFERROR(MATCH($C20&amp;"#"&amp;($AC20+1),$AA$6:$AA15,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE20">
+        <f>IF($AD20=0,"",INDEX($A$6:$A15,$AD20))</f>
         <v/>
       </c>
     </row>
@@ -9206,7 +9584,7 @@
         <v/>
       </c>
       <c r="F21">
-        <f>IF($E21=0,0,IF(OR($D21="Licenza - settimana intera",$D21="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M21=1,0,IF($E21=0,0,IF(OR($D21="Licenza - settimana intera",$D21="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G21">
@@ -9230,7 +9608,7 @@
         <v/>
       </c>
       <c r="L21">
-        <f>IFERROR(INDEX($C16:$C20,MATCH(1,INDEX(($T16:$T20=$C21)*1,0),0)),"")</f>
+        <f>IF($AD21=0,"",INDEX($C$6:$C20,$AD21))</f>
         <v/>
       </c>
       <c r="M21">
@@ -9238,23 +9616,23 @@
         <v/>
       </c>
       <c r="N21">
-        <f>IF($G21=0,100000,IF(Partecipanti!$B$5=$C21,100000,COUNTIF($S$6:$S20,Partecipanti!$B$5)*100+MOD(1-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G21=0,100000,IF(Partecipanti!$B$5=$C21,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S20,Partecipanti!$B$5)*100+MOD(1-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O21">
-        <f>IF($H21=0,100000,IF(Partecipanti!$B$6=$C21,100000,COUNTIF($S$6:$S20,Partecipanti!$B$6)*100+MOD(2-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H21=0,100000,IF(Partecipanti!$B$6=$C21,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S20,Partecipanti!$B$6)*100+MOD(2-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P21">
-        <f>IF($I21=0,100000,IF(Partecipanti!$B$7=$C21,100000,COUNTIF($S$6:$S20,Partecipanti!$B$7)*100+MOD(3-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I21=0,100000,IF(Partecipanti!$B$7=$C21,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S20,Partecipanti!$B$7)*100+MOD(3-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q21">
-        <f>IF($J21=0,100000,IF(Partecipanti!$B$8=$C21,100000,COUNTIF($S$6:$S20,Partecipanti!$B$8)*100+MOD(4-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J21=0,100000,IF(Partecipanti!$B$8=$C21,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S20,Partecipanti!$B$8)*100+MOD(4-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R21">
-        <f>IF($K21=0,100000,IF(Partecipanti!$B$9=$C21,100000,COUNTIF($S$6:$S20,Partecipanti!$B$9)*100+MOD(5-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K21=0,100000,IF(Partecipanti!$B$9=$C21,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S20,Partecipanti!$B$9)*100+MOD(5-MATCH($C21,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S21">
@@ -9278,11 +9656,35 @@
         <v/>
       </c>
       <c r="X21">
-        <f>IF($M21=1,$L21&amp;" recupera il turno saltato nella settimana "&amp;($A21-1)&amp;"; "&amp;$C21&amp;" a riposo compensativo",IF($E21=1,$C21&amp;" assente ("&amp;$D21&amp;")"&amp;IF($S21="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S21&amp;" con doppio turno")&amp;IF($F21=1,"; turno da recuperare nella settimana "&amp;($A21+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M21=1,IF($E21=1,$L21&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE21&amp;"; "&amp;$C21&amp;" assente ("&amp;$D21&amp;")",$L21&amp;" recupera il turno saltato nella settimana "&amp;$AE21&amp;"; "&amp;$C21&amp;" a riposo compensativo"),IF($E21=1,$C21&amp;" assente ("&amp;$D21&amp;")"&amp;IF($S21="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S21&amp;" con doppio turno")&amp;IF($F21=1,"; turno da recuperare a partire dalla settimana "&amp;($A21+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>IF($M21=1,"recupera il turno saltato nella settimana "&amp;($A21-1)&amp;", "&amp;$C21&amp;" a riposo",IF($E21=1,IF($S21="DA ASSEGNARE","turno da assegnare: "&amp;$C21&amp;" assente","in sostituzione di "&amp;$C21&amp;", doppio turno"),""))</f>
+        <f>IF($M21=1,IF($E21=1,"recupero del turno saltato nella settimana "&amp;$AE21&amp;", "&amp;$C21&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE21&amp;", "&amp;$C21&amp;" a riposo"),IF($E21=1,IF($S21="DA ASSEGNARE","turno da assegnare: "&amp;$C21&amp;" assente","in sostituzione di "&amp;$C21&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>IF($T21="","",COUNTIF($T$6:$T21,$T21))</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>IF($T21="","",$T21&amp;"#"&amp;$Z21)</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>COUNTIF($T$6:$T20,$C21)</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>COUNTIFS($C$6:$C20,$C21,$M$6:$M20,1)</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>IF($AB21&gt;$AC21,IFERROR(MATCH($C21&amp;"#"&amp;($AC21+1),$AA$6:$AA20,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>IF($AD21=0,"",INDEX($A$6:$A20,$AD21))</f>
         <v/>
       </c>
     </row>
@@ -9306,7 +9708,7 @@
         <v/>
       </c>
       <c r="F22">
-        <f>IF($E22=0,0,IF(OR($D22="Licenza - settimana intera",$D22="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M22=1,0,IF($E22=0,0,IF(OR($D22="Licenza - settimana intera",$D22="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G22">
@@ -9330,7 +9732,7 @@
         <v/>
       </c>
       <c r="L22">
-        <f>IFERROR(INDEX($C16:$C20,MATCH(1,INDEX(($T16:$T20=$C22)*1,0),0)),"")</f>
+        <f>IF($AD22=0,"",INDEX($C$6:$C20,$AD22))</f>
         <v/>
       </c>
       <c r="M22">
@@ -9338,23 +9740,23 @@
         <v/>
       </c>
       <c r="N22">
-        <f>IF($G22=0,100000,IF(Partecipanti!$B$5=$C22,100000,COUNTIF($S$6:$S21,Partecipanti!$B$5)*100+MOD(1-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G22=0,100000,IF(Partecipanti!$B$5=$C22,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S21,Partecipanti!$B$5)*100+MOD(1-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O22">
-        <f>IF($H22=0,100000,IF(Partecipanti!$B$6=$C22,100000,COUNTIF($S$6:$S21,Partecipanti!$B$6)*100+MOD(2-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H22=0,100000,IF(Partecipanti!$B$6=$C22,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S21,Partecipanti!$B$6)*100+MOD(2-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P22">
-        <f>IF($I22=0,100000,IF(Partecipanti!$B$7=$C22,100000,COUNTIF($S$6:$S21,Partecipanti!$B$7)*100+MOD(3-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I22=0,100000,IF(Partecipanti!$B$7=$C22,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S21,Partecipanti!$B$7)*100+MOD(3-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q22">
-        <f>IF($J22=0,100000,IF(Partecipanti!$B$8=$C22,100000,COUNTIF($S$6:$S21,Partecipanti!$B$8)*100+MOD(4-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J22=0,100000,IF(Partecipanti!$B$8=$C22,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S21,Partecipanti!$B$8)*100+MOD(4-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R22">
-        <f>IF($K22=0,100000,IF(Partecipanti!$B$9=$C22,100000,COUNTIF($S$6:$S21,Partecipanti!$B$9)*100+MOD(5-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K22=0,100000,IF(Partecipanti!$B$9=$C22,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S21,Partecipanti!$B$9)*100+MOD(5-MATCH($C22,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S22">
@@ -9378,11 +9780,35 @@
         <v/>
       </c>
       <c r="X22">
-        <f>IF($M22=1,$L22&amp;" recupera il turno saltato nella settimana "&amp;($A22-1)&amp;"; "&amp;$C22&amp;" a riposo compensativo",IF($E22=1,$C22&amp;" assente ("&amp;$D22&amp;")"&amp;IF($S22="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S22&amp;" con doppio turno")&amp;IF($F22=1,"; turno da recuperare nella settimana "&amp;($A22+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M22=1,IF($E22=1,$L22&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE22&amp;"; "&amp;$C22&amp;" assente ("&amp;$D22&amp;")",$L22&amp;" recupera il turno saltato nella settimana "&amp;$AE22&amp;"; "&amp;$C22&amp;" a riposo compensativo"),IF($E22=1,$C22&amp;" assente ("&amp;$D22&amp;")"&amp;IF($S22="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S22&amp;" con doppio turno")&amp;IF($F22=1,"; turno da recuperare a partire dalla settimana "&amp;($A22+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>IF($M22=1,"recupera il turno saltato nella settimana "&amp;($A22-1)&amp;", "&amp;$C22&amp;" a riposo",IF($E22=1,IF($S22="DA ASSEGNARE","turno da assegnare: "&amp;$C22&amp;" assente","in sostituzione di "&amp;$C22&amp;", doppio turno"),""))</f>
+        <f>IF($M22=1,IF($E22=1,"recupero del turno saltato nella settimana "&amp;$AE22&amp;", "&amp;$C22&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE22&amp;", "&amp;$C22&amp;" a riposo"),IF($E22=1,IF($S22="DA ASSEGNARE","turno da assegnare: "&amp;$C22&amp;" assente","in sostituzione di "&amp;$C22&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>IF($T22="","",COUNTIF($T$6:$T22,$T22))</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>IF($T22="","",$T22&amp;"#"&amp;$Z22)</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>COUNTIF($T$6:$T20,$C22)</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>COUNTIFS($C$6:$C20,$C22,$M$6:$M20,1)</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>IF($AB22&gt;$AC22,IFERROR(MATCH($C22&amp;"#"&amp;($AC22+1),$AA$6:$AA20,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>IF($AD22=0,"",INDEX($A$6:$A20,$AD22))</f>
         <v/>
       </c>
     </row>
@@ -9406,7 +9832,7 @@
         <v/>
       </c>
       <c r="F23">
-        <f>IF($E23=0,0,IF(OR($D23="Licenza - settimana intera",$D23="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M23=1,0,IF($E23=0,0,IF(OR($D23="Licenza - settimana intera",$D23="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G23">
@@ -9430,7 +9856,7 @@
         <v/>
       </c>
       <c r="L23">
-        <f>IFERROR(INDEX($C16:$C20,MATCH(1,INDEX(($T16:$T20=$C23)*1,0),0)),"")</f>
+        <f>IF($AD23=0,"",INDEX($C$6:$C20,$AD23))</f>
         <v/>
       </c>
       <c r="M23">
@@ -9438,23 +9864,23 @@
         <v/>
       </c>
       <c r="N23">
-        <f>IF($G23=0,100000,IF(Partecipanti!$B$5=$C23,100000,COUNTIF($S$6:$S22,Partecipanti!$B$5)*100+MOD(1-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G23=0,100000,IF(Partecipanti!$B$5=$C23,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S22,Partecipanti!$B$5)*100+MOD(1-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O23">
-        <f>IF($H23=0,100000,IF(Partecipanti!$B$6=$C23,100000,COUNTIF($S$6:$S22,Partecipanti!$B$6)*100+MOD(2-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H23=0,100000,IF(Partecipanti!$B$6=$C23,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S22,Partecipanti!$B$6)*100+MOD(2-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P23">
-        <f>IF($I23=0,100000,IF(Partecipanti!$B$7=$C23,100000,COUNTIF($S$6:$S22,Partecipanti!$B$7)*100+MOD(3-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I23=0,100000,IF(Partecipanti!$B$7=$C23,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S22,Partecipanti!$B$7)*100+MOD(3-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q23">
-        <f>IF($J23=0,100000,IF(Partecipanti!$B$8=$C23,100000,COUNTIF($S$6:$S22,Partecipanti!$B$8)*100+MOD(4-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J23=0,100000,IF(Partecipanti!$B$8=$C23,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S22,Partecipanti!$B$8)*100+MOD(4-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R23">
-        <f>IF($K23=0,100000,IF(Partecipanti!$B$9=$C23,100000,COUNTIF($S$6:$S22,Partecipanti!$B$9)*100+MOD(5-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K23=0,100000,IF(Partecipanti!$B$9=$C23,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S22,Partecipanti!$B$9)*100+MOD(5-MATCH($C23,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S23">
@@ -9478,11 +9904,35 @@
         <v/>
       </c>
       <c r="X23">
-        <f>IF($M23=1,$L23&amp;" recupera il turno saltato nella settimana "&amp;($A23-1)&amp;"; "&amp;$C23&amp;" a riposo compensativo",IF($E23=1,$C23&amp;" assente ("&amp;$D23&amp;")"&amp;IF($S23="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S23&amp;" con doppio turno")&amp;IF($F23=1,"; turno da recuperare nella settimana "&amp;($A23+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M23=1,IF($E23=1,$L23&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE23&amp;"; "&amp;$C23&amp;" assente ("&amp;$D23&amp;")",$L23&amp;" recupera il turno saltato nella settimana "&amp;$AE23&amp;"; "&amp;$C23&amp;" a riposo compensativo"),IF($E23=1,$C23&amp;" assente ("&amp;$D23&amp;")"&amp;IF($S23="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S23&amp;" con doppio turno")&amp;IF($F23=1,"; turno da recuperare a partire dalla settimana "&amp;($A23+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>IF($M23=1,"recupera il turno saltato nella settimana "&amp;($A23-1)&amp;", "&amp;$C23&amp;" a riposo",IF($E23=1,IF($S23="DA ASSEGNARE","turno da assegnare: "&amp;$C23&amp;" assente","in sostituzione di "&amp;$C23&amp;", doppio turno"),""))</f>
+        <f>IF($M23=1,IF($E23=1,"recupero del turno saltato nella settimana "&amp;$AE23&amp;", "&amp;$C23&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE23&amp;", "&amp;$C23&amp;" a riposo"),IF($E23=1,IF($S23="DA ASSEGNARE","turno da assegnare: "&amp;$C23&amp;" assente","in sostituzione di "&amp;$C23&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>IF($T23="","",COUNTIF($T$6:$T23,$T23))</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>IF($T23="","",$T23&amp;"#"&amp;$Z23)</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>COUNTIF($T$6:$T20,$C23)</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>COUNTIFS($C$6:$C20,$C23,$M$6:$M20,1)</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>IF($AB23&gt;$AC23,IFERROR(MATCH($C23&amp;"#"&amp;($AC23+1),$AA$6:$AA20,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>IF($AD23=0,"",INDEX($A$6:$A20,$AD23))</f>
         <v/>
       </c>
     </row>
@@ -9506,7 +9956,7 @@
         <v/>
       </c>
       <c r="F24">
-        <f>IF($E24=0,0,IF(OR($D24="Licenza - settimana intera",$D24="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M24=1,0,IF($E24=0,0,IF(OR($D24="Licenza - settimana intera",$D24="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G24">
@@ -9530,7 +9980,7 @@
         <v/>
       </c>
       <c r="L24">
-        <f>IFERROR(INDEX($C16:$C20,MATCH(1,INDEX(($T16:$T20=$C24)*1,0),0)),"")</f>
+        <f>IF($AD24=0,"",INDEX($C$6:$C20,$AD24))</f>
         <v/>
       </c>
       <c r="M24">
@@ -9538,23 +9988,23 @@
         <v/>
       </c>
       <c r="N24">
-        <f>IF($G24=0,100000,IF(Partecipanti!$B$5=$C24,100000,COUNTIF($S$6:$S23,Partecipanti!$B$5)*100+MOD(1-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G24=0,100000,IF(Partecipanti!$B$5=$C24,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S23,Partecipanti!$B$5)*100+MOD(1-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O24">
-        <f>IF($H24=0,100000,IF(Partecipanti!$B$6=$C24,100000,COUNTIF($S$6:$S23,Partecipanti!$B$6)*100+MOD(2-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H24=0,100000,IF(Partecipanti!$B$6=$C24,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S23,Partecipanti!$B$6)*100+MOD(2-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P24">
-        <f>IF($I24=0,100000,IF(Partecipanti!$B$7=$C24,100000,COUNTIF($S$6:$S23,Partecipanti!$B$7)*100+MOD(3-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I24=0,100000,IF(Partecipanti!$B$7=$C24,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S23,Partecipanti!$B$7)*100+MOD(3-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q24">
-        <f>IF($J24=0,100000,IF(Partecipanti!$B$8=$C24,100000,COUNTIF($S$6:$S23,Partecipanti!$B$8)*100+MOD(4-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J24=0,100000,IF(Partecipanti!$B$8=$C24,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S23,Partecipanti!$B$8)*100+MOD(4-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R24">
-        <f>IF($K24=0,100000,IF(Partecipanti!$B$9=$C24,100000,COUNTIF($S$6:$S23,Partecipanti!$B$9)*100+MOD(5-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K24=0,100000,IF(Partecipanti!$B$9=$C24,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S23,Partecipanti!$B$9)*100+MOD(5-MATCH($C24,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S24">
@@ -9578,11 +10028,35 @@
         <v/>
       </c>
       <c r="X24">
-        <f>IF($M24=1,$L24&amp;" recupera il turno saltato nella settimana "&amp;($A24-1)&amp;"; "&amp;$C24&amp;" a riposo compensativo",IF($E24=1,$C24&amp;" assente ("&amp;$D24&amp;")"&amp;IF($S24="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S24&amp;" con doppio turno")&amp;IF($F24=1,"; turno da recuperare nella settimana "&amp;($A24+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M24=1,IF($E24=1,$L24&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE24&amp;"; "&amp;$C24&amp;" assente ("&amp;$D24&amp;")",$L24&amp;" recupera il turno saltato nella settimana "&amp;$AE24&amp;"; "&amp;$C24&amp;" a riposo compensativo"),IF($E24=1,$C24&amp;" assente ("&amp;$D24&amp;")"&amp;IF($S24="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S24&amp;" con doppio turno")&amp;IF($F24=1,"; turno da recuperare a partire dalla settimana "&amp;($A24+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>IF($M24=1,"recupera il turno saltato nella settimana "&amp;($A24-1)&amp;", "&amp;$C24&amp;" a riposo",IF($E24=1,IF($S24="DA ASSEGNARE","turno da assegnare: "&amp;$C24&amp;" assente","in sostituzione di "&amp;$C24&amp;", doppio turno"),""))</f>
+        <f>IF($M24=1,IF($E24=1,"recupero del turno saltato nella settimana "&amp;$AE24&amp;", "&amp;$C24&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE24&amp;", "&amp;$C24&amp;" a riposo"),IF($E24=1,IF($S24="DA ASSEGNARE","turno da assegnare: "&amp;$C24&amp;" assente","in sostituzione di "&amp;$C24&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>IF($T24="","",COUNTIF($T$6:$T24,$T24))</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>IF($T24="","",$T24&amp;"#"&amp;$Z24)</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>COUNTIF($T$6:$T20,$C24)</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>COUNTIFS($C$6:$C20,$C24,$M$6:$M20,1)</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>IF($AB24&gt;$AC24,IFERROR(MATCH($C24&amp;"#"&amp;($AC24+1),$AA$6:$AA20,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>IF($AD24=0,"",INDEX($A$6:$A20,$AD24))</f>
         <v/>
       </c>
     </row>
@@ -9606,7 +10080,7 @@
         <v/>
       </c>
       <c r="F25">
-        <f>IF($E25=0,0,IF(OR($D25="Licenza - settimana intera",$D25="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M25=1,0,IF($E25=0,0,IF(OR($D25="Licenza - settimana intera",$D25="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G25">
@@ -9630,7 +10104,7 @@
         <v/>
       </c>
       <c r="L25">
-        <f>IFERROR(INDEX($C16:$C20,MATCH(1,INDEX(($T16:$T20=$C25)*1,0),0)),"")</f>
+        <f>IF($AD25=0,"",INDEX($C$6:$C20,$AD25))</f>
         <v/>
       </c>
       <c r="M25">
@@ -9638,23 +10112,23 @@
         <v/>
       </c>
       <c r="N25">
-        <f>IF($G25=0,100000,IF(Partecipanti!$B$5=$C25,100000,COUNTIF($S$6:$S24,Partecipanti!$B$5)*100+MOD(1-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G25=0,100000,IF(Partecipanti!$B$5=$C25,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S24,Partecipanti!$B$5)*100+MOD(1-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O25">
-        <f>IF($H25=0,100000,IF(Partecipanti!$B$6=$C25,100000,COUNTIF($S$6:$S24,Partecipanti!$B$6)*100+MOD(2-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H25=0,100000,IF(Partecipanti!$B$6=$C25,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S24,Partecipanti!$B$6)*100+MOD(2-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P25">
-        <f>IF($I25=0,100000,IF(Partecipanti!$B$7=$C25,100000,COUNTIF($S$6:$S24,Partecipanti!$B$7)*100+MOD(3-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I25=0,100000,IF(Partecipanti!$B$7=$C25,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S24,Partecipanti!$B$7)*100+MOD(3-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q25">
-        <f>IF($J25=0,100000,IF(Partecipanti!$B$8=$C25,100000,COUNTIF($S$6:$S24,Partecipanti!$B$8)*100+MOD(4-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J25=0,100000,IF(Partecipanti!$B$8=$C25,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S24,Partecipanti!$B$8)*100+MOD(4-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R25">
-        <f>IF($K25=0,100000,IF(Partecipanti!$B$9=$C25,100000,COUNTIF($S$6:$S24,Partecipanti!$B$9)*100+MOD(5-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K25=0,100000,IF(Partecipanti!$B$9=$C25,100000,IF(SUMPRODUCT(($M$21:$M$25=1)*($L$21:$L$25=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S24,Partecipanti!$B$9)*100+MOD(5-MATCH($C25,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S25">
@@ -9678,11 +10152,35 @@
         <v/>
       </c>
       <c r="X25">
-        <f>IF($M25=1,$L25&amp;" recupera il turno saltato nella settimana "&amp;($A25-1)&amp;"; "&amp;$C25&amp;" a riposo compensativo",IF($E25=1,$C25&amp;" assente ("&amp;$D25&amp;")"&amp;IF($S25="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S25&amp;" con doppio turno")&amp;IF($F25=1,"; turno da recuperare nella settimana "&amp;($A25+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M25=1,IF($E25=1,$L25&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE25&amp;"; "&amp;$C25&amp;" assente ("&amp;$D25&amp;")",$L25&amp;" recupera il turno saltato nella settimana "&amp;$AE25&amp;"; "&amp;$C25&amp;" a riposo compensativo"),IF($E25=1,$C25&amp;" assente ("&amp;$D25&amp;")"&amp;IF($S25="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S25&amp;" con doppio turno")&amp;IF($F25=1,"; turno da recuperare a partire dalla settimana "&amp;($A25+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>IF($M25=1,"recupera il turno saltato nella settimana "&amp;($A25-1)&amp;", "&amp;$C25&amp;" a riposo",IF($E25=1,IF($S25="DA ASSEGNARE","turno da assegnare: "&amp;$C25&amp;" assente","in sostituzione di "&amp;$C25&amp;", doppio turno"),""))</f>
+        <f>IF($M25=1,IF($E25=1,"recupero del turno saltato nella settimana "&amp;$AE25&amp;", "&amp;$C25&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE25&amp;", "&amp;$C25&amp;" a riposo"),IF($E25=1,IF($S25="DA ASSEGNARE","turno da assegnare: "&amp;$C25&amp;" assente","in sostituzione di "&amp;$C25&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z25">
+        <f>IF($T25="","",COUNTIF($T$6:$T25,$T25))</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>IF($T25="","",$T25&amp;"#"&amp;$Z25)</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>COUNTIF($T$6:$T20,$C25)</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>COUNTIFS($C$6:$C20,$C25,$M$6:$M20,1)</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>IF($AB25&gt;$AC25,IFERROR(MATCH($C25&amp;"#"&amp;($AC25+1),$AA$6:$AA20,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>IF($AD25=0,"",INDEX($A$6:$A20,$AD25))</f>
         <v/>
       </c>
     </row>
@@ -9706,7 +10204,7 @@
         <v/>
       </c>
       <c r="F26">
-        <f>IF($E26=0,0,IF(OR($D26="Licenza - settimana intera",$D26="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M26=1,0,IF($E26=0,0,IF(OR($D26="Licenza - settimana intera",$D26="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G26">
@@ -9730,7 +10228,7 @@
         <v/>
       </c>
       <c r="L26">
-        <f>IFERROR(INDEX($C21:$C25,MATCH(1,INDEX(($T21:$T25=$C26)*1,0),0)),"")</f>
+        <f>IF($AD26=0,"",INDEX($C$6:$C25,$AD26))</f>
         <v/>
       </c>
       <c r="M26">
@@ -9738,23 +10236,23 @@
         <v/>
       </c>
       <c r="N26">
-        <f>IF($G26=0,100000,IF(Partecipanti!$B$5=$C26,100000,COUNTIF($S$6:$S25,Partecipanti!$B$5)*100+MOD(1-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G26=0,100000,IF(Partecipanti!$B$5=$C26,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S25,Partecipanti!$B$5)*100+MOD(1-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O26">
-        <f>IF($H26=0,100000,IF(Partecipanti!$B$6=$C26,100000,COUNTIF($S$6:$S25,Partecipanti!$B$6)*100+MOD(2-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H26=0,100000,IF(Partecipanti!$B$6=$C26,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S25,Partecipanti!$B$6)*100+MOD(2-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P26">
-        <f>IF($I26=0,100000,IF(Partecipanti!$B$7=$C26,100000,COUNTIF($S$6:$S25,Partecipanti!$B$7)*100+MOD(3-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I26=0,100000,IF(Partecipanti!$B$7=$C26,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S25,Partecipanti!$B$7)*100+MOD(3-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q26">
-        <f>IF($J26=0,100000,IF(Partecipanti!$B$8=$C26,100000,COUNTIF($S$6:$S25,Partecipanti!$B$8)*100+MOD(4-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J26=0,100000,IF(Partecipanti!$B$8=$C26,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S25,Partecipanti!$B$8)*100+MOD(4-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R26">
-        <f>IF($K26=0,100000,IF(Partecipanti!$B$9=$C26,100000,COUNTIF($S$6:$S25,Partecipanti!$B$9)*100+MOD(5-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K26=0,100000,IF(Partecipanti!$B$9=$C26,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S25,Partecipanti!$B$9)*100+MOD(5-MATCH($C26,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S26">
@@ -9778,11 +10276,35 @@
         <v/>
       </c>
       <c r="X26">
-        <f>IF($M26=1,$L26&amp;" recupera il turno saltato nella settimana "&amp;($A26-1)&amp;"; "&amp;$C26&amp;" a riposo compensativo",IF($E26=1,$C26&amp;" assente ("&amp;$D26&amp;")"&amp;IF($S26="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S26&amp;" con doppio turno")&amp;IF($F26=1,"; turno da recuperare nella settimana "&amp;($A26+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M26=1,IF($E26=1,$L26&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE26&amp;"; "&amp;$C26&amp;" assente ("&amp;$D26&amp;")",$L26&amp;" recupera il turno saltato nella settimana "&amp;$AE26&amp;"; "&amp;$C26&amp;" a riposo compensativo"),IF($E26=1,$C26&amp;" assente ("&amp;$D26&amp;")"&amp;IF($S26="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S26&amp;" con doppio turno")&amp;IF($F26=1,"; turno da recuperare a partire dalla settimana "&amp;($A26+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>IF($M26=1,"recupera il turno saltato nella settimana "&amp;($A26-1)&amp;", "&amp;$C26&amp;" a riposo",IF($E26=1,IF($S26="DA ASSEGNARE","turno da assegnare: "&amp;$C26&amp;" assente","in sostituzione di "&amp;$C26&amp;", doppio turno"),""))</f>
+        <f>IF($M26=1,IF($E26=1,"recupero del turno saltato nella settimana "&amp;$AE26&amp;", "&amp;$C26&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE26&amp;", "&amp;$C26&amp;" a riposo"),IF($E26=1,IF($S26="DA ASSEGNARE","turno da assegnare: "&amp;$C26&amp;" assente","in sostituzione di "&amp;$C26&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z26">
+        <f>IF($T26="","",COUNTIF($T$6:$T26,$T26))</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>IF($T26="","",$T26&amp;"#"&amp;$Z26)</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>COUNTIF($T$6:$T25,$C26)</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>COUNTIFS($C$6:$C25,$C26,$M$6:$M25,1)</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>IF($AB26&gt;$AC26,IFERROR(MATCH($C26&amp;"#"&amp;($AC26+1),$AA$6:$AA25,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>IF($AD26=0,"",INDEX($A$6:$A25,$AD26))</f>
         <v/>
       </c>
     </row>
@@ -9806,7 +10328,7 @@
         <v/>
       </c>
       <c r="F27">
-        <f>IF($E27=0,0,IF(OR($D27="Licenza - settimana intera",$D27="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M27=1,0,IF($E27=0,0,IF(OR($D27="Licenza - settimana intera",$D27="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G27">
@@ -9830,7 +10352,7 @@
         <v/>
       </c>
       <c r="L27">
-        <f>IFERROR(INDEX($C21:$C25,MATCH(1,INDEX(($T21:$T25=$C27)*1,0),0)),"")</f>
+        <f>IF($AD27=0,"",INDEX($C$6:$C25,$AD27))</f>
         <v/>
       </c>
       <c r="M27">
@@ -9838,23 +10360,23 @@
         <v/>
       </c>
       <c r="N27">
-        <f>IF($G27=0,100000,IF(Partecipanti!$B$5=$C27,100000,COUNTIF($S$6:$S26,Partecipanti!$B$5)*100+MOD(1-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G27=0,100000,IF(Partecipanti!$B$5=$C27,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S26,Partecipanti!$B$5)*100+MOD(1-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O27">
-        <f>IF($H27=0,100000,IF(Partecipanti!$B$6=$C27,100000,COUNTIF($S$6:$S26,Partecipanti!$B$6)*100+MOD(2-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H27=0,100000,IF(Partecipanti!$B$6=$C27,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S26,Partecipanti!$B$6)*100+MOD(2-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P27">
-        <f>IF($I27=0,100000,IF(Partecipanti!$B$7=$C27,100000,COUNTIF($S$6:$S26,Partecipanti!$B$7)*100+MOD(3-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I27=0,100000,IF(Partecipanti!$B$7=$C27,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S26,Partecipanti!$B$7)*100+MOD(3-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q27">
-        <f>IF($J27=0,100000,IF(Partecipanti!$B$8=$C27,100000,COUNTIF($S$6:$S26,Partecipanti!$B$8)*100+MOD(4-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J27=0,100000,IF(Partecipanti!$B$8=$C27,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S26,Partecipanti!$B$8)*100+MOD(4-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R27">
-        <f>IF($K27=0,100000,IF(Partecipanti!$B$9=$C27,100000,COUNTIF($S$6:$S26,Partecipanti!$B$9)*100+MOD(5-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K27=0,100000,IF(Partecipanti!$B$9=$C27,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S26,Partecipanti!$B$9)*100+MOD(5-MATCH($C27,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S27">
@@ -9878,11 +10400,35 @@
         <v/>
       </c>
       <c r="X27">
-        <f>IF($M27=1,$L27&amp;" recupera il turno saltato nella settimana "&amp;($A27-1)&amp;"; "&amp;$C27&amp;" a riposo compensativo",IF($E27=1,$C27&amp;" assente ("&amp;$D27&amp;")"&amp;IF($S27="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S27&amp;" con doppio turno")&amp;IF($F27=1,"; turno da recuperare nella settimana "&amp;($A27+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M27=1,IF($E27=1,$L27&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE27&amp;"; "&amp;$C27&amp;" assente ("&amp;$D27&amp;")",$L27&amp;" recupera il turno saltato nella settimana "&amp;$AE27&amp;"; "&amp;$C27&amp;" a riposo compensativo"),IF($E27=1,$C27&amp;" assente ("&amp;$D27&amp;")"&amp;IF($S27="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S27&amp;" con doppio turno")&amp;IF($F27=1,"; turno da recuperare a partire dalla settimana "&amp;($A27+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>IF($M27=1,"recupera il turno saltato nella settimana "&amp;($A27-1)&amp;", "&amp;$C27&amp;" a riposo",IF($E27=1,IF($S27="DA ASSEGNARE","turno da assegnare: "&amp;$C27&amp;" assente","in sostituzione di "&amp;$C27&amp;", doppio turno"),""))</f>
+        <f>IF($M27=1,IF($E27=1,"recupero del turno saltato nella settimana "&amp;$AE27&amp;", "&amp;$C27&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE27&amp;", "&amp;$C27&amp;" a riposo"),IF($E27=1,IF($S27="DA ASSEGNARE","turno da assegnare: "&amp;$C27&amp;" assente","in sostituzione di "&amp;$C27&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z27">
+        <f>IF($T27="","",COUNTIF($T$6:$T27,$T27))</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>IF($T27="","",$T27&amp;"#"&amp;$Z27)</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>COUNTIF($T$6:$T25,$C27)</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>COUNTIFS($C$6:$C25,$C27,$M$6:$M25,1)</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>IF($AB27&gt;$AC27,IFERROR(MATCH($C27&amp;"#"&amp;($AC27+1),$AA$6:$AA25,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>IF($AD27=0,"",INDEX($A$6:$A25,$AD27))</f>
         <v/>
       </c>
     </row>
@@ -9906,7 +10452,7 @@
         <v/>
       </c>
       <c r="F28">
-        <f>IF($E28=0,0,IF(OR($D28="Licenza - settimana intera",$D28="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M28=1,0,IF($E28=0,0,IF(OR($D28="Licenza - settimana intera",$D28="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G28">
@@ -9930,7 +10476,7 @@
         <v/>
       </c>
       <c r="L28">
-        <f>IFERROR(INDEX($C21:$C25,MATCH(1,INDEX(($T21:$T25=$C28)*1,0),0)),"")</f>
+        <f>IF($AD28=0,"",INDEX($C$6:$C25,$AD28))</f>
         <v/>
       </c>
       <c r="M28">
@@ -9938,23 +10484,23 @@
         <v/>
       </c>
       <c r="N28">
-        <f>IF($G28=0,100000,IF(Partecipanti!$B$5=$C28,100000,COUNTIF($S$6:$S27,Partecipanti!$B$5)*100+MOD(1-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G28=0,100000,IF(Partecipanti!$B$5=$C28,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S27,Partecipanti!$B$5)*100+MOD(1-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O28">
-        <f>IF($H28=0,100000,IF(Partecipanti!$B$6=$C28,100000,COUNTIF($S$6:$S27,Partecipanti!$B$6)*100+MOD(2-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H28=0,100000,IF(Partecipanti!$B$6=$C28,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S27,Partecipanti!$B$6)*100+MOD(2-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P28">
-        <f>IF($I28=0,100000,IF(Partecipanti!$B$7=$C28,100000,COUNTIF($S$6:$S27,Partecipanti!$B$7)*100+MOD(3-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I28=0,100000,IF(Partecipanti!$B$7=$C28,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S27,Partecipanti!$B$7)*100+MOD(3-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q28">
-        <f>IF($J28=0,100000,IF(Partecipanti!$B$8=$C28,100000,COUNTIF($S$6:$S27,Partecipanti!$B$8)*100+MOD(4-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J28=0,100000,IF(Partecipanti!$B$8=$C28,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S27,Partecipanti!$B$8)*100+MOD(4-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R28">
-        <f>IF($K28=0,100000,IF(Partecipanti!$B$9=$C28,100000,COUNTIF($S$6:$S27,Partecipanti!$B$9)*100+MOD(5-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K28=0,100000,IF(Partecipanti!$B$9=$C28,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S27,Partecipanti!$B$9)*100+MOD(5-MATCH($C28,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S28">
@@ -9978,11 +10524,35 @@
         <v/>
       </c>
       <c r="X28">
-        <f>IF($M28=1,$L28&amp;" recupera il turno saltato nella settimana "&amp;($A28-1)&amp;"; "&amp;$C28&amp;" a riposo compensativo",IF($E28=1,$C28&amp;" assente ("&amp;$D28&amp;")"&amp;IF($S28="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S28&amp;" con doppio turno")&amp;IF($F28=1,"; turno da recuperare nella settimana "&amp;($A28+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M28=1,IF($E28=1,$L28&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE28&amp;"; "&amp;$C28&amp;" assente ("&amp;$D28&amp;")",$L28&amp;" recupera il turno saltato nella settimana "&amp;$AE28&amp;"; "&amp;$C28&amp;" a riposo compensativo"),IF($E28=1,$C28&amp;" assente ("&amp;$D28&amp;")"&amp;IF($S28="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S28&amp;" con doppio turno")&amp;IF($F28=1,"; turno da recuperare a partire dalla settimana "&amp;($A28+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>IF($M28=1,"recupera il turno saltato nella settimana "&amp;($A28-1)&amp;", "&amp;$C28&amp;" a riposo",IF($E28=1,IF($S28="DA ASSEGNARE","turno da assegnare: "&amp;$C28&amp;" assente","in sostituzione di "&amp;$C28&amp;", doppio turno"),""))</f>
+        <f>IF($M28=1,IF($E28=1,"recupero del turno saltato nella settimana "&amp;$AE28&amp;", "&amp;$C28&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE28&amp;", "&amp;$C28&amp;" a riposo"),IF($E28=1,IF($S28="DA ASSEGNARE","turno da assegnare: "&amp;$C28&amp;" assente","in sostituzione di "&amp;$C28&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z28">
+        <f>IF($T28="","",COUNTIF($T$6:$T28,$T28))</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>IF($T28="","",$T28&amp;"#"&amp;$Z28)</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>COUNTIF($T$6:$T25,$C28)</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>COUNTIFS($C$6:$C25,$C28,$M$6:$M25,1)</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>IF($AB28&gt;$AC28,IFERROR(MATCH($C28&amp;"#"&amp;($AC28+1),$AA$6:$AA25,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>IF($AD28=0,"",INDEX($A$6:$A25,$AD28))</f>
         <v/>
       </c>
     </row>
@@ -10006,7 +10576,7 @@
         <v/>
       </c>
       <c r="F29">
-        <f>IF($E29=0,0,IF(OR($D29="Licenza - settimana intera",$D29="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M29=1,0,IF($E29=0,0,IF(OR($D29="Licenza - settimana intera",$D29="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G29">
@@ -10030,7 +10600,7 @@
         <v/>
       </c>
       <c r="L29">
-        <f>IFERROR(INDEX($C21:$C25,MATCH(1,INDEX(($T21:$T25=$C29)*1,0),0)),"")</f>
+        <f>IF($AD29=0,"",INDEX($C$6:$C25,$AD29))</f>
         <v/>
       </c>
       <c r="M29">
@@ -10038,23 +10608,23 @@
         <v/>
       </c>
       <c r="N29">
-        <f>IF($G29=0,100000,IF(Partecipanti!$B$5=$C29,100000,COUNTIF($S$6:$S28,Partecipanti!$B$5)*100+MOD(1-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G29=0,100000,IF(Partecipanti!$B$5=$C29,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S28,Partecipanti!$B$5)*100+MOD(1-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O29">
-        <f>IF($H29=0,100000,IF(Partecipanti!$B$6=$C29,100000,COUNTIF($S$6:$S28,Partecipanti!$B$6)*100+MOD(2-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H29=0,100000,IF(Partecipanti!$B$6=$C29,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S28,Partecipanti!$B$6)*100+MOD(2-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P29">
-        <f>IF($I29=0,100000,IF(Partecipanti!$B$7=$C29,100000,COUNTIF($S$6:$S28,Partecipanti!$B$7)*100+MOD(3-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I29=0,100000,IF(Partecipanti!$B$7=$C29,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S28,Partecipanti!$B$7)*100+MOD(3-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q29">
-        <f>IF($J29=0,100000,IF(Partecipanti!$B$8=$C29,100000,COUNTIF($S$6:$S28,Partecipanti!$B$8)*100+MOD(4-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J29=0,100000,IF(Partecipanti!$B$8=$C29,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S28,Partecipanti!$B$8)*100+MOD(4-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R29">
-        <f>IF($K29=0,100000,IF(Partecipanti!$B$9=$C29,100000,COUNTIF($S$6:$S28,Partecipanti!$B$9)*100+MOD(5-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K29=0,100000,IF(Partecipanti!$B$9=$C29,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S28,Partecipanti!$B$9)*100+MOD(5-MATCH($C29,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S29">
@@ -10078,11 +10648,35 @@
         <v/>
       </c>
       <c r="X29">
-        <f>IF($M29=1,$L29&amp;" recupera il turno saltato nella settimana "&amp;($A29-1)&amp;"; "&amp;$C29&amp;" a riposo compensativo",IF($E29=1,$C29&amp;" assente ("&amp;$D29&amp;")"&amp;IF($S29="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S29&amp;" con doppio turno")&amp;IF($F29=1,"; turno da recuperare nella settimana "&amp;($A29+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M29=1,IF($E29=1,$L29&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE29&amp;"; "&amp;$C29&amp;" assente ("&amp;$D29&amp;")",$L29&amp;" recupera il turno saltato nella settimana "&amp;$AE29&amp;"; "&amp;$C29&amp;" a riposo compensativo"),IF($E29=1,$C29&amp;" assente ("&amp;$D29&amp;")"&amp;IF($S29="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S29&amp;" con doppio turno")&amp;IF($F29=1,"; turno da recuperare a partire dalla settimana "&amp;($A29+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>IF($M29=1,"recupera il turno saltato nella settimana "&amp;($A29-1)&amp;", "&amp;$C29&amp;" a riposo",IF($E29=1,IF($S29="DA ASSEGNARE","turno da assegnare: "&amp;$C29&amp;" assente","in sostituzione di "&amp;$C29&amp;", doppio turno"),""))</f>
+        <f>IF($M29=1,IF($E29=1,"recupero del turno saltato nella settimana "&amp;$AE29&amp;", "&amp;$C29&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE29&amp;", "&amp;$C29&amp;" a riposo"),IF($E29=1,IF($S29="DA ASSEGNARE","turno da assegnare: "&amp;$C29&amp;" assente","in sostituzione di "&amp;$C29&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z29">
+        <f>IF($T29="","",COUNTIF($T$6:$T29,$T29))</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>IF($T29="","",$T29&amp;"#"&amp;$Z29)</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>COUNTIF($T$6:$T25,$C29)</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>COUNTIFS($C$6:$C25,$C29,$M$6:$M25,1)</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>IF($AB29&gt;$AC29,IFERROR(MATCH($C29&amp;"#"&amp;($AC29+1),$AA$6:$AA25,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>IF($AD29=0,"",INDEX($A$6:$A25,$AD29))</f>
         <v/>
       </c>
     </row>
@@ -10106,7 +10700,7 @@
         <v/>
       </c>
       <c r="F30">
-        <f>IF($E30=0,0,IF(OR($D30="Licenza - settimana intera",$D30="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M30=1,0,IF($E30=0,0,IF(OR($D30="Licenza - settimana intera",$D30="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G30">
@@ -10130,7 +10724,7 @@
         <v/>
       </c>
       <c r="L30">
-        <f>IFERROR(INDEX($C21:$C25,MATCH(1,INDEX(($T21:$T25=$C30)*1,0),0)),"")</f>
+        <f>IF($AD30=0,"",INDEX($C$6:$C25,$AD30))</f>
         <v/>
       </c>
       <c r="M30">
@@ -10138,23 +10732,23 @@
         <v/>
       </c>
       <c r="N30">
-        <f>IF($G30=0,100000,IF(Partecipanti!$B$5=$C30,100000,COUNTIF($S$6:$S29,Partecipanti!$B$5)*100+MOD(1-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G30=0,100000,IF(Partecipanti!$B$5=$C30,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S29,Partecipanti!$B$5)*100+MOD(1-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O30">
-        <f>IF($H30=0,100000,IF(Partecipanti!$B$6=$C30,100000,COUNTIF($S$6:$S29,Partecipanti!$B$6)*100+MOD(2-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H30=0,100000,IF(Partecipanti!$B$6=$C30,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S29,Partecipanti!$B$6)*100+MOD(2-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P30">
-        <f>IF($I30=0,100000,IF(Partecipanti!$B$7=$C30,100000,COUNTIF($S$6:$S29,Partecipanti!$B$7)*100+MOD(3-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I30=0,100000,IF(Partecipanti!$B$7=$C30,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S29,Partecipanti!$B$7)*100+MOD(3-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q30">
-        <f>IF($J30=0,100000,IF(Partecipanti!$B$8=$C30,100000,COUNTIF($S$6:$S29,Partecipanti!$B$8)*100+MOD(4-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J30=0,100000,IF(Partecipanti!$B$8=$C30,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S29,Partecipanti!$B$8)*100+MOD(4-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R30">
-        <f>IF($K30=0,100000,IF(Partecipanti!$B$9=$C30,100000,COUNTIF($S$6:$S29,Partecipanti!$B$9)*100+MOD(5-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K30=0,100000,IF(Partecipanti!$B$9=$C30,100000,IF(SUMPRODUCT(($M$26:$M$30=1)*($L$26:$L$30=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S29,Partecipanti!$B$9)*100+MOD(5-MATCH($C30,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S30">
@@ -10178,11 +10772,35 @@
         <v/>
       </c>
       <c r="X30">
-        <f>IF($M30=1,$L30&amp;" recupera il turno saltato nella settimana "&amp;($A30-1)&amp;"; "&amp;$C30&amp;" a riposo compensativo",IF($E30=1,$C30&amp;" assente ("&amp;$D30&amp;")"&amp;IF($S30="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S30&amp;" con doppio turno")&amp;IF($F30=1,"; turno da recuperare nella settimana "&amp;($A30+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M30=1,IF($E30=1,$L30&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE30&amp;"; "&amp;$C30&amp;" assente ("&amp;$D30&amp;")",$L30&amp;" recupera il turno saltato nella settimana "&amp;$AE30&amp;"; "&amp;$C30&amp;" a riposo compensativo"),IF($E30=1,$C30&amp;" assente ("&amp;$D30&amp;")"&amp;IF($S30="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S30&amp;" con doppio turno")&amp;IF($F30=1,"; turno da recuperare a partire dalla settimana "&amp;($A30+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>IF($M30=1,"recupera il turno saltato nella settimana "&amp;($A30-1)&amp;", "&amp;$C30&amp;" a riposo",IF($E30=1,IF($S30="DA ASSEGNARE","turno da assegnare: "&amp;$C30&amp;" assente","in sostituzione di "&amp;$C30&amp;", doppio turno"),""))</f>
+        <f>IF($M30=1,IF($E30=1,"recupero del turno saltato nella settimana "&amp;$AE30&amp;", "&amp;$C30&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE30&amp;", "&amp;$C30&amp;" a riposo"),IF($E30=1,IF($S30="DA ASSEGNARE","turno da assegnare: "&amp;$C30&amp;" assente","in sostituzione di "&amp;$C30&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z30">
+        <f>IF($T30="","",COUNTIF($T$6:$T30,$T30))</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>IF($T30="","",$T30&amp;"#"&amp;$Z30)</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>COUNTIF($T$6:$T25,$C30)</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>COUNTIFS($C$6:$C25,$C30,$M$6:$M25,1)</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>IF($AB30&gt;$AC30,IFERROR(MATCH($C30&amp;"#"&amp;($AC30+1),$AA$6:$AA25,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>IF($AD30=0,"",INDEX($A$6:$A25,$AD30))</f>
         <v/>
       </c>
     </row>
@@ -10206,7 +10824,7 @@
         <v/>
       </c>
       <c r="F31">
-        <f>IF($E31=0,0,IF(OR($D31="Licenza - settimana intera",$D31="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M31=1,0,IF($E31=0,0,IF(OR($D31="Licenza - settimana intera",$D31="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G31">
@@ -10230,7 +10848,7 @@
         <v/>
       </c>
       <c r="L31">
-        <f>IFERROR(INDEX($C26:$C30,MATCH(1,INDEX(($T26:$T30=$C31)*1,0),0)),"")</f>
+        <f>IF($AD31=0,"",INDEX($C$6:$C30,$AD31))</f>
         <v/>
       </c>
       <c r="M31">
@@ -10238,23 +10856,23 @@
         <v/>
       </c>
       <c r="N31">
-        <f>IF($G31=0,100000,IF(Partecipanti!$B$5=$C31,100000,COUNTIF($S$6:$S30,Partecipanti!$B$5)*100+MOD(1-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G31=0,100000,IF(Partecipanti!$B$5=$C31,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S30,Partecipanti!$B$5)*100+MOD(1-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O31">
-        <f>IF($H31=0,100000,IF(Partecipanti!$B$6=$C31,100000,COUNTIF($S$6:$S30,Partecipanti!$B$6)*100+MOD(2-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H31=0,100000,IF(Partecipanti!$B$6=$C31,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S30,Partecipanti!$B$6)*100+MOD(2-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P31">
-        <f>IF($I31=0,100000,IF(Partecipanti!$B$7=$C31,100000,COUNTIF($S$6:$S30,Partecipanti!$B$7)*100+MOD(3-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I31=0,100000,IF(Partecipanti!$B$7=$C31,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S30,Partecipanti!$B$7)*100+MOD(3-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q31">
-        <f>IF($J31=0,100000,IF(Partecipanti!$B$8=$C31,100000,COUNTIF($S$6:$S30,Partecipanti!$B$8)*100+MOD(4-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J31=0,100000,IF(Partecipanti!$B$8=$C31,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S30,Partecipanti!$B$8)*100+MOD(4-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R31">
-        <f>IF($K31=0,100000,IF(Partecipanti!$B$9=$C31,100000,COUNTIF($S$6:$S30,Partecipanti!$B$9)*100+MOD(5-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K31=0,100000,IF(Partecipanti!$B$9=$C31,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S30,Partecipanti!$B$9)*100+MOD(5-MATCH($C31,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S31">
@@ -10278,11 +10896,35 @@
         <v/>
       </c>
       <c r="X31">
-        <f>IF($M31=1,$L31&amp;" recupera il turno saltato nella settimana "&amp;($A31-1)&amp;"; "&amp;$C31&amp;" a riposo compensativo",IF($E31=1,$C31&amp;" assente ("&amp;$D31&amp;")"&amp;IF($S31="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S31&amp;" con doppio turno")&amp;IF($F31=1,"; turno da recuperare nella settimana "&amp;($A31+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M31=1,IF($E31=1,$L31&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE31&amp;"; "&amp;$C31&amp;" assente ("&amp;$D31&amp;")",$L31&amp;" recupera il turno saltato nella settimana "&amp;$AE31&amp;"; "&amp;$C31&amp;" a riposo compensativo"),IF($E31=1,$C31&amp;" assente ("&amp;$D31&amp;")"&amp;IF($S31="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S31&amp;" con doppio turno")&amp;IF($F31=1,"; turno da recuperare a partire dalla settimana "&amp;($A31+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>IF($M31=1,"recupera il turno saltato nella settimana "&amp;($A31-1)&amp;", "&amp;$C31&amp;" a riposo",IF($E31=1,IF($S31="DA ASSEGNARE","turno da assegnare: "&amp;$C31&amp;" assente","in sostituzione di "&amp;$C31&amp;", doppio turno"),""))</f>
+        <f>IF($M31=1,IF($E31=1,"recupero del turno saltato nella settimana "&amp;$AE31&amp;", "&amp;$C31&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE31&amp;", "&amp;$C31&amp;" a riposo"),IF($E31=1,IF($S31="DA ASSEGNARE","turno da assegnare: "&amp;$C31&amp;" assente","in sostituzione di "&amp;$C31&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z31">
+        <f>IF($T31="","",COUNTIF($T$6:$T31,$T31))</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>IF($T31="","",$T31&amp;"#"&amp;$Z31)</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>COUNTIF($T$6:$T30,$C31)</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>COUNTIFS($C$6:$C30,$C31,$M$6:$M30,1)</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>IF($AB31&gt;$AC31,IFERROR(MATCH($C31&amp;"#"&amp;($AC31+1),$AA$6:$AA30,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>IF($AD31=0,"",INDEX($A$6:$A30,$AD31))</f>
         <v/>
       </c>
     </row>
@@ -10306,7 +10948,7 @@
         <v/>
       </c>
       <c r="F32">
-        <f>IF($E32=0,0,IF(OR($D32="Licenza - settimana intera",$D32="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M32=1,0,IF($E32=0,0,IF(OR($D32="Licenza - settimana intera",$D32="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G32">
@@ -10330,7 +10972,7 @@
         <v/>
       </c>
       <c r="L32">
-        <f>IFERROR(INDEX($C26:$C30,MATCH(1,INDEX(($T26:$T30=$C32)*1,0),0)),"")</f>
+        <f>IF($AD32=0,"",INDEX($C$6:$C30,$AD32))</f>
         <v/>
       </c>
       <c r="M32">
@@ -10338,23 +10980,23 @@
         <v/>
       </c>
       <c r="N32">
-        <f>IF($G32=0,100000,IF(Partecipanti!$B$5=$C32,100000,COUNTIF($S$6:$S31,Partecipanti!$B$5)*100+MOD(1-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G32=0,100000,IF(Partecipanti!$B$5=$C32,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S31,Partecipanti!$B$5)*100+MOD(1-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O32">
-        <f>IF($H32=0,100000,IF(Partecipanti!$B$6=$C32,100000,COUNTIF($S$6:$S31,Partecipanti!$B$6)*100+MOD(2-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H32=0,100000,IF(Partecipanti!$B$6=$C32,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S31,Partecipanti!$B$6)*100+MOD(2-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P32">
-        <f>IF($I32=0,100000,IF(Partecipanti!$B$7=$C32,100000,COUNTIF($S$6:$S31,Partecipanti!$B$7)*100+MOD(3-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I32=0,100000,IF(Partecipanti!$B$7=$C32,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S31,Partecipanti!$B$7)*100+MOD(3-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q32">
-        <f>IF($J32=0,100000,IF(Partecipanti!$B$8=$C32,100000,COUNTIF($S$6:$S31,Partecipanti!$B$8)*100+MOD(4-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J32=0,100000,IF(Partecipanti!$B$8=$C32,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S31,Partecipanti!$B$8)*100+MOD(4-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R32">
-        <f>IF($K32=0,100000,IF(Partecipanti!$B$9=$C32,100000,COUNTIF($S$6:$S31,Partecipanti!$B$9)*100+MOD(5-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K32=0,100000,IF(Partecipanti!$B$9=$C32,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S31,Partecipanti!$B$9)*100+MOD(5-MATCH($C32,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S32">
@@ -10378,11 +11020,35 @@
         <v/>
       </c>
       <c r="X32">
-        <f>IF($M32=1,$L32&amp;" recupera il turno saltato nella settimana "&amp;($A32-1)&amp;"; "&amp;$C32&amp;" a riposo compensativo",IF($E32=1,$C32&amp;" assente ("&amp;$D32&amp;")"&amp;IF($S32="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S32&amp;" con doppio turno")&amp;IF($F32=1,"; turno da recuperare nella settimana "&amp;($A32+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M32=1,IF($E32=1,$L32&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE32&amp;"; "&amp;$C32&amp;" assente ("&amp;$D32&amp;")",$L32&amp;" recupera il turno saltato nella settimana "&amp;$AE32&amp;"; "&amp;$C32&amp;" a riposo compensativo"),IF($E32=1,$C32&amp;" assente ("&amp;$D32&amp;")"&amp;IF($S32="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S32&amp;" con doppio turno")&amp;IF($F32=1,"; turno da recuperare a partire dalla settimana "&amp;($A32+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>IF($M32=1,"recupera il turno saltato nella settimana "&amp;($A32-1)&amp;", "&amp;$C32&amp;" a riposo",IF($E32=1,IF($S32="DA ASSEGNARE","turno da assegnare: "&amp;$C32&amp;" assente","in sostituzione di "&amp;$C32&amp;", doppio turno"),""))</f>
+        <f>IF($M32=1,IF($E32=1,"recupero del turno saltato nella settimana "&amp;$AE32&amp;", "&amp;$C32&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE32&amp;", "&amp;$C32&amp;" a riposo"),IF($E32=1,IF($S32="DA ASSEGNARE","turno da assegnare: "&amp;$C32&amp;" assente","in sostituzione di "&amp;$C32&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z32">
+        <f>IF($T32="","",COUNTIF($T$6:$T32,$T32))</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>IF($T32="","",$T32&amp;"#"&amp;$Z32)</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>COUNTIF($T$6:$T30,$C32)</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>COUNTIFS($C$6:$C30,$C32,$M$6:$M30,1)</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>IF($AB32&gt;$AC32,IFERROR(MATCH($C32&amp;"#"&amp;($AC32+1),$AA$6:$AA30,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>IF($AD32=0,"",INDEX($A$6:$A30,$AD32))</f>
         <v/>
       </c>
     </row>
@@ -10406,7 +11072,7 @@
         <v/>
       </c>
       <c r="F33">
-        <f>IF($E33=0,0,IF(OR($D33="Licenza - settimana intera",$D33="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M33=1,0,IF($E33=0,0,IF(OR($D33="Licenza - settimana intera",$D33="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G33">
@@ -10430,7 +11096,7 @@
         <v/>
       </c>
       <c r="L33">
-        <f>IFERROR(INDEX($C26:$C30,MATCH(1,INDEX(($T26:$T30=$C33)*1,0),0)),"")</f>
+        <f>IF($AD33=0,"",INDEX($C$6:$C30,$AD33))</f>
         <v/>
       </c>
       <c r="M33">
@@ -10438,23 +11104,23 @@
         <v/>
       </c>
       <c r="N33">
-        <f>IF($G33=0,100000,IF(Partecipanti!$B$5=$C33,100000,COUNTIF($S$6:$S32,Partecipanti!$B$5)*100+MOD(1-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G33=0,100000,IF(Partecipanti!$B$5=$C33,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S32,Partecipanti!$B$5)*100+MOD(1-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O33">
-        <f>IF($H33=0,100000,IF(Partecipanti!$B$6=$C33,100000,COUNTIF($S$6:$S32,Partecipanti!$B$6)*100+MOD(2-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H33=0,100000,IF(Partecipanti!$B$6=$C33,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S32,Partecipanti!$B$6)*100+MOD(2-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P33">
-        <f>IF($I33=0,100000,IF(Partecipanti!$B$7=$C33,100000,COUNTIF($S$6:$S32,Partecipanti!$B$7)*100+MOD(3-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I33=0,100000,IF(Partecipanti!$B$7=$C33,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S32,Partecipanti!$B$7)*100+MOD(3-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q33">
-        <f>IF($J33=0,100000,IF(Partecipanti!$B$8=$C33,100000,COUNTIF($S$6:$S32,Partecipanti!$B$8)*100+MOD(4-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J33=0,100000,IF(Partecipanti!$B$8=$C33,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S32,Partecipanti!$B$8)*100+MOD(4-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R33">
-        <f>IF($K33=0,100000,IF(Partecipanti!$B$9=$C33,100000,COUNTIF($S$6:$S32,Partecipanti!$B$9)*100+MOD(5-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K33=0,100000,IF(Partecipanti!$B$9=$C33,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S32,Partecipanti!$B$9)*100+MOD(5-MATCH($C33,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S33">
@@ -10478,11 +11144,35 @@
         <v/>
       </c>
       <c r="X33">
-        <f>IF($M33=1,$L33&amp;" recupera il turno saltato nella settimana "&amp;($A33-1)&amp;"; "&amp;$C33&amp;" a riposo compensativo",IF($E33=1,$C33&amp;" assente ("&amp;$D33&amp;")"&amp;IF($S33="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S33&amp;" con doppio turno")&amp;IF($F33=1,"; turno da recuperare nella settimana "&amp;($A33+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M33=1,IF($E33=1,$L33&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE33&amp;"; "&amp;$C33&amp;" assente ("&amp;$D33&amp;")",$L33&amp;" recupera il turno saltato nella settimana "&amp;$AE33&amp;"; "&amp;$C33&amp;" a riposo compensativo"),IF($E33=1,$C33&amp;" assente ("&amp;$D33&amp;")"&amp;IF($S33="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S33&amp;" con doppio turno")&amp;IF($F33=1,"; turno da recuperare a partire dalla settimana "&amp;($A33+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>IF($M33=1,"recupera il turno saltato nella settimana "&amp;($A33-1)&amp;", "&amp;$C33&amp;" a riposo",IF($E33=1,IF($S33="DA ASSEGNARE","turno da assegnare: "&amp;$C33&amp;" assente","in sostituzione di "&amp;$C33&amp;", doppio turno"),""))</f>
+        <f>IF($M33=1,IF($E33=1,"recupero del turno saltato nella settimana "&amp;$AE33&amp;", "&amp;$C33&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE33&amp;", "&amp;$C33&amp;" a riposo"),IF($E33=1,IF($S33="DA ASSEGNARE","turno da assegnare: "&amp;$C33&amp;" assente","in sostituzione di "&amp;$C33&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z33">
+        <f>IF($T33="","",COUNTIF($T$6:$T33,$T33))</f>
+        <v/>
+      </c>
+      <c r="AA33">
+        <f>IF($T33="","",$T33&amp;"#"&amp;$Z33)</f>
+        <v/>
+      </c>
+      <c r="AB33">
+        <f>COUNTIF($T$6:$T30,$C33)</f>
+        <v/>
+      </c>
+      <c r="AC33">
+        <f>COUNTIFS($C$6:$C30,$C33,$M$6:$M30,1)</f>
+        <v/>
+      </c>
+      <c r="AD33">
+        <f>IF($AB33&gt;$AC33,IFERROR(MATCH($C33&amp;"#"&amp;($AC33+1),$AA$6:$AA30,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>IF($AD33=0,"",INDEX($A$6:$A30,$AD33))</f>
         <v/>
       </c>
     </row>
@@ -10506,7 +11196,7 @@
         <v/>
       </c>
       <c r="F34">
-        <f>IF($E34=0,0,IF(OR($D34="Licenza - settimana intera",$D34="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M34=1,0,IF($E34=0,0,IF(OR($D34="Licenza - settimana intera",$D34="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G34">
@@ -10530,7 +11220,7 @@
         <v/>
       </c>
       <c r="L34">
-        <f>IFERROR(INDEX($C26:$C30,MATCH(1,INDEX(($T26:$T30=$C34)*1,0),0)),"")</f>
+        <f>IF($AD34=0,"",INDEX($C$6:$C30,$AD34))</f>
         <v/>
       </c>
       <c r="M34">
@@ -10538,23 +11228,23 @@
         <v/>
       </c>
       <c r="N34">
-        <f>IF($G34=0,100000,IF(Partecipanti!$B$5=$C34,100000,COUNTIF($S$6:$S33,Partecipanti!$B$5)*100+MOD(1-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G34=0,100000,IF(Partecipanti!$B$5=$C34,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S33,Partecipanti!$B$5)*100+MOD(1-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O34">
-        <f>IF($H34=0,100000,IF(Partecipanti!$B$6=$C34,100000,COUNTIF($S$6:$S33,Partecipanti!$B$6)*100+MOD(2-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H34=0,100000,IF(Partecipanti!$B$6=$C34,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S33,Partecipanti!$B$6)*100+MOD(2-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P34">
-        <f>IF($I34=0,100000,IF(Partecipanti!$B$7=$C34,100000,COUNTIF($S$6:$S33,Partecipanti!$B$7)*100+MOD(3-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I34=0,100000,IF(Partecipanti!$B$7=$C34,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S33,Partecipanti!$B$7)*100+MOD(3-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q34">
-        <f>IF($J34=0,100000,IF(Partecipanti!$B$8=$C34,100000,COUNTIF($S$6:$S33,Partecipanti!$B$8)*100+MOD(4-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J34=0,100000,IF(Partecipanti!$B$8=$C34,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S33,Partecipanti!$B$8)*100+MOD(4-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R34">
-        <f>IF($K34=0,100000,IF(Partecipanti!$B$9=$C34,100000,COUNTIF($S$6:$S33,Partecipanti!$B$9)*100+MOD(5-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K34=0,100000,IF(Partecipanti!$B$9=$C34,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S33,Partecipanti!$B$9)*100+MOD(5-MATCH($C34,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S34">
@@ -10578,11 +11268,35 @@
         <v/>
       </c>
       <c r="X34">
-        <f>IF($M34=1,$L34&amp;" recupera il turno saltato nella settimana "&amp;($A34-1)&amp;"; "&amp;$C34&amp;" a riposo compensativo",IF($E34=1,$C34&amp;" assente ("&amp;$D34&amp;")"&amp;IF($S34="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S34&amp;" con doppio turno")&amp;IF($F34=1,"; turno da recuperare nella settimana "&amp;($A34+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M34=1,IF($E34=1,$L34&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE34&amp;"; "&amp;$C34&amp;" assente ("&amp;$D34&amp;")",$L34&amp;" recupera il turno saltato nella settimana "&amp;$AE34&amp;"; "&amp;$C34&amp;" a riposo compensativo"),IF($E34=1,$C34&amp;" assente ("&amp;$D34&amp;")"&amp;IF($S34="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S34&amp;" con doppio turno")&amp;IF($F34=1,"; turno da recuperare a partire dalla settimana "&amp;($A34+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>IF($M34=1,"recupera il turno saltato nella settimana "&amp;($A34-1)&amp;", "&amp;$C34&amp;" a riposo",IF($E34=1,IF($S34="DA ASSEGNARE","turno da assegnare: "&amp;$C34&amp;" assente","in sostituzione di "&amp;$C34&amp;", doppio turno"),""))</f>
+        <f>IF($M34=1,IF($E34=1,"recupero del turno saltato nella settimana "&amp;$AE34&amp;", "&amp;$C34&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE34&amp;", "&amp;$C34&amp;" a riposo"),IF($E34=1,IF($S34="DA ASSEGNARE","turno da assegnare: "&amp;$C34&amp;" assente","in sostituzione di "&amp;$C34&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z34">
+        <f>IF($T34="","",COUNTIF($T$6:$T34,$T34))</f>
+        <v/>
+      </c>
+      <c r="AA34">
+        <f>IF($T34="","",$T34&amp;"#"&amp;$Z34)</f>
+        <v/>
+      </c>
+      <c r="AB34">
+        <f>COUNTIF($T$6:$T30,$C34)</f>
+        <v/>
+      </c>
+      <c r="AC34">
+        <f>COUNTIFS($C$6:$C30,$C34,$M$6:$M30,1)</f>
+        <v/>
+      </c>
+      <c r="AD34">
+        <f>IF($AB34&gt;$AC34,IFERROR(MATCH($C34&amp;"#"&amp;($AC34+1),$AA$6:$AA30,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>IF($AD34=0,"",INDEX($A$6:$A30,$AD34))</f>
         <v/>
       </c>
     </row>
@@ -10606,7 +11320,7 @@
         <v/>
       </c>
       <c r="F35">
-        <f>IF($E35=0,0,IF(OR($D35="Licenza - settimana intera",$D35="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M35=1,0,IF($E35=0,0,IF(OR($D35="Licenza - settimana intera",$D35="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G35">
@@ -10630,7 +11344,7 @@
         <v/>
       </c>
       <c r="L35">
-        <f>IFERROR(INDEX($C26:$C30,MATCH(1,INDEX(($T26:$T30=$C35)*1,0),0)),"")</f>
+        <f>IF($AD35=0,"",INDEX($C$6:$C30,$AD35))</f>
         <v/>
       </c>
       <c r="M35">
@@ -10638,23 +11352,23 @@
         <v/>
       </c>
       <c r="N35">
-        <f>IF($G35=0,100000,IF(Partecipanti!$B$5=$C35,100000,COUNTIF($S$6:$S34,Partecipanti!$B$5)*100+MOD(1-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G35=0,100000,IF(Partecipanti!$B$5=$C35,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S34,Partecipanti!$B$5)*100+MOD(1-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O35">
-        <f>IF($H35=0,100000,IF(Partecipanti!$B$6=$C35,100000,COUNTIF($S$6:$S34,Partecipanti!$B$6)*100+MOD(2-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H35=0,100000,IF(Partecipanti!$B$6=$C35,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S34,Partecipanti!$B$6)*100+MOD(2-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P35">
-        <f>IF($I35=0,100000,IF(Partecipanti!$B$7=$C35,100000,COUNTIF($S$6:$S34,Partecipanti!$B$7)*100+MOD(3-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I35=0,100000,IF(Partecipanti!$B$7=$C35,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S34,Partecipanti!$B$7)*100+MOD(3-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q35">
-        <f>IF($J35=0,100000,IF(Partecipanti!$B$8=$C35,100000,COUNTIF($S$6:$S34,Partecipanti!$B$8)*100+MOD(4-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J35=0,100000,IF(Partecipanti!$B$8=$C35,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S34,Partecipanti!$B$8)*100+MOD(4-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R35">
-        <f>IF($K35=0,100000,IF(Partecipanti!$B$9=$C35,100000,COUNTIF($S$6:$S34,Partecipanti!$B$9)*100+MOD(5-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K35=0,100000,IF(Partecipanti!$B$9=$C35,100000,IF(SUMPRODUCT(($M$31:$M$35=1)*($L$31:$L$35=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S34,Partecipanti!$B$9)*100+MOD(5-MATCH($C35,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S35">
@@ -10678,11 +11392,35 @@
         <v/>
       </c>
       <c r="X35">
-        <f>IF($M35=1,$L35&amp;" recupera il turno saltato nella settimana "&amp;($A35-1)&amp;"; "&amp;$C35&amp;" a riposo compensativo",IF($E35=1,$C35&amp;" assente ("&amp;$D35&amp;")"&amp;IF($S35="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S35&amp;" con doppio turno")&amp;IF($F35=1,"; turno da recuperare nella settimana "&amp;($A35+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M35=1,IF($E35=1,$L35&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE35&amp;"; "&amp;$C35&amp;" assente ("&amp;$D35&amp;")",$L35&amp;" recupera il turno saltato nella settimana "&amp;$AE35&amp;"; "&amp;$C35&amp;" a riposo compensativo"),IF($E35=1,$C35&amp;" assente ("&amp;$D35&amp;")"&amp;IF($S35="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S35&amp;" con doppio turno")&amp;IF($F35=1,"; turno da recuperare a partire dalla settimana "&amp;($A35+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>IF($M35=1,"recupera il turno saltato nella settimana "&amp;($A35-1)&amp;", "&amp;$C35&amp;" a riposo",IF($E35=1,IF($S35="DA ASSEGNARE","turno da assegnare: "&amp;$C35&amp;" assente","in sostituzione di "&amp;$C35&amp;", doppio turno"),""))</f>
+        <f>IF($M35=1,IF($E35=1,"recupero del turno saltato nella settimana "&amp;$AE35&amp;", "&amp;$C35&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE35&amp;", "&amp;$C35&amp;" a riposo"),IF($E35=1,IF($S35="DA ASSEGNARE","turno da assegnare: "&amp;$C35&amp;" assente","in sostituzione di "&amp;$C35&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z35">
+        <f>IF($T35="","",COUNTIF($T$6:$T35,$T35))</f>
+        <v/>
+      </c>
+      <c r="AA35">
+        <f>IF($T35="","",$T35&amp;"#"&amp;$Z35)</f>
+        <v/>
+      </c>
+      <c r="AB35">
+        <f>COUNTIF($T$6:$T30,$C35)</f>
+        <v/>
+      </c>
+      <c r="AC35">
+        <f>COUNTIFS($C$6:$C30,$C35,$M$6:$M30,1)</f>
+        <v/>
+      </c>
+      <c r="AD35">
+        <f>IF($AB35&gt;$AC35,IFERROR(MATCH($C35&amp;"#"&amp;($AC35+1),$AA$6:$AA30,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>IF($AD35=0,"",INDEX($A$6:$A30,$AD35))</f>
         <v/>
       </c>
     </row>
@@ -10706,7 +11444,7 @@
         <v/>
       </c>
       <c r="F36">
-        <f>IF($E36=0,0,IF(OR($D36="Licenza - settimana intera",$D36="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M36=1,0,IF($E36=0,0,IF(OR($D36="Licenza - settimana intera",$D36="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G36">
@@ -10730,7 +11468,7 @@
         <v/>
       </c>
       <c r="L36">
-        <f>IFERROR(INDEX($C31:$C35,MATCH(1,INDEX(($T31:$T35=$C36)*1,0),0)),"")</f>
+        <f>IF($AD36=0,"",INDEX($C$6:$C35,$AD36))</f>
         <v/>
       </c>
       <c r="M36">
@@ -10738,23 +11476,23 @@
         <v/>
       </c>
       <c r="N36">
-        <f>IF($G36=0,100000,IF(Partecipanti!$B$5=$C36,100000,COUNTIF($S$6:$S35,Partecipanti!$B$5)*100+MOD(1-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G36=0,100000,IF(Partecipanti!$B$5=$C36,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S35,Partecipanti!$B$5)*100+MOD(1-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O36">
-        <f>IF($H36=0,100000,IF(Partecipanti!$B$6=$C36,100000,COUNTIF($S$6:$S35,Partecipanti!$B$6)*100+MOD(2-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H36=0,100000,IF(Partecipanti!$B$6=$C36,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S35,Partecipanti!$B$6)*100+MOD(2-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P36">
-        <f>IF($I36=0,100000,IF(Partecipanti!$B$7=$C36,100000,COUNTIF($S$6:$S35,Partecipanti!$B$7)*100+MOD(3-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I36=0,100000,IF(Partecipanti!$B$7=$C36,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S35,Partecipanti!$B$7)*100+MOD(3-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q36">
-        <f>IF($J36=0,100000,IF(Partecipanti!$B$8=$C36,100000,COUNTIF($S$6:$S35,Partecipanti!$B$8)*100+MOD(4-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J36=0,100000,IF(Partecipanti!$B$8=$C36,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S35,Partecipanti!$B$8)*100+MOD(4-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R36">
-        <f>IF($K36=0,100000,IF(Partecipanti!$B$9=$C36,100000,COUNTIF($S$6:$S35,Partecipanti!$B$9)*100+MOD(5-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K36=0,100000,IF(Partecipanti!$B$9=$C36,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S35,Partecipanti!$B$9)*100+MOD(5-MATCH($C36,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S36">
@@ -10778,11 +11516,35 @@
         <v/>
       </c>
       <c r="X36">
-        <f>IF($M36=1,$L36&amp;" recupera il turno saltato nella settimana "&amp;($A36-1)&amp;"; "&amp;$C36&amp;" a riposo compensativo",IF($E36=1,$C36&amp;" assente ("&amp;$D36&amp;")"&amp;IF($S36="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S36&amp;" con doppio turno")&amp;IF($F36=1,"; turno da recuperare nella settimana "&amp;($A36+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M36=1,IF($E36=1,$L36&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE36&amp;"; "&amp;$C36&amp;" assente ("&amp;$D36&amp;")",$L36&amp;" recupera il turno saltato nella settimana "&amp;$AE36&amp;"; "&amp;$C36&amp;" a riposo compensativo"),IF($E36=1,$C36&amp;" assente ("&amp;$D36&amp;")"&amp;IF($S36="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S36&amp;" con doppio turno")&amp;IF($F36=1,"; turno da recuperare a partire dalla settimana "&amp;($A36+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>IF($M36=1,"recupera il turno saltato nella settimana "&amp;($A36-1)&amp;", "&amp;$C36&amp;" a riposo",IF($E36=1,IF($S36="DA ASSEGNARE","turno da assegnare: "&amp;$C36&amp;" assente","in sostituzione di "&amp;$C36&amp;", doppio turno"),""))</f>
+        <f>IF($M36=1,IF($E36=1,"recupero del turno saltato nella settimana "&amp;$AE36&amp;", "&amp;$C36&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE36&amp;", "&amp;$C36&amp;" a riposo"),IF($E36=1,IF($S36="DA ASSEGNARE","turno da assegnare: "&amp;$C36&amp;" assente","in sostituzione di "&amp;$C36&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z36">
+        <f>IF($T36="","",COUNTIF($T$6:$T36,$T36))</f>
+        <v/>
+      </c>
+      <c r="AA36">
+        <f>IF($T36="","",$T36&amp;"#"&amp;$Z36)</f>
+        <v/>
+      </c>
+      <c r="AB36">
+        <f>COUNTIF($T$6:$T35,$C36)</f>
+        <v/>
+      </c>
+      <c r="AC36">
+        <f>COUNTIFS($C$6:$C35,$C36,$M$6:$M35,1)</f>
+        <v/>
+      </c>
+      <c r="AD36">
+        <f>IF($AB36&gt;$AC36,IFERROR(MATCH($C36&amp;"#"&amp;($AC36+1),$AA$6:$AA35,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE36">
+        <f>IF($AD36=0,"",INDEX($A$6:$A35,$AD36))</f>
         <v/>
       </c>
     </row>
@@ -10806,7 +11568,7 @@
         <v/>
       </c>
       <c r="F37">
-        <f>IF($E37=0,0,IF(OR($D37="Licenza - settimana intera",$D37="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M37=1,0,IF($E37=0,0,IF(OR($D37="Licenza - settimana intera",$D37="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G37">
@@ -10830,7 +11592,7 @@
         <v/>
       </c>
       <c r="L37">
-        <f>IFERROR(INDEX($C31:$C35,MATCH(1,INDEX(($T31:$T35=$C37)*1,0),0)),"")</f>
+        <f>IF($AD37=0,"",INDEX($C$6:$C35,$AD37))</f>
         <v/>
       </c>
       <c r="M37">
@@ -10838,23 +11600,23 @@
         <v/>
       </c>
       <c r="N37">
-        <f>IF($G37=0,100000,IF(Partecipanti!$B$5=$C37,100000,COUNTIF($S$6:$S36,Partecipanti!$B$5)*100+MOD(1-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G37=0,100000,IF(Partecipanti!$B$5=$C37,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S36,Partecipanti!$B$5)*100+MOD(1-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O37">
-        <f>IF($H37=0,100000,IF(Partecipanti!$B$6=$C37,100000,COUNTIF($S$6:$S36,Partecipanti!$B$6)*100+MOD(2-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H37=0,100000,IF(Partecipanti!$B$6=$C37,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S36,Partecipanti!$B$6)*100+MOD(2-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P37">
-        <f>IF($I37=0,100000,IF(Partecipanti!$B$7=$C37,100000,COUNTIF($S$6:$S36,Partecipanti!$B$7)*100+MOD(3-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I37=0,100000,IF(Partecipanti!$B$7=$C37,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S36,Partecipanti!$B$7)*100+MOD(3-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q37">
-        <f>IF($J37=0,100000,IF(Partecipanti!$B$8=$C37,100000,COUNTIF($S$6:$S36,Partecipanti!$B$8)*100+MOD(4-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J37=0,100000,IF(Partecipanti!$B$8=$C37,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S36,Partecipanti!$B$8)*100+MOD(4-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R37">
-        <f>IF($K37=0,100000,IF(Partecipanti!$B$9=$C37,100000,COUNTIF($S$6:$S36,Partecipanti!$B$9)*100+MOD(5-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K37=0,100000,IF(Partecipanti!$B$9=$C37,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S36,Partecipanti!$B$9)*100+MOD(5-MATCH($C37,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S37">
@@ -10878,11 +11640,35 @@
         <v/>
       </c>
       <c r="X37">
-        <f>IF($M37=1,$L37&amp;" recupera il turno saltato nella settimana "&amp;($A37-1)&amp;"; "&amp;$C37&amp;" a riposo compensativo",IF($E37=1,$C37&amp;" assente ("&amp;$D37&amp;")"&amp;IF($S37="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S37&amp;" con doppio turno")&amp;IF($F37=1,"; turno da recuperare nella settimana "&amp;($A37+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M37=1,IF($E37=1,$L37&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE37&amp;"; "&amp;$C37&amp;" assente ("&amp;$D37&amp;")",$L37&amp;" recupera il turno saltato nella settimana "&amp;$AE37&amp;"; "&amp;$C37&amp;" a riposo compensativo"),IF($E37=1,$C37&amp;" assente ("&amp;$D37&amp;")"&amp;IF($S37="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S37&amp;" con doppio turno")&amp;IF($F37=1,"; turno da recuperare a partire dalla settimana "&amp;($A37+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>IF($M37=1,"recupera il turno saltato nella settimana "&amp;($A37-1)&amp;", "&amp;$C37&amp;" a riposo",IF($E37=1,IF($S37="DA ASSEGNARE","turno da assegnare: "&amp;$C37&amp;" assente","in sostituzione di "&amp;$C37&amp;", doppio turno"),""))</f>
+        <f>IF($M37=1,IF($E37=1,"recupero del turno saltato nella settimana "&amp;$AE37&amp;", "&amp;$C37&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE37&amp;", "&amp;$C37&amp;" a riposo"),IF($E37=1,IF($S37="DA ASSEGNARE","turno da assegnare: "&amp;$C37&amp;" assente","in sostituzione di "&amp;$C37&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z37">
+        <f>IF($T37="","",COUNTIF($T$6:$T37,$T37))</f>
+        <v/>
+      </c>
+      <c r="AA37">
+        <f>IF($T37="","",$T37&amp;"#"&amp;$Z37)</f>
+        <v/>
+      </c>
+      <c r="AB37">
+        <f>COUNTIF($T$6:$T35,$C37)</f>
+        <v/>
+      </c>
+      <c r="AC37">
+        <f>COUNTIFS($C$6:$C35,$C37,$M$6:$M35,1)</f>
+        <v/>
+      </c>
+      <c r="AD37">
+        <f>IF($AB37&gt;$AC37,IFERROR(MATCH($C37&amp;"#"&amp;($AC37+1),$AA$6:$AA35,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>IF($AD37=0,"",INDEX($A$6:$A35,$AD37))</f>
         <v/>
       </c>
     </row>
@@ -10906,7 +11692,7 @@
         <v/>
       </c>
       <c r="F38">
-        <f>IF($E38=0,0,IF(OR($D38="Licenza - settimana intera",$D38="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M38=1,0,IF($E38=0,0,IF(OR($D38="Licenza - settimana intera",$D38="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G38">
@@ -10930,7 +11716,7 @@
         <v/>
       </c>
       <c r="L38">
-        <f>IFERROR(INDEX($C31:$C35,MATCH(1,INDEX(($T31:$T35=$C38)*1,0),0)),"")</f>
+        <f>IF($AD38=0,"",INDEX($C$6:$C35,$AD38))</f>
         <v/>
       </c>
       <c r="M38">
@@ -10938,23 +11724,23 @@
         <v/>
       </c>
       <c r="N38">
-        <f>IF($G38=0,100000,IF(Partecipanti!$B$5=$C38,100000,COUNTIF($S$6:$S37,Partecipanti!$B$5)*100+MOD(1-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G38=0,100000,IF(Partecipanti!$B$5=$C38,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S37,Partecipanti!$B$5)*100+MOD(1-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O38">
-        <f>IF($H38=0,100000,IF(Partecipanti!$B$6=$C38,100000,COUNTIF($S$6:$S37,Partecipanti!$B$6)*100+MOD(2-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H38=0,100000,IF(Partecipanti!$B$6=$C38,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S37,Partecipanti!$B$6)*100+MOD(2-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P38">
-        <f>IF($I38=0,100000,IF(Partecipanti!$B$7=$C38,100000,COUNTIF($S$6:$S37,Partecipanti!$B$7)*100+MOD(3-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I38=0,100000,IF(Partecipanti!$B$7=$C38,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S37,Partecipanti!$B$7)*100+MOD(3-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q38">
-        <f>IF($J38=0,100000,IF(Partecipanti!$B$8=$C38,100000,COUNTIF($S$6:$S37,Partecipanti!$B$8)*100+MOD(4-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J38=0,100000,IF(Partecipanti!$B$8=$C38,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S37,Partecipanti!$B$8)*100+MOD(4-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R38">
-        <f>IF($K38=0,100000,IF(Partecipanti!$B$9=$C38,100000,COUNTIF($S$6:$S37,Partecipanti!$B$9)*100+MOD(5-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K38=0,100000,IF(Partecipanti!$B$9=$C38,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S37,Partecipanti!$B$9)*100+MOD(5-MATCH($C38,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S38">
@@ -10978,11 +11764,35 @@
         <v/>
       </c>
       <c r="X38">
-        <f>IF($M38=1,$L38&amp;" recupera il turno saltato nella settimana "&amp;($A38-1)&amp;"; "&amp;$C38&amp;" a riposo compensativo",IF($E38=1,$C38&amp;" assente ("&amp;$D38&amp;")"&amp;IF($S38="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S38&amp;" con doppio turno")&amp;IF($F38=1,"; turno da recuperare nella settimana "&amp;($A38+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M38=1,IF($E38=1,$L38&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE38&amp;"; "&amp;$C38&amp;" assente ("&amp;$D38&amp;")",$L38&amp;" recupera il turno saltato nella settimana "&amp;$AE38&amp;"; "&amp;$C38&amp;" a riposo compensativo"),IF($E38=1,$C38&amp;" assente ("&amp;$D38&amp;")"&amp;IF($S38="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S38&amp;" con doppio turno")&amp;IF($F38=1,"; turno da recuperare a partire dalla settimana "&amp;($A38+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>IF($M38=1,"recupera il turno saltato nella settimana "&amp;($A38-1)&amp;", "&amp;$C38&amp;" a riposo",IF($E38=1,IF($S38="DA ASSEGNARE","turno da assegnare: "&amp;$C38&amp;" assente","in sostituzione di "&amp;$C38&amp;", doppio turno"),""))</f>
+        <f>IF($M38=1,IF($E38=1,"recupero del turno saltato nella settimana "&amp;$AE38&amp;", "&amp;$C38&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE38&amp;", "&amp;$C38&amp;" a riposo"),IF($E38=1,IF($S38="DA ASSEGNARE","turno da assegnare: "&amp;$C38&amp;" assente","in sostituzione di "&amp;$C38&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z38">
+        <f>IF($T38="","",COUNTIF($T$6:$T38,$T38))</f>
+        <v/>
+      </c>
+      <c r="AA38">
+        <f>IF($T38="","",$T38&amp;"#"&amp;$Z38)</f>
+        <v/>
+      </c>
+      <c r="AB38">
+        <f>COUNTIF($T$6:$T35,$C38)</f>
+        <v/>
+      </c>
+      <c r="AC38">
+        <f>COUNTIFS($C$6:$C35,$C38,$M$6:$M35,1)</f>
+        <v/>
+      </c>
+      <c r="AD38">
+        <f>IF($AB38&gt;$AC38,IFERROR(MATCH($C38&amp;"#"&amp;($AC38+1),$AA$6:$AA35,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>IF($AD38=0,"",INDEX($A$6:$A35,$AD38))</f>
         <v/>
       </c>
     </row>
@@ -11006,7 +11816,7 @@
         <v/>
       </c>
       <c r="F39">
-        <f>IF($E39=0,0,IF(OR($D39="Licenza - settimana intera",$D39="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M39=1,0,IF($E39=0,0,IF(OR($D39="Licenza - settimana intera",$D39="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G39">
@@ -11030,7 +11840,7 @@
         <v/>
       </c>
       <c r="L39">
-        <f>IFERROR(INDEX($C31:$C35,MATCH(1,INDEX(($T31:$T35=$C39)*1,0),0)),"")</f>
+        <f>IF($AD39=0,"",INDEX($C$6:$C35,$AD39))</f>
         <v/>
       </c>
       <c r="M39">
@@ -11038,23 +11848,23 @@
         <v/>
       </c>
       <c r="N39">
-        <f>IF($G39=0,100000,IF(Partecipanti!$B$5=$C39,100000,COUNTIF($S$6:$S38,Partecipanti!$B$5)*100+MOD(1-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G39=0,100000,IF(Partecipanti!$B$5=$C39,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S38,Partecipanti!$B$5)*100+MOD(1-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O39">
-        <f>IF($H39=0,100000,IF(Partecipanti!$B$6=$C39,100000,COUNTIF($S$6:$S38,Partecipanti!$B$6)*100+MOD(2-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H39=0,100000,IF(Partecipanti!$B$6=$C39,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S38,Partecipanti!$B$6)*100+MOD(2-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P39">
-        <f>IF($I39=0,100000,IF(Partecipanti!$B$7=$C39,100000,COUNTIF($S$6:$S38,Partecipanti!$B$7)*100+MOD(3-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I39=0,100000,IF(Partecipanti!$B$7=$C39,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S38,Partecipanti!$B$7)*100+MOD(3-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q39">
-        <f>IF($J39=0,100000,IF(Partecipanti!$B$8=$C39,100000,COUNTIF($S$6:$S38,Partecipanti!$B$8)*100+MOD(4-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J39=0,100000,IF(Partecipanti!$B$8=$C39,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S38,Partecipanti!$B$8)*100+MOD(4-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R39">
-        <f>IF($K39=0,100000,IF(Partecipanti!$B$9=$C39,100000,COUNTIF($S$6:$S38,Partecipanti!$B$9)*100+MOD(5-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K39=0,100000,IF(Partecipanti!$B$9=$C39,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S38,Partecipanti!$B$9)*100+MOD(5-MATCH($C39,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S39">
@@ -11078,11 +11888,35 @@
         <v/>
       </c>
       <c r="X39">
-        <f>IF($M39=1,$L39&amp;" recupera il turno saltato nella settimana "&amp;($A39-1)&amp;"; "&amp;$C39&amp;" a riposo compensativo",IF($E39=1,$C39&amp;" assente ("&amp;$D39&amp;")"&amp;IF($S39="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S39&amp;" con doppio turno")&amp;IF($F39=1,"; turno da recuperare nella settimana "&amp;($A39+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M39=1,IF($E39=1,$L39&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE39&amp;"; "&amp;$C39&amp;" assente ("&amp;$D39&amp;")",$L39&amp;" recupera il turno saltato nella settimana "&amp;$AE39&amp;"; "&amp;$C39&amp;" a riposo compensativo"),IF($E39=1,$C39&amp;" assente ("&amp;$D39&amp;")"&amp;IF($S39="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S39&amp;" con doppio turno")&amp;IF($F39=1,"; turno da recuperare a partire dalla settimana "&amp;($A39+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>IF($M39=1,"recupera il turno saltato nella settimana "&amp;($A39-1)&amp;", "&amp;$C39&amp;" a riposo",IF($E39=1,IF($S39="DA ASSEGNARE","turno da assegnare: "&amp;$C39&amp;" assente","in sostituzione di "&amp;$C39&amp;", doppio turno"),""))</f>
+        <f>IF($M39=1,IF($E39=1,"recupero del turno saltato nella settimana "&amp;$AE39&amp;", "&amp;$C39&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE39&amp;", "&amp;$C39&amp;" a riposo"),IF($E39=1,IF($S39="DA ASSEGNARE","turno da assegnare: "&amp;$C39&amp;" assente","in sostituzione di "&amp;$C39&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z39">
+        <f>IF($T39="","",COUNTIF($T$6:$T39,$T39))</f>
+        <v/>
+      </c>
+      <c r="AA39">
+        <f>IF($T39="","",$T39&amp;"#"&amp;$Z39)</f>
+        <v/>
+      </c>
+      <c r="AB39">
+        <f>COUNTIF($T$6:$T35,$C39)</f>
+        <v/>
+      </c>
+      <c r="AC39">
+        <f>COUNTIFS($C$6:$C35,$C39,$M$6:$M35,1)</f>
+        <v/>
+      </c>
+      <c r="AD39">
+        <f>IF($AB39&gt;$AC39,IFERROR(MATCH($C39&amp;"#"&amp;($AC39+1),$AA$6:$AA35,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE39">
+        <f>IF($AD39=0,"",INDEX($A$6:$A35,$AD39))</f>
         <v/>
       </c>
     </row>
@@ -11106,7 +11940,7 @@
         <v/>
       </c>
       <c r="F40">
-        <f>IF($E40=0,0,IF(OR($D40="Licenza - settimana intera",$D40="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M40=1,0,IF($E40=0,0,IF(OR($D40="Licenza - settimana intera",$D40="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G40">
@@ -11130,7 +11964,7 @@
         <v/>
       </c>
       <c r="L40">
-        <f>IFERROR(INDEX($C31:$C35,MATCH(1,INDEX(($T31:$T35=$C40)*1,0),0)),"")</f>
+        <f>IF($AD40=0,"",INDEX($C$6:$C35,$AD40))</f>
         <v/>
       </c>
       <c r="M40">
@@ -11138,23 +11972,23 @@
         <v/>
       </c>
       <c r="N40">
-        <f>IF($G40=0,100000,IF(Partecipanti!$B$5=$C40,100000,COUNTIF($S$6:$S39,Partecipanti!$B$5)*100+MOD(1-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G40=0,100000,IF(Partecipanti!$B$5=$C40,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S39,Partecipanti!$B$5)*100+MOD(1-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O40">
-        <f>IF($H40=0,100000,IF(Partecipanti!$B$6=$C40,100000,COUNTIF($S$6:$S39,Partecipanti!$B$6)*100+MOD(2-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H40=0,100000,IF(Partecipanti!$B$6=$C40,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S39,Partecipanti!$B$6)*100+MOD(2-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P40">
-        <f>IF($I40=0,100000,IF(Partecipanti!$B$7=$C40,100000,COUNTIF($S$6:$S39,Partecipanti!$B$7)*100+MOD(3-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I40=0,100000,IF(Partecipanti!$B$7=$C40,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S39,Partecipanti!$B$7)*100+MOD(3-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q40">
-        <f>IF($J40=0,100000,IF(Partecipanti!$B$8=$C40,100000,COUNTIF($S$6:$S39,Partecipanti!$B$8)*100+MOD(4-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J40=0,100000,IF(Partecipanti!$B$8=$C40,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S39,Partecipanti!$B$8)*100+MOD(4-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R40">
-        <f>IF($K40=0,100000,IF(Partecipanti!$B$9=$C40,100000,COUNTIF($S$6:$S39,Partecipanti!$B$9)*100+MOD(5-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K40=0,100000,IF(Partecipanti!$B$9=$C40,100000,IF(SUMPRODUCT(($M$36:$M$40=1)*($L$36:$L$40=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S39,Partecipanti!$B$9)*100+MOD(5-MATCH($C40,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S40">
@@ -11178,11 +12012,35 @@
         <v/>
       </c>
       <c r="X40">
-        <f>IF($M40=1,$L40&amp;" recupera il turno saltato nella settimana "&amp;($A40-1)&amp;"; "&amp;$C40&amp;" a riposo compensativo",IF($E40=1,$C40&amp;" assente ("&amp;$D40&amp;")"&amp;IF($S40="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S40&amp;" con doppio turno")&amp;IF($F40=1,"; turno da recuperare nella settimana "&amp;($A40+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M40=1,IF($E40=1,$L40&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE40&amp;"; "&amp;$C40&amp;" assente ("&amp;$D40&amp;")",$L40&amp;" recupera il turno saltato nella settimana "&amp;$AE40&amp;"; "&amp;$C40&amp;" a riposo compensativo"),IF($E40=1,$C40&amp;" assente ("&amp;$D40&amp;")"&amp;IF($S40="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S40&amp;" con doppio turno")&amp;IF($F40=1,"; turno da recuperare a partire dalla settimana "&amp;($A40+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>IF($M40=1,"recupera il turno saltato nella settimana "&amp;($A40-1)&amp;", "&amp;$C40&amp;" a riposo",IF($E40=1,IF($S40="DA ASSEGNARE","turno da assegnare: "&amp;$C40&amp;" assente","in sostituzione di "&amp;$C40&amp;", doppio turno"),""))</f>
+        <f>IF($M40=1,IF($E40=1,"recupero del turno saltato nella settimana "&amp;$AE40&amp;", "&amp;$C40&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE40&amp;", "&amp;$C40&amp;" a riposo"),IF($E40=1,IF($S40="DA ASSEGNARE","turno da assegnare: "&amp;$C40&amp;" assente","in sostituzione di "&amp;$C40&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z40">
+        <f>IF($T40="","",COUNTIF($T$6:$T40,$T40))</f>
+        <v/>
+      </c>
+      <c r="AA40">
+        <f>IF($T40="","",$T40&amp;"#"&amp;$Z40)</f>
+        <v/>
+      </c>
+      <c r="AB40">
+        <f>COUNTIF($T$6:$T35,$C40)</f>
+        <v/>
+      </c>
+      <c r="AC40">
+        <f>COUNTIFS($C$6:$C35,$C40,$M$6:$M35,1)</f>
+        <v/>
+      </c>
+      <c r="AD40">
+        <f>IF($AB40&gt;$AC40,IFERROR(MATCH($C40&amp;"#"&amp;($AC40+1),$AA$6:$AA35,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>IF($AD40=0,"",INDEX($A$6:$A35,$AD40))</f>
         <v/>
       </c>
     </row>
@@ -11206,7 +12064,7 @@
         <v/>
       </c>
       <c r="F41">
-        <f>IF($E41=0,0,IF(OR($D41="Licenza - settimana intera",$D41="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M41=1,0,IF($E41=0,0,IF(OR($D41="Licenza - settimana intera",$D41="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G41">
@@ -11230,7 +12088,7 @@
         <v/>
       </c>
       <c r="L41">
-        <f>IFERROR(INDEX($C36:$C40,MATCH(1,INDEX(($T36:$T40=$C41)*1,0),0)),"")</f>
+        <f>IF($AD41=0,"",INDEX($C$6:$C40,$AD41))</f>
         <v/>
       </c>
       <c r="M41">
@@ -11238,23 +12096,23 @@
         <v/>
       </c>
       <c r="N41">
-        <f>IF($G41=0,100000,IF(Partecipanti!$B$5=$C41,100000,COUNTIF($S$6:$S40,Partecipanti!$B$5)*100+MOD(1-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G41=0,100000,IF(Partecipanti!$B$5=$C41,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S40,Partecipanti!$B$5)*100+MOD(1-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O41">
-        <f>IF($H41=0,100000,IF(Partecipanti!$B$6=$C41,100000,COUNTIF($S$6:$S40,Partecipanti!$B$6)*100+MOD(2-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H41=0,100000,IF(Partecipanti!$B$6=$C41,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S40,Partecipanti!$B$6)*100+MOD(2-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P41">
-        <f>IF($I41=0,100000,IF(Partecipanti!$B$7=$C41,100000,COUNTIF($S$6:$S40,Partecipanti!$B$7)*100+MOD(3-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I41=0,100000,IF(Partecipanti!$B$7=$C41,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S40,Partecipanti!$B$7)*100+MOD(3-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q41">
-        <f>IF($J41=0,100000,IF(Partecipanti!$B$8=$C41,100000,COUNTIF($S$6:$S40,Partecipanti!$B$8)*100+MOD(4-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J41=0,100000,IF(Partecipanti!$B$8=$C41,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S40,Partecipanti!$B$8)*100+MOD(4-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R41">
-        <f>IF($K41=0,100000,IF(Partecipanti!$B$9=$C41,100000,COUNTIF($S$6:$S40,Partecipanti!$B$9)*100+MOD(5-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K41=0,100000,IF(Partecipanti!$B$9=$C41,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S40,Partecipanti!$B$9)*100+MOD(5-MATCH($C41,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S41">
@@ -11278,11 +12136,35 @@
         <v/>
       </c>
       <c r="X41">
-        <f>IF($M41=1,$L41&amp;" recupera il turno saltato nella settimana "&amp;($A41-1)&amp;"; "&amp;$C41&amp;" a riposo compensativo",IF($E41=1,$C41&amp;" assente ("&amp;$D41&amp;")"&amp;IF($S41="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S41&amp;" con doppio turno")&amp;IF($F41=1,"; turno da recuperare nella settimana "&amp;($A41+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M41=1,IF($E41=1,$L41&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE41&amp;"; "&amp;$C41&amp;" assente ("&amp;$D41&amp;")",$L41&amp;" recupera il turno saltato nella settimana "&amp;$AE41&amp;"; "&amp;$C41&amp;" a riposo compensativo"),IF($E41=1,$C41&amp;" assente ("&amp;$D41&amp;")"&amp;IF($S41="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S41&amp;" con doppio turno")&amp;IF($F41=1,"; turno da recuperare a partire dalla settimana "&amp;($A41+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>IF($M41=1,"recupera il turno saltato nella settimana "&amp;($A41-1)&amp;", "&amp;$C41&amp;" a riposo",IF($E41=1,IF($S41="DA ASSEGNARE","turno da assegnare: "&amp;$C41&amp;" assente","in sostituzione di "&amp;$C41&amp;", doppio turno"),""))</f>
+        <f>IF($M41=1,IF($E41=1,"recupero del turno saltato nella settimana "&amp;$AE41&amp;", "&amp;$C41&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE41&amp;", "&amp;$C41&amp;" a riposo"),IF($E41=1,IF($S41="DA ASSEGNARE","turno da assegnare: "&amp;$C41&amp;" assente","in sostituzione di "&amp;$C41&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z41">
+        <f>IF($T41="","",COUNTIF($T$6:$T41,$T41))</f>
+        <v/>
+      </c>
+      <c r="AA41">
+        <f>IF($T41="","",$T41&amp;"#"&amp;$Z41)</f>
+        <v/>
+      </c>
+      <c r="AB41">
+        <f>COUNTIF($T$6:$T40,$C41)</f>
+        <v/>
+      </c>
+      <c r="AC41">
+        <f>COUNTIFS($C$6:$C40,$C41,$M$6:$M40,1)</f>
+        <v/>
+      </c>
+      <c r="AD41">
+        <f>IF($AB41&gt;$AC41,IFERROR(MATCH($C41&amp;"#"&amp;($AC41+1),$AA$6:$AA40,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>IF($AD41=0,"",INDEX($A$6:$A40,$AD41))</f>
         <v/>
       </c>
     </row>
@@ -11306,7 +12188,7 @@
         <v/>
       </c>
       <c r="F42">
-        <f>IF($E42=0,0,IF(OR($D42="Licenza - settimana intera",$D42="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M42=1,0,IF($E42=0,0,IF(OR($D42="Licenza - settimana intera",$D42="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G42">
@@ -11330,7 +12212,7 @@
         <v/>
       </c>
       <c r="L42">
-        <f>IFERROR(INDEX($C36:$C40,MATCH(1,INDEX(($T36:$T40=$C42)*1,0),0)),"")</f>
+        <f>IF($AD42=0,"",INDEX($C$6:$C40,$AD42))</f>
         <v/>
       </c>
       <c r="M42">
@@ -11338,23 +12220,23 @@
         <v/>
       </c>
       <c r="N42">
-        <f>IF($G42=0,100000,IF(Partecipanti!$B$5=$C42,100000,COUNTIF($S$6:$S41,Partecipanti!$B$5)*100+MOD(1-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G42=0,100000,IF(Partecipanti!$B$5=$C42,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S41,Partecipanti!$B$5)*100+MOD(1-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O42">
-        <f>IF($H42=0,100000,IF(Partecipanti!$B$6=$C42,100000,COUNTIF($S$6:$S41,Partecipanti!$B$6)*100+MOD(2-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H42=0,100000,IF(Partecipanti!$B$6=$C42,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S41,Partecipanti!$B$6)*100+MOD(2-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P42">
-        <f>IF($I42=0,100000,IF(Partecipanti!$B$7=$C42,100000,COUNTIF($S$6:$S41,Partecipanti!$B$7)*100+MOD(3-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I42=0,100000,IF(Partecipanti!$B$7=$C42,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S41,Partecipanti!$B$7)*100+MOD(3-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q42">
-        <f>IF($J42=0,100000,IF(Partecipanti!$B$8=$C42,100000,COUNTIF($S$6:$S41,Partecipanti!$B$8)*100+MOD(4-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J42=0,100000,IF(Partecipanti!$B$8=$C42,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S41,Partecipanti!$B$8)*100+MOD(4-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R42">
-        <f>IF($K42=0,100000,IF(Partecipanti!$B$9=$C42,100000,COUNTIF($S$6:$S41,Partecipanti!$B$9)*100+MOD(5-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K42=0,100000,IF(Partecipanti!$B$9=$C42,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S41,Partecipanti!$B$9)*100+MOD(5-MATCH($C42,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S42">
@@ -11378,11 +12260,35 @@
         <v/>
       </c>
       <c r="X42">
-        <f>IF($M42=1,$L42&amp;" recupera il turno saltato nella settimana "&amp;($A42-1)&amp;"; "&amp;$C42&amp;" a riposo compensativo",IF($E42=1,$C42&amp;" assente ("&amp;$D42&amp;")"&amp;IF($S42="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S42&amp;" con doppio turno")&amp;IF($F42=1,"; turno da recuperare nella settimana "&amp;($A42+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M42=1,IF($E42=1,$L42&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE42&amp;"; "&amp;$C42&amp;" assente ("&amp;$D42&amp;")",$L42&amp;" recupera il turno saltato nella settimana "&amp;$AE42&amp;"; "&amp;$C42&amp;" a riposo compensativo"),IF($E42=1,$C42&amp;" assente ("&amp;$D42&amp;")"&amp;IF($S42="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S42&amp;" con doppio turno")&amp;IF($F42=1,"; turno da recuperare a partire dalla settimana "&amp;($A42+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>IF($M42=1,"recupera il turno saltato nella settimana "&amp;($A42-1)&amp;", "&amp;$C42&amp;" a riposo",IF($E42=1,IF($S42="DA ASSEGNARE","turno da assegnare: "&amp;$C42&amp;" assente","in sostituzione di "&amp;$C42&amp;", doppio turno"),""))</f>
+        <f>IF($M42=1,IF($E42=1,"recupero del turno saltato nella settimana "&amp;$AE42&amp;", "&amp;$C42&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE42&amp;", "&amp;$C42&amp;" a riposo"),IF($E42=1,IF($S42="DA ASSEGNARE","turno da assegnare: "&amp;$C42&amp;" assente","in sostituzione di "&amp;$C42&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z42">
+        <f>IF($T42="","",COUNTIF($T$6:$T42,$T42))</f>
+        <v/>
+      </c>
+      <c r="AA42">
+        <f>IF($T42="","",$T42&amp;"#"&amp;$Z42)</f>
+        <v/>
+      </c>
+      <c r="AB42">
+        <f>COUNTIF($T$6:$T40,$C42)</f>
+        <v/>
+      </c>
+      <c r="AC42">
+        <f>COUNTIFS($C$6:$C40,$C42,$M$6:$M40,1)</f>
+        <v/>
+      </c>
+      <c r="AD42">
+        <f>IF($AB42&gt;$AC42,IFERROR(MATCH($C42&amp;"#"&amp;($AC42+1),$AA$6:$AA40,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>IF($AD42=0,"",INDEX($A$6:$A40,$AD42))</f>
         <v/>
       </c>
     </row>
@@ -11406,7 +12312,7 @@
         <v/>
       </c>
       <c r="F43">
-        <f>IF($E43=0,0,IF(OR($D43="Licenza - settimana intera",$D43="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M43=1,0,IF($E43=0,0,IF(OR($D43="Licenza - settimana intera",$D43="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G43">
@@ -11430,7 +12336,7 @@
         <v/>
       </c>
       <c r="L43">
-        <f>IFERROR(INDEX($C36:$C40,MATCH(1,INDEX(($T36:$T40=$C43)*1,0),0)),"")</f>
+        <f>IF($AD43=0,"",INDEX($C$6:$C40,$AD43))</f>
         <v/>
       </c>
       <c r="M43">
@@ -11438,23 +12344,23 @@
         <v/>
       </c>
       <c r="N43">
-        <f>IF($G43=0,100000,IF(Partecipanti!$B$5=$C43,100000,COUNTIF($S$6:$S42,Partecipanti!$B$5)*100+MOD(1-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G43=0,100000,IF(Partecipanti!$B$5=$C43,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S42,Partecipanti!$B$5)*100+MOD(1-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O43">
-        <f>IF($H43=0,100000,IF(Partecipanti!$B$6=$C43,100000,COUNTIF($S$6:$S42,Partecipanti!$B$6)*100+MOD(2-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H43=0,100000,IF(Partecipanti!$B$6=$C43,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S42,Partecipanti!$B$6)*100+MOD(2-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P43">
-        <f>IF($I43=0,100000,IF(Partecipanti!$B$7=$C43,100000,COUNTIF($S$6:$S42,Partecipanti!$B$7)*100+MOD(3-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I43=0,100000,IF(Partecipanti!$B$7=$C43,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S42,Partecipanti!$B$7)*100+MOD(3-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q43">
-        <f>IF($J43=0,100000,IF(Partecipanti!$B$8=$C43,100000,COUNTIF($S$6:$S42,Partecipanti!$B$8)*100+MOD(4-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J43=0,100000,IF(Partecipanti!$B$8=$C43,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S42,Partecipanti!$B$8)*100+MOD(4-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R43">
-        <f>IF($K43=0,100000,IF(Partecipanti!$B$9=$C43,100000,COUNTIF($S$6:$S42,Partecipanti!$B$9)*100+MOD(5-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K43=0,100000,IF(Partecipanti!$B$9=$C43,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S42,Partecipanti!$B$9)*100+MOD(5-MATCH($C43,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S43">
@@ -11478,11 +12384,35 @@
         <v/>
       </c>
       <c r="X43">
-        <f>IF($M43=1,$L43&amp;" recupera il turno saltato nella settimana "&amp;($A43-1)&amp;"; "&amp;$C43&amp;" a riposo compensativo",IF($E43=1,$C43&amp;" assente ("&amp;$D43&amp;")"&amp;IF($S43="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S43&amp;" con doppio turno")&amp;IF($F43=1,"; turno da recuperare nella settimana "&amp;($A43+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M43=1,IF($E43=1,$L43&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE43&amp;"; "&amp;$C43&amp;" assente ("&amp;$D43&amp;")",$L43&amp;" recupera il turno saltato nella settimana "&amp;$AE43&amp;"; "&amp;$C43&amp;" a riposo compensativo"),IF($E43=1,$C43&amp;" assente ("&amp;$D43&amp;")"&amp;IF($S43="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S43&amp;" con doppio turno")&amp;IF($F43=1,"; turno da recuperare a partire dalla settimana "&amp;($A43+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>IF($M43=1,"recupera il turno saltato nella settimana "&amp;($A43-1)&amp;", "&amp;$C43&amp;" a riposo",IF($E43=1,IF($S43="DA ASSEGNARE","turno da assegnare: "&amp;$C43&amp;" assente","in sostituzione di "&amp;$C43&amp;", doppio turno"),""))</f>
+        <f>IF($M43=1,IF($E43=1,"recupero del turno saltato nella settimana "&amp;$AE43&amp;", "&amp;$C43&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE43&amp;", "&amp;$C43&amp;" a riposo"),IF($E43=1,IF($S43="DA ASSEGNARE","turno da assegnare: "&amp;$C43&amp;" assente","in sostituzione di "&amp;$C43&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z43">
+        <f>IF($T43="","",COUNTIF($T$6:$T43,$T43))</f>
+        <v/>
+      </c>
+      <c r="AA43">
+        <f>IF($T43="","",$T43&amp;"#"&amp;$Z43)</f>
+        <v/>
+      </c>
+      <c r="AB43">
+        <f>COUNTIF($T$6:$T40,$C43)</f>
+        <v/>
+      </c>
+      <c r="AC43">
+        <f>COUNTIFS($C$6:$C40,$C43,$M$6:$M40,1)</f>
+        <v/>
+      </c>
+      <c r="AD43">
+        <f>IF($AB43&gt;$AC43,IFERROR(MATCH($C43&amp;"#"&amp;($AC43+1),$AA$6:$AA40,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>IF($AD43=0,"",INDEX($A$6:$A40,$AD43))</f>
         <v/>
       </c>
     </row>
@@ -11506,7 +12436,7 @@
         <v/>
       </c>
       <c r="F44">
-        <f>IF($E44=0,0,IF(OR($D44="Licenza - settimana intera",$D44="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M44=1,0,IF($E44=0,0,IF(OR($D44="Licenza - settimana intera",$D44="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G44">
@@ -11530,7 +12460,7 @@
         <v/>
       </c>
       <c r="L44">
-        <f>IFERROR(INDEX($C36:$C40,MATCH(1,INDEX(($T36:$T40=$C44)*1,0),0)),"")</f>
+        <f>IF($AD44=0,"",INDEX($C$6:$C40,$AD44))</f>
         <v/>
       </c>
       <c r="M44">
@@ -11538,23 +12468,23 @@
         <v/>
       </c>
       <c r="N44">
-        <f>IF($G44=0,100000,IF(Partecipanti!$B$5=$C44,100000,COUNTIF($S$6:$S43,Partecipanti!$B$5)*100+MOD(1-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G44=0,100000,IF(Partecipanti!$B$5=$C44,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S43,Partecipanti!$B$5)*100+MOD(1-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O44">
-        <f>IF($H44=0,100000,IF(Partecipanti!$B$6=$C44,100000,COUNTIF($S$6:$S43,Partecipanti!$B$6)*100+MOD(2-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H44=0,100000,IF(Partecipanti!$B$6=$C44,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S43,Partecipanti!$B$6)*100+MOD(2-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P44">
-        <f>IF($I44=0,100000,IF(Partecipanti!$B$7=$C44,100000,COUNTIF($S$6:$S43,Partecipanti!$B$7)*100+MOD(3-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I44=0,100000,IF(Partecipanti!$B$7=$C44,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S43,Partecipanti!$B$7)*100+MOD(3-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q44">
-        <f>IF($J44=0,100000,IF(Partecipanti!$B$8=$C44,100000,COUNTIF($S$6:$S43,Partecipanti!$B$8)*100+MOD(4-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J44=0,100000,IF(Partecipanti!$B$8=$C44,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S43,Partecipanti!$B$8)*100+MOD(4-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R44">
-        <f>IF($K44=0,100000,IF(Partecipanti!$B$9=$C44,100000,COUNTIF($S$6:$S43,Partecipanti!$B$9)*100+MOD(5-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K44=0,100000,IF(Partecipanti!$B$9=$C44,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S43,Partecipanti!$B$9)*100+MOD(5-MATCH($C44,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S44">
@@ -11578,11 +12508,35 @@
         <v/>
       </c>
       <c r="X44">
-        <f>IF($M44=1,$L44&amp;" recupera il turno saltato nella settimana "&amp;($A44-1)&amp;"; "&amp;$C44&amp;" a riposo compensativo",IF($E44=1,$C44&amp;" assente ("&amp;$D44&amp;")"&amp;IF($S44="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S44&amp;" con doppio turno")&amp;IF($F44=1,"; turno da recuperare nella settimana "&amp;($A44+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M44=1,IF($E44=1,$L44&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE44&amp;"; "&amp;$C44&amp;" assente ("&amp;$D44&amp;")",$L44&amp;" recupera il turno saltato nella settimana "&amp;$AE44&amp;"; "&amp;$C44&amp;" a riposo compensativo"),IF($E44=1,$C44&amp;" assente ("&amp;$D44&amp;")"&amp;IF($S44="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S44&amp;" con doppio turno")&amp;IF($F44=1,"; turno da recuperare a partire dalla settimana "&amp;($A44+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>IF($M44=1,"recupera il turno saltato nella settimana "&amp;($A44-1)&amp;", "&amp;$C44&amp;" a riposo",IF($E44=1,IF($S44="DA ASSEGNARE","turno da assegnare: "&amp;$C44&amp;" assente","in sostituzione di "&amp;$C44&amp;", doppio turno"),""))</f>
+        <f>IF($M44=1,IF($E44=1,"recupero del turno saltato nella settimana "&amp;$AE44&amp;", "&amp;$C44&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE44&amp;", "&amp;$C44&amp;" a riposo"),IF($E44=1,IF($S44="DA ASSEGNARE","turno da assegnare: "&amp;$C44&amp;" assente","in sostituzione di "&amp;$C44&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z44">
+        <f>IF($T44="","",COUNTIF($T$6:$T44,$T44))</f>
+        <v/>
+      </c>
+      <c r="AA44">
+        <f>IF($T44="","",$T44&amp;"#"&amp;$Z44)</f>
+        <v/>
+      </c>
+      <c r="AB44">
+        <f>COUNTIF($T$6:$T40,$C44)</f>
+        <v/>
+      </c>
+      <c r="AC44">
+        <f>COUNTIFS($C$6:$C40,$C44,$M$6:$M40,1)</f>
+        <v/>
+      </c>
+      <c r="AD44">
+        <f>IF($AB44&gt;$AC44,IFERROR(MATCH($C44&amp;"#"&amp;($AC44+1),$AA$6:$AA40,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>IF($AD44=0,"",INDEX($A$6:$A40,$AD44))</f>
         <v/>
       </c>
     </row>
@@ -11606,7 +12560,7 @@
         <v/>
       </c>
       <c r="F45">
-        <f>IF($E45=0,0,IF(OR($D45="Licenza - settimana intera",$D45="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M45=1,0,IF($E45=0,0,IF(OR($D45="Licenza - settimana intera",$D45="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G45">
@@ -11630,7 +12584,7 @@
         <v/>
       </c>
       <c r="L45">
-        <f>IFERROR(INDEX($C36:$C40,MATCH(1,INDEX(($T36:$T40=$C45)*1,0),0)),"")</f>
+        <f>IF($AD45=0,"",INDEX($C$6:$C40,$AD45))</f>
         <v/>
       </c>
       <c r="M45">
@@ -11638,23 +12592,23 @@
         <v/>
       </c>
       <c r="N45">
-        <f>IF($G45=0,100000,IF(Partecipanti!$B$5=$C45,100000,COUNTIF($S$6:$S44,Partecipanti!$B$5)*100+MOD(1-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G45=0,100000,IF(Partecipanti!$B$5=$C45,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S44,Partecipanti!$B$5)*100+MOD(1-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O45">
-        <f>IF($H45=0,100000,IF(Partecipanti!$B$6=$C45,100000,COUNTIF($S$6:$S44,Partecipanti!$B$6)*100+MOD(2-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H45=0,100000,IF(Partecipanti!$B$6=$C45,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S44,Partecipanti!$B$6)*100+MOD(2-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P45">
-        <f>IF($I45=0,100000,IF(Partecipanti!$B$7=$C45,100000,COUNTIF($S$6:$S44,Partecipanti!$B$7)*100+MOD(3-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I45=0,100000,IF(Partecipanti!$B$7=$C45,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S44,Partecipanti!$B$7)*100+MOD(3-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q45">
-        <f>IF($J45=0,100000,IF(Partecipanti!$B$8=$C45,100000,COUNTIF($S$6:$S44,Partecipanti!$B$8)*100+MOD(4-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J45=0,100000,IF(Partecipanti!$B$8=$C45,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S44,Partecipanti!$B$8)*100+MOD(4-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R45">
-        <f>IF($K45=0,100000,IF(Partecipanti!$B$9=$C45,100000,COUNTIF($S$6:$S44,Partecipanti!$B$9)*100+MOD(5-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K45=0,100000,IF(Partecipanti!$B$9=$C45,100000,IF(SUMPRODUCT(($M$41:$M$45=1)*($L$41:$L$45=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S44,Partecipanti!$B$9)*100+MOD(5-MATCH($C45,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S45">
@@ -11678,11 +12632,35 @@
         <v/>
       </c>
       <c r="X45">
-        <f>IF($M45=1,$L45&amp;" recupera il turno saltato nella settimana "&amp;($A45-1)&amp;"; "&amp;$C45&amp;" a riposo compensativo",IF($E45=1,$C45&amp;" assente ("&amp;$D45&amp;")"&amp;IF($S45="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S45&amp;" con doppio turno")&amp;IF($F45=1,"; turno da recuperare nella settimana "&amp;($A45+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M45=1,IF($E45=1,$L45&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE45&amp;"; "&amp;$C45&amp;" assente ("&amp;$D45&amp;")",$L45&amp;" recupera il turno saltato nella settimana "&amp;$AE45&amp;"; "&amp;$C45&amp;" a riposo compensativo"),IF($E45=1,$C45&amp;" assente ("&amp;$D45&amp;")"&amp;IF($S45="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S45&amp;" con doppio turno")&amp;IF($F45=1,"; turno da recuperare a partire dalla settimana "&amp;($A45+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>IF($M45=1,"recupera il turno saltato nella settimana "&amp;($A45-1)&amp;", "&amp;$C45&amp;" a riposo",IF($E45=1,IF($S45="DA ASSEGNARE","turno da assegnare: "&amp;$C45&amp;" assente","in sostituzione di "&amp;$C45&amp;", doppio turno"),""))</f>
+        <f>IF($M45=1,IF($E45=1,"recupero del turno saltato nella settimana "&amp;$AE45&amp;", "&amp;$C45&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE45&amp;", "&amp;$C45&amp;" a riposo"),IF($E45=1,IF($S45="DA ASSEGNARE","turno da assegnare: "&amp;$C45&amp;" assente","in sostituzione di "&amp;$C45&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z45">
+        <f>IF($T45="","",COUNTIF($T$6:$T45,$T45))</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>IF($T45="","",$T45&amp;"#"&amp;$Z45)</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>COUNTIF($T$6:$T40,$C45)</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>COUNTIFS($C$6:$C40,$C45,$M$6:$M40,1)</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>IF($AB45&gt;$AC45,IFERROR(MATCH($C45&amp;"#"&amp;($AC45+1),$AA$6:$AA40,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>IF($AD45=0,"",INDEX($A$6:$A40,$AD45))</f>
         <v/>
       </c>
     </row>
@@ -11706,7 +12684,7 @@
         <v/>
       </c>
       <c r="F46">
-        <f>IF($E46=0,0,IF(OR($D46="Licenza - settimana intera",$D46="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M46=1,0,IF($E46=0,0,IF(OR($D46="Licenza - settimana intera",$D46="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G46">
@@ -11730,7 +12708,7 @@
         <v/>
       </c>
       <c r="L46">
-        <f>IFERROR(INDEX($C41:$C45,MATCH(1,INDEX(($T41:$T45=$C46)*1,0),0)),"")</f>
+        <f>IF($AD46=0,"",INDEX($C$6:$C45,$AD46))</f>
         <v/>
       </c>
       <c r="M46">
@@ -11738,23 +12716,23 @@
         <v/>
       </c>
       <c r="N46">
-        <f>IF($G46=0,100000,IF(Partecipanti!$B$5=$C46,100000,COUNTIF($S$6:$S45,Partecipanti!$B$5)*100+MOD(1-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G46=0,100000,IF(Partecipanti!$B$5=$C46,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S45,Partecipanti!$B$5)*100+MOD(1-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O46">
-        <f>IF($H46=0,100000,IF(Partecipanti!$B$6=$C46,100000,COUNTIF($S$6:$S45,Partecipanti!$B$6)*100+MOD(2-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H46=0,100000,IF(Partecipanti!$B$6=$C46,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S45,Partecipanti!$B$6)*100+MOD(2-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P46">
-        <f>IF($I46=0,100000,IF(Partecipanti!$B$7=$C46,100000,COUNTIF($S$6:$S45,Partecipanti!$B$7)*100+MOD(3-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I46=0,100000,IF(Partecipanti!$B$7=$C46,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S45,Partecipanti!$B$7)*100+MOD(3-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q46">
-        <f>IF($J46=0,100000,IF(Partecipanti!$B$8=$C46,100000,COUNTIF($S$6:$S45,Partecipanti!$B$8)*100+MOD(4-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J46=0,100000,IF(Partecipanti!$B$8=$C46,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S45,Partecipanti!$B$8)*100+MOD(4-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R46">
-        <f>IF($K46=0,100000,IF(Partecipanti!$B$9=$C46,100000,COUNTIF($S$6:$S45,Partecipanti!$B$9)*100+MOD(5-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K46=0,100000,IF(Partecipanti!$B$9=$C46,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S45,Partecipanti!$B$9)*100+MOD(5-MATCH($C46,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S46">
@@ -11778,11 +12756,35 @@
         <v/>
       </c>
       <c r="X46">
-        <f>IF($M46=1,$L46&amp;" recupera il turno saltato nella settimana "&amp;($A46-1)&amp;"; "&amp;$C46&amp;" a riposo compensativo",IF($E46=1,$C46&amp;" assente ("&amp;$D46&amp;")"&amp;IF($S46="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S46&amp;" con doppio turno")&amp;IF($F46=1,"; turno da recuperare nella settimana "&amp;($A46+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M46=1,IF($E46=1,$L46&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE46&amp;"; "&amp;$C46&amp;" assente ("&amp;$D46&amp;")",$L46&amp;" recupera il turno saltato nella settimana "&amp;$AE46&amp;"; "&amp;$C46&amp;" a riposo compensativo"),IF($E46=1,$C46&amp;" assente ("&amp;$D46&amp;")"&amp;IF($S46="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S46&amp;" con doppio turno")&amp;IF($F46=1,"; turno da recuperare a partire dalla settimana "&amp;($A46+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>IF($M46=1,"recupera il turno saltato nella settimana "&amp;($A46-1)&amp;", "&amp;$C46&amp;" a riposo",IF($E46=1,IF($S46="DA ASSEGNARE","turno da assegnare: "&amp;$C46&amp;" assente","in sostituzione di "&amp;$C46&amp;", doppio turno"),""))</f>
+        <f>IF($M46=1,IF($E46=1,"recupero del turno saltato nella settimana "&amp;$AE46&amp;", "&amp;$C46&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE46&amp;", "&amp;$C46&amp;" a riposo"),IF($E46=1,IF($S46="DA ASSEGNARE","turno da assegnare: "&amp;$C46&amp;" assente","in sostituzione di "&amp;$C46&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z46">
+        <f>IF($T46="","",COUNTIF($T$6:$T46,$T46))</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>IF($T46="","",$T46&amp;"#"&amp;$Z46)</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>COUNTIF($T$6:$T45,$C46)</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>COUNTIFS($C$6:$C45,$C46,$M$6:$M45,1)</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>IF($AB46&gt;$AC46,IFERROR(MATCH($C46&amp;"#"&amp;($AC46+1),$AA$6:$AA45,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>IF($AD46=0,"",INDEX($A$6:$A45,$AD46))</f>
         <v/>
       </c>
     </row>
@@ -11806,7 +12808,7 @@
         <v/>
       </c>
       <c r="F47">
-        <f>IF($E47=0,0,IF(OR($D47="Licenza - settimana intera",$D47="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M47=1,0,IF($E47=0,0,IF(OR($D47="Licenza - settimana intera",$D47="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G47">
@@ -11830,7 +12832,7 @@
         <v/>
       </c>
       <c r="L47">
-        <f>IFERROR(INDEX($C41:$C45,MATCH(1,INDEX(($T41:$T45=$C47)*1,0),0)),"")</f>
+        <f>IF($AD47=0,"",INDEX($C$6:$C45,$AD47))</f>
         <v/>
       </c>
       <c r="M47">
@@ -11838,23 +12840,23 @@
         <v/>
       </c>
       <c r="N47">
-        <f>IF($G47=0,100000,IF(Partecipanti!$B$5=$C47,100000,COUNTIF($S$6:$S46,Partecipanti!$B$5)*100+MOD(1-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G47=0,100000,IF(Partecipanti!$B$5=$C47,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S46,Partecipanti!$B$5)*100+MOD(1-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O47">
-        <f>IF($H47=0,100000,IF(Partecipanti!$B$6=$C47,100000,COUNTIF($S$6:$S46,Partecipanti!$B$6)*100+MOD(2-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H47=0,100000,IF(Partecipanti!$B$6=$C47,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S46,Partecipanti!$B$6)*100+MOD(2-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P47">
-        <f>IF($I47=0,100000,IF(Partecipanti!$B$7=$C47,100000,COUNTIF($S$6:$S46,Partecipanti!$B$7)*100+MOD(3-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I47=0,100000,IF(Partecipanti!$B$7=$C47,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S46,Partecipanti!$B$7)*100+MOD(3-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q47">
-        <f>IF($J47=0,100000,IF(Partecipanti!$B$8=$C47,100000,COUNTIF($S$6:$S46,Partecipanti!$B$8)*100+MOD(4-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J47=0,100000,IF(Partecipanti!$B$8=$C47,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S46,Partecipanti!$B$8)*100+MOD(4-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R47">
-        <f>IF($K47=0,100000,IF(Partecipanti!$B$9=$C47,100000,COUNTIF($S$6:$S46,Partecipanti!$B$9)*100+MOD(5-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K47=0,100000,IF(Partecipanti!$B$9=$C47,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S46,Partecipanti!$B$9)*100+MOD(5-MATCH($C47,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S47">
@@ -11878,11 +12880,35 @@
         <v/>
       </c>
       <c r="X47">
-        <f>IF($M47=1,$L47&amp;" recupera il turno saltato nella settimana "&amp;($A47-1)&amp;"; "&amp;$C47&amp;" a riposo compensativo",IF($E47=1,$C47&amp;" assente ("&amp;$D47&amp;")"&amp;IF($S47="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S47&amp;" con doppio turno")&amp;IF($F47=1,"; turno da recuperare nella settimana "&amp;($A47+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M47=1,IF($E47=1,$L47&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE47&amp;"; "&amp;$C47&amp;" assente ("&amp;$D47&amp;")",$L47&amp;" recupera il turno saltato nella settimana "&amp;$AE47&amp;"; "&amp;$C47&amp;" a riposo compensativo"),IF($E47=1,$C47&amp;" assente ("&amp;$D47&amp;")"&amp;IF($S47="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S47&amp;" con doppio turno")&amp;IF($F47=1,"; turno da recuperare a partire dalla settimana "&amp;($A47+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>IF($M47=1,"recupera il turno saltato nella settimana "&amp;($A47-1)&amp;", "&amp;$C47&amp;" a riposo",IF($E47=1,IF($S47="DA ASSEGNARE","turno da assegnare: "&amp;$C47&amp;" assente","in sostituzione di "&amp;$C47&amp;", doppio turno"),""))</f>
+        <f>IF($M47=1,IF($E47=1,"recupero del turno saltato nella settimana "&amp;$AE47&amp;", "&amp;$C47&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE47&amp;", "&amp;$C47&amp;" a riposo"),IF($E47=1,IF($S47="DA ASSEGNARE","turno da assegnare: "&amp;$C47&amp;" assente","in sostituzione di "&amp;$C47&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z47">
+        <f>IF($T47="","",COUNTIF($T$6:$T47,$T47))</f>
+        <v/>
+      </c>
+      <c r="AA47">
+        <f>IF($T47="","",$T47&amp;"#"&amp;$Z47)</f>
+        <v/>
+      </c>
+      <c r="AB47">
+        <f>COUNTIF($T$6:$T45,$C47)</f>
+        <v/>
+      </c>
+      <c r="AC47">
+        <f>COUNTIFS($C$6:$C45,$C47,$M$6:$M45,1)</f>
+        <v/>
+      </c>
+      <c r="AD47">
+        <f>IF($AB47&gt;$AC47,IFERROR(MATCH($C47&amp;"#"&amp;($AC47+1),$AA$6:$AA45,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE47">
+        <f>IF($AD47=0,"",INDEX($A$6:$A45,$AD47))</f>
         <v/>
       </c>
     </row>
@@ -11906,7 +12932,7 @@
         <v/>
       </c>
       <c r="F48">
-        <f>IF($E48=0,0,IF(OR($D48="Licenza - settimana intera",$D48="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M48=1,0,IF($E48=0,0,IF(OR($D48="Licenza - settimana intera",$D48="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G48">
@@ -11930,7 +12956,7 @@
         <v/>
       </c>
       <c r="L48">
-        <f>IFERROR(INDEX($C41:$C45,MATCH(1,INDEX(($T41:$T45=$C48)*1,0),0)),"")</f>
+        <f>IF($AD48=0,"",INDEX($C$6:$C45,$AD48))</f>
         <v/>
       </c>
       <c r="M48">
@@ -11938,23 +12964,23 @@
         <v/>
       </c>
       <c r="N48">
-        <f>IF($G48=0,100000,IF(Partecipanti!$B$5=$C48,100000,COUNTIF($S$6:$S47,Partecipanti!$B$5)*100+MOD(1-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G48=0,100000,IF(Partecipanti!$B$5=$C48,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S47,Partecipanti!$B$5)*100+MOD(1-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O48">
-        <f>IF($H48=0,100000,IF(Partecipanti!$B$6=$C48,100000,COUNTIF($S$6:$S47,Partecipanti!$B$6)*100+MOD(2-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H48=0,100000,IF(Partecipanti!$B$6=$C48,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S47,Partecipanti!$B$6)*100+MOD(2-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P48">
-        <f>IF($I48=0,100000,IF(Partecipanti!$B$7=$C48,100000,COUNTIF($S$6:$S47,Partecipanti!$B$7)*100+MOD(3-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I48=0,100000,IF(Partecipanti!$B$7=$C48,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S47,Partecipanti!$B$7)*100+MOD(3-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q48">
-        <f>IF($J48=0,100000,IF(Partecipanti!$B$8=$C48,100000,COUNTIF($S$6:$S47,Partecipanti!$B$8)*100+MOD(4-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J48=0,100000,IF(Partecipanti!$B$8=$C48,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S47,Partecipanti!$B$8)*100+MOD(4-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R48">
-        <f>IF($K48=0,100000,IF(Partecipanti!$B$9=$C48,100000,COUNTIF($S$6:$S47,Partecipanti!$B$9)*100+MOD(5-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K48=0,100000,IF(Partecipanti!$B$9=$C48,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S47,Partecipanti!$B$9)*100+MOD(5-MATCH($C48,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S48">
@@ -11978,11 +13004,35 @@
         <v/>
       </c>
       <c r="X48">
-        <f>IF($M48=1,$L48&amp;" recupera il turno saltato nella settimana "&amp;($A48-1)&amp;"; "&amp;$C48&amp;" a riposo compensativo",IF($E48=1,$C48&amp;" assente ("&amp;$D48&amp;")"&amp;IF($S48="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S48&amp;" con doppio turno")&amp;IF($F48=1,"; turno da recuperare nella settimana "&amp;($A48+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M48=1,IF($E48=1,$L48&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE48&amp;"; "&amp;$C48&amp;" assente ("&amp;$D48&amp;")",$L48&amp;" recupera il turno saltato nella settimana "&amp;$AE48&amp;"; "&amp;$C48&amp;" a riposo compensativo"),IF($E48=1,$C48&amp;" assente ("&amp;$D48&amp;")"&amp;IF($S48="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S48&amp;" con doppio turno")&amp;IF($F48=1,"; turno da recuperare a partire dalla settimana "&amp;($A48+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>IF($M48=1,"recupera il turno saltato nella settimana "&amp;($A48-1)&amp;", "&amp;$C48&amp;" a riposo",IF($E48=1,IF($S48="DA ASSEGNARE","turno da assegnare: "&amp;$C48&amp;" assente","in sostituzione di "&amp;$C48&amp;", doppio turno"),""))</f>
+        <f>IF($M48=1,IF($E48=1,"recupero del turno saltato nella settimana "&amp;$AE48&amp;", "&amp;$C48&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE48&amp;", "&amp;$C48&amp;" a riposo"),IF($E48=1,IF($S48="DA ASSEGNARE","turno da assegnare: "&amp;$C48&amp;" assente","in sostituzione di "&amp;$C48&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z48">
+        <f>IF($T48="","",COUNTIF($T$6:$T48,$T48))</f>
+        <v/>
+      </c>
+      <c r="AA48">
+        <f>IF($T48="","",$T48&amp;"#"&amp;$Z48)</f>
+        <v/>
+      </c>
+      <c r="AB48">
+        <f>COUNTIF($T$6:$T45,$C48)</f>
+        <v/>
+      </c>
+      <c r="AC48">
+        <f>COUNTIFS($C$6:$C45,$C48,$M$6:$M45,1)</f>
+        <v/>
+      </c>
+      <c r="AD48">
+        <f>IF($AB48&gt;$AC48,IFERROR(MATCH($C48&amp;"#"&amp;($AC48+1),$AA$6:$AA45,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE48">
+        <f>IF($AD48=0,"",INDEX($A$6:$A45,$AD48))</f>
         <v/>
       </c>
     </row>
@@ -12006,7 +13056,7 @@
         <v/>
       </c>
       <c r="F49">
-        <f>IF($E49=0,0,IF(OR($D49="Licenza - settimana intera",$D49="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M49=1,0,IF($E49=0,0,IF(OR($D49="Licenza - settimana intera",$D49="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G49">
@@ -12030,7 +13080,7 @@
         <v/>
       </c>
       <c r="L49">
-        <f>IFERROR(INDEX($C41:$C45,MATCH(1,INDEX(($T41:$T45=$C49)*1,0),0)),"")</f>
+        <f>IF($AD49=0,"",INDEX($C$6:$C45,$AD49))</f>
         <v/>
       </c>
       <c r="M49">
@@ -12038,23 +13088,23 @@
         <v/>
       </c>
       <c r="N49">
-        <f>IF($G49=0,100000,IF(Partecipanti!$B$5=$C49,100000,COUNTIF($S$6:$S48,Partecipanti!$B$5)*100+MOD(1-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G49=0,100000,IF(Partecipanti!$B$5=$C49,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S48,Partecipanti!$B$5)*100+MOD(1-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O49">
-        <f>IF($H49=0,100000,IF(Partecipanti!$B$6=$C49,100000,COUNTIF($S$6:$S48,Partecipanti!$B$6)*100+MOD(2-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H49=0,100000,IF(Partecipanti!$B$6=$C49,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S48,Partecipanti!$B$6)*100+MOD(2-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P49">
-        <f>IF($I49=0,100000,IF(Partecipanti!$B$7=$C49,100000,COUNTIF($S$6:$S48,Partecipanti!$B$7)*100+MOD(3-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I49=0,100000,IF(Partecipanti!$B$7=$C49,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S48,Partecipanti!$B$7)*100+MOD(3-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q49">
-        <f>IF($J49=0,100000,IF(Partecipanti!$B$8=$C49,100000,COUNTIF($S$6:$S48,Partecipanti!$B$8)*100+MOD(4-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J49=0,100000,IF(Partecipanti!$B$8=$C49,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S48,Partecipanti!$B$8)*100+MOD(4-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R49">
-        <f>IF($K49=0,100000,IF(Partecipanti!$B$9=$C49,100000,COUNTIF($S$6:$S48,Partecipanti!$B$9)*100+MOD(5-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K49=0,100000,IF(Partecipanti!$B$9=$C49,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S48,Partecipanti!$B$9)*100+MOD(5-MATCH($C49,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S49">
@@ -12078,11 +13128,35 @@
         <v/>
       </c>
       <c r="X49">
-        <f>IF($M49=1,$L49&amp;" recupera il turno saltato nella settimana "&amp;($A49-1)&amp;"; "&amp;$C49&amp;" a riposo compensativo",IF($E49=1,$C49&amp;" assente ("&amp;$D49&amp;")"&amp;IF($S49="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S49&amp;" con doppio turno")&amp;IF($F49=1,"; turno da recuperare nella settimana "&amp;($A49+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M49=1,IF($E49=1,$L49&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE49&amp;"; "&amp;$C49&amp;" assente ("&amp;$D49&amp;")",$L49&amp;" recupera il turno saltato nella settimana "&amp;$AE49&amp;"; "&amp;$C49&amp;" a riposo compensativo"),IF($E49=1,$C49&amp;" assente ("&amp;$D49&amp;")"&amp;IF($S49="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S49&amp;" con doppio turno")&amp;IF($F49=1,"; turno da recuperare a partire dalla settimana "&amp;($A49+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>IF($M49=1,"recupera il turno saltato nella settimana "&amp;($A49-1)&amp;", "&amp;$C49&amp;" a riposo",IF($E49=1,IF($S49="DA ASSEGNARE","turno da assegnare: "&amp;$C49&amp;" assente","in sostituzione di "&amp;$C49&amp;", doppio turno"),""))</f>
+        <f>IF($M49=1,IF($E49=1,"recupero del turno saltato nella settimana "&amp;$AE49&amp;", "&amp;$C49&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE49&amp;", "&amp;$C49&amp;" a riposo"),IF($E49=1,IF($S49="DA ASSEGNARE","turno da assegnare: "&amp;$C49&amp;" assente","in sostituzione di "&amp;$C49&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z49">
+        <f>IF($T49="","",COUNTIF($T$6:$T49,$T49))</f>
+        <v/>
+      </c>
+      <c r="AA49">
+        <f>IF($T49="","",$T49&amp;"#"&amp;$Z49)</f>
+        <v/>
+      </c>
+      <c r="AB49">
+        <f>COUNTIF($T$6:$T45,$C49)</f>
+        <v/>
+      </c>
+      <c r="AC49">
+        <f>COUNTIFS($C$6:$C45,$C49,$M$6:$M45,1)</f>
+        <v/>
+      </c>
+      <c r="AD49">
+        <f>IF($AB49&gt;$AC49,IFERROR(MATCH($C49&amp;"#"&amp;($AC49+1),$AA$6:$AA45,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE49">
+        <f>IF($AD49=0,"",INDEX($A$6:$A45,$AD49))</f>
         <v/>
       </c>
     </row>
@@ -12106,7 +13180,7 @@
         <v/>
       </c>
       <c r="F50">
-        <f>IF($E50=0,0,IF(OR($D50="Licenza - settimana intera",$D50="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M50=1,0,IF($E50=0,0,IF(OR($D50="Licenza - settimana intera",$D50="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G50">
@@ -12130,7 +13204,7 @@
         <v/>
       </c>
       <c r="L50">
-        <f>IFERROR(INDEX($C41:$C45,MATCH(1,INDEX(($T41:$T45=$C50)*1,0),0)),"")</f>
+        <f>IF($AD50=0,"",INDEX($C$6:$C45,$AD50))</f>
         <v/>
       </c>
       <c r="M50">
@@ -12138,23 +13212,23 @@
         <v/>
       </c>
       <c r="N50">
-        <f>IF($G50=0,100000,IF(Partecipanti!$B$5=$C50,100000,COUNTIF($S$6:$S49,Partecipanti!$B$5)*100+MOD(1-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G50=0,100000,IF(Partecipanti!$B$5=$C50,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S49,Partecipanti!$B$5)*100+MOD(1-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O50">
-        <f>IF($H50=0,100000,IF(Partecipanti!$B$6=$C50,100000,COUNTIF($S$6:$S49,Partecipanti!$B$6)*100+MOD(2-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H50=0,100000,IF(Partecipanti!$B$6=$C50,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S49,Partecipanti!$B$6)*100+MOD(2-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P50">
-        <f>IF($I50=0,100000,IF(Partecipanti!$B$7=$C50,100000,COUNTIF($S$6:$S49,Partecipanti!$B$7)*100+MOD(3-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I50=0,100000,IF(Partecipanti!$B$7=$C50,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S49,Partecipanti!$B$7)*100+MOD(3-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q50">
-        <f>IF($J50=0,100000,IF(Partecipanti!$B$8=$C50,100000,COUNTIF($S$6:$S49,Partecipanti!$B$8)*100+MOD(4-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J50=0,100000,IF(Partecipanti!$B$8=$C50,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S49,Partecipanti!$B$8)*100+MOD(4-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R50">
-        <f>IF($K50=0,100000,IF(Partecipanti!$B$9=$C50,100000,COUNTIF($S$6:$S49,Partecipanti!$B$9)*100+MOD(5-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K50=0,100000,IF(Partecipanti!$B$9=$C50,100000,IF(SUMPRODUCT(($M$46:$M$50=1)*($L$46:$L$50=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S49,Partecipanti!$B$9)*100+MOD(5-MATCH($C50,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S50">
@@ -12178,11 +13252,35 @@
         <v/>
       </c>
       <c r="X50">
-        <f>IF($M50=1,$L50&amp;" recupera il turno saltato nella settimana "&amp;($A50-1)&amp;"; "&amp;$C50&amp;" a riposo compensativo",IF($E50=1,$C50&amp;" assente ("&amp;$D50&amp;")"&amp;IF($S50="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S50&amp;" con doppio turno")&amp;IF($F50=1,"; turno da recuperare nella settimana "&amp;($A50+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M50=1,IF($E50=1,$L50&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE50&amp;"; "&amp;$C50&amp;" assente ("&amp;$D50&amp;")",$L50&amp;" recupera il turno saltato nella settimana "&amp;$AE50&amp;"; "&amp;$C50&amp;" a riposo compensativo"),IF($E50=1,$C50&amp;" assente ("&amp;$D50&amp;")"&amp;IF($S50="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S50&amp;" con doppio turno")&amp;IF($F50=1,"; turno da recuperare a partire dalla settimana "&amp;($A50+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>IF($M50=1,"recupera il turno saltato nella settimana "&amp;($A50-1)&amp;", "&amp;$C50&amp;" a riposo",IF($E50=1,IF($S50="DA ASSEGNARE","turno da assegnare: "&amp;$C50&amp;" assente","in sostituzione di "&amp;$C50&amp;", doppio turno"),""))</f>
+        <f>IF($M50=1,IF($E50=1,"recupero del turno saltato nella settimana "&amp;$AE50&amp;", "&amp;$C50&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE50&amp;", "&amp;$C50&amp;" a riposo"),IF($E50=1,IF($S50="DA ASSEGNARE","turno da assegnare: "&amp;$C50&amp;" assente","in sostituzione di "&amp;$C50&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z50">
+        <f>IF($T50="","",COUNTIF($T$6:$T50,$T50))</f>
+        <v/>
+      </c>
+      <c r="AA50">
+        <f>IF($T50="","",$T50&amp;"#"&amp;$Z50)</f>
+        <v/>
+      </c>
+      <c r="AB50">
+        <f>COUNTIF($T$6:$T45,$C50)</f>
+        <v/>
+      </c>
+      <c r="AC50">
+        <f>COUNTIFS($C$6:$C45,$C50,$M$6:$M45,1)</f>
+        <v/>
+      </c>
+      <c r="AD50">
+        <f>IF($AB50&gt;$AC50,IFERROR(MATCH($C50&amp;"#"&amp;($AC50+1),$AA$6:$AA45,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE50">
+        <f>IF($AD50=0,"",INDEX($A$6:$A45,$AD50))</f>
         <v/>
       </c>
     </row>
@@ -12206,7 +13304,7 @@
         <v/>
       </c>
       <c r="F51">
-        <f>IF($E51=0,0,IF(OR($D51="Licenza - settimana intera",$D51="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M51=1,0,IF($E51=0,0,IF(OR($D51="Licenza - settimana intera",$D51="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G51">
@@ -12230,7 +13328,7 @@
         <v/>
       </c>
       <c r="L51">
-        <f>IFERROR(INDEX($C46:$C50,MATCH(1,INDEX(($T46:$T50=$C51)*1,0),0)),"")</f>
+        <f>IF($AD51=0,"",INDEX($C$6:$C50,$AD51))</f>
         <v/>
       </c>
       <c r="M51">
@@ -12238,23 +13336,23 @@
         <v/>
       </c>
       <c r="N51">
-        <f>IF($G51=0,100000,IF(Partecipanti!$B$5=$C51,100000,COUNTIF($S$6:$S50,Partecipanti!$B$5)*100+MOD(1-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G51=0,100000,IF(Partecipanti!$B$5=$C51,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S50,Partecipanti!$B$5)*100+MOD(1-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O51">
-        <f>IF($H51=0,100000,IF(Partecipanti!$B$6=$C51,100000,COUNTIF($S$6:$S50,Partecipanti!$B$6)*100+MOD(2-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H51=0,100000,IF(Partecipanti!$B$6=$C51,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S50,Partecipanti!$B$6)*100+MOD(2-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P51">
-        <f>IF($I51=0,100000,IF(Partecipanti!$B$7=$C51,100000,COUNTIF($S$6:$S50,Partecipanti!$B$7)*100+MOD(3-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I51=0,100000,IF(Partecipanti!$B$7=$C51,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S50,Partecipanti!$B$7)*100+MOD(3-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q51">
-        <f>IF($J51=0,100000,IF(Partecipanti!$B$8=$C51,100000,COUNTIF($S$6:$S50,Partecipanti!$B$8)*100+MOD(4-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J51=0,100000,IF(Partecipanti!$B$8=$C51,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S50,Partecipanti!$B$8)*100+MOD(4-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R51">
-        <f>IF($K51=0,100000,IF(Partecipanti!$B$9=$C51,100000,COUNTIF($S$6:$S50,Partecipanti!$B$9)*100+MOD(5-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K51=0,100000,IF(Partecipanti!$B$9=$C51,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S50,Partecipanti!$B$9)*100+MOD(5-MATCH($C51,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S51">
@@ -12278,11 +13376,35 @@
         <v/>
       </c>
       <c r="X51">
-        <f>IF($M51=1,$L51&amp;" recupera il turno saltato nella settimana "&amp;($A51-1)&amp;"; "&amp;$C51&amp;" a riposo compensativo",IF($E51=1,$C51&amp;" assente ("&amp;$D51&amp;")"&amp;IF($S51="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S51&amp;" con doppio turno")&amp;IF($F51=1,"; turno da recuperare nella settimana "&amp;($A51+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M51=1,IF($E51=1,$L51&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE51&amp;"; "&amp;$C51&amp;" assente ("&amp;$D51&amp;")",$L51&amp;" recupera il turno saltato nella settimana "&amp;$AE51&amp;"; "&amp;$C51&amp;" a riposo compensativo"),IF($E51=1,$C51&amp;" assente ("&amp;$D51&amp;")"&amp;IF($S51="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S51&amp;" con doppio turno")&amp;IF($F51=1,"; turno da recuperare a partire dalla settimana "&amp;($A51+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>IF($M51=1,"recupera il turno saltato nella settimana "&amp;($A51-1)&amp;", "&amp;$C51&amp;" a riposo",IF($E51=1,IF($S51="DA ASSEGNARE","turno da assegnare: "&amp;$C51&amp;" assente","in sostituzione di "&amp;$C51&amp;", doppio turno"),""))</f>
+        <f>IF($M51=1,IF($E51=1,"recupero del turno saltato nella settimana "&amp;$AE51&amp;", "&amp;$C51&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE51&amp;", "&amp;$C51&amp;" a riposo"),IF($E51=1,IF($S51="DA ASSEGNARE","turno da assegnare: "&amp;$C51&amp;" assente","in sostituzione di "&amp;$C51&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z51">
+        <f>IF($T51="","",COUNTIF($T$6:$T51,$T51))</f>
+        <v/>
+      </c>
+      <c r="AA51">
+        <f>IF($T51="","",$T51&amp;"#"&amp;$Z51)</f>
+        <v/>
+      </c>
+      <c r="AB51">
+        <f>COUNTIF($T$6:$T50,$C51)</f>
+        <v/>
+      </c>
+      <c r="AC51">
+        <f>COUNTIFS($C$6:$C50,$C51,$M$6:$M50,1)</f>
+        <v/>
+      </c>
+      <c r="AD51">
+        <f>IF($AB51&gt;$AC51,IFERROR(MATCH($C51&amp;"#"&amp;($AC51+1),$AA$6:$AA50,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE51">
+        <f>IF($AD51=0,"",INDEX($A$6:$A50,$AD51))</f>
         <v/>
       </c>
     </row>
@@ -12306,7 +13428,7 @@
         <v/>
       </c>
       <c r="F52">
-        <f>IF($E52=0,0,IF(OR($D52="Licenza - settimana intera",$D52="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M52=1,0,IF($E52=0,0,IF(OR($D52="Licenza - settimana intera",$D52="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G52">
@@ -12330,7 +13452,7 @@
         <v/>
       </c>
       <c r="L52">
-        <f>IFERROR(INDEX($C46:$C50,MATCH(1,INDEX(($T46:$T50=$C52)*1,0),0)),"")</f>
+        <f>IF($AD52=0,"",INDEX($C$6:$C50,$AD52))</f>
         <v/>
       </c>
       <c r="M52">
@@ -12338,23 +13460,23 @@
         <v/>
       </c>
       <c r="N52">
-        <f>IF($G52=0,100000,IF(Partecipanti!$B$5=$C52,100000,COUNTIF($S$6:$S51,Partecipanti!$B$5)*100+MOD(1-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G52=0,100000,IF(Partecipanti!$B$5=$C52,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S51,Partecipanti!$B$5)*100+MOD(1-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O52">
-        <f>IF($H52=0,100000,IF(Partecipanti!$B$6=$C52,100000,COUNTIF($S$6:$S51,Partecipanti!$B$6)*100+MOD(2-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H52=0,100000,IF(Partecipanti!$B$6=$C52,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S51,Partecipanti!$B$6)*100+MOD(2-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P52">
-        <f>IF($I52=0,100000,IF(Partecipanti!$B$7=$C52,100000,COUNTIF($S$6:$S51,Partecipanti!$B$7)*100+MOD(3-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I52=0,100000,IF(Partecipanti!$B$7=$C52,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S51,Partecipanti!$B$7)*100+MOD(3-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q52">
-        <f>IF($J52=0,100000,IF(Partecipanti!$B$8=$C52,100000,COUNTIF($S$6:$S51,Partecipanti!$B$8)*100+MOD(4-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J52=0,100000,IF(Partecipanti!$B$8=$C52,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S51,Partecipanti!$B$8)*100+MOD(4-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R52">
-        <f>IF($K52=0,100000,IF(Partecipanti!$B$9=$C52,100000,COUNTIF($S$6:$S51,Partecipanti!$B$9)*100+MOD(5-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K52=0,100000,IF(Partecipanti!$B$9=$C52,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S51,Partecipanti!$B$9)*100+MOD(5-MATCH($C52,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S52">
@@ -12378,11 +13500,35 @@
         <v/>
       </c>
       <c r="X52">
-        <f>IF($M52=1,$L52&amp;" recupera il turno saltato nella settimana "&amp;($A52-1)&amp;"; "&amp;$C52&amp;" a riposo compensativo",IF($E52=1,$C52&amp;" assente ("&amp;$D52&amp;")"&amp;IF($S52="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S52&amp;" con doppio turno")&amp;IF($F52=1,"; turno da recuperare nella settimana "&amp;($A52+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M52=1,IF($E52=1,$L52&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE52&amp;"; "&amp;$C52&amp;" assente ("&amp;$D52&amp;")",$L52&amp;" recupera il turno saltato nella settimana "&amp;$AE52&amp;"; "&amp;$C52&amp;" a riposo compensativo"),IF($E52=1,$C52&amp;" assente ("&amp;$D52&amp;")"&amp;IF($S52="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S52&amp;" con doppio turno")&amp;IF($F52=1,"; turno da recuperare a partire dalla settimana "&amp;($A52+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>IF($M52=1,"recupera il turno saltato nella settimana "&amp;($A52-1)&amp;", "&amp;$C52&amp;" a riposo",IF($E52=1,IF($S52="DA ASSEGNARE","turno da assegnare: "&amp;$C52&amp;" assente","in sostituzione di "&amp;$C52&amp;", doppio turno"),""))</f>
+        <f>IF($M52=1,IF($E52=1,"recupero del turno saltato nella settimana "&amp;$AE52&amp;", "&amp;$C52&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE52&amp;", "&amp;$C52&amp;" a riposo"),IF($E52=1,IF($S52="DA ASSEGNARE","turno da assegnare: "&amp;$C52&amp;" assente","in sostituzione di "&amp;$C52&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z52">
+        <f>IF($T52="","",COUNTIF($T$6:$T52,$T52))</f>
+        <v/>
+      </c>
+      <c r="AA52">
+        <f>IF($T52="","",$T52&amp;"#"&amp;$Z52)</f>
+        <v/>
+      </c>
+      <c r="AB52">
+        <f>COUNTIF($T$6:$T50,$C52)</f>
+        <v/>
+      </c>
+      <c r="AC52">
+        <f>COUNTIFS($C$6:$C50,$C52,$M$6:$M50,1)</f>
+        <v/>
+      </c>
+      <c r="AD52">
+        <f>IF($AB52&gt;$AC52,IFERROR(MATCH($C52&amp;"#"&amp;($AC52+1),$AA$6:$AA50,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE52">
+        <f>IF($AD52=0,"",INDEX($A$6:$A50,$AD52))</f>
         <v/>
       </c>
     </row>
@@ -12406,7 +13552,7 @@
         <v/>
       </c>
       <c r="F53">
-        <f>IF($E53=0,0,IF(OR($D53="Licenza - settimana intera",$D53="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M53=1,0,IF($E53=0,0,IF(OR($D53="Licenza - settimana intera",$D53="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G53">
@@ -12430,7 +13576,7 @@
         <v/>
       </c>
       <c r="L53">
-        <f>IFERROR(INDEX($C46:$C50,MATCH(1,INDEX(($T46:$T50=$C53)*1,0),0)),"")</f>
+        <f>IF($AD53=0,"",INDEX($C$6:$C50,$AD53))</f>
         <v/>
       </c>
       <c r="M53">
@@ -12438,23 +13584,23 @@
         <v/>
       </c>
       <c r="N53">
-        <f>IF($G53=0,100000,IF(Partecipanti!$B$5=$C53,100000,COUNTIF($S$6:$S52,Partecipanti!$B$5)*100+MOD(1-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G53=0,100000,IF(Partecipanti!$B$5=$C53,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S52,Partecipanti!$B$5)*100+MOD(1-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O53">
-        <f>IF($H53=0,100000,IF(Partecipanti!$B$6=$C53,100000,COUNTIF($S$6:$S52,Partecipanti!$B$6)*100+MOD(2-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H53=0,100000,IF(Partecipanti!$B$6=$C53,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S52,Partecipanti!$B$6)*100+MOD(2-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P53">
-        <f>IF($I53=0,100000,IF(Partecipanti!$B$7=$C53,100000,COUNTIF($S$6:$S52,Partecipanti!$B$7)*100+MOD(3-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I53=0,100000,IF(Partecipanti!$B$7=$C53,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S52,Partecipanti!$B$7)*100+MOD(3-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q53">
-        <f>IF($J53=0,100000,IF(Partecipanti!$B$8=$C53,100000,COUNTIF($S$6:$S52,Partecipanti!$B$8)*100+MOD(4-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J53=0,100000,IF(Partecipanti!$B$8=$C53,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S52,Partecipanti!$B$8)*100+MOD(4-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R53">
-        <f>IF($K53=0,100000,IF(Partecipanti!$B$9=$C53,100000,COUNTIF($S$6:$S52,Partecipanti!$B$9)*100+MOD(5-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K53=0,100000,IF(Partecipanti!$B$9=$C53,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S52,Partecipanti!$B$9)*100+MOD(5-MATCH($C53,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S53">
@@ -12478,11 +13624,35 @@
         <v/>
       </c>
       <c r="X53">
-        <f>IF($M53=1,$L53&amp;" recupera il turno saltato nella settimana "&amp;($A53-1)&amp;"; "&amp;$C53&amp;" a riposo compensativo",IF($E53=1,$C53&amp;" assente ("&amp;$D53&amp;")"&amp;IF($S53="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S53&amp;" con doppio turno")&amp;IF($F53=1,"; turno da recuperare nella settimana "&amp;($A53+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M53=1,IF($E53=1,$L53&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE53&amp;"; "&amp;$C53&amp;" assente ("&amp;$D53&amp;")",$L53&amp;" recupera il turno saltato nella settimana "&amp;$AE53&amp;"; "&amp;$C53&amp;" a riposo compensativo"),IF($E53=1,$C53&amp;" assente ("&amp;$D53&amp;")"&amp;IF($S53="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S53&amp;" con doppio turno")&amp;IF($F53=1,"; turno da recuperare a partire dalla settimana "&amp;($A53+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>IF($M53=1,"recupera il turno saltato nella settimana "&amp;($A53-1)&amp;", "&amp;$C53&amp;" a riposo",IF($E53=1,IF($S53="DA ASSEGNARE","turno da assegnare: "&amp;$C53&amp;" assente","in sostituzione di "&amp;$C53&amp;", doppio turno"),""))</f>
+        <f>IF($M53=1,IF($E53=1,"recupero del turno saltato nella settimana "&amp;$AE53&amp;", "&amp;$C53&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE53&amp;", "&amp;$C53&amp;" a riposo"),IF($E53=1,IF($S53="DA ASSEGNARE","turno da assegnare: "&amp;$C53&amp;" assente","in sostituzione di "&amp;$C53&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z53">
+        <f>IF($T53="","",COUNTIF($T$6:$T53,$T53))</f>
+        <v/>
+      </c>
+      <c r="AA53">
+        <f>IF($T53="","",$T53&amp;"#"&amp;$Z53)</f>
+        <v/>
+      </c>
+      <c r="AB53">
+        <f>COUNTIF($T$6:$T50,$C53)</f>
+        <v/>
+      </c>
+      <c r="AC53">
+        <f>COUNTIFS($C$6:$C50,$C53,$M$6:$M50,1)</f>
+        <v/>
+      </c>
+      <c r="AD53">
+        <f>IF($AB53&gt;$AC53,IFERROR(MATCH($C53&amp;"#"&amp;($AC53+1),$AA$6:$AA50,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE53">
+        <f>IF($AD53=0,"",INDEX($A$6:$A50,$AD53))</f>
         <v/>
       </c>
     </row>
@@ -12506,7 +13676,7 @@
         <v/>
       </c>
       <c r="F54">
-        <f>IF($E54=0,0,IF(OR($D54="Licenza - settimana intera",$D54="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M54=1,0,IF($E54=0,0,IF(OR($D54="Licenza - settimana intera",$D54="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G54">
@@ -12530,7 +13700,7 @@
         <v/>
       </c>
       <c r="L54">
-        <f>IFERROR(INDEX($C46:$C50,MATCH(1,INDEX(($T46:$T50=$C54)*1,0),0)),"")</f>
+        <f>IF($AD54=0,"",INDEX($C$6:$C50,$AD54))</f>
         <v/>
       </c>
       <c r="M54">
@@ -12538,23 +13708,23 @@
         <v/>
       </c>
       <c r="N54">
-        <f>IF($G54=0,100000,IF(Partecipanti!$B$5=$C54,100000,COUNTIF($S$6:$S53,Partecipanti!$B$5)*100+MOD(1-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G54=0,100000,IF(Partecipanti!$B$5=$C54,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S53,Partecipanti!$B$5)*100+MOD(1-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O54">
-        <f>IF($H54=0,100000,IF(Partecipanti!$B$6=$C54,100000,COUNTIF($S$6:$S53,Partecipanti!$B$6)*100+MOD(2-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H54=0,100000,IF(Partecipanti!$B$6=$C54,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S53,Partecipanti!$B$6)*100+MOD(2-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P54">
-        <f>IF($I54=0,100000,IF(Partecipanti!$B$7=$C54,100000,COUNTIF($S$6:$S53,Partecipanti!$B$7)*100+MOD(3-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I54=0,100000,IF(Partecipanti!$B$7=$C54,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S53,Partecipanti!$B$7)*100+MOD(3-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q54">
-        <f>IF($J54=0,100000,IF(Partecipanti!$B$8=$C54,100000,COUNTIF($S$6:$S53,Partecipanti!$B$8)*100+MOD(4-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J54=0,100000,IF(Partecipanti!$B$8=$C54,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S53,Partecipanti!$B$8)*100+MOD(4-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R54">
-        <f>IF($K54=0,100000,IF(Partecipanti!$B$9=$C54,100000,COUNTIF($S$6:$S53,Partecipanti!$B$9)*100+MOD(5-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K54=0,100000,IF(Partecipanti!$B$9=$C54,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S53,Partecipanti!$B$9)*100+MOD(5-MATCH($C54,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S54">
@@ -12578,11 +13748,35 @@
         <v/>
       </c>
       <c r="X54">
-        <f>IF($M54=1,$L54&amp;" recupera il turno saltato nella settimana "&amp;($A54-1)&amp;"; "&amp;$C54&amp;" a riposo compensativo",IF($E54=1,$C54&amp;" assente ("&amp;$D54&amp;")"&amp;IF($S54="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S54&amp;" con doppio turno")&amp;IF($F54=1,"; turno da recuperare nella settimana "&amp;($A54+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M54=1,IF($E54=1,$L54&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE54&amp;"; "&amp;$C54&amp;" assente ("&amp;$D54&amp;")",$L54&amp;" recupera il turno saltato nella settimana "&amp;$AE54&amp;"; "&amp;$C54&amp;" a riposo compensativo"),IF($E54=1,$C54&amp;" assente ("&amp;$D54&amp;")"&amp;IF($S54="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S54&amp;" con doppio turno")&amp;IF($F54=1,"; turno da recuperare a partire dalla settimana "&amp;($A54+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>IF($M54=1,"recupera il turno saltato nella settimana "&amp;($A54-1)&amp;", "&amp;$C54&amp;" a riposo",IF($E54=1,IF($S54="DA ASSEGNARE","turno da assegnare: "&amp;$C54&amp;" assente","in sostituzione di "&amp;$C54&amp;", doppio turno"),""))</f>
+        <f>IF($M54=1,IF($E54=1,"recupero del turno saltato nella settimana "&amp;$AE54&amp;", "&amp;$C54&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE54&amp;", "&amp;$C54&amp;" a riposo"),IF($E54=1,IF($S54="DA ASSEGNARE","turno da assegnare: "&amp;$C54&amp;" assente","in sostituzione di "&amp;$C54&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z54">
+        <f>IF($T54="","",COUNTIF($T$6:$T54,$T54))</f>
+        <v/>
+      </c>
+      <c r="AA54">
+        <f>IF($T54="","",$T54&amp;"#"&amp;$Z54)</f>
+        <v/>
+      </c>
+      <c r="AB54">
+        <f>COUNTIF($T$6:$T50,$C54)</f>
+        <v/>
+      </c>
+      <c r="AC54">
+        <f>COUNTIFS($C$6:$C50,$C54,$M$6:$M50,1)</f>
+        <v/>
+      </c>
+      <c r="AD54">
+        <f>IF($AB54&gt;$AC54,IFERROR(MATCH($C54&amp;"#"&amp;($AC54+1),$AA$6:$AA50,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE54">
+        <f>IF($AD54=0,"",INDEX($A$6:$A50,$AD54))</f>
         <v/>
       </c>
     </row>
@@ -12606,7 +13800,7 @@
         <v/>
       </c>
       <c r="F55">
-        <f>IF($E55=0,0,IF(OR($D55="Licenza - settimana intera",$D55="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M55=1,0,IF($E55=0,0,IF(OR($D55="Licenza - settimana intera",$D55="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G55">
@@ -12630,7 +13824,7 @@
         <v/>
       </c>
       <c r="L55">
-        <f>IFERROR(INDEX($C46:$C50,MATCH(1,INDEX(($T46:$T50=$C55)*1,0),0)),"")</f>
+        <f>IF($AD55=0,"",INDEX($C$6:$C50,$AD55))</f>
         <v/>
       </c>
       <c r="M55">
@@ -12638,23 +13832,23 @@
         <v/>
       </c>
       <c r="N55">
-        <f>IF($G55=0,100000,IF(Partecipanti!$B$5=$C55,100000,COUNTIF($S$6:$S54,Partecipanti!$B$5)*100+MOD(1-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G55=0,100000,IF(Partecipanti!$B$5=$C55,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S54,Partecipanti!$B$5)*100+MOD(1-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O55">
-        <f>IF($H55=0,100000,IF(Partecipanti!$B$6=$C55,100000,COUNTIF($S$6:$S54,Partecipanti!$B$6)*100+MOD(2-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H55=0,100000,IF(Partecipanti!$B$6=$C55,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S54,Partecipanti!$B$6)*100+MOD(2-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P55">
-        <f>IF($I55=0,100000,IF(Partecipanti!$B$7=$C55,100000,COUNTIF($S$6:$S54,Partecipanti!$B$7)*100+MOD(3-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I55=0,100000,IF(Partecipanti!$B$7=$C55,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S54,Partecipanti!$B$7)*100+MOD(3-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q55">
-        <f>IF($J55=0,100000,IF(Partecipanti!$B$8=$C55,100000,COUNTIF($S$6:$S54,Partecipanti!$B$8)*100+MOD(4-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J55=0,100000,IF(Partecipanti!$B$8=$C55,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S54,Partecipanti!$B$8)*100+MOD(4-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R55">
-        <f>IF($K55=0,100000,IF(Partecipanti!$B$9=$C55,100000,COUNTIF($S$6:$S54,Partecipanti!$B$9)*100+MOD(5-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K55=0,100000,IF(Partecipanti!$B$9=$C55,100000,IF(SUMPRODUCT(($M$51:$M$55=1)*($L$51:$L$55=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S54,Partecipanti!$B$9)*100+MOD(5-MATCH($C55,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S55">
@@ -12678,11 +13872,35 @@
         <v/>
       </c>
       <c r="X55">
-        <f>IF($M55=1,$L55&amp;" recupera il turno saltato nella settimana "&amp;($A55-1)&amp;"; "&amp;$C55&amp;" a riposo compensativo",IF($E55=1,$C55&amp;" assente ("&amp;$D55&amp;")"&amp;IF($S55="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S55&amp;" con doppio turno")&amp;IF($F55=1,"; turno da recuperare nella settimana "&amp;($A55+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M55=1,IF($E55=1,$L55&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE55&amp;"; "&amp;$C55&amp;" assente ("&amp;$D55&amp;")",$L55&amp;" recupera il turno saltato nella settimana "&amp;$AE55&amp;"; "&amp;$C55&amp;" a riposo compensativo"),IF($E55=1,$C55&amp;" assente ("&amp;$D55&amp;")"&amp;IF($S55="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S55&amp;" con doppio turno")&amp;IF($F55=1,"; turno da recuperare a partire dalla settimana "&amp;($A55+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y55">
-        <f>IF($M55=1,"recupera il turno saltato nella settimana "&amp;($A55-1)&amp;", "&amp;$C55&amp;" a riposo",IF($E55=1,IF($S55="DA ASSEGNARE","turno da assegnare: "&amp;$C55&amp;" assente","in sostituzione di "&amp;$C55&amp;", doppio turno"),""))</f>
+        <f>IF($M55=1,IF($E55=1,"recupero del turno saltato nella settimana "&amp;$AE55&amp;", "&amp;$C55&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE55&amp;", "&amp;$C55&amp;" a riposo"),IF($E55=1,IF($S55="DA ASSEGNARE","turno da assegnare: "&amp;$C55&amp;" assente","in sostituzione di "&amp;$C55&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z55">
+        <f>IF($T55="","",COUNTIF($T$6:$T55,$T55))</f>
+        <v/>
+      </c>
+      <c r="AA55">
+        <f>IF($T55="","",$T55&amp;"#"&amp;$Z55)</f>
+        <v/>
+      </c>
+      <c r="AB55">
+        <f>COUNTIF($T$6:$T50,$C55)</f>
+        <v/>
+      </c>
+      <c r="AC55">
+        <f>COUNTIFS($C$6:$C50,$C55,$M$6:$M50,1)</f>
+        <v/>
+      </c>
+      <c r="AD55">
+        <f>IF($AB55&gt;$AC55,IFERROR(MATCH($C55&amp;"#"&amp;($AC55+1),$AA$6:$AA50,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE55">
+        <f>IF($AD55=0,"",INDEX($A$6:$A50,$AD55))</f>
         <v/>
       </c>
     </row>
@@ -12706,7 +13924,7 @@
         <v/>
       </c>
       <c r="F56">
-        <f>IF($E56=0,0,IF(OR($D56="Licenza - settimana intera",$D56="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M56=1,0,IF($E56=0,0,IF(OR($D56="Licenza - settimana intera",$D56="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G56">
@@ -12730,7 +13948,7 @@
         <v/>
       </c>
       <c r="L56">
-        <f>IFERROR(INDEX($C51:$C55,MATCH(1,INDEX(($T51:$T55=$C56)*1,0),0)),"")</f>
+        <f>IF($AD56=0,"",INDEX($C$6:$C55,$AD56))</f>
         <v/>
       </c>
       <c r="M56">
@@ -12738,23 +13956,23 @@
         <v/>
       </c>
       <c r="N56">
-        <f>IF($G56=0,100000,IF(Partecipanti!$B$5=$C56,100000,COUNTIF($S$6:$S55,Partecipanti!$B$5)*100+MOD(1-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G56=0,100000,IF(Partecipanti!$B$5=$C56,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S55,Partecipanti!$B$5)*100+MOD(1-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O56">
-        <f>IF($H56=0,100000,IF(Partecipanti!$B$6=$C56,100000,COUNTIF($S$6:$S55,Partecipanti!$B$6)*100+MOD(2-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H56=0,100000,IF(Partecipanti!$B$6=$C56,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S55,Partecipanti!$B$6)*100+MOD(2-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P56">
-        <f>IF($I56=0,100000,IF(Partecipanti!$B$7=$C56,100000,COUNTIF($S$6:$S55,Partecipanti!$B$7)*100+MOD(3-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I56=0,100000,IF(Partecipanti!$B$7=$C56,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S55,Partecipanti!$B$7)*100+MOD(3-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q56">
-        <f>IF($J56=0,100000,IF(Partecipanti!$B$8=$C56,100000,COUNTIF($S$6:$S55,Partecipanti!$B$8)*100+MOD(4-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J56=0,100000,IF(Partecipanti!$B$8=$C56,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S55,Partecipanti!$B$8)*100+MOD(4-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R56">
-        <f>IF($K56=0,100000,IF(Partecipanti!$B$9=$C56,100000,COUNTIF($S$6:$S55,Partecipanti!$B$9)*100+MOD(5-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K56=0,100000,IF(Partecipanti!$B$9=$C56,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S55,Partecipanti!$B$9)*100+MOD(5-MATCH($C56,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S56">
@@ -12778,11 +13996,35 @@
         <v/>
       </c>
       <c r="X56">
-        <f>IF($M56=1,$L56&amp;" recupera il turno saltato nella settimana "&amp;($A56-1)&amp;"; "&amp;$C56&amp;" a riposo compensativo",IF($E56=1,$C56&amp;" assente ("&amp;$D56&amp;")"&amp;IF($S56="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S56&amp;" con doppio turno")&amp;IF($F56=1,"; turno da recuperare nella settimana "&amp;($A56+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M56=1,IF($E56=1,$L56&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE56&amp;"; "&amp;$C56&amp;" assente ("&amp;$D56&amp;")",$L56&amp;" recupera il turno saltato nella settimana "&amp;$AE56&amp;"; "&amp;$C56&amp;" a riposo compensativo"),IF($E56=1,$C56&amp;" assente ("&amp;$D56&amp;")"&amp;IF($S56="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S56&amp;" con doppio turno")&amp;IF($F56=1,"; turno da recuperare a partire dalla settimana "&amp;($A56+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>IF($M56=1,"recupera il turno saltato nella settimana "&amp;($A56-1)&amp;", "&amp;$C56&amp;" a riposo",IF($E56=1,IF($S56="DA ASSEGNARE","turno da assegnare: "&amp;$C56&amp;" assente","in sostituzione di "&amp;$C56&amp;", doppio turno"),""))</f>
+        <f>IF($M56=1,IF($E56=1,"recupero del turno saltato nella settimana "&amp;$AE56&amp;", "&amp;$C56&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE56&amp;", "&amp;$C56&amp;" a riposo"),IF($E56=1,IF($S56="DA ASSEGNARE","turno da assegnare: "&amp;$C56&amp;" assente","in sostituzione di "&amp;$C56&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z56">
+        <f>IF($T56="","",COUNTIF($T$6:$T56,$T56))</f>
+        <v/>
+      </c>
+      <c r="AA56">
+        <f>IF($T56="","",$T56&amp;"#"&amp;$Z56)</f>
+        <v/>
+      </c>
+      <c r="AB56">
+        <f>COUNTIF($T$6:$T55,$C56)</f>
+        <v/>
+      </c>
+      <c r="AC56">
+        <f>COUNTIFS($C$6:$C55,$C56,$M$6:$M55,1)</f>
+        <v/>
+      </c>
+      <c r="AD56">
+        <f>IF($AB56&gt;$AC56,IFERROR(MATCH($C56&amp;"#"&amp;($AC56+1),$AA$6:$AA55,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE56">
+        <f>IF($AD56=0,"",INDEX($A$6:$A55,$AD56))</f>
         <v/>
       </c>
     </row>
@@ -12806,7 +14048,7 @@
         <v/>
       </c>
       <c r="F57">
-        <f>IF($E57=0,0,IF(OR($D57="Licenza - settimana intera",$D57="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M57=1,0,IF($E57=0,0,IF(OR($D57="Licenza - settimana intera",$D57="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G57">
@@ -12830,7 +14072,7 @@
         <v/>
       </c>
       <c r="L57">
-        <f>IFERROR(INDEX($C51:$C55,MATCH(1,INDEX(($T51:$T55=$C57)*1,0),0)),"")</f>
+        <f>IF($AD57=0,"",INDEX($C$6:$C55,$AD57))</f>
         <v/>
       </c>
       <c r="M57">
@@ -12838,23 +14080,23 @@
         <v/>
       </c>
       <c r="N57">
-        <f>IF($G57=0,100000,IF(Partecipanti!$B$5=$C57,100000,COUNTIF($S$6:$S56,Partecipanti!$B$5)*100+MOD(1-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G57=0,100000,IF(Partecipanti!$B$5=$C57,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S56,Partecipanti!$B$5)*100+MOD(1-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O57">
-        <f>IF($H57=0,100000,IF(Partecipanti!$B$6=$C57,100000,COUNTIF($S$6:$S56,Partecipanti!$B$6)*100+MOD(2-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H57=0,100000,IF(Partecipanti!$B$6=$C57,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S56,Partecipanti!$B$6)*100+MOD(2-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P57">
-        <f>IF($I57=0,100000,IF(Partecipanti!$B$7=$C57,100000,COUNTIF($S$6:$S56,Partecipanti!$B$7)*100+MOD(3-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I57=0,100000,IF(Partecipanti!$B$7=$C57,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S56,Partecipanti!$B$7)*100+MOD(3-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q57">
-        <f>IF($J57=0,100000,IF(Partecipanti!$B$8=$C57,100000,COUNTIF($S$6:$S56,Partecipanti!$B$8)*100+MOD(4-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J57=0,100000,IF(Partecipanti!$B$8=$C57,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S56,Partecipanti!$B$8)*100+MOD(4-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R57">
-        <f>IF($K57=0,100000,IF(Partecipanti!$B$9=$C57,100000,COUNTIF($S$6:$S56,Partecipanti!$B$9)*100+MOD(5-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K57=0,100000,IF(Partecipanti!$B$9=$C57,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S56,Partecipanti!$B$9)*100+MOD(5-MATCH($C57,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S57">
@@ -12878,11 +14120,35 @@
         <v/>
       </c>
       <c r="X57">
-        <f>IF($M57=1,$L57&amp;" recupera il turno saltato nella settimana "&amp;($A57-1)&amp;"; "&amp;$C57&amp;" a riposo compensativo",IF($E57=1,$C57&amp;" assente ("&amp;$D57&amp;")"&amp;IF($S57="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S57&amp;" con doppio turno")&amp;IF($F57=1,"; turno da recuperare nella settimana "&amp;($A57+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M57=1,IF($E57=1,$L57&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE57&amp;"; "&amp;$C57&amp;" assente ("&amp;$D57&amp;")",$L57&amp;" recupera il turno saltato nella settimana "&amp;$AE57&amp;"; "&amp;$C57&amp;" a riposo compensativo"),IF($E57=1,$C57&amp;" assente ("&amp;$D57&amp;")"&amp;IF($S57="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S57&amp;" con doppio turno")&amp;IF($F57=1,"; turno da recuperare a partire dalla settimana "&amp;($A57+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>IF($M57=1,"recupera il turno saltato nella settimana "&amp;($A57-1)&amp;", "&amp;$C57&amp;" a riposo",IF($E57=1,IF($S57="DA ASSEGNARE","turno da assegnare: "&amp;$C57&amp;" assente","in sostituzione di "&amp;$C57&amp;", doppio turno"),""))</f>
+        <f>IF($M57=1,IF($E57=1,"recupero del turno saltato nella settimana "&amp;$AE57&amp;", "&amp;$C57&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE57&amp;", "&amp;$C57&amp;" a riposo"),IF($E57=1,IF($S57="DA ASSEGNARE","turno da assegnare: "&amp;$C57&amp;" assente","in sostituzione di "&amp;$C57&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z57">
+        <f>IF($T57="","",COUNTIF($T$6:$T57,$T57))</f>
+        <v/>
+      </c>
+      <c r="AA57">
+        <f>IF($T57="","",$T57&amp;"#"&amp;$Z57)</f>
+        <v/>
+      </c>
+      <c r="AB57">
+        <f>COUNTIF($T$6:$T55,$C57)</f>
+        <v/>
+      </c>
+      <c r="AC57">
+        <f>COUNTIFS($C$6:$C55,$C57,$M$6:$M55,1)</f>
+        <v/>
+      </c>
+      <c r="AD57">
+        <f>IF($AB57&gt;$AC57,IFERROR(MATCH($C57&amp;"#"&amp;($AC57+1),$AA$6:$AA55,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE57">
+        <f>IF($AD57=0,"",INDEX($A$6:$A55,$AD57))</f>
         <v/>
       </c>
     </row>
@@ -12906,7 +14172,7 @@
         <v/>
       </c>
       <c r="F58">
-        <f>IF($E58=0,0,IF(OR($D58="Licenza - settimana intera",$D58="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M58=1,0,IF($E58=0,0,IF(OR($D58="Licenza - settimana intera",$D58="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G58">
@@ -12930,7 +14196,7 @@
         <v/>
       </c>
       <c r="L58">
-        <f>IFERROR(INDEX($C51:$C55,MATCH(1,INDEX(($T51:$T55=$C58)*1,0),0)),"")</f>
+        <f>IF($AD58=0,"",INDEX($C$6:$C55,$AD58))</f>
         <v/>
       </c>
       <c r="M58">
@@ -12938,23 +14204,23 @@
         <v/>
       </c>
       <c r="N58">
-        <f>IF($G58=0,100000,IF(Partecipanti!$B$5=$C58,100000,COUNTIF($S$6:$S57,Partecipanti!$B$5)*100+MOD(1-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G58=0,100000,IF(Partecipanti!$B$5=$C58,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S57,Partecipanti!$B$5)*100+MOD(1-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O58">
-        <f>IF($H58=0,100000,IF(Partecipanti!$B$6=$C58,100000,COUNTIF($S$6:$S57,Partecipanti!$B$6)*100+MOD(2-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H58=0,100000,IF(Partecipanti!$B$6=$C58,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S57,Partecipanti!$B$6)*100+MOD(2-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P58">
-        <f>IF($I58=0,100000,IF(Partecipanti!$B$7=$C58,100000,COUNTIF($S$6:$S57,Partecipanti!$B$7)*100+MOD(3-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I58=0,100000,IF(Partecipanti!$B$7=$C58,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S57,Partecipanti!$B$7)*100+MOD(3-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q58">
-        <f>IF($J58=0,100000,IF(Partecipanti!$B$8=$C58,100000,COUNTIF($S$6:$S57,Partecipanti!$B$8)*100+MOD(4-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J58=0,100000,IF(Partecipanti!$B$8=$C58,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S57,Partecipanti!$B$8)*100+MOD(4-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R58">
-        <f>IF($K58=0,100000,IF(Partecipanti!$B$9=$C58,100000,COUNTIF($S$6:$S57,Partecipanti!$B$9)*100+MOD(5-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K58=0,100000,IF(Partecipanti!$B$9=$C58,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S57,Partecipanti!$B$9)*100+MOD(5-MATCH($C58,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S58">
@@ -12978,11 +14244,35 @@
         <v/>
       </c>
       <c r="X58">
-        <f>IF($M58=1,$L58&amp;" recupera il turno saltato nella settimana "&amp;($A58-1)&amp;"; "&amp;$C58&amp;" a riposo compensativo",IF($E58=1,$C58&amp;" assente ("&amp;$D58&amp;")"&amp;IF($S58="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S58&amp;" con doppio turno")&amp;IF($F58=1,"; turno da recuperare nella settimana "&amp;($A58+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M58=1,IF($E58=1,$L58&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE58&amp;"; "&amp;$C58&amp;" assente ("&amp;$D58&amp;")",$L58&amp;" recupera il turno saltato nella settimana "&amp;$AE58&amp;"; "&amp;$C58&amp;" a riposo compensativo"),IF($E58=1,$C58&amp;" assente ("&amp;$D58&amp;")"&amp;IF($S58="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S58&amp;" con doppio turno")&amp;IF($F58=1,"; turno da recuperare a partire dalla settimana "&amp;($A58+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>IF($M58=1,"recupera il turno saltato nella settimana "&amp;($A58-1)&amp;", "&amp;$C58&amp;" a riposo",IF($E58=1,IF($S58="DA ASSEGNARE","turno da assegnare: "&amp;$C58&amp;" assente","in sostituzione di "&amp;$C58&amp;", doppio turno"),""))</f>
+        <f>IF($M58=1,IF($E58=1,"recupero del turno saltato nella settimana "&amp;$AE58&amp;", "&amp;$C58&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE58&amp;", "&amp;$C58&amp;" a riposo"),IF($E58=1,IF($S58="DA ASSEGNARE","turno da assegnare: "&amp;$C58&amp;" assente","in sostituzione di "&amp;$C58&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z58">
+        <f>IF($T58="","",COUNTIF($T$6:$T58,$T58))</f>
+        <v/>
+      </c>
+      <c r="AA58">
+        <f>IF($T58="","",$T58&amp;"#"&amp;$Z58)</f>
+        <v/>
+      </c>
+      <c r="AB58">
+        <f>COUNTIF($T$6:$T55,$C58)</f>
+        <v/>
+      </c>
+      <c r="AC58">
+        <f>COUNTIFS($C$6:$C55,$C58,$M$6:$M55,1)</f>
+        <v/>
+      </c>
+      <c r="AD58">
+        <f>IF($AB58&gt;$AC58,IFERROR(MATCH($C58&amp;"#"&amp;($AC58+1),$AA$6:$AA55,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE58">
+        <f>IF($AD58=0,"",INDEX($A$6:$A55,$AD58))</f>
         <v/>
       </c>
     </row>
@@ -13006,7 +14296,7 @@
         <v/>
       </c>
       <c r="F59">
-        <f>IF($E59=0,0,IF(OR($D59="Licenza - settimana intera",$D59="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M59=1,0,IF($E59=0,0,IF(OR($D59="Licenza - settimana intera",$D59="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G59">
@@ -13030,7 +14320,7 @@
         <v/>
       </c>
       <c r="L59">
-        <f>IFERROR(INDEX($C51:$C55,MATCH(1,INDEX(($T51:$T55=$C59)*1,0),0)),"")</f>
+        <f>IF($AD59=0,"",INDEX($C$6:$C55,$AD59))</f>
         <v/>
       </c>
       <c r="M59">
@@ -13038,23 +14328,23 @@
         <v/>
       </c>
       <c r="N59">
-        <f>IF($G59=0,100000,IF(Partecipanti!$B$5=$C59,100000,COUNTIF($S$6:$S58,Partecipanti!$B$5)*100+MOD(1-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G59=0,100000,IF(Partecipanti!$B$5=$C59,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S58,Partecipanti!$B$5)*100+MOD(1-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O59">
-        <f>IF($H59=0,100000,IF(Partecipanti!$B$6=$C59,100000,COUNTIF($S$6:$S58,Partecipanti!$B$6)*100+MOD(2-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H59=0,100000,IF(Partecipanti!$B$6=$C59,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S58,Partecipanti!$B$6)*100+MOD(2-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P59">
-        <f>IF($I59=0,100000,IF(Partecipanti!$B$7=$C59,100000,COUNTIF($S$6:$S58,Partecipanti!$B$7)*100+MOD(3-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I59=0,100000,IF(Partecipanti!$B$7=$C59,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S58,Partecipanti!$B$7)*100+MOD(3-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q59">
-        <f>IF($J59=0,100000,IF(Partecipanti!$B$8=$C59,100000,COUNTIF($S$6:$S58,Partecipanti!$B$8)*100+MOD(4-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J59=0,100000,IF(Partecipanti!$B$8=$C59,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S58,Partecipanti!$B$8)*100+MOD(4-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R59">
-        <f>IF($K59=0,100000,IF(Partecipanti!$B$9=$C59,100000,COUNTIF($S$6:$S58,Partecipanti!$B$9)*100+MOD(5-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K59=0,100000,IF(Partecipanti!$B$9=$C59,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S58,Partecipanti!$B$9)*100+MOD(5-MATCH($C59,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S59">
@@ -13078,11 +14368,35 @@
         <v/>
       </c>
       <c r="X59">
-        <f>IF($M59=1,$L59&amp;" recupera il turno saltato nella settimana "&amp;($A59-1)&amp;"; "&amp;$C59&amp;" a riposo compensativo",IF($E59=1,$C59&amp;" assente ("&amp;$D59&amp;")"&amp;IF($S59="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S59&amp;" con doppio turno")&amp;IF($F59=1,"; turno da recuperare nella settimana "&amp;($A59+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M59=1,IF($E59=1,$L59&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE59&amp;"; "&amp;$C59&amp;" assente ("&amp;$D59&amp;")",$L59&amp;" recupera il turno saltato nella settimana "&amp;$AE59&amp;"; "&amp;$C59&amp;" a riposo compensativo"),IF($E59=1,$C59&amp;" assente ("&amp;$D59&amp;")"&amp;IF($S59="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S59&amp;" con doppio turno")&amp;IF($F59=1,"; turno da recuperare a partire dalla settimana "&amp;($A59+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>IF($M59=1,"recupera il turno saltato nella settimana "&amp;($A59-1)&amp;", "&amp;$C59&amp;" a riposo",IF($E59=1,IF($S59="DA ASSEGNARE","turno da assegnare: "&amp;$C59&amp;" assente","in sostituzione di "&amp;$C59&amp;", doppio turno"),""))</f>
+        <f>IF($M59=1,IF($E59=1,"recupero del turno saltato nella settimana "&amp;$AE59&amp;", "&amp;$C59&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE59&amp;", "&amp;$C59&amp;" a riposo"),IF($E59=1,IF($S59="DA ASSEGNARE","turno da assegnare: "&amp;$C59&amp;" assente","in sostituzione di "&amp;$C59&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z59">
+        <f>IF($T59="","",COUNTIF($T$6:$T59,$T59))</f>
+        <v/>
+      </c>
+      <c r="AA59">
+        <f>IF($T59="","",$T59&amp;"#"&amp;$Z59)</f>
+        <v/>
+      </c>
+      <c r="AB59">
+        <f>COUNTIF($T$6:$T55,$C59)</f>
+        <v/>
+      </c>
+      <c r="AC59">
+        <f>COUNTIFS($C$6:$C55,$C59,$M$6:$M55,1)</f>
+        <v/>
+      </c>
+      <c r="AD59">
+        <f>IF($AB59&gt;$AC59,IFERROR(MATCH($C59&amp;"#"&amp;($AC59+1),$AA$6:$AA55,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE59">
+        <f>IF($AD59=0,"",INDEX($A$6:$A55,$AD59))</f>
         <v/>
       </c>
     </row>
@@ -13106,7 +14420,7 @@
         <v/>
       </c>
       <c r="F60">
-        <f>IF($E60=0,0,IF(OR($D60="Licenza - settimana intera",$D60="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M60=1,0,IF($E60=0,0,IF(OR($D60="Licenza - settimana intera",$D60="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G60">
@@ -13130,7 +14444,7 @@
         <v/>
       </c>
       <c r="L60">
-        <f>IFERROR(INDEX($C51:$C55,MATCH(1,INDEX(($T51:$T55=$C60)*1,0),0)),"")</f>
+        <f>IF($AD60=0,"",INDEX($C$6:$C55,$AD60))</f>
         <v/>
       </c>
       <c r="M60">
@@ -13138,23 +14452,23 @@
         <v/>
       </c>
       <c r="N60">
-        <f>IF($G60=0,100000,IF(Partecipanti!$B$5=$C60,100000,COUNTIF($S$6:$S59,Partecipanti!$B$5)*100+MOD(1-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G60=0,100000,IF(Partecipanti!$B$5=$C60,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S59,Partecipanti!$B$5)*100+MOD(1-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O60">
-        <f>IF($H60=0,100000,IF(Partecipanti!$B$6=$C60,100000,COUNTIF($S$6:$S59,Partecipanti!$B$6)*100+MOD(2-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H60=0,100000,IF(Partecipanti!$B$6=$C60,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S59,Partecipanti!$B$6)*100+MOD(2-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P60">
-        <f>IF($I60=0,100000,IF(Partecipanti!$B$7=$C60,100000,COUNTIF($S$6:$S59,Partecipanti!$B$7)*100+MOD(3-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I60=0,100000,IF(Partecipanti!$B$7=$C60,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S59,Partecipanti!$B$7)*100+MOD(3-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q60">
-        <f>IF($J60=0,100000,IF(Partecipanti!$B$8=$C60,100000,COUNTIF($S$6:$S59,Partecipanti!$B$8)*100+MOD(4-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J60=0,100000,IF(Partecipanti!$B$8=$C60,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S59,Partecipanti!$B$8)*100+MOD(4-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R60">
-        <f>IF($K60=0,100000,IF(Partecipanti!$B$9=$C60,100000,COUNTIF($S$6:$S59,Partecipanti!$B$9)*100+MOD(5-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K60=0,100000,IF(Partecipanti!$B$9=$C60,100000,IF(SUMPRODUCT(($M$56:$M$60=1)*($L$56:$L$60=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S59,Partecipanti!$B$9)*100+MOD(5-MATCH($C60,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S60">
@@ -13178,11 +14492,35 @@
         <v/>
       </c>
       <c r="X60">
-        <f>IF($M60=1,$L60&amp;" recupera il turno saltato nella settimana "&amp;($A60-1)&amp;"; "&amp;$C60&amp;" a riposo compensativo",IF($E60=1,$C60&amp;" assente ("&amp;$D60&amp;")"&amp;IF($S60="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S60&amp;" con doppio turno")&amp;IF($F60=1,"; turno da recuperare nella settimana "&amp;($A60+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M60=1,IF($E60=1,$L60&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE60&amp;"; "&amp;$C60&amp;" assente ("&amp;$D60&amp;")",$L60&amp;" recupera il turno saltato nella settimana "&amp;$AE60&amp;"; "&amp;$C60&amp;" a riposo compensativo"),IF($E60=1,$C60&amp;" assente ("&amp;$D60&amp;")"&amp;IF($S60="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S60&amp;" con doppio turno")&amp;IF($F60=1,"; turno da recuperare a partire dalla settimana "&amp;($A60+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y60">
-        <f>IF($M60=1,"recupera il turno saltato nella settimana "&amp;($A60-1)&amp;", "&amp;$C60&amp;" a riposo",IF($E60=1,IF($S60="DA ASSEGNARE","turno da assegnare: "&amp;$C60&amp;" assente","in sostituzione di "&amp;$C60&amp;", doppio turno"),""))</f>
+        <f>IF($M60=1,IF($E60=1,"recupero del turno saltato nella settimana "&amp;$AE60&amp;", "&amp;$C60&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE60&amp;", "&amp;$C60&amp;" a riposo"),IF($E60=1,IF($S60="DA ASSEGNARE","turno da assegnare: "&amp;$C60&amp;" assente","in sostituzione di "&amp;$C60&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z60">
+        <f>IF($T60="","",COUNTIF($T$6:$T60,$T60))</f>
+        <v/>
+      </c>
+      <c r="AA60">
+        <f>IF($T60="","",$T60&amp;"#"&amp;$Z60)</f>
+        <v/>
+      </c>
+      <c r="AB60">
+        <f>COUNTIF($T$6:$T55,$C60)</f>
+        <v/>
+      </c>
+      <c r="AC60">
+        <f>COUNTIFS($C$6:$C55,$C60,$M$6:$M55,1)</f>
+        <v/>
+      </c>
+      <c r="AD60">
+        <f>IF($AB60&gt;$AC60,IFERROR(MATCH($C60&amp;"#"&amp;($AC60+1),$AA$6:$AA55,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE60">
+        <f>IF($AD60=0,"",INDEX($A$6:$A55,$AD60))</f>
         <v/>
       </c>
     </row>
@@ -13206,7 +14544,7 @@
         <v/>
       </c>
       <c r="F61">
-        <f>IF($E61=0,0,IF(OR($D61="Licenza - settimana intera",$D61="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M61=1,0,IF($E61=0,0,IF(OR($D61="Licenza - settimana intera",$D61="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G61">
@@ -13230,7 +14568,7 @@
         <v/>
       </c>
       <c r="L61">
-        <f>IFERROR(INDEX($C56:$C60,MATCH(1,INDEX(($T56:$T60=$C61)*1,0),0)),"")</f>
+        <f>IF($AD61=0,"",INDEX($C$6:$C60,$AD61))</f>
         <v/>
       </c>
       <c r="M61">
@@ -13238,23 +14576,23 @@
         <v/>
       </c>
       <c r="N61">
-        <f>IF($G61=0,100000,IF(Partecipanti!$B$5=$C61,100000,COUNTIF($S$6:$S60,Partecipanti!$B$5)*100+MOD(1-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G61=0,100000,IF(Partecipanti!$B$5=$C61,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S60,Partecipanti!$B$5)*100+MOD(1-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O61">
-        <f>IF($H61=0,100000,IF(Partecipanti!$B$6=$C61,100000,COUNTIF($S$6:$S60,Partecipanti!$B$6)*100+MOD(2-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H61=0,100000,IF(Partecipanti!$B$6=$C61,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S60,Partecipanti!$B$6)*100+MOD(2-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P61">
-        <f>IF($I61=0,100000,IF(Partecipanti!$B$7=$C61,100000,COUNTIF($S$6:$S60,Partecipanti!$B$7)*100+MOD(3-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I61=0,100000,IF(Partecipanti!$B$7=$C61,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S60,Partecipanti!$B$7)*100+MOD(3-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q61">
-        <f>IF($J61=0,100000,IF(Partecipanti!$B$8=$C61,100000,COUNTIF($S$6:$S60,Partecipanti!$B$8)*100+MOD(4-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J61=0,100000,IF(Partecipanti!$B$8=$C61,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S60,Partecipanti!$B$8)*100+MOD(4-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R61">
-        <f>IF($K61=0,100000,IF(Partecipanti!$B$9=$C61,100000,COUNTIF($S$6:$S60,Partecipanti!$B$9)*100+MOD(5-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K61=0,100000,IF(Partecipanti!$B$9=$C61,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S60,Partecipanti!$B$9)*100+MOD(5-MATCH($C61,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S61">
@@ -13278,11 +14616,35 @@
         <v/>
       </c>
       <c r="X61">
-        <f>IF($M61=1,$L61&amp;" recupera il turno saltato nella settimana "&amp;($A61-1)&amp;"; "&amp;$C61&amp;" a riposo compensativo",IF($E61=1,$C61&amp;" assente ("&amp;$D61&amp;")"&amp;IF($S61="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S61&amp;" con doppio turno")&amp;IF($F61=1,"; turno da recuperare nella settimana "&amp;($A61+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M61=1,IF($E61=1,$L61&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE61&amp;"; "&amp;$C61&amp;" assente ("&amp;$D61&amp;")",$L61&amp;" recupera il turno saltato nella settimana "&amp;$AE61&amp;"; "&amp;$C61&amp;" a riposo compensativo"),IF($E61=1,$C61&amp;" assente ("&amp;$D61&amp;")"&amp;IF($S61="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S61&amp;" con doppio turno")&amp;IF($F61=1,"; turno da recuperare a partire dalla settimana "&amp;($A61+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>IF($M61=1,"recupera il turno saltato nella settimana "&amp;($A61-1)&amp;", "&amp;$C61&amp;" a riposo",IF($E61=1,IF($S61="DA ASSEGNARE","turno da assegnare: "&amp;$C61&amp;" assente","in sostituzione di "&amp;$C61&amp;", doppio turno"),""))</f>
+        <f>IF($M61=1,IF($E61=1,"recupero del turno saltato nella settimana "&amp;$AE61&amp;", "&amp;$C61&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE61&amp;", "&amp;$C61&amp;" a riposo"),IF($E61=1,IF($S61="DA ASSEGNARE","turno da assegnare: "&amp;$C61&amp;" assente","in sostituzione di "&amp;$C61&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z61">
+        <f>IF($T61="","",COUNTIF($T$6:$T61,$T61))</f>
+        <v/>
+      </c>
+      <c r="AA61">
+        <f>IF($T61="","",$T61&amp;"#"&amp;$Z61)</f>
+        <v/>
+      </c>
+      <c r="AB61">
+        <f>COUNTIF($T$6:$T60,$C61)</f>
+        <v/>
+      </c>
+      <c r="AC61">
+        <f>COUNTIFS($C$6:$C60,$C61,$M$6:$M60,1)</f>
+        <v/>
+      </c>
+      <c r="AD61">
+        <f>IF($AB61&gt;$AC61,IFERROR(MATCH($C61&amp;"#"&amp;($AC61+1),$AA$6:$AA60,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE61">
+        <f>IF($AD61=0,"",INDEX($A$6:$A60,$AD61))</f>
         <v/>
       </c>
     </row>
@@ -13306,7 +14668,7 @@
         <v/>
       </c>
       <c r="F62">
-        <f>IF($E62=0,0,IF(OR($D62="Licenza - settimana intera",$D62="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M62=1,0,IF($E62=0,0,IF(OR($D62="Licenza - settimana intera",$D62="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G62">
@@ -13330,7 +14692,7 @@
         <v/>
       </c>
       <c r="L62">
-        <f>IFERROR(INDEX($C56:$C60,MATCH(1,INDEX(($T56:$T60=$C62)*1,0),0)),"")</f>
+        <f>IF($AD62=0,"",INDEX($C$6:$C60,$AD62))</f>
         <v/>
       </c>
       <c r="M62">
@@ -13338,23 +14700,23 @@
         <v/>
       </c>
       <c r="N62">
-        <f>IF($G62=0,100000,IF(Partecipanti!$B$5=$C62,100000,COUNTIF($S$6:$S61,Partecipanti!$B$5)*100+MOD(1-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G62=0,100000,IF(Partecipanti!$B$5=$C62,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S61,Partecipanti!$B$5)*100+MOD(1-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O62">
-        <f>IF($H62=0,100000,IF(Partecipanti!$B$6=$C62,100000,COUNTIF($S$6:$S61,Partecipanti!$B$6)*100+MOD(2-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H62=0,100000,IF(Partecipanti!$B$6=$C62,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S61,Partecipanti!$B$6)*100+MOD(2-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P62">
-        <f>IF($I62=0,100000,IF(Partecipanti!$B$7=$C62,100000,COUNTIF($S$6:$S61,Partecipanti!$B$7)*100+MOD(3-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I62=0,100000,IF(Partecipanti!$B$7=$C62,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S61,Partecipanti!$B$7)*100+MOD(3-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q62">
-        <f>IF($J62=0,100000,IF(Partecipanti!$B$8=$C62,100000,COUNTIF($S$6:$S61,Partecipanti!$B$8)*100+MOD(4-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J62=0,100000,IF(Partecipanti!$B$8=$C62,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S61,Partecipanti!$B$8)*100+MOD(4-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R62">
-        <f>IF($K62=0,100000,IF(Partecipanti!$B$9=$C62,100000,COUNTIF($S$6:$S61,Partecipanti!$B$9)*100+MOD(5-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K62=0,100000,IF(Partecipanti!$B$9=$C62,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S61,Partecipanti!$B$9)*100+MOD(5-MATCH($C62,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S62">
@@ -13378,11 +14740,35 @@
         <v/>
       </c>
       <c r="X62">
-        <f>IF($M62=1,$L62&amp;" recupera il turno saltato nella settimana "&amp;($A62-1)&amp;"; "&amp;$C62&amp;" a riposo compensativo",IF($E62=1,$C62&amp;" assente ("&amp;$D62&amp;")"&amp;IF($S62="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S62&amp;" con doppio turno")&amp;IF($F62=1,"; turno da recuperare nella settimana "&amp;($A62+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M62=1,IF($E62=1,$L62&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE62&amp;"; "&amp;$C62&amp;" assente ("&amp;$D62&amp;")",$L62&amp;" recupera il turno saltato nella settimana "&amp;$AE62&amp;"; "&amp;$C62&amp;" a riposo compensativo"),IF($E62=1,$C62&amp;" assente ("&amp;$D62&amp;")"&amp;IF($S62="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S62&amp;" con doppio turno")&amp;IF($F62=1,"; turno da recuperare a partire dalla settimana "&amp;($A62+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>IF($M62=1,"recupera il turno saltato nella settimana "&amp;($A62-1)&amp;", "&amp;$C62&amp;" a riposo",IF($E62=1,IF($S62="DA ASSEGNARE","turno da assegnare: "&amp;$C62&amp;" assente","in sostituzione di "&amp;$C62&amp;", doppio turno"),""))</f>
+        <f>IF($M62=1,IF($E62=1,"recupero del turno saltato nella settimana "&amp;$AE62&amp;", "&amp;$C62&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE62&amp;", "&amp;$C62&amp;" a riposo"),IF($E62=1,IF($S62="DA ASSEGNARE","turno da assegnare: "&amp;$C62&amp;" assente","in sostituzione di "&amp;$C62&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z62">
+        <f>IF($T62="","",COUNTIF($T$6:$T62,$T62))</f>
+        <v/>
+      </c>
+      <c r="AA62">
+        <f>IF($T62="","",$T62&amp;"#"&amp;$Z62)</f>
+        <v/>
+      </c>
+      <c r="AB62">
+        <f>COUNTIF($T$6:$T60,$C62)</f>
+        <v/>
+      </c>
+      <c r="AC62">
+        <f>COUNTIFS($C$6:$C60,$C62,$M$6:$M60,1)</f>
+        <v/>
+      </c>
+      <c r="AD62">
+        <f>IF($AB62&gt;$AC62,IFERROR(MATCH($C62&amp;"#"&amp;($AC62+1),$AA$6:$AA60,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE62">
+        <f>IF($AD62=0,"",INDEX($A$6:$A60,$AD62))</f>
         <v/>
       </c>
     </row>
@@ -13406,7 +14792,7 @@
         <v/>
       </c>
       <c r="F63">
-        <f>IF($E63=0,0,IF(OR($D63="Licenza - settimana intera",$D63="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M63=1,0,IF($E63=0,0,IF(OR($D63="Licenza - settimana intera",$D63="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G63">
@@ -13430,7 +14816,7 @@
         <v/>
       </c>
       <c r="L63">
-        <f>IFERROR(INDEX($C56:$C60,MATCH(1,INDEX(($T56:$T60=$C63)*1,0),0)),"")</f>
+        <f>IF($AD63=0,"",INDEX($C$6:$C60,$AD63))</f>
         <v/>
       </c>
       <c r="M63">
@@ -13438,23 +14824,23 @@
         <v/>
       </c>
       <c r="N63">
-        <f>IF($G63=0,100000,IF(Partecipanti!$B$5=$C63,100000,COUNTIF($S$6:$S62,Partecipanti!$B$5)*100+MOD(1-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G63=0,100000,IF(Partecipanti!$B$5=$C63,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S62,Partecipanti!$B$5)*100+MOD(1-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O63">
-        <f>IF($H63=0,100000,IF(Partecipanti!$B$6=$C63,100000,COUNTIF($S$6:$S62,Partecipanti!$B$6)*100+MOD(2-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H63=0,100000,IF(Partecipanti!$B$6=$C63,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S62,Partecipanti!$B$6)*100+MOD(2-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P63">
-        <f>IF($I63=0,100000,IF(Partecipanti!$B$7=$C63,100000,COUNTIF($S$6:$S62,Partecipanti!$B$7)*100+MOD(3-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I63=0,100000,IF(Partecipanti!$B$7=$C63,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S62,Partecipanti!$B$7)*100+MOD(3-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q63">
-        <f>IF($J63=0,100000,IF(Partecipanti!$B$8=$C63,100000,COUNTIF($S$6:$S62,Partecipanti!$B$8)*100+MOD(4-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J63=0,100000,IF(Partecipanti!$B$8=$C63,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S62,Partecipanti!$B$8)*100+MOD(4-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R63">
-        <f>IF($K63=0,100000,IF(Partecipanti!$B$9=$C63,100000,COUNTIF($S$6:$S62,Partecipanti!$B$9)*100+MOD(5-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K63=0,100000,IF(Partecipanti!$B$9=$C63,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S62,Partecipanti!$B$9)*100+MOD(5-MATCH($C63,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S63">
@@ -13478,11 +14864,35 @@
         <v/>
       </c>
       <c r="X63">
-        <f>IF($M63=1,$L63&amp;" recupera il turno saltato nella settimana "&amp;($A63-1)&amp;"; "&amp;$C63&amp;" a riposo compensativo",IF($E63=1,$C63&amp;" assente ("&amp;$D63&amp;")"&amp;IF($S63="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S63&amp;" con doppio turno")&amp;IF($F63=1,"; turno da recuperare nella settimana "&amp;($A63+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M63=1,IF($E63=1,$L63&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE63&amp;"; "&amp;$C63&amp;" assente ("&amp;$D63&amp;")",$L63&amp;" recupera il turno saltato nella settimana "&amp;$AE63&amp;"; "&amp;$C63&amp;" a riposo compensativo"),IF($E63=1,$C63&amp;" assente ("&amp;$D63&amp;")"&amp;IF($S63="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S63&amp;" con doppio turno")&amp;IF($F63=1,"; turno da recuperare a partire dalla settimana "&amp;($A63+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>IF($M63=1,"recupera il turno saltato nella settimana "&amp;($A63-1)&amp;", "&amp;$C63&amp;" a riposo",IF($E63=1,IF($S63="DA ASSEGNARE","turno da assegnare: "&amp;$C63&amp;" assente","in sostituzione di "&amp;$C63&amp;", doppio turno"),""))</f>
+        <f>IF($M63=1,IF($E63=1,"recupero del turno saltato nella settimana "&amp;$AE63&amp;", "&amp;$C63&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE63&amp;", "&amp;$C63&amp;" a riposo"),IF($E63=1,IF($S63="DA ASSEGNARE","turno da assegnare: "&amp;$C63&amp;" assente","in sostituzione di "&amp;$C63&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z63">
+        <f>IF($T63="","",COUNTIF($T$6:$T63,$T63))</f>
+        <v/>
+      </c>
+      <c r="AA63">
+        <f>IF($T63="","",$T63&amp;"#"&amp;$Z63)</f>
+        <v/>
+      </c>
+      <c r="AB63">
+        <f>COUNTIF($T$6:$T60,$C63)</f>
+        <v/>
+      </c>
+      <c r="AC63">
+        <f>COUNTIFS($C$6:$C60,$C63,$M$6:$M60,1)</f>
+        <v/>
+      </c>
+      <c r="AD63">
+        <f>IF($AB63&gt;$AC63,IFERROR(MATCH($C63&amp;"#"&amp;($AC63+1),$AA$6:$AA60,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE63">
+        <f>IF($AD63=0,"",INDEX($A$6:$A60,$AD63))</f>
         <v/>
       </c>
     </row>
@@ -13506,7 +14916,7 @@
         <v/>
       </c>
       <c r="F64">
-        <f>IF($E64=0,0,IF(OR($D64="Licenza - settimana intera",$D64="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M64=1,0,IF($E64=0,0,IF(OR($D64="Licenza - settimana intera",$D64="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G64">
@@ -13530,7 +14940,7 @@
         <v/>
       </c>
       <c r="L64">
-        <f>IFERROR(INDEX($C56:$C60,MATCH(1,INDEX(($T56:$T60=$C64)*1,0),0)),"")</f>
+        <f>IF($AD64=0,"",INDEX($C$6:$C60,$AD64))</f>
         <v/>
       </c>
       <c r="M64">
@@ -13538,23 +14948,23 @@
         <v/>
       </c>
       <c r="N64">
-        <f>IF($G64=0,100000,IF(Partecipanti!$B$5=$C64,100000,COUNTIF($S$6:$S63,Partecipanti!$B$5)*100+MOD(1-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G64=0,100000,IF(Partecipanti!$B$5=$C64,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S63,Partecipanti!$B$5)*100+MOD(1-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O64">
-        <f>IF($H64=0,100000,IF(Partecipanti!$B$6=$C64,100000,COUNTIF($S$6:$S63,Partecipanti!$B$6)*100+MOD(2-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H64=0,100000,IF(Partecipanti!$B$6=$C64,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S63,Partecipanti!$B$6)*100+MOD(2-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P64">
-        <f>IF($I64=0,100000,IF(Partecipanti!$B$7=$C64,100000,COUNTIF($S$6:$S63,Partecipanti!$B$7)*100+MOD(3-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I64=0,100000,IF(Partecipanti!$B$7=$C64,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S63,Partecipanti!$B$7)*100+MOD(3-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q64">
-        <f>IF($J64=0,100000,IF(Partecipanti!$B$8=$C64,100000,COUNTIF($S$6:$S63,Partecipanti!$B$8)*100+MOD(4-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J64=0,100000,IF(Partecipanti!$B$8=$C64,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S63,Partecipanti!$B$8)*100+MOD(4-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R64">
-        <f>IF($K64=0,100000,IF(Partecipanti!$B$9=$C64,100000,COUNTIF($S$6:$S63,Partecipanti!$B$9)*100+MOD(5-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K64=0,100000,IF(Partecipanti!$B$9=$C64,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S63,Partecipanti!$B$9)*100+MOD(5-MATCH($C64,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S64">
@@ -13578,11 +14988,35 @@
         <v/>
       </c>
       <c r="X64">
-        <f>IF($M64=1,$L64&amp;" recupera il turno saltato nella settimana "&amp;($A64-1)&amp;"; "&amp;$C64&amp;" a riposo compensativo",IF($E64=1,$C64&amp;" assente ("&amp;$D64&amp;")"&amp;IF($S64="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S64&amp;" con doppio turno")&amp;IF($F64=1,"; turno da recuperare nella settimana "&amp;($A64+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M64=1,IF($E64=1,$L64&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE64&amp;"; "&amp;$C64&amp;" assente ("&amp;$D64&amp;")",$L64&amp;" recupera il turno saltato nella settimana "&amp;$AE64&amp;"; "&amp;$C64&amp;" a riposo compensativo"),IF($E64=1,$C64&amp;" assente ("&amp;$D64&amp;")"&amp;IF($S64="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S64&amp;" con doppio turno")&amp;IF($F64=1,"; turno da recuperare a partire dalla settimana "&amp;($A64+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>IF($M64=1,"recupera il turno saltato nella settimana "&amp;($A64-1)&amp;", "&amp;$C64&amp;" a riposo",IF($E64=1,IF($S64="DA ASSEGNARE","turno da assegnare: "&amp;$C64&amp;" assente","in sostituzione di "&amp;$C64&amp;", doppio turno"),""))</f>
+        <f>IF($M64=1,IF($E64=1,"recupero del turno saltato nella settimana "&amp;$AE64&amp;", "&amp;$C64&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE64&amp;", "&amp;$C64&amp;" a riposo"),IF($E64=1,IF($S64="DA ASSEGNARE","turno da assegnare: "&amp;$C64&amp;" assente","in sostituzione di "&amp;$C64&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z64">
+        <f>IF($T64="","",COUNTIF($T$6:$T64,$T64))</f>
+        <v/>
+      </c>
+      <c r="AA64">
+        <f>IF($T64="","",$T64&amp;"#"&amp;$Z64)</f>
+        <v/>
+      </c>
+      <c r="AB64">
+        <f>COUNTIF($T$6:$T60,$C64)</f>
+        <v/>
+      </c>
+      <c r="AC64">
+        <f>COUNTIFS($C$6:$C60,$C64,$M$6:$M60,1)</f>
+        <v/>
+      </c>
+      <c r="AD64">
+        <f>IF($AB64&gt;$AC64,IFERROR(MATCH($C64&amp;"#"&amp;($AC64+1),$AA$6:$AA60,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE64">
+        <f>IF($AD64=0,"",INDEX($A$6:$A60,$AD64))</f>
         <v/>
       </c>
     </row>
@@ -13606,7 +15040,7 @@
         <v/>
       </c>
       <c r="F65">
-        <f>IF($E65=0,0,IF(OR($D65="Licenza - settimana intera",$D65="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M65=1,0,IF($E65=0,0,IF(OR($D65="Licenza - settimana intera",$D65="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G65">
@@ -13630,7 +15064,7 @@
         <v/>
       </c>
       <c r="L65">
-        <f>IFERROR(INDEX($C56:$C60,MATCH(1,INDEX(($T56:$T60=$C65)*1,0),0)),"")</f>
+        <f>IF($AD65=0,"",INDEX($C$6:$C60,$AD65))</f>
         <v/>
       </c>
       <c r="M65">
@@ -13638,23 +15072,23 @@
         <v/>
       </c>
       <c r="N65">
-        <f>IF($G65=0,100000,IF(Partecipanti!$B$5=$C65,100000,COUNTIF($S$6:$S64,Partecipanti!$B$5)*100+MOD(1-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G65=0,100000,IF(Partecipanti!$B$5=$C65,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S64,Partecipanti!$B$5)*100+MOD(1-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O65">
-        <f>IF($H65=0,100000,IF(Partecipanti!$B$6=$C65,100000,COUNTIF($S$6:$S64,Partecipanti!$B$6)*100+MOD(2-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H65=0,100000,IF(Partecipanti!$B$6=$C65,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S64,Partecipanti!$B$6)*100+MOD(2-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P65">
-        <f>IF($I65=0,100000,IF(Partecipanti!$B$7=$C65,100000,COUNTIF($S$6:$S64,Partecipanti!$B$7)*100+MOD(3-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I65=0,100000,IF(Partecipanti!$B$7=$C65,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S64,Partecipanti!$B$7)*100+MOD(3-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q65">
-        <f>IF($J65=0,100000,IF(Partecipanti!$B$8=$C65,100000,COUNTIF($S$6:$S64,Partecipanti!$B$8)*100+MOD(4-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J65=0,100000,IF(Partecipanti!$B$8=$C65,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S64,Partecipanti!$B$8)*100+MOD(4-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R65">
-        <f>IF($K65=0,100000,IF(Partecipanti!$B$9=$C65,100000,COUNTIF($S$6:$S64,Partecipanti!$B$9)*100+MOD(5-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K65=0,100000,IF(Partecipanti!$B$9=$C65,100000,IF(SUMPRODUCT(($M$61:$M$65=1)*($L$61:$L$65=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S64,Partecipanti!$B$9)*100+MOD(5-MATCH($C65,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S65">
@@ -13678,11 +15112,35 @@
         <v/>
       </c>
       <c r="X65">
-        <f>IF($M65=1,$L65&amp;" recupera il turno saltato nella settimana "&amp;($A65-1)&amp;"; "&amp;$C65&amp;" a riposo compensativo",IF($E65=1,$C65&amp;" assente ("&amp;$D65&amp;")"&amp;IF($S65="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S65&amp;" con doppio turno")&amp;IF($F65=1,"; turno da recuperare nella settimana "&amp;($A65+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M65=1,IF($E65=1,$L65&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE65&amp;"; "&amp;$C65&amp;" assente ("&amp;$D65&amp;")",$L65&amp;" recupera il turno saltato nella settimana "&amp;$AE65&amp;"; "&amp;$C65&amp;" a riposo compensativo"),IF($E65=1,$C65&amp;" assente ("&amp;$D65&amp;")"&amp;IF($S65="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S65&amp;" con doppio turno")&amp;IF($F65=1,"; turno da recuperare a partire dalla settimana "&amp;($A65+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>IF($M65=1,"recupera il turno saltato nella settimana "&amp;($A65-1)&amp;", "&amp;$C65&amp;" a riposo",IF($E65=1,IF($S65="DA ASSEGNARE","turno da assegnare: "&amp;$C65&amp;" assente","in sostituzione di "&amp;$C65&amp;", doppio turno"),""))</f>
+        <f>IF($M65=1,IF($E65=1,"recupero del turno saltato nella settimana "&amp;$AE65&amp;", "&amp;$C65&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE65&amp;", "&amp;$C65&amp;" a riposo"),IF($E65=1,IF($S65="DA ASSEGNARE","turno da assegnare: "&amp;$C65&amp;" assente","in sostituzione di "&amp;$C65&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z65">
+        <f>IF($T65="","",COUNTIF($T$6:$T65,$T65))</f>
+        <v/>
+      </c>
+      <c r="AA65">
+        <f>IF($T65="","",$T65&amp;"#"&amp;$Z65)</f>
+        <v/>
+      </c>
+      <c r="AB65">
+        <f>COUNTIF($T$6:$T60,$C65)</f>
+        <v/>
+      </c>
+      <c r="AC65">
+        <f>COUNTIFS($C$6:$C60,$C65,$M$6:$M60,1)</f>
+        <v/>
+      </c>
+      <c r="AD65">
+        <f>IF($AB65&gt;$AC65,IFERROR(MATCH($C65&amp;"#"&amp;($AC65+1),$AA$6:$AA60,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE65">
+        <f>IF($AD65=0,"",INDEX($A$6:$A60,$AD65))</f>
         <v/>
       </c>
     </row>
@@ -13706,7 +15164,7 @@
         <v/>
       </c>
       <c r="F66">
-        <f>IF($E66=0,0,IF(OR($D66="Licenza - settimana intera",$D66="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M66=1,0,IF($E66=0,0,IF(OR($D66="Licenza - settimana intera",$D66="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G66">
@@ -13730,7 +15188,7 @@
         <v/>
       </c>
       <c r="L66">
-        <f>IFERROR(INDEX($C61:$C65,MATCH(1,INDEX(($T61:$T65=$C66)*1,0),0)),"")</f>
+        <f>IF($AD66=0,"",INDEX($C$6:$C65,$AD66))</f>
         <v/>
       </c>
       <c r="M66">
@@ -13738,23 +15196,23 @@
         <v/>
       </c>
       <c r="N66">
-        <f>IF($G66=0,100000,IF(Partecipanti!$B$5=$C66,100000,COUNTIF($S$6:$S65,Partecipanti!$B$5)*100+MOD(1-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G66=0,100000,IF(Partecipanti!$B$5=$C66,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S65,Partecipanti!$B$5)*100+MOD(1-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O66">
-        <f>IF($H66=0,100000,IF(Partecipanti!$B$6=$C66,100000,COUNTIF($S$6:$S65,Partecipanti!$B$6)*100+MOD(2-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H66=0,100000,IF(Partecipanti!$B$6=$C66,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S65,Partecipanti!$B$6)*100+MOD(2-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P66">
-        <f>IF($I66=0,100000,IF(Partecipanti!$B$7=$C66,100000,COUNTIF($S$6:$S65,Partecipanti!$B$7)*100+MOD(3-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I66=0,100000,IF(Partecipanti!$B$7=$C66,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S65,Partecipanti!$B$7)*100+MOD(3-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q66">
-        <f>IF($J66=0,100000,IF(Partecipanti!$B$8=$C66,100000,COUNTIF($S$6:$S65,Partecipanti!$B$8)*100+MOD(4-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J66=0,100000,IF(Partecipanti!$B$8=$C66,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S65,Partecipanti!$B$8)*100+MOD(4-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R66">
-        <f>IF($K66=0,100000,IF(Partecipanti!$B$9=$C66,100000,COUNTIF($S$6:$S65,Partecipanti!$B$9)*100+MOD(5-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K66=0,100000,IF(Partecipanti!$B$9=$C66,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S65,Partecipanti!$B$9)*100+MOD(5-MATCH($C66,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S66">
@@ -13778,11 +15236,35 @@
         <v/>
       </c>
       <c r="X66">
-        <f>IF($M66=1,$L66&amp;" recupera il turno saltato nella settimana "&amp;($A66-1)&amp;"; "&amp;$C66&amp;" a riposo compensativo",IF($E66=1,$C66&amp;" assente ("&amp;$D66&amp;")"&amp;IF($S66="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S66&amp;" con doppio turno")&amp;IF($F66=1,"; turno da recuperare nella settimana "&amp;($A66+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M66=1,IF($E66=1,$L66&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE66&amp;"; "&amp;$C66&amp;" assente ("&amp;$D66&amp;")",$L66&amp;" recupera il turno saltato nella settimana "&amp;$AE66&amp;"; "&amp;$C66&amp;" a riposo compensativo"),IF($E66=1,$C66&amp;" assente ("&amp;$D66&amp;")"&amp;IF($S66="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S66&amp;" con doppio turno")&amp;IF($F66=1,"; turno da recuperare a partire dalla settimana "&amp;($A66+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y66">
-        <f>IF($M66=1,"recupera il turno saltato nella settimana "&amp;($A66-1)&amp;", "&amp;$C66&amp;" a riposo",IF($E66=1,IF($S66="DA ASSEGNARE","turno da assegnare: "&amp;$C66&amp;" assente","in sostituzione di "&amp;$C66&amp;", doppio turno"),""))</f>
+        <f>IF($M66=1,IF($E66=1,"recupero del turno saltato nella settimana "&amp;$AE66&amp;", "&amp;$C66&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE66&amp;", "&amp;$C66&amp;" a riposo"),IF($E66=1,IF($S66="DA ASSEGNARE","turno da assegnare: "&amp;$C66&amp;" assente","in sostituzione di "&amp;$C66&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z66">
+        <f>IF($T66="","",COUNTIF($T$6:$T66,$T66))</f>
+        <v/>
+      </c>
+      <c r="AA66">
+        <f>IF($T66="","",$T66&amp;"#"&amp;$Z66)</f>
+        <v/>
+      </c>
+      <c r="AB66">
+        <f>COUNTIF($T$6:$T65,$C66)</f>
+        <v/>
+      </c>
+      <c r="AC66">
+        <f>COUNTIFS($C$6:$C65,$C66,$M$6:$M65,1)</f>
+        <v/>
+      </c>
+      <c r="AD66">
+        <f>IF($AB66&gt;$AC66,IFERROR(MATCH($C66&amp;"#"&amp;($AC66+1),$AA$6:$AA65,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE66">
+        <f>IF($AD66=0,"",INDEX($A$6:$A65,$AD66))</f>
         <v/>
       </c>
     </row>
@@ -13806,7 +15288,7 @@
         <v/>
       </c>
       <c r="F67">
-        <f>IF($E67=0,0,IF(OR($D67="Licenza - settimana intera",$D67="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M67=1,0,IF($E67=0,0,IF(OR($D67="Licenza - settimana intera",$D67="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G67">
@@ -13830,7 +15312,7 @@
         <v/>
       </c>
       <c r="L67">
-        <f>IFERROR(INDEX($C61:$C65,MATCH(1,INDEX(($T61:$T65=$C67)*1,0),0)),"")</f>
+        <f>IF($AD67=0,"",INDEX($C$6:$C65,$AD67))</f>
         <v/>
       </c>
       <c r="M67">
@@ -13838,23 +15320,23 @@
         <v/>
       </c>
       <c r="N67">
-        <f>IF($G67=0,100000,IF(Partecipanti!$B$5=$C67,100000,COUNTIF($S$6:$S66,Partecipanti!$B$5)*100+MOD(1-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G67=0,100000,IF(Partecipanti!$B$5=$C67,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S66,Partecipanti!$B$5)*100+MOD(1-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O67">
-        <f>IF($H67=0,100000,IF(Partecipanti!$B$6=$C67,100000,COUNTIF($S$6:$S66,Partecipanti!$B$6)*100+MOD(2-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H67=0,100000,IF(Partecipanti!$B$6=$C67,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S66,Partecipanti!$B$6)*100+MOD(2-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P67">
-        <f>IF($I67=0,100000,IF(Partecipanti!$B$7=$C67,100000,COUNTIF($S$6:$S66,Partecipanti!$B$7)*100+MOD(3-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I67=0,100000,IF(Partecipanti!$B$7=$C67,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S66,Partecipanti!$B$7)*100+MOD(3-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q67">
-        <f>IF($J67=0,100000,IF(Partecipanti!$B$8=$C67,100000,COUNTIF($S$6:$S66,Partecipanti!$B$8)*100+MOD(4-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J67=0,100000,IF(Partecipanti!$B$8=$C67,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S66,Partecipanti!$B$8)*100+MOD(4-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R67">
-        <f>IF($K67=0,100000,IF(Partecipanti!$B$9=$C67,100000,COUNTIF($S$6:$S66,Partecipanti!$B$9)*100+MOD(5-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K67=0,100000,IF(Partecipanti!$B$9=$C67,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S66,Partecipanti!$B$9)*100+MOD(5-MATCH($C67,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S67">
@@ -13878,11 +15360,35 @@
         <v/>
       </c>
       <c r="X67">
-        <f>IF($M67=1,$L67&amp;" recupera il turno saltato nella settimana "&amp;($A67-1)&amp;"; "&amp;$C67&amp;" a riposo compensativo",IF($E67=1,$C67&amp;" assente ("&amp;$D67&amp;")"&amp;IF($S67="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S67&amp;" con doppio turno")&amp;IF($F67=1,"; turno da recuperare nella settimana "&amp;($A67+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M67=1,IF($E67=1,$L67&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE67&amp;"; "&amp;$C67&amp;" assente ("&amp;$D67&amp;")",$L67&amp;" recupera il turno saltato nella settimana "&amp;$AE67&amp;"; "&amp;$C67&amp;" a riposo compensativo"),IF($E67=1,$C67&amp;" assente ("&amp;$D67&amp;")"&amp;IF($S67="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S67&amp;" con doppio turno")&amp;IF($F67=1,"; turno da recuperare a partire dalla settimana "&amp;($A67+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y67">
-        <f>IF($M67=1,"recupera il turno saltato nella settimana "&amp;($A67-1)&amp;", "&amp;$C67&amp;" a riposo",IF($E67=1,IF($S67="DA ASSEGNARE","turno da assegnare: "&amp;$C67&amp;" assente","in sostituzione di "&amp;$C67&amp;", doppio turno"),""))</f>
+        <f>IF($M67=1,IF($E67=1,"recupero del turno saltato nella settimana "&amp;$AE67&amp;", "&amp;$C67&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE67&amp;", "&amp;$C67&amp;" a riposo"),IF($E67=1,IF($S67="DA ASSEGNARE","turno da assegnare: "&amp;$C67&amp;" assente","in sostituzione di "&amp;$C67&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z67">
+        <f>IF($T67="","",COUNTIF($T$6:$T67,$T67))</f>
+        <v/>
+      </c>
+      <c r="AA67">
+        <f>IF($T67="","",$T67&amp;"#"&amp;$Z67)</f>
+        <v/>
+      </c>
+      <c r="AB67">
+        <f>COUNTIF($T$6:$T65,$C67)</f>
+        <v/>
+      </c>
+      <c r="AC67">
+        <f>COUNTIFS($C$6:$C65,$C67,$M$6:$M65,1)</f>
+        <v/>
+      </c>
+      <c r="AD67">
+        <f>IF($AB67&gt;$AC67,IFERROR(MATCH($C67&amp;"#"&amp;($AC67+1),$AA$6:$AA65,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE67">
+        <f>IF($AD67=0,"",INDEX($A$6:$A65,$AD67))</f>
         <v/>
       </c>
     </row>
@@ -13906,7 +15412,7 @@
         <v/>
       </c>
       <c r="F68">
-        <f>IF($E68=0,0,IF(OR($D68="Licenza - settimana intera",$D68="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M68=1,0,IF($E68=0,0,IF(OR($D68="Licenza - settimana intera",$D68="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G68">
@@ -13930,7 +15436,7 @@
         <v/>
       </c>
       <c r="L68">
-        <f>IFERROR(INDEX($C61:$C65,MATCH(1,INDEX(($T61:$T65=$C68)*1,0),0)),"")</f>
+        <f>IF($AD68=0,"",INDEX($C$6:$C65,$AD68))</f>
         <v/>
       </c>
       <c r="M68">
@@ -13938,23 +15444,23 @@
         <v/>
       </c>
       <c r="N68">
-        <f>IF($G68=0,100000,IF(Partecipanti!$B$5=$C68,100000,COUNTIF($S$6:$S67,Partecipanti!$B$5)*100+MOD(1-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G68=0,100000,IF(Partecipanti!$B$5=$C68,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S67,Partecipanti!$B$5)*100+MOD(1-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O68">
-        <f>IF($H68=0,100000,IF(Partecipanti!$B$6=$C68,100000,COUNTIF($S$6:$S67,Partecipanti!$B$6)*100+MOD(2-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H68=0,100000,IF(Partecipanti!$B$6=$C68,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S67,Partecipanti!$B$6)*100+MOD(2-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P68">
-        <f>IF($I68=0,100000,IF(Partecipanti!$B$7=$C68,100000,COUNTIF($S$6:$S67,Partecipanti!$B$7)*100+MOD(3-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I68=0,100000,IF(Partecipanti!$B$7=$C68,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S67,Partecipanti!$B$7)*100+MOD(3-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q68">
-        <f>IF($J68=0,100000,IF(Partecipanti!$B$8=$C68,100000,COUNTIF($S$6:$S67,Partecipanti!$B$8)*100+MOD(4-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J68=0,100000,IF(Partecipanti!$B$8=$C68,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S67,Partecipanti!$B$8)*100+MOD(4-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R68">
-        <f>IF($K68=0,100000,IF(Partecipanti!$B$9=$C68,100000,COUNTIF($S$6:$S67,Partecipanti!$B$9)*100+MOD(5-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K68=0,100000,IF(Partecipanti!$B$9=$C68,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S67,Partecipanti!$B$9)*100+MOD(5-MATCH($C68,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S68">
@@ -13978,11 +15484,35 @@
         <v/>
       </c>
       <c r="X68">
-        <f>IF($M68=1,$L68&amp;" recupera il turno saltato nella settimana "&amp;($A68-1)&amp;"; "&amp;$C68&amp;" a riposo compensativo",IF($E68=1,$C68&amp;" assente ("&amp;$D68&amp;")"&amp;IF($S68="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S68&amp;" con doppio turno")&amp;IF($F68=1,"; turno da recuperare nella settimana "&amp;($A68+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M68=1,IF($E68=1,$L68&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE68&amp;"; "&amp;$C68&amp;" assente ("&amp;$D68&amp;")",$L68&amp;" recupera il turno saltato nella settimana "&amp;$AE68&amp;"; "&amp;$C68&amp;" a riposo compensativo"),IF($E68=1,$C68&amp;" assente ("&amp;$D68&amp;")"&amp;IF($S68="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S68&amp;" con doppio turno")&amp;IF($F68=1,"; turno da recuperare a partire dalla settimana "&amp;($A68+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y68">
-        <f>IF($M68=1,"recupera il turno saltato nella settimana "&amp;($A68-1)&amp;", "&amp;$C68&amp;" a riposo",IF($E68=1,IF($S68="DA ASSEGNARE","turno da assegnare: "&amp;$C68&amp;" assente","in sostituzione di "&amp;$C68&amp;", doppio turno"),""))</f>
+        <f>IF($M68=1,IF($E68=1,"recupero del turno saltato nella settimana "&amp;$AE68&amp;", "&amp;$C68&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE68&amp;", "&amp;$C68&amp;" a riposo"),IF($E68=1,IF($S68="DA ASSEGNARE","turno da assegnare: "&amp;$C68&amp;" assente","in sostituzione di "&amp;$C68&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z68">
+        <f>IF($T68="","",COUNTIF($T$6:$T68,$T68))</f>
+        <v/>
+      </c>
+      <c r="AA68">
+        <f>IF($T68="","",$T68&amp;"#"&amp;$Z68)</f>
+        <v/>
+      </c>
+      <c r="AB68">
+        <f>COUNTIF($T$6:$T65,$C68)</f>
+        <v/>
+      </c>
+      <c r="AC68">
+        <f>COUNTIFS($C$6:$C65,$C68,$M$6:$M65,1)</f>
+        <v/>
+      </c>
+      <c r="AD68">
+        <f>IF($AB68&gt;$AC68,IFERROR(MATCH($C68&amp;"#"&amp;($AC68+1),$AA$6:$AA65,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE68">
+        <f>IF($AD68=0,"",INDEX($A$6:$A65,$AD68))</f>
         <v/>
       </c>
     </row>
@@ -14006,7 +15536,7 @@
         <v/>
       </c>
       <c r="F69">
-        <f>IF($E69=0,0,IF(OR($D69="Licenza - settimana intera",$D69="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M69=1,0,IF($E69=0,0,IF(OR($D69="Licenza - settimana intera",$D69="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G69">
@@ -14030,7 +15560,7 @@
         <v/>
       </c>
       <c r="L69">
-        <f>IFERROR(INDEX($C61:$C65,MATCH(1,INDEX(($T61:$T65=$C69)*1,0),0)),"")</f>
+        <f>IF($AD69=0,"",INDEX($C$6:$C65,$AD69))</f>
         <v/>
       </c>
       <c r="M69">
@@ -14038,23 +15568,23 @@
         <v/>
       </c>
       <c r="N69">
-        <f>IF($G69=0,100000,IF(Partecipanti!$B$5=$C69,100000,COUNTIF($S$6:$S68,Partecipanti!$B$5)*100+MOD(1-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G69=0,100000,IF(Partecipanti!$B$5=$C69,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S68,Partecipanti!$B$5)*100+MOD(1-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O69">
-        <f>IF($H69=0,100000,IF(Partecipanti!$B$6=$C69,100000,COUNTIF($S$6:$S68,Partecipanti!$B$6)*100+MOD(2-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H69=0,100000,IF(Partecipanti!$B$6=$C69,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S68,Partecipanti!$B$6)*100+MOD(2-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P69">
-        <f>IF($I69=0,100000,IF(Partecipanti!$B$7=$C69,100000,COUNTIF($S$6:$S68,Partecipanti!$B$7)*100+MOD(3-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I69=0,100000,IF(Partecipanti!$B$7=$C69,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S68,Partecipanti!$B$7)*100+MOD(3-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q69">
-        <f>IF($J69=0,100000,IF(Partecipanti!$B$8=$C69,100000,COUNTIF($S$6:$S68,Partecipanti!$B$8)*100+MOD(4-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J69=0,100000,IF(Partecipanti!$B$8=$C69,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S68,Partecipanti!$B$8)*100+MOD(4-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R69">
-        <f>IF($K69=0,100000,IF(Partecipanti!$B$9=$C69,100000,COUNTIF($S$6:$S68,Partecipanti!$B$9)*100+MOD(5-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K69=0,100000,IF(Partecipanti!$B$9=$C69,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S68,Partecipanti!$B$9)*100+MOD(5-MATCH($C69,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S69">
@@ -14078,11 +15608,35 @@
         <v/>
       </c>
       <c r="X69">
-        <f>IF($M69=1,$L69&amp;" recupera il turno saltato nella settimana "&amp;($A69-1)&amp;"; "&amp;$C69&amp;" a riposo compensativo",IF($E69=1,$C69&amp;" assente ("&amp;$D69&amp;")"&amp;IF($S69="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S69&amp;" con doppio turno")&amp;IF($F69=1,"; turno da recuperare nella settimana "&amp;($A69+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M69=1,IF($E69=1,$L69&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE69&amp;"; "&amp;$C69&amp;" assente ("&amp;$D69&amp;")",$L69&amp;" recupera il turno saltato nella settimana "&amp;$AE69&amp;"; "&amp;$C69&amp;" a riposo compensativo"),IF($E69=1,$C69&amp;" assente ("&amp;$D69&amp;")"&amp;IF($S69="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S69&amp;" con doppio turno")&amp;IF($F69=1,"; turno da recuperare a partire dalla settimana "&amp;($A69+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y69">
-        <f>IF($M69=1,"recupera il turno saltato nella settimana "&amp;($A69-1)&amp;", "&amp;$C69&amp;" a riposo",IF($E69=1,IF($S69="DA ASSEGNARE","turno da assegnare: "&amp;$C69&amp;" assente","in sostituzione di "&amp;$C69&amp;", doppio turno"),""))</f>
+        <f>IF($M69=1,IF($E69=1,"recupero del turno saltato nella settimana "&amp;$AE69&amp;", "&amp;$C69&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE69&amp;", "&amp;$C69&amp;" a riposo"),IF($E69=1,IF($S69="DA ASSEGNARE","turno da assegnare: "&amp;$C69&amp;" assente","in sostituzione di "&amp;$C69&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z69">
+        <f>IF($T69="","",COUNTIF($T$6:$T69,$T69))</f>
+        <v/>
+      </c>
+      <c r="AA69">
+        <f>IF($T69="","",$T69&amp;"#"&amp;$Z69)</f>
+        <v/>
+      </c>
+      <c r="AB69">
+        <f>COUNTIF($T$6:$T65,$C69)</f>
+        <v/>
+      </c>
+      <c r="AC69">
+        <f>COUNTIFS($C$6:$C65,$C69,$M$6:$M65,1)</f>
+        <v/>
+      </c>
+      <c r="AD69">
+        <f>IF($AB69&gt;$AC69,IFERROR(MATCH($C69&amp;"#"&amp;($AC69+1),$AA$6:$AA65,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE69">
+        <f>IF($AD69=0,"",INDEX($A$6:$A65,$AD69))</f>
         <v/>
       </c>
     </row>
@@ -14106,7 +15660,7 @@
         <v/>
       </c>
       <c r="F70">
-        <f>IF($E70=0,0,IF(OR($D70="Licenza - settimana intera",$D70="Attività esterna - settimana intera"),0,1))</f>
+        <f>IF($M70=1,0,IF($E70=0,0,IF(OR($D70="Licenza - settimana intera",$D70="Attività esterna - settimana intera"),0,1)))</f>
         <v/>
       </c>
       <c r="G70">
@@ -14130,7 +15684,7 @@
         <v/>
       </c>
       <c r="L70">
-        <f>IFERROR(INDEX($C61:$C65,MATCH(1,INDEX(($T61:$T65=$C70)*1,0),0)),"")</f>
+        <f>IF($AD70=0,"",INDEX($C$6:$C65,$AD70))</f>
         <v/>
       </c>
       <c r="M70">
@@ -14138,23 +15692,23 @@
         <v/>
       </c>
       <c r="N70">
-        <f>IF($G70=0,100000,IF(Partecipanti!$B$5=$C70,100000,COUNTIF($S$6:$S69,Partecipanti!$B$5)*100+MOD(1-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($G70=0,100000,IF(Partecipanti!$B$5=$C70,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$5))&gt;0,100000,COUNTIF($S$6:$S69,Partecipanti!$B$5)*100+MOD(1-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="O70">
-        <f>IF($H70=0,100000,IF(Partecipanti!$B$6=$C70,100000,COUNTIF($S$6:$S69,Partecipanti!$B$6)*100+MOD(2-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($H70=0,100000,IF(Partecipanti!$B$6=$C70,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$6))&gt;0,100000,COUNTIF($S$6:$S69,Partecipanti!$B$6)*100+MOD(2-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="P70">
-        <f>IF($I70=0,100000,IF(Partecipanti!$B$7=$C70,100000,COUNTIF($S$6:$S69,Partecipanti!$B$7)*100+MOD(3-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($I70=0,100000,IF(Partecipanti!$B$7=$C70,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$7))&gt;0,100000,COUNTIF($S$6:$S69,Partecipanti!$B$7)*100+MOD(3-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="Q70">
-        <f>IF($J70=0,100000,IF(Partecipanti!$B$8=$C70,100000,COUNTIF($S$6:$S69,Partecipanti!$B$8)*100+MOD(4-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($J70=0,100000,IF(Partecipanti!$B$8=$C70,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$8))&gt;0,100000,COUNTIF($S$6:$S69,Partecipanti!$B$8)*100+MOD(4-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="R70">
-        <f>IF($K70=0,100000,IF(Partecipanti!$B$9=$C70,100000,COUNTIF($S$6:$S69,Partecipanti!$B$9)*100+MOD(5-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5)))</f>
+        <f>IF($K70=0,100000,IF(Partecipanti!$B$9=$C70,100000,IF(SUMPRODUCT(($M$66:$M$70=1)*($L$66:$L$70=Partecipanti!$B$9))&gt;0,100000,COUNTIF($S$6:$S69,Partecipanti!$B$9)*100+MOD(5-MATCH($C70,Partecipanti!$B$5:$B$9,0)-1,5))))</f>
         <v/>
       </c>
       <c r="S70">
@@ -14178,11 +15732,35 @@
         <v/>
       </c>
       <c r="X70">
-        <f>IF($M70=1,$L70&amp;" recupera il turno saltato nella settimana "&amp;($A70-1)&amp;"; "&amp;$C70&amp;" a riposo compensativo",IF($E70=1,$C70&amp;" assente ("&amp;$D70&amp;")"&amp;IF($S70="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S70&amp;" con doppio turno")&amp;IF($F70=1,"; turno da recuperare nella settimana "&amp;($A70+1),"; turno non da recuperare"),""))</f>
+        <f>IF($M70=1,IF($E70=1,$L70&amp;" copre il turno recuperando quello saltato nella settimana "&amp;$AE70&amp;"; "&amp;$C70&amp;" assente ("&amp;$D70&amp;")",$L70&amp;" recupera il turno saltato nella settimana "&amp;$AE70&amp;"; "&amp;$C70&amp;" a riposo compensativo"),IF($E70=1,$C70&amp;" assente ("&amp;$D70&amp;")"&amp;IF($S70="DA ASSEGNARE","; nessun sostituto disponibile","; sostituisce "&amp;$S70&amp;" con doppio turno")&amp;IF($F70=1,"; turno da recuperare a partire dalla settimana "&amp;($A70+1),"; turno non da recuperare"),""))</f>
         <v/>
       </c>
       <c r="Y70">
-        <f>IF($M70=1,"recupera il turno saltato nella settimana "&amp;($A70-1)&amp;", "&amp;$C70&amp;" a riposo",IF($E70=1,IF($S70="DA ASSEGNARE","turno da assegnare: "&amp;$C70&amp;" assente","in sostituzione di "&amp;$C70&amp;", doppio turno"),""))</f>
+        <f>IF($M70=1,IF($E70=1,"recupero del turno saltato nella settimana "&amp;$AE70&amp;", "&amp;$C70&amp;" assente","recupera il turno saltato nella settimana "&amp;$AE70&amp;", "&amp;$C70&amp;" a riposo"),IF($E70=1,IF($S70="DA ASSEGNARE","turno da assegnare: "&amp;$C70&amp;" assente","in sostituzione di "&amp;$C70&amp;", doppio turno"),""))</f>
+        <v/>
+      </c>
+      <c r="Z70">
+        <f>IF($T70="","",COUNTIF($T$6:$T70,$T70))</f>
+        <v/>
+      </c>
+      <c r="AA70">
+        <f>IF($T70="","",$T70&amp;"#"&amp;$Z70)</f>
+        <v/>
+      </c>
+      <c r="AB70">
+        <f>COUNTIF($T$6:$T65,$C70)</f>
+        <v/>
+      </c>
+      <c r="AC70">
+        <f>COUNTIFS($C$6:$C65,$C70,$M$6:$M65,1)</f>
+        <v/>
+      </c>
+      <c r="AD70">
+        <f>IF($AB70&gt;$AC70,IFERROR(MATCH($C70&amp;"#"&amp;($AC70+1),$AA$6:$AA65,0),0),0)</f>
+        <v/>
+      </c>
+      <c r="AE70">
+        <f>IF($AD70=0,"",INDEX($A$6:$A65,$AD70))</f>
         <v/>
       </c>
     </row>

--- a/turnazione-auto-trinitapoli-foggia-20260921.xlsx
+++ b/turnazione-auto-trinitapoli-foggia-20260921.xlsx
@@ -171,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -281,6 +281,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -362,6 +365,286 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F3864"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Composizione dei turni per partecipante</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Riepilogo'!B5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Riepilogo'!$A$6:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Riepilogo'!$B$6:$B$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Riepilogo'!C5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Riepilogo'!$A$6:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Riepilogo'!$C$6:$C$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Riepilogo'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Riepilogo'!$A$6:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Riepilogo'!$D$6:$D$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="D8D8D4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="1000" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="18"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8D8D4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="D8D8D4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <majorUnit val="2"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="0B0B0B"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7164,12 +7447,12 @@
   <sheetPr>
     <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -7460,70 +7743,80 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>DISTRIBUZIONE DEL CARICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="inlineStr">
         <is>
           <t>Come leggere il riepilogo</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="31" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="41" t="inlineStr">
         <is>
           <t>Totale guide</t>
         </is>
       </c>
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B34" s="42" t="inlineStr">
         <is>
           <t>Numero di volte in cui la persona prende effettivamente la macchina.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="31" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="41" t="inlineStr">
         <is>
           <t>Turni saltati non recuperabili</t>
         </is>
       </c>
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B35" s="42" t="inlineStr">
         <is>
           <t>Turni persi per licenza o attività esterna di settimana intera: non vanno recuperati (R1, R2).</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>Turni saltati da recuperare</t>
         </is>
       </c>
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B36" s="42" t="inlineStr">
         <is>
           <t>Turni persi per altri motivi: generano un recupero nella settimana successiva (R3).</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="41" t="inlineStr">
         <is>
           <t>Recuperi ancora da saldare</t>
         </is>
       </c>
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B37" s="42" t="inlineStr">
         <is>
           <t>Recuperi maturati e non ancora effettuati entro la fine del periodo. Durante il periodo il recupero slitta da solo alla prima settimana utile (R7): un valore diverso da zero segnala un debito rimasto aperto, da riportare nel calendario successivo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="B17:H17"/>
+  <mergeCells count="7">
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B37:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7577,157 +7870,157 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>Titolare</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>Tipo assenza titolare</t>
         </is>
       </c>
-      <c r="E5" s="42" t="inlineStr">
+      <c r="E5" s="43" t="inlineStr">
         <is>
           <t>Titolare assente</t>
         </is>
       </c>
-      <c r="F5" s="42" t="inlineStr">
+      <c r="F5" s="43" t="inlineStr">
         <is>
           <t>Recuperabile</t>
         </is>
       </c>
-      <c r="G5" s="42" t="inlineStr">
+      <c r="G5" s="43" t="inlineStr">
         <is>
           <t>Disp. Nicola</t>
         </is>
       </c>
-      <c r="H5" s="42" t="inlineStr">
+      <c r="H5" s="43" t="inlineStr">
         <is>
           <t>Disp. Stefano</t>
         </is>
       </c>
-      <c r="I5" s="42" t="inlineStr">
+      <c r="I5" s="43" t="inlineStr">
         <is>
           <t>Disp. Rocco</t>
         </is>
       </c>
-      <c r="J5" s="42" t="inlineStr">
+      <c r="J5" s="43" t="inlineStr">
         <is>
           <t>Disp. Giuseppe</t>
         </is>
       </c>
-      <c r="K5" s="42" t="inlineStr">
+      <c r="K5" s="43" t="inlineStr">
         <is>
           <t>Disp. Savino</t>
         </is>
       </c>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="L5" s="43" t="inlineStr">
         <is>
           <t>Debitore del recupero</t>
         </is>
       </c>
-      <c r="M5" s="42" t="inlineStr">
+      <c r="M5" s="43" t="inlineStr">
         <is>
           <t>Recupero attivo</t>
         </is>
       </c>
-      <c r="N5" s="42" t="inlineStr">
+      <c r="N5" s="43" t="inlineStr">
         <is>
           <t>Punt. Nicola</t>
         </is>
       </c>
-      <c r="O5" s="42" t="inlineStr">
+      <c r="O5" s="43" t="inlineStr">
         <is>
           <t>Punt. Stefano</t>
         </is>
       </c>
-      <c r="P5" s="42" t="inlineStr">
+      <c r="P5" s="43" t="inlineStr">
         <is>
           <t>Punt. Rocco</t>
         </is>
       </c>
-      <c r="Q5" s="42" t="inlineStr">
+      <c r="Q5" s="43" t="inlineStr">
         <is>
           <t>Punt. Giuseppe</t>
         </is>
       </c>
-      <c r="R5" s="42" t="inlineStr">
+      <c r="R5" s="43" t="inlineStr">
         <is>
           <t>Punt. Savino</t>
         </is>
       </c>
-      <c r="S5" s="42" t="inlineStr">
+      <c r="S5" s="43" t="inlineStr">
         <is>
           <t>Sostituto</t>
         </is>
       </c>
-      <c r="T5" s="42" t="inlineStr">
+      <c r="T5" s="43" t="inlineStr">
         <is>
           <t>Sostituto recuperabile</t>
         </is>
       </c>
-      <c r="U5" s="42" t="inlineStr">
+      <c r="U5" s="43" t="inlineStr">
         <is>
           <t>Conducente effettivo</t>
         </is>
       </c>
-      <c r="V5" s="42" t="inlineStr">
+      <c r="V5" s="43" t="inlineStr">
         <is>
           <t>Tipo turno</t>
         </is>
       </c>
-      <c r="W5" s="42" t="inlineStr">
+      <c r="W5" s="43" t="inlineStr">
         <is>
           <t>A riposo</t>
         </is>
       </c>
-      <c r="X5" s="42" t="inlineStr">
+      <c r="X5" s="43" t="inlineStr">
         <is>
           <t>Motivo variazione</t>
         </is>
       </c>
-      <c r="Y5" s="42" t="inlineStr">
+      <c r="Y5" s="43" t="inlineStr">
         <is>
           <t>Nota sintetica</t>
         </is>
       </c>
-      <c r="Z5" s="42" t="inlineStr">
+      <c r="Z5" s="43" t="inlineStr">
         <is>
           <t>Progressivo debito</t>
         </is>
       </c>
-      <c r="AA5" s="42" t="inlineStr">
+      <c r="AA5" s="43" t="inlineStr">
         <is>
           <t>Chiave debito</t>
         </is>
       </c>
-      <c r="AB5" s="42" t="inlineStr">
+      <c r="AB5" s="43" t="inlineStr">
         <is>
           <t>Debiti maturati</t>
         </is>
       </c>
-      <c r="AC5" s="42" t="inlineStr">
+      <c r="AC5" s="43" t="inlineStr">
         <is>
           <t>Debiti saldati</t>
         </is>
       </c>
-      <c r="AD5" s="42" t="inlineStr">
+      <c r="AD5" s="43" t="inlineStr">
         <is>
           <t>Riga del debito</t>
         </is>
       </c>
-      <c r="AE5" s="42" t="inlineStr">
+      <c r="AE5" s="43" t="inlineStr">
         <is>
           <t>Settimana del debito</t>
         </is>
@@ -7742,7 +8035,7 @@
       <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="43" t="n">
+      <c r="B6" s="44" t="n">
         <v>46293</v>
       </c>
       <c r="C6">
@@ -7852,7 +8145,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="inlineStr"/>
-      <c r="AG6" s="43" t="n">
+      <c r="AG6" s="44" t="n">
         <v>46293</v>
       </c>
     </row>
@@ -7860,7 +8153,7 @@
       <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="43" t="n">
+      <c r="B7" s="44" t="n">
         <v>46294</v>
       </c>
       <c r="C7">
@@ -7983,7 +8276,7 @@
       <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="43" t="n">
+      <c r="B8" s="44" t="n">
         <v>46295</v>
       </c>
       <c r="C8">
@@ -8098,7 +8391,7 @@
       <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="43" t="n">
+      <c r="B9" s="44" t="n">
         <v>46296</v>
       </c>
       <c r="C9">
@@ -8213,7 +8506,7 @@
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="43" t="n">
+      <c r="B10" s="44" t="n">
         <v>46297</v>
       </c>
       <c r="C10">
@@ -8328,7 +8621,7 @@
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="43" t="n">
+      <c r="B11" s="44" t="n">
         <v>46300</v>
       </c>
       <c r="C11">
@@ -8452,7 +8745,7 @@
       <c r="A12" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="43" t="n">
+      <c r="B12" s="44" t="n">
         <v>46301</v>
       </c>
       <c r="C12">
@@ -8576,7 +8869,7 @@
       <c r="A13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="43" t="n">
+      <c r="B13" s="44" t="n">
         <v>46302</v>
       </c>
       <c r="C13">
@@ -8700,7 +8993,7 @@
       <c r="A14" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="43" t="n">
+      <c r="B14" s="44" t="n">
         <v>46303</v>
       </c>
       <c r="C14">
@@ -8824,7 +9117,7 @@
       <c r="A15" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="43" t="n">
+      <c r="B15" s="44" t="n">
         <v>46304</v>
       </c>
       <c r="C15">
@@ -8948,7 +9241,7 @@
       <c r="A16" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="43" t="n">
+      <c r="B16" s="44" t="n">
         <v>46307</v>
       </c>
       <c r="C16">
@@ -9072,7 +9365,7 @@
       <c r="A17" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="43" t="n">
+      <c r="B17" s="44" t="n">
         <v>46308</v>
       </c>
       <c r="C17">
@@ -9196,7 +9489,7 @@
       <c r="A18" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="43" t="n">
+      <c r="B18" s="44" t="n">
         <v>46309</v>
       </c>
       <c r="C18">
@@ -9320,7 +9613,7 @@
       <c r="A19" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="43" t="n">
+      <c r="B19" s="44" t="n">
         <v>46310</v>
       </c>
       <c r="C19">
@@ -9444,7 +9737,7 @@
       <c r="A20" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="43" t="n">
+      <c r="B20" s="44" t="n">
         <v>46311</v>
       </c>
       <c r="C20">
@@ -9568,7 +9861,7 @@
       <c r="A21" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="43" t="n">
+      <c r="B21" s="44" t="n">
         <v>46314</v>
       </c>
       <c r="C21">
@@ -9692,7 +9985,7 @@
       <c r="A22" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="43" t="n">
+      <c r="B22" s="44" t="n">
         <v>46315</v>
       </c>
       <c r="C22">
@@ -9816,7 +10109,7 @@
       <c r="A23" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="43" t="n">
+      <c r="B23" s="44" t="n">
         <v>46316</v>
       </c>
       <c r="C23">
@@ -9940,7 +10233,7 @@
       <c r="A24" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="43" t="n">
+      <c r="B24" s="44" t="n">
         <v>46317</v>
       </c>
       <c r="C24">
@@ -10064,7 +10357,7 @@
       <c r="A25" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="43" t="n">
+      <c r="B25" s="44" t="n">
         <v>46318</v>
       </c>
       <c r="C25">
@@ -10188,7 +10481,7 @@
       <c r="A26" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="43" t="n">
+      <c r="B26" s="44" t="n">
         <v>46321</v>
       </c>
       <c r="C26">
@@ -10312,7 +10605,7 @@
       <c r="A27" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="43" t="n">
+      <c r="B27" s="44" t="n">
         <v>46322</v>
       </c>
       <c r="C27">
@@ -10436,7 +10729,7 @@
       <c r="A28" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="43" t="n">
+      <c r="B28" s="44" t="n">
         <v>46323</v>
       </c>
       <c r="C28">
@@ -10560,7 +10853,7 @@
       <c r="A29" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="43" t="n">
+      <c r="B29" s="44" t="n">
         <v>46324</v>
       </c>
       <c r="C29">
@@ -10684,7 +10977,7 @@
       <c r="A30" t="n">
         <v>5</v>
       </c>
-      <c r="B30" s="43" t="n">
+      <c r="B30" s="44" t="n">
         <v>46325</v>
       </c>
       <c r="C30">
@@ -10808,7 +11101,7 @@
       <c r="A31" t="n">
         <v>6</v>
       </c>
-      <c r="B31" s="43" t="n">
+      <c r="B31" s="44" t="n">
         <v>46328</v>
       </c>
       <c r="C31">
@@ -10932,7 +11225,7 @@
       <c r="A32" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="43" t="n">
+      <c r="B32" s="44" t="n">
         <v>46329</v>
       </c>
       <c r="C32">
@@ -11056,7 +11349,7 @@
       <c r="A33" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="43" t="n">
+      <c r="B33" s="44" t="n">
         <v>46330</v>
       </c>
       <c r="C33">
@@ -11180,7 +11473,7 @@
       <c r="A34" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="43" t="n">
+      <c r="B34" s="44" t="n">
         <v>46331</v>
       </c>
       <c r="C34">
@@ -11304,7 +11597,7 @@
       <c r="A35" t="n">
         <v>6</v>
       </c>
-      <c r="B35" s="43" t="n">
+      <c r="B35" s="44" t="n">
         <v>46332</v>
       </c>
       <c r="C35">
@@ -11428,7 +11721,7 @@
       <c r="A36" t="n">
         <v>7</v>
       </c>
-      <c r="B36" s="43" t="n">
+      <c r="B36" s="44" t="n">
         <v>46335</v>
       </c>
       <c r="C36">
@@ -11552,7 +11845,7 @@
       <c r="A37" t="n">
         <v>7</v>
       </c>
-      <c r="B37" s="43" t="n">
+      <c r="B37" s="44" t="n">
         <v>46336</v>
       </c>
       <c r="C37">
@@ -11676,7 +11969,7 @@
       <c r="A38" t="n">
         <v>7</v>
       </c>
-      <c r="B38" s="43" t="n">
+      <c r="B38" s="44" t="n">
         <v>46337</v>
       </c>
       <c r="C38">
@@ -11800,7 +12093,7 @@
       <c r="A39" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="43" t="n">
+      <c r="B39" s="44" t="n">
         <v>46338</v>
       </c>
       <c r="C39">
@@ -11924,7 +12217,7 @@
       <c r="A40" t="n">
         <v>7</v>
       </c>
-      <c r="B40" s="43" t="n">
+      <c r="B40" s="44" t="n">
         <v>46339</v>
       </c>
       <c r="C40">
@@ -12048,7 +12341,7 @@
       <c r="A41" t="n">
         <v>8</v>
       </c>
-      <c r="B41" s="43" t="n">
+      <c r="B41" s="44" t="n">
         <v>46342</v>
       </c>
       <c r="C41">
@@ -12172,7 +12465,7 @@
       <c r="A42" t="n">
         <v>8</v>
       </c>
-      <c r="B42" s="43" t="n">
+      <c r="B42" s="44" t="n">
         <v>46343</v>
       </c>
       <c r="C42">
@@ -12296,7 +12589,7 @@
       <c r="A43" t="n">
         <v>8</v>
       </c>
-      <c r="B43" s="43" t="n">
+      <c r="B43" s="44" t="n">
         <v>46344</v>
       </c>
       <c r="C43">
@@ -12420,7 +12713,7 @@
       <c r="A44" t="n">
         <v>8</v>
       </c>
-      <c r="B44" s="43" t="n">
+      <c r="B44" s="44" t="n">
         <v>46345</v>
       </c>
       <c r="C44">
@@ -12544,7 +12837,7 @@
       <c r="A45" t="n">
         <v>8</v>
       </c>
-      <c r="B45" s="43" t="n">
+      <c r="B45" s="44" t="n">
         <v>46346</v>
       </c>
       <c r="C45">
@@ -12668,7 +12961,7 @@
       <c r="A46" t="n">
         <v>9</v>
       </c>
-      <c r="B46" s="43" t="n">
+      <c r="B46" s="44" t="n">
         <v>46349</v>
       </c>
       <c r="C46">
@@ -12792,7 +13085,7 @@
       <c r="A47" t="n">
         <v>9</v>
       </c>
-      <c r="B47" s="43" t="n">
+      <c r="B47" s="44" t="n">
         <v>46350</v>
       </c>
       <c r="C47">
@@ -12916,7 +13209,7 @@
       <c r="A48" t="n">
         <v>9</v>
       </c>
-      <c r="B48" s="43" t="n">
+      <c r="B48" s="44" t="n">
         <v>46351</v>
       </c>
       <c r="C48">
@@ -13040,7 +13333,7 @@
       <c r="A49" t="n">
         <v>9</v>
       </c>
-      <c r="B49" s="43" t="n">
+      <c r="B49" s="44" t="n">
         <v>46352</v>
       </c>
       <c r="C49">
@@ -13164,7 +13457,7 @@
       <c r="A50" t="n">
         <v>9</v>
       </c>
-      <c r="B50" s="43" t="n">
+      <c r="B50" s="44" t="n">
         <v>46353</v>
       </c>
       <c r="C50">
@@ -13288,7 +13581,7 @@
       <c r="A51" t="n">
         <v>10</v>
       </c>
-      <c r="B51" s="43" t="n">
+      <c r="B51" s="44" t="n">
         <v>46356</v>
       </c>
       <c r="C51">
@@ -13412,7 +13705,7 @@
       <c r="A52" t="n">
         <v>10</v>
       </c>
-      <c r="B52" s="43" t="n">
+      <c r="B52" s="44" t="n">
         <v>46357</v>
       </c>
       <c r="C52">
@@ -13536,7 +13829,7 @@
       <c r="A53" t="n">
         <v>10</v>
       </c>
-      <c r="B53" s="43" t="n">
+      <c r="B53" s="44" t="n">
         <v>46358</v>
       </c>
       <c r="C53">
@@ -13660,7 +13953,7 @@
       <c r="A54" t="n">
         <v>10</v>
       </c>
-      <c r="B54" s="43" t="n">
+      <c r="B54" s="44" t="n">
         <v>46359</v>
       </c>
       <c r="C54">
@@ -13784,7 +14077,7 @@
       <c r="A55" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="43" t="n">
+      <c r="B55" s="44" t="n">
         <v>46360</v>
       </c>
       <c r="C55">
@@ -13908,7 +14201,7 @@
       <c r="A56" t="n">
         <v>11</v>
       </c>
-      <c r="B56" s="43" t="n">
+      <c r="B56" s="44" t="n">
         <v>46363</v>
       </c>
       <c r="C56">
@@ -14032,7 +14325,7 @@
       <c r="A57" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="43" t="n">
+      <c r="B57" s="44" t="n">
         <v>46364</v>
       </c>
       <c r="C57">
@@ -14156,7 +14449,7 @@
       <c r="A58" t="n">
         <v>11</v>
       </c>
-      <c r="B58" s="43" t="n">
+      <c r="B58" s="44" t="n">
         <v>46365</v>
       </c>
       <c r="C58">
@@ -14280,7 +14573,7 @@
       <c r="A59" t="n">
         <v>11</v>
       </c>
-      <c r="B59" s="43" t="n">
+      <c r="B59" s="44" t="n">
         <v>46366</v>
       </c>
       <c r="C59">
@@ -14404,7 +14697,7 @@
       <c r="A60" t="n">
         <v>11</v>
       </c>
-      <c r="B60" s="43" t="n">
+      <c r="B60" s="44" t="n">
         <v>46367</v>
       </c>
       <c r="C60">
@@ -14528,7 +14821,7 @@
       <c r="A61" t="n">
         <v>12</v>
       </c>
-      <c r="B61" s="43" t="n">
+      <c r="B61" s="44" t="n">
         <v>46370</v>
       </c>
       <c r="C61">
@@ -14652,7 +14945,7 @@
       <c r="A62" t="n">
         <v>12</v>
       </c>
-      <c r="B62" s="43" t="n">
+      <c r="B62" s="44" t="n">
         <v>46371</v>
       </c>
       <c r="C62">
@@ -14776,7 +15069,7 @@
       <c r="A63" t="n">
         <v>12</v>
       </c>
-      <c r="B63" s="43" t="n">
+      <c r="B63" s="44" t="n">
         <v>46372</v>
       </c>
       <c r="C63">
@@ -14900,7 +15193,7 @@
       <c r="A64" t="n">
         <v>12</v>
       </c>
-      <c r="B64" s="43" t="n">
+      <c r="B64" s="44" t="n">
         <v>46373</v>
       </c>
       <c r="C64">
@@ -15024,7 +15317,7 @@
       <c r="A65" t="n">
         <v>12</v>
       </c>
-      <c r="B65" s="43" t="n">
+      <c r="B65" s="44" t="n">
         <v>46374</v>
       </c>
       <c r="C65">
@@ -15148,7 +15441,7 @@
       <c r="A66" t="n">
         <v>13</v>
       </c>
-      <c r="B66" s="43" t="n">
+      <c r="B66" s="44" t="n">
         <v>46377</v>
       </c>
       <c r="C66">
@@ -15272,7 +15565,7 @@
       <c r="A67" t="n">
         <v>13</v>
       </c>
-      <c r="B67" s="43" t="n">
+      <c r="B67" s="44" t="n">
         <v>46378</v>
       </c>
       <c r="C67">
@@ -15396,7 +15689,7 @@
       <c r="A68" t="n">
         <v>13</v>
       </c>
-      <c r="B68" s="43" t="n">
+      <c r="B68" s="44" t="n">
         <v>46379</v>
       </c>
       <c r="C68">
@@ -15520,7 +15813,7 @@
       <c r="A69" t="n">
         <v>13</v>
       </c>
-      <c r="B69" s="43" t="n">
+      <c r="B69" s="44" t="n">
         <v>46380</v>
       </c>
       <c r="C69">
@@ -15644,7 +15937,7 @@
       <c r="A70" t="n">
         <v>13</v>
       </c>
-      <c r="B70" s="43" t="n">
+      <c r="B70" s="44" t="n">
         <v>46381</v>
       </c>
       <c r="C70">

--- a/turnazione-auto-trinitapoli-foggia-20260921.xlsx
+++ b/turnazione-auto-trinitapoli-foggia-20260921.xlsx
@@ -171,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -278,6 +278,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -620,6 +623,289 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="1F3864"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Composizione dei turni settimana per settimana</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Riepilogo'!C35</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Riepilogo'!$A$36:$A$48</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Riepilogo'!$C$36:$C$48</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Riepilogo'!D35</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Riepilogo'!$A$36:$A$48</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Riepilogo'!$D$36:$D$48</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Riepilogo'!E35</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Riepilogo'!$A$36:$A$48</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Riepilogo'!$E$36:$E$48</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Riepilogo'!F35</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="EDA100"/>
+            </a:solidFill>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Riepilogo'!$A$36:$A$48</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Riepilogo'!$F$36:$F$48</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="50"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="D8D8D4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="0B0B0B"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="5"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8D8D4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:solidFill>
+              <a:srgbClr val="D8D8D4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="52514E"/>
+                </a:solidFill>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="52514E"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+        <majorUnit val="1"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="0B0B0B"/>
+              </a:solidFill>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="0B0B0B"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -639,6 +925,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -7213,7 +7521,7 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7449,11 +7757,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -7750,72 +8058,498 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="40" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>ANDAMENTO SETTIMANALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Settimana</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Turni ordinari</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>Sostituzioni
+(doppi turni)</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Recuperi</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>Da assegnare</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>Variazioni totali</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(1-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(1-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C36" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A36,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D36" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A36,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E36" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A36,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F36" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A36,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G36" s="40">
+        <f>$D36+$E36+$F36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(2-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(2-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C37" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A37,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D37" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A37,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E37" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A37,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F37" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A37,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G37" s="40">
+        <f>$D37+$E37+$F37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B38" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(3-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(3-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C38" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A38,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D38" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A38,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E38" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A38,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F38" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A38,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G38" s="40">
+        <f>$D38+$E38+$F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B39" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(4-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(4-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C39" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A39,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D39" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A39,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E39" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A39,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F39" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A39,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G39" s="40">
+        <f>$D39+$E39+$F39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B40" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(5-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(5-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C40" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A40,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D40" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A40,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E40" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A40,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F40" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A40,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G40" s="40">
+        <f>$D40+$E40+$F40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(6-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(6-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C41" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A41,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D41" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A41,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E41" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A41,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F41" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A41,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G41" s="40">
+        <f>$D41+$E41+$F41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B42" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(7-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(7-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C42" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A42,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D42" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A42,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E42" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A42,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F42" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A42,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G42" s="40">
+        <f>$D42+$E42+$F42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B43" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(8-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(8-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C43" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A43,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D43" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A43,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E43" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A43,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F43" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A43,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G43" s="40">
+        <f>$D43+$E43+$F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B44" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(9-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(9-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C44" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A44,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D44" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A44,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E44" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A44,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F44" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A44,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G44" s="40">
+        <f>$D44+$E44+$F44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B45" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(10-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(10-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C45" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A45,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D45" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A45,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E45" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A45,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F45" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A45,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G45" s="40">
+        <f>$D45+$E45+$F45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B46" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(11-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(11-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C46" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A46,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D46" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A46,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E46" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A46,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F46" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A46,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G46" s="40">
+        <f>$D46+$E46+$F46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(12-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(12-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C47" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A47,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D47" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A47,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E47" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A47,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F47" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A47,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G47" s="40">
+        <f>$D47+$E47+$F47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B48" s="10">
+        <f>TEXT(INDEX(Turnazione!$B$6:$B$70,(13-1)*5+1),"dd/mm")&amp;" - "&amp;TEXT(INDEX(Turnazione!$B$6:$B$70,(13-1)*5+1+4),"dd/mm/yyyy")</f>
+        <v/>
+      </c>
+      <c r="C48" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A48,Turnazione!$G$6:$G$70,"Ordinario")</f>
+        <v/>
+      </c>
+      <c r="D48" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A48,Turnazione!$G$6:$G$70,"Sostituzione (doppio turno)")</f>
+        <v/>
+      </c>
+      <c r="E48" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A48,Turnazione!$G$6:$G$70,"Recupero")</f>
+        <v/>
+      </c>
+      <c r="F48" s="8">
+        <f>COUNTIFS(Turnazione!$A$6:$A$70,$A48,Turnazione!$G$6:$G$70,"DA ASSEGNARE")</f>
+        <v/>
+      </c>
+      <c r="G48" s="40">
+        <f>$D48+$E48+$F48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="41" t="inlineStr">
         <is>
           <t>Come leggere il riepilogo</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="41" t="inlineStr">
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="42" t="inlineStr">
         <is>
           <t>Totale guide</t>
         </is>
       </c>
-      <c r="B34" s="42" t="inlineStr">
+      <c r="B69" s="43" t="inlineStr">
         <is>
           <t>Numero di volte in cui la persona prende effettivamente la macchina.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="41" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="42" t="inlineStr">
         <is>
           <t>Turni saltati non recuperabili</t>
         </is>
       </c>
-      <c r="B35" s="42" t="inlineStr">
+      <c r="B70" s="43" t="inlineStr">
         <is>
           <t>Turni persi per licenza o attività esterna di settimana intera: non vanno recuperati (R1, R2).</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="41" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="42" t="inlineStr">
         <is>
           <t>Turni saltati da recuperare</t>
         </is>
       </c>
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B71" s="43" t="inlineStr">
         <is>
           <t>Turni persi per altri motivi: generano un recupero nella settimana successiva (R3).</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="41" t="inlineStr">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="42" t="inlineStr">
         <is>
           <t>Recuperi ancora da saldare</t>
         </is>
       </c>
-      <c r="B37" s="42" t="inlineStr">
+      <c r="B72" s="43" t="inlineStr">
         <is>
           <t>Recuperi maturati e non ancora effettuati entro la fine del periodo. Durante il periodo il recupero slitta da solo alla prima settimana utile (R7): un valore diverso da zero segnala un debito rimasto aperto, da riportare nel calendario successivo.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B35:H35"/>
+  <mergeCells count="8">
+    <mergeCell ref="B71:H71"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="B69:H69"/>
+    <mergeCell ref="B70:H70"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B72:H72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="32" min="0" max="16383" man="1"/>
+  </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -7870,157 +8604,157 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>Sett.</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Titolare</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>Tipo assenza titolare</t>
         </is>
       </c>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>Titolare assente</t>
         </is>
       </c>
-      <c r="F5" s="43" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>Recuperabile</t>
         </is>
       </c>
-      <c r="G5" s="43" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>Disp. Nicola</t>
         </is>
       </c>
-      <c r="H5" s="43" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>Disp. Stefano</t>
         </is>
       </c>
-      <c r="I5" s="43" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>Disp. Rocco</t>
         </is>
       </c>
-      <c r="J5" s="43" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>Disp. Giuseppe</t>
         </is>
       </c>
-      <c r="K5" s="43" t="inlineStr">
+      <c r="K5" s="44" t="inlineStr">
         <is>
           <t>Disp. Savino</t>
         </is>
       </c>
-      <c r="L5" s="43" t="inlineStr">
+      <c r="L5" s="44" t="inlineStr">
         <is>
           <t>Debitore del recupero</t>
         </is>
       </c>
-      <c r="M5" s="43" t="inlineStr">
+      <c r="M5" s="44" t="inlineStr">
         <is>
           <t>Recupero attivo</t>
         </is>
       </c>
-      <c r="N5" s="43" t="inlineStr">
+      <c r="N5" s="44" t="inlineStr">
         <is>
           <t>Punt. Nicola</t>
         </is>
       </c>
-      <c r="O5" s="43" t="inlineStr">
+      <c r="O5" s="44" t="inlineStr">
         <is>
           <t>Punt. Stefano</t>
         </is>
       </c>
-      <c r="P5" s="43" t="inlineStr">
+      <c r="P5" s="44" t="inlineStr">
         <is>
           <t>Punt. Rocco</t>
         </is>
       </c>
-      <c r="Q5" s="43" t="inlineStr">
+      <c r="Q5" s="44" t="inlineStr">
         <is>
           <t>Punt. Giuseppe</t>
         </is>
       </c>
-      <c r="R5" s="43" t="inlineStr">
+      <c r="R5" s="44" t="inlineStr">
         <is>
           <t>Punt. Savino</t>
         </is>
       </c>
-      <c r="S5" s="43" t="inlineStr">
+      <c r="S5" s="44" t="inlineStr">
         <is>
           <t>Sostituto</t>
         </is>
       </c>
-      <c r="T5" s="43" t="inlineStr">
+      <c r="T5" s="44" t="inlineStr">
         <is>
           <t>Sostituto recuperabile</t>
         </is>
       </c>
-      <c r="U5" s="43" t="inlineStr">
+      <c r="U5" s="44" t="inlineStr">
         <is>
           <t>Conducente effettivo</t>
         </is>
       </c>
-      <c r="V5" s="43" t="inlineStr">
+      <c r="V5" s="44" t="inlineStr">
         <is>
           <t>Tipo turno</t>
         </is>
       </c>
-      <c r="W5" s="43" t="inlineStr">
+      <c r="W5" s="44" t="inlineStr">
         <is>
           <t>A riposo</t>
         </is>
       </c>
-      <c r="X5" s="43" t="inlineStr">
+      <c r="X5" s="44" t="inlineStr">
         <is>
           <t>Motivo variazione</t>
         </is>
       </c>
-      <c r="Y5" s="43" t="inlineStr">
+      <c r="Y5" s="44" t="inlineStr">
         <is>
           <t>Nota sintetica</t>
         </is>
       </c>
-      <c r="Z5" s="43" t="inlineStr">
+      <c r="Z5" s="44" t="inlineStr">
         <is>
           <t>Progressivo debito</t>
         </is>
       </c>
-      <c r="AA5" s="43" t="inlineStr">
+      <c r="AA5" s="44" t="inlineStr">
         <is>
           <t>Chiave debito</t>
         </is>
       </c>
-      <c r="AB5" s="43" t="inlineStr">
+      <c r="AB5" s="44" t="inlineStr">
         <is>
           <t>Debiti maturati</t>
         </is>
       </c>
-      <c r="AC5" s="43" t="inlineStr">
+      <c r="AC5" s="44" t="inlineStr">
         <is>
           <t>Debiti saldati</t>
         </is>
       </c>
-      <c r="AD5" s="43" t="inlineStr">
+      <c r="AD5" s="44" t="inlineStr">
         <is>
           <t>Riga del debito</t>
         </is>
       </c>
-      <c r="AE5" s="43" t="inlineStr">
+      <c r="AE5" s="44" t="inlineStr">
         <is>
           <t>Settimana del debito</t>
         </is>
@@ -8035,7 +8769,7 @@
       <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="45" t="n">
         <v>46293</v>
       </c>
       <c r="C6">
@@ -8145,7 +8879,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="inlineStr"/>
-      <c r="AG6" s="44" t="n">
+      <c r="AG6" s="45" t="n">
         <v>46293</v>
       </c>
     </row>
@@ -8153,7 +8887,7 @@
       <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="44" t="n">
+      <c r="B7" s="45" t="n">
         <v>46294</v>
       </c>
       <c r="C7">
@@ -8276,7 +9010,7 @@
       <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="44" t="n">
+      <c r="B8" s="45" t="n">
         <v>46295</v>
       </c>
       <c r="C8">
@@ -8391,7 +9125,7 @@
       <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="44" t="n">
+      <c r="B9" s="45" t="n">
         <v>46296</v>
       </c>
       <c r="C9">
@@ -8506,7 +9240,7 @@
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="44" t="n">
+      <c r="B10" s="45" t="n">
         <v>46297</v>
       </c>
       <c r="C10">
@@ -8621,7 +9355,7 @@
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="44" t="n">
+      <c r="B11" s="45" t="n">
         <v>46300</v>
       </c>
       <c r="C11">
@@ -8745,7 +9479,7 @@
       <c r="A12" t="n">
         <v>2</v>
       </c>
-      <c r="B12" s="44" t="n">
+      <c r="B12" s="45" t="n">
         <v>46301</v>
       </c>
       <c r="C12">
@@ -8869,7 +9603,7 @@
       <c r="A13" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="44" t="n">
+      <c r="B13" s="45" t="n">
         <v>46302</v>
       </c>
       <c r="C13">
@@ -8993,7 +9727,7 @@
       <c r="A14" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="44" t="n">
+      <c r="B14" s="45" t="n">
         <v>46303</v>
       </c>
       <c r="C14">
@@ -9117,7 +9851,7 @@
       <c r="A15" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="44" t="n">
+      <c r="B15" s="45" t="n">
         <v>46304</v>
       </c>
       <c r="C15">
@@ -9241,7 +9975,7 @@
       <c r="A16" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="44" t="n">
+      <c r="B16" s="45" t="n">
         <v>46307</v>
       </c>
       <c r="C16">
@@ -9365,7 +10099,7 @@
       <c r="A17" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="44" t="n">
+      <c r="B17" s="45" t="n">
         <v>46308</v>
       </c>
       <c r="C17">
@@ -9489,7 +10223,7 @@
       <c r="A18" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="44" t="n">
+      <c r="B18" s="45" t="n">
         <v>46309</v>
       </c>
       <c r="C18">
@@ -9613,7 +10347,7 @@
       <c r="A19" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="44" t="n">
+      <c r="B19" s="45" t="n">
         <v>46310</v>
       </c>
       <c r="C19">
@@ -9737,7 +10471,7 @@
       <c r="A20" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="44" t="n">
+      <c r="B20" s="45" t="n">
         <v>46311</v>
       </c>
       <c r="C20">
@@ -9861,7 +10595,7 @@
       <c r="A21" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="44" t="n">
+      <c r="B21" s="45" t="n">
         <v>46314</v>
       </c>
       <c r="C21">
@@ -9985,7 +10719,7 @@
       <c r="A22" t="n">
         <v>4</v>
       </c>
-      <c r="B22" s="44" t="n">
+      <c r="B22" s="45" t="n">
         <v>46315</v>
       </c>
       <c r="C22">
@@ -10109,7 +10843,7 @@
       <c r="A23" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="44" t="n">
+      <c r="B23" s="45" t="n">
         <v>46316</v>
       </c>
       <c r="C23">
@@ -10233,7 +10967,7 @@
       <c r="A24" t="n">
         <v>4</v>
       </c>
-      <c r="B24" s="44" t="n">
+      <c r="B24" s="45" t="n">
         <v>46317</v>
       </c>
       <c r="C24">
@@ -10357,7 +11091,7 @@
       <c r="A25" t="n">
         <v>4</v>
       </c>
-      <c r="B25" s="44" t="n">
+      <c r="B25" s="45" t="n">
         <v>46318</v>
       </c>
       <c r="C25">
@@ -10481,7 +11215,7 @@
       <c r="A26" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="44" t="n">
+      <c r="B26" s="45" t="n">
         <v>46321</v>
       </c>
       <c r="C26">
@@ -10605,7 +11339,7 @@
       <c r="A27" t="n">
         <v>5</v>
       </c>
-      <c r="B27" s="44" t="n">
+      <c r="B27" s="45" t="n">
         <v>46322</v>
       </c>
       <c r="C27">
@@ -10729,7 +11463,7 @@
       <c r="A28" t="n">
         <v>5</v>
       </c>
-      <c r="B28" s="44" t="n">
+      <c r="B28" s="45" t="n">
         <v>46323</v>
       </c>
       <c r="C28">
@@ -10853,7 +11587,7 @@
       <c r="A29" t="n">
         <v>5</v>
       </c>
-      <c r="B29" s="44" t="n">
+      <c r="B29" s="45" t="n">
         <v>46324</v>
       </c>
       <c r="C29">
@@ -10977,7 +11711,7 @@
       <c r="A30" t="n">
         <v>5</v>
       </c>
-      <c r="B30" s="44" t="n">
+      <c r="B30" s="45" t="n">
         <v>46325</v>
       </c>
       <c r="C30">
@@ -11101,7 +11835,7 @@
       <c r="A31" t="n">
         <v>6</v>
       </c>
-      <c r="B31" s="44" t="n">
+      <c r="B31" s="45" t="n">
         <v>46328</v>
       </c>
       <c r="C31">
@@ -11225,7 +11959,7 @@
       <c r="A32" t="n">
         <v>6</v>
       </c>
-      <c r="B32" s="44" t="n">
+      <c r="B32" s="45" t="n">
         <v>46329</v>
       </c>
       <c r="C32">
@@ -11349,7 +12083,7 @@
       <c r="A33" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="44" t="n">
+      <c r="B33" s="45" t="n">
         <v>46330</v>
       </c>
       <c r="C33">
@@ -11473,7 +12207,7 @@
       <c r="A34" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="44" t="n">
+      <c r="B34" s="45" t="n">
         <v>46331</v>
       </c>
       <c r="C34">
@@ -11597,7 +12331,7 @@
       <c r="A35" t="n">
         <v>6</v>
       </c>
-      <c r="B35" s="44" t="n">
+      <c r="B35" s="45" t="n">
         <v>46332</v>
       </c>
       <c r="C35">
@@ -11721,7 +12455,7 @@
       <c r="A36" t="n">
         <v>7</v>
       </c>
-      <c r="B36" s="44" t="n">
+      <c r="B36" s="45" t="n">
         <v>46335</v>
       </c>
       <c r="C36">
@@ -11845,7 +12579,7 @@
       <c r="A37" t="n">
         <v>7</v>
       </c>
-      <c r="B37" s="44" t="n">
+      <c r="B37" s="45" t="n">
         <v>46336</v>
       </c>
       <c r="C37">
@@ -11969,7 +12703,7 @@
       <c r="A38" t="n">
         <v>7</v>
       </c>
-      <c r="B38" s="44" t="n">
+      <c r="B38" s="45" t="n">
         <v>46337</v>
       </c>
       <c r="C38">
@@ -12093,7 +12827,7 @@
       <c r="A39" t="n">
         <v>7</v>
       </c>
-      <c r="B39" s="44" t="n">
+      <c r="B39" s="45" t="n">
         <v>46338</v>
       </c>
       <c r="C39">
@@ -12217,7 +12951,7 @@
       <c r="A40" t="n">
         <v>7</v>
       </c>
-      <c r="B40" s="44" t="n">
+      <c r="B40" s="45" t="n">
         <v>46339</v>
       </c>
       <c r="C40">
@@ -12341,7 +13075,7 @@
       <c r="A41" t="n">
         <v>8</v>
       </c>
-      <c r="B41" s="44" t="n">
+      <c r="B41" s="45" t="n">
         <v>46342</v>
       </c>
       <c r="C41">
@@ -12465,7 +13199,7 @@
       <c r="A42" t="n">
         <v>8</v>
       </c>
-      <c r="B42" s="44" t="n">
+      <c r="B42" s="45" t="n">
         <v>46343</v>
       </c>
       <c r="C42">
@@ -12589,7 +13323,7 @@
       <c r="A43" t="n">
         <v>8</v>
       </c>
-      <c r="B43" s="44" t="n">
+      <c r="B43" s="45" t="n">
         <v>46344</v>
       </c>
       <c r="C43">
@@ -12713,7 +13447,7 @@
       <c r="A44" t="n">
         <v>8</v>
       </c>
-      <c r="B44" s="44" t="n">
+      <c r="B44" s="45" t="n">
         <v>46345</v>
       </c>
       <c r="C44">
@@ -12837,7 +13571,7 @@
       <c r="A45" t="n">
         <v>8</v>
       </c>
-      <c r="B45" s="44" t="n">
+      <c r="B45" s="45" t="n">
         <v>46346</v>
       </c>
       <c r="C45">
@@ -12961,7 +13695,7 @@
       <c r="A46" t="n">
         <v>9</v>
       </c>
-      <c r="B46" s="44" t="n">
+      <c r="B46" s="45" t="n">
         <v>46349</v>
       </c>
       <c r="C46">
@@ -13085,7 +13819,7 @@
       <c r="A47" t="n">
         <v>9</v>
       </c>
-      <c r="B47" s="44" t="n">
+      <c r="B47" s="45" t="n">
         <v>46350</v>
       </c>
       <c r="C47">
@@ -13209,7 +13943,7 @@
       <c r="A48" t="n">
         <v>9</v>
       </c>
-      <c r="B48" s="44" t="n">
+      <c r="B48" s="45" t="n">
         <v>46351</v>
       </c>
       <c r="C48">
@@ -13333,7 +14067,7 @@
       <c r="A49" t="n">
         <v>9</v>
       </c>
-      <c r="B49" s="44" t="n">
+      <c r="B49" s="45" t="n">
         <v>46352</v>
       </c>
       <c r="C49">
@@ -13457,7 +14191,7 @@
       <c r="A50" t="n">
         <v>9</v>
       </c>
-      <c r="B50" s="44" t="n">
+      <c r="B50" s="45" t="n">
         <v>46353</v>
       </c>
       <c r="C50">
@@ -13581,7 +14315,7 @@
       <c r="A51" t="n">
         <v>10</v>
       </c>
-      <c r="B51" s="44" t="n">
+      <c r="B51" s="45" t="n">
         <v>46356</v>
       </c>
       <c r="C51">
@@ -13705,7 +14439,7 @@
       <c r="A52" t="n">
         <v>10</v>
       </c>
-      <c r="B52" s="44" t="n">
+      <c r="B52" s="45" t="n">
         <v>46357</v>
       </c>
       <c r="C52">
@@ -13829,7 +14563,7 @@
       <c r="A53" t="n">
         <v>10</v>
       </c>
-      <c r="B53" s="44" t="n">
+      <c r="B53" s="45" t="n">
         <v>46358</v>
       </c>
       <c r="C53">
@@ -13953,7 +14687,7 @@
       <c r="A54" t="n">
         <v>10</v>
       </c>
-      <c r="B54" s="44" t="n">
+      <c r="B54" s="45" t="n">
         <v>46359</v>
       </c>
       <c r="C54">
@@ -14077,7 +14811,7 @@
       <c r="A55" t="n">
         <v>10</v>
       </c>
-      <c r="B55" s="44" t="n">
+      <c r="B55" s="45" t="n">
         <v>46360</v>
       </c>
       <c r="C55">
@@ -14201,7 +14935,7 @@
       <c r="A56" t="n">
         <v>11</v>
       </c>
-      <c r="B56" s="44" t="n">
+      <c r="B56" s="45" t="n">
         <v>46363</v>
       </c>
       <c r="C56">
@@ -14325,7 +15059,7 @@
       <c r="A57" t="n">
         <v>11</v>
       </c>
-      <c r="B57" s="44" t="n">
+      <c r="B57" s="45" t="n">
         <v>46364</v>
       </c>
       <c r="C57">
@@ -14449,7 +15183,7 @@
       <c r="A58" t="n">
         <v>11</v>
       </c>
-      <c r="B58" s="44" t="n">
+      <c r="B58" s="45" t="n">
         <v>46365</v>
       </c>
       <c r="C58">
@@ -14573,7 +15307,7 @@
       <c r="A59" t="n">
         <v>11</v>
       </c>
-      <c r="B59" s="44" t="n">
+      <c r="B59" s="45" t="n">
         <v>46366</v>
       </c>
       <c r="C59">
@@ -14697,7 +15431,7 @@
       <c r="A60" t="n">
         <v>11</v>
       </c>
-      <c r="B60" s="44" t="n">
+      <c r="B60" s="45" t="n">
         <v>46367</v>
       </c>
       <c r="C60">
@@ -14821,7 +15555,7 @@
       <c r="A61" t="n">
         <v>12</v>
       </c>
-      <c r="B61" s="44" t="n">
+      <c r="B61" s="45" t="n">
         <v>46370</v>
       </c>
       <c r="C61">
@@ -14945,7 +15679,7 @@
       <c r="A62" t="n">
         <v>12</v>
       </c>
-      <c r="B62" s="44" t="n">
+      <c r="B62" s="45" t="n">
         <v>46371</v>
       </c>
       <c r="C62">
@@ -15069,7 +15803,7 @@
       <c r="A63" t="n">
         <v>12</v>
       </c>
-      <c r="B63" s="44" t="n">
+      <c r="B63" s="45" t="n">
         <v>46372</v>
       </c>
       <c r="C63">
@@ -15193,7 +15927,7 @@
       <c r="A64" t="n">
         <v>12</v>
       </c>
-      <c r="B64" s="44" t="n">
+      <c r="B64" s="45" t="n">
         <v>46373</v>
       </c>
       <c r="C64">
@@ -15317,7 +16051,7 @@
       <c r="A65" t="n">
         <v>12</v>
       </c>
-      <c r="B65" s="44" t="n">
+      <c r="B65" s="45" t="n">
         <v>46374</v>
       </c>
       <c r="C65">
@@ -15441,7 +16175,7 @@
       <c r="A66" t="n">
         <v>13</v>
       </c>
-      <c r="B66" s="44" t="n">
+      <c r="B66" s="45" t="n">
         <v>46377</v>
       </c>
       <c r="C66">
@@ -15565,7 +16299,7 @@
       <c r="A67" t="n">
         <v>13</v>
       </c>
-      <c r="B67" s="44" t="n">
+      <c r="B67" s="45" t="n">
         <v>46378</v>
       </c>
       <c r="C67">
@@ -15689,7 +16423,7 @@
       <c r="A68" t="n">
         <v>13</v>
       </c>
-      <c r="B68" s="44" t="n">
+      <c r="B68" s="45" t="n">
         <v>46379</v>
       </c>
       <c r="C68">
@@ -15813,7 +16547,7 @@
       <c r="A69" t="n">
         <v>13</v>
       </c>
-      <c r="B69" s="44" t="n">
+      <c r="B69" s="45" t="n">
         <v>46380</v>
       </c>
       <c r="C69">
@@ -15937,7 +16671,7 @@
       <c r="A70" t="n">
         <v>13</v>
       </c>
-      <c r="B70" s="44" t="n">
+      <c r="B70" s="45" t="n">
         <v>46381</v>
       </c>
       <c r="C70">
